--- a/ig/DM_FINESS_New/CodeSystem-tre-r397-categorie-entite-geographique-exercice.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-tre-r397-categorie-entite-geographique-exercice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1359" uniqueCount="908">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1360" uniqueCount="909">
   <si>
     <t>Property</t>
   </si>
@@ -89,6 +89,9 @@
   </si>
   <si>
     <t>Value Set (all codes)</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r397-categorie-entite-geographique-exercice?vs</t>
   </si>
   <si>
     <t>Hierarchy</t>
@@ -2990,48 +2993,50 @@
       <c r="A15" t="s" s="2">
         <v>24</v>
       </c>
-      <c r="B15" s="2"/>
+      <c r="B15" t="s" s="2">
+        <v>25</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -3046,142 +3051,142 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C1" t="s" s="1">
         <v>19</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="C6" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="D6" t="s" s="2">
         <v>53</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>54</v>
-      </c>
-      <c r="C6" t="s" s="2">
-        <v>55</v>
-      </c>
-      <c r="D6" t="s" s="2">
-        <v>52</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C8" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C9" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -3196,5123 +3201,5123 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C8" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C9" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D21" s="2"/>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D22" s="2"/>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D23" s="2"/>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D24" s="2"/>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D25" s="2"/>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D26" s="2"/>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D27" s="2"/>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D28" s="2"/>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D29" s="2"/>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D30" s="2"/>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D31" s="2"/>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D32" s="2"/>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D33" s="2"/>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D34" s="2"/>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D35" s="2"/>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D36" s="2"/>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D37" s="2"/>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D38" s="2"/>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D39" s="2"/>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D40" s="2"/>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D41" s="2"/>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D42" s="2"/>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D43" s="2"/>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D44" s="2"/>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D45" s="2"/>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D46" s="2"/>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D47" s="2"/>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D48" s="2"/>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D49" s="2"/>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D50" s="2"/>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D51" s="2"/>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D52" s="2"/>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D53" s="2"/>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D54" s="2"/>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D55" s="2"/>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D56" s="2"/>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D57" s="2"/>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D58" s="2"/>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D59" s="2"/>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D60" s="2"/>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D61" s="2"/>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D62" s="2"/>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D63" s="2"/>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D64" s="2"/>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D65" s="2"/>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D66" s="2"/>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D67" s="2"/>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D68" s="2"/>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D69" s="2"/>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D70" s="2"/>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D71" s="2"/>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D72" s="2"/>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D73" s="2"/>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D74" s="2"/>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D75" s="2"/>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D76" s="2"/>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D77" s="2"/>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D78" s="2"/>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D79" s="2"/>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D80" s="2"/>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D81" s="2"/>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C82" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D82" s="2"/>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C83" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D83" s="2"/>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D84" s="2"/>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C85" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D85" s="2"/>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D86" s="2"/>
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C87" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D87" s="2"/>
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D88" s="2"/>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C89" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D89" s="2"/>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D90" s="2"/>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D91" s="2"/>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C92" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D92" s="2"/>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D93" s="2"/>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C94" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D94" s="2"/>
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D95" s="2"/>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D96" s="2"/>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D97" s="2"/>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D98" s="2"/>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D99" s="2"/>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D100" s="2"/>
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D101" s="2"/>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C102" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D102" s="2"/>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D103" s="2"/>
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D104" s="2"/>
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D105" s="2"/>
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D106" s="2"/>
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D107" s="2"/>
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D108" s="2"/>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D109" s="2"/>
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C110" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D110" s="2"/>
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D111" s="2"/>
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D112" s="2"/>
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C113" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D113" s="2"/>
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C114" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D114" s="2"/>
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C115" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D115" s="2"/>
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C116" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D116" s="2"/>
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C117" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D117" s="2"/>
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C118" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D118" s="2"/>
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D119" s="2"/>
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C120" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D120" s="2"/>
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C121" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D121" s="2"/>
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C122" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D122" s="2"/>
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C123" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D123" s="2"/>
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C124" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D124" s="2"/>
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C125" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D125" s="2"/>
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C126" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D126" s="2"/>
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C127" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D127" s="2"/>
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C128" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D128" s="2"/>
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C129" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D129" s="2"/>
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C130" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D130" s="2"/>
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C131" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D131" s="2"/>
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C132" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D132" s="2"/>
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C133" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D133" s="2"/>
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C134" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D134" s="2"/>
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C135" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D135" s="2"/>
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C136" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D136" s="2"/>
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C137" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D137" s="2"/>
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C138" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D138" s="2"/>
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C139" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D139" s="2"/>
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C140" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D140" s="2"/>
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C141" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D141" s="2"/>
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C142" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D142" s="2"/>
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C143" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D143" s="2"/>
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C144" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D144" s="2"/>
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C145" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D145" s="2"/>
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C146" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D146" s="2"/>
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C147" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D147" s="2"/>
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C148" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D148" s="2"/>
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C149" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D149" s="2"/>
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C150" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D150" s="2"/>
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C151" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D151" s="2"/>
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C152" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D152" s="2"/>
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C153" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D153" s="2"/>
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C154" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D154" s="2"/>
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C155" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D155" s="2"/>
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C156" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D156" s="2"/>
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C157" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D157" s="2"/>
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C158" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D158" s="2"/>
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C159" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D159" s="2"/>
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C160" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D160" s="2"/>
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C161" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D161" s="2"/>
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C162" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D162" s="2"/>
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C163" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D163" s="2"/>
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C164" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D164" s="2"/>
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C165" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D165" s="2"/>
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C166" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D166" s="2"/>
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C167" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D167" s="2"/>
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C168" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D168" s="2"/>
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C169" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D169" s="2"/>
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C170" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D170" s="2"/>
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C171" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D171" s="2"/>
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C172" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D172" s="2"/>
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C173" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D173" s="2"/>
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C174" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D174" s="2"/>
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C175" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D175" s="2"/>
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C176" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D176" s="2"/>
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C177" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D177" s="2"/>
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C178" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D178" s="2"/>
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C179" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D179" s="2"/>
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C180" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D180" s="2"/>
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C181" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D181" s="2"/>
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C182" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D182" s="2"/>
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C183" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D183" s="2"/>
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C184" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D184" s="2"/>
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C185" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D185" s="2"/>
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C186" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D186" s="2"/>
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C187" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D187" s="2"/>
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C188" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D188" s="2"/>
     </row>
     <row r="189">
       <c r="A189" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C189" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D189" s="2"/>
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C190" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D190" s="2"/>
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C191" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D191" s="2"/>
     </row>
     <row r="192">
       <c r="A192" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C192" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D192" s="2"/>
     </row>
     <row r="193">
       <c r="A193" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C193" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D193" s="2"/>
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C194" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D194" s="2"/>
     </row>
     <row r="195">
       <c r="A195" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C195" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D195" s="2"/>
     </row>
     <row r="196">
       <c r="A196" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C196" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D196" s="2"/>
     </row>
     <row r="197">
       <c r="A197" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C197" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D197" s="2"/>
     </row>
     <row r="198">
       <c r="A198" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C198" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D198" s="2"/>
     </row>
     <row r="199">
       <c r="A199" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C199" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D199" s="2"/>
     </row>
     <row r="200">
       <c r="A200" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C200" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D200" s="2"/>
     </row>
     <row r="201">
       <c r="A201" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C201" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D201" s="2"/>
     </row>
     <row r="202">
       <c r="A202" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C202" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D202" s="2"/>
     </row>
     <row r="203">
       <c r="A203" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C203" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D203" s="2"/>
     </row>
     <row r="204">
       <c r="A204" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C204" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D204" s="2"/>
     </row>
     <row r="205">
       <c r="A205" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C205" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D205" s="2"/>
     </row>
     <row r="206">
       <c r="A206" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C206" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D206" s="2"/>
     </row>
     <row r="207">
       <c r="A207" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C207" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D207" s="2"/>
     </row>
     <row r="208">
       <c r="A208" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C208" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D208" s="2"/>
     </row>
     <row r="209">
       <c r="A209" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C209" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D209" s="2"/>
     </row>
     <row r="210">
       <c r="A210" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C210" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="D210" s="2"/>
     </row>
     <row r="211">
       <c r="A211" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C211" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D211" s="2"/>
     </row>
     <row r="212">
       <c r="A212" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C212" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="D212" s="2"/>
     </row>
     <row r="213">
       <c r="A213" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C213" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D213" s="2"/>
     </row>
     <row r="214">
       <c r="A214" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C214" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="D214" s="2"/>
     </row>
     <row r="215">
       <c r="A215" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C215" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D215" s="2"/>
     </row>
     <row r="216">
       <c r="A216" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C216" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="D216" s="2"/>
     </row>
     <row r="217">
       <c r="A217" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C217" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D217" s="2"/>
     </row>
     <row r="218">
       <c r="A218" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C218" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D218" s="2"/>
     </row>
     <row r="219">
       <c r="A219" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C219" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D219" s="2"/>
     </row>
     <row r="220">
       <c r="A220" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C220" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D220" s="2"/>
     </row>
     <row r="221">
       <c r="A221" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C221" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D221" s="2"/>
     </row>
     <row r="222">
       <c r="A222" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C222" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D222" s="2"/>
     </row>
     <row r="223">
       <c r="A223" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C223" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D223" s="2"/>
     </row>
     <row r="224">
       <c r="A224" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C224" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D224" s="2"/>
     </row>
     <row r="225">
       <c r="A225" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C225" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D225" s="2"/>
     </row>
     <row r="226">
       <c r="A226" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C226" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="D226" s="2"/>
     </row>
     <row r="227">
       <c r="A227" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C227" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D227" s="2"/>
     </row>
     <row r="228">
       <c r="A228" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C228" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D228" s="2"/>
     </row>
     <row r="229">
       <c r="A229" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C229" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D229" s="2"/>
     </row>
     <row r="230">
       <c r="A230" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C230" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="D230" s="2"/>
     </row>
     <row r="231">
       <c r="A231" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C231" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="D231" s="2"/>
     </row>
     <row r="232">
       <c r="A232" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C232" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D232" s="2"/>
     </row>
     <row r="233">
       <c r="A233" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C233" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="D233" s="2"/>
     </row>
     <row r="234">
       <c r="A234" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C234" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="D234" s="2"/>
     </row>
     <row r="235">
       <c r="A235" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C235" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="D235" s="2"/>
     </row>
     <row r="236">
       <c r="A236" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C236" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D236" s="2"/>
     </row>
     <row r="237">
       <c r="A237" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C237" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="D237" s="2"/>
     </row>
     <row r="238">
       <c r="A238" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C238" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="D238" s="2"/>
     </row>
     <row r="239">
       <c r="A239" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C239" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D239" s="2"/>
     </row>
     <row r="240">
       <c r="A240" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C240" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="D240" s="2"/>
     </row>
     <row r="241">
       <c r="A241" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C241" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D241" s="2"/>
     </row>
     <row r="242">
       <c r="A242" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C242" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="D242" s="2"/>
     </row>
     <row r="243">
       <c r="A243" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C243" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="D243" s="2"/>
     </row>
     <row r="244">
       <c r="A244" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C244" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="D244" s="2"/>
     </row>
     <row r="245">
       <c r="A245" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C245" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D245" s="2"/>
     </row>
     <row r="246">
       <c r="A246" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C246" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="D246" s="2"/>
     </row>
     <row r="247">
       <c r="A247" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B247" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C247" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D247" s="2"/>
     </row>
     <row r="248">
       <c r="A248" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B248" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C248" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="D248" s="2"/>
     </row>
     <row r="249">
       <c r="A249" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B249" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C249" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D249" s="2"/>
     </row>
     <row r="250">
       <c r="A250" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B250" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C250" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D250" s="2"/>
     </row>
     <row r="251">
       <c r="A251" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B251" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C251" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D251" s="2"/>
     </row>
     <row r="252">
       <c r="A252" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B252" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C252" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="D252" s="2"/>
     </row>
     <row r="253">
       <c r="A253" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B253" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C253" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D253" s="2"/>
     </row>
     <row r="254">
       <c r="A254" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B254" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C254" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D254" s="2"/>
     </row>
     <row r="255">
       <c r="A255" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B255" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C255" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D255" s="2"/>
     </row>
     <row r="256">
       <c r="A256" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B256" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C256" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="D256" s="2"/>
     </row>
     <row r="257">
       <c r="A257" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B257" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C257" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="D257" s="2"/>
     </row>
     <row r="258">
       <c r="A258" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B258" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C258" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="D258" s="2"/>
     </row>
     <row r="259">
       <c r="A259" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B259" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C259" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D259" s="2"/>
     </row>
     <row r="260">
       <c r="A260" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B260" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C260" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="D260" s="2"/>
     </row>
     <row r="261">
       <c r="A261" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B261" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C261" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="D261" s="2"/>
     </row>
     <row r="262">
       <c r="A262" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B262" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C262" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="D262" s="2"/>
     </row>
     <row r="263">
       <c r="A263" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B263" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C263" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D263" s="2"/>
     </row>
     <row r="264">
       <c r="A264" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B264" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C264" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="D264" s="2"/>
     </row>
     <row r="265">
       <c r="A265" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B265" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C265" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="D265" s="2"/>
     </row>
     <row r="266">
       <c r="A266" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B266" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C266" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D266" s="2"/>
     </row>
     <row r="267">
       <c r="A267" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B267" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C267" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D267" s="2"/>
     </row>
     <row r="268">
       <c r="A268" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B268" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C268" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="D268" s="2"/>
     </row>
     <row r="269">
       <c r="A269" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B269" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C269" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="D269" s="2"/>
     </row>
     <row r="270">
       <c r="A270" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B270" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C270" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D270" s="2"/>
     </row>
     <row r="271">
       <c r="A271" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B271" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C271" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="D271" s="2"/>
     </row>
     <row r="272">
       <c r="A272" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B272" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C272" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="D272" s="2"/>
     </row>
     <row r="273">
       <c r="A273" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B273" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C273" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="D273" s="2"/>
     </row>
     <row r="274">
       <c r="A274" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B274" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C274" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="D274" s="2"/>
     </row>
     <row r="275">
       <c r="A275" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B275" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C275" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D275" s="2"/>
     </row>
     <row r="276">
       <c r="A276" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B276" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C276" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="D276" s="2"/>
     </row>
     <row r="277">
       <c r="A277" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B277" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C277" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="D277" s="2"/>
     </row>
     <row r="278">
       <c r="A278" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B278" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C278" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="D278" s="2"/>
     </row>
     <row r="279">
       <c r="A279" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B279" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C279" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="D279" s="2"/>
     </row>
     <row r="280">
       <c r="A280" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B280" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C280" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="D280" s="2"/>
     </row>
     <row r="281">
       <c r="A281" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B281" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C281" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="D281" s="2"/>
     </row>
     <row r="282">
       <c r="A282" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B282" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C282" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="D282" s="2"/>
     </row>
     <row r="283">
       <c r="A283" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B283" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C283" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="D283" s="2"/>
     </row>
     <row r="284">
       <c r="A284" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B284" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C284" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="D284" s="2"/>
     </row>
     <row r="285">
       <c r="A285" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B285" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C285" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="D285" s="2"/>
     </row>
     <row r="286">
       <c r="A286" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B286" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C286" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="D286" s="2"/>
     </row>
     <row r="287">
       <c r="A287" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B287" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C287" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="D287" s="2"/>
     </row>
     <row r="288">
       <c r="A288" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B288" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C288" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="D288" s="2"/>
     </row>
     <row r="289">
       <c r="A289" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B289" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C289" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="D289" s="2"/>
     </row>
     <row r="290">
       <c r="A290" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B290" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C290" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="D290" s="2"/>
     </row>
     <row r="291">
       <c r="A291" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B291" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C291" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="D291" s="2"/>
     </row>
     <row r="292">
       <c r="A292" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B292" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C292" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D292" s="2"/>
     </row>
     <row r="293">
       <c r="A293" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B293" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C293" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="D293" s="2"/>
     </row>
     <row r="294">
       <c r="A294" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B294" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C294" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="D294" s="2"/>
     </row>
     <row r="295">
       <c r="A295" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B295" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C295" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="D295" s="2"/>
     </row>
     <row r="296">
       <c r="A296" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B296" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C296" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="D296" s="2"/>
     </row>
     <row r="297">
       <c r="A297" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B297" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C297" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="D297" s="2"/>
     </row>
     <row r="298">
       <c r="A298" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B298" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C298" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="D298" s="2"/>
     </row>
     <row r="299">
       <c r="A299" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B299" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C299" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="D299" s="2"/>
     </row>
     <row r="300">
       <c r="A300" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B300" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C300" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="D300" s="2"/>
     </row>
     <row r="301">
       <c r="A301" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B301" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C301" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="D301" s="2"/>
     </row>
     <row r="302">
       <c r="A302" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B302" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C302" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="D302" s="2"/>
     </row>
     <row r="303">
       <c r="A303" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B303" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C303" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="D303" s="2"/>
     </row>
     <row r="304">
       <c r="A304" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B304" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C304" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="D304" s="2"/>
     </row>
     <row r="305">
       <c r="A305" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B305" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C305" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="D305" s="2"/>
     </row>
     <row r="306">
       <c r="A306" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B306" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C306" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="D306" s="2"/>
     </row>
     <row r="307">
       <c r="A307" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B307" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C307" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="D307" s="2"/>
     </row>
     <row r="308">
       <c r="A308" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B308" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C308" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="D308" s="2"/>
     </row>
     <row r="309">
       <c r="A309" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B309" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C309" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="D309" s="2"/>
     </row>
     <row r="310">
       <c r="A310" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B310" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C310" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="D310" s="2"/>
     </row>
     <row r="311">
       <c r="A311" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B311" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C311" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="D311" s="2"/>
     </row>
     <row r="312">
       <c r="A312" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B312" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C312" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="D312" s="2"/>
     </row>
     <row r="313">
       <c r="A313" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B313" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C313" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="D313" s="2"/>
     </row>
     <row r="314">
       <c r="A314" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B314" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C314" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="D314" s="2"/>
     </row>
     <row r="315">
       <c r="A315" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B315" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C315" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="D315" s="2"/>
     </row>
     <row r="316">
       <c r="A316" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B316" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C316" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="D316" s="2"/>
     </row>
     <row r="317">
       <c r="A317" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B317" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C317" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="D317" s="2"/>
     </row>
     <row r="318">
       <c r="A318" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B318" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C318" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="D318" s="2"/>
     </row>
     <row r="319">
       <c r="A319" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B319" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C319" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="D319" s="2"/>
     </row>
     <row r="320">
       <c r="A320" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B320" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C320" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="D320" s="2"/>
     </row>
     <row r="321">
       <c r="A321" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B321" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C321" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="D321" s="2"/>
     </row>
     <row r="322">
       <c r="A322" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B322" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C322" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="D322" s="2"/>
     </row>
     <row r="323">
       <c r="A323" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B323" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C323" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="D323" s="2"/>
     </row>
     <row r="324">
       <c r="A324" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B324" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C324" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="D324" s="2"/>
     </row>
     <row r="325">
       <c r="A325" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B325" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C325" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="D325" s="2"/>
     </row>
     <row r="326">
       <c r="A326" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B326" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="C326" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="D326" s="2"/>
     </row>
     <row r="327">
       <c r="A327" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B327" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="C327" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="D327" s="2"/>
     </row>
     <row r="328">
       <c r="A328" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B328" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="C328" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="D328" s="2"/>
     </row>
     <row r="329">
       <c r="A329" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B329" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C329" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="D329" s="2"/>
     </row>
     <row r="330">
       <c r="A330" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B330" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="C330" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="D330" s="2"/>
     </row>
     <row r="331">
       <c r="A331" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B331" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="C331" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="D331" s="2"/>
     </row>
     <row r="332">
       <c r="A332" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B332" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C332" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="D332" s="2"/>
     </row>
     <row r="333">
       <c r="A333" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B333" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="C333" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="D333" s="2"/>
     </row>
     <row r="334">
       <c r="A334" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B334" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="C334" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="D334" s="2"/>
     </row>
     <row r="335">
       <c r="A335" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B335" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="C335" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="D335" s="2"/>
     </row>
     <row r="336">
       <c r="A336" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B336" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="C336" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="D336" s="2"/>
     </row>
     <row r="337">
       <c r="A337" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B337" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="C337" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="D337" s="2"/>
     </row>
     <row r="338">
       <c r="A338" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B338" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="C338" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="D338" s="2"/>
     </row>
     <row r="339">
       <c r="A339" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B339" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C339" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="D339" s="2"/>
     </row>
     <row r="340">
       <c r="A340" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B340" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="C340" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="D340" s="2"/>
     </row>
     <row r="341">
       <c r="A341" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B341" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C341" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="D341" s="2"/>
     </row>
     <row r="342">
       <c r="A342" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B342" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="C342" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="D342" s="2"/>
     </row>
     <row r="343">
       <c r="A343" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B343" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="C343" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="D343" s="2"/>
     </row>
     <row r="344">
       <c r="A344" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B344" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C344" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="D344" s="2"/>
     </row>
     <row r="345">
       <c r="A345" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B345" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="C345" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="D345" s="2"/>
     </row>
     <row r="346">
       <c r="A346" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B346" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="C346" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="D346" s="2"/>
     </row>
     <row r="347">
       <c r="A347" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B347" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="C347" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="D347" s="2"/>
     </row>
     <row r="348">
       <c r="A348" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B348" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="C348" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="D348" s="2"/>
     </row>
     <row r="349">
       <c r="A349" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B349" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="C349" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="D349" s="2"/>
     </row>
     <row r="350">
       <c r="A350" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B350" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="C350" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="D350" s="2"/>
     </row>
     <row r="351">
       <c r="A351" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B351" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="C351" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="D351" s="2"/>
     </row>
     <row r="352">
       <c r="A352" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B352" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="C352" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="D352" s="2"/>
     </row>
     <row r="353">
       <c r="A353" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B353" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C353" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="D353" s="2"/>
     </row>
     <row r="354">
       <c r="A354" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B354" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="C354" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="D354" s="2"/>
     </row>
     <row r="355">
       <c r="A355" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B355" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="C355" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="D355" s="2"/>
     </row>
     <row r="356">
       <c r="A356" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B356" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C356" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="D356" s="2"/>
     </row>
     <row r="357">
       <c r="A357" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B357" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="C357" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="D357" s="2"/>
     </row>
     <row r="358">
       <c r="A358" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B358" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="C358" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="D358" s="2"/>
     </row>
     <row r="359">
       <c r="A359" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B359" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="C359" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="D359" s="2"/>
     </row>
     <row r="360">
       <c r="A360" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B360" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="C360" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="D360" s="2"/>
     </row>
     <row r="361">
       <c r="A361" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B361" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="C361" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="D361" s="2"/>
     </row>
     <row r="362">
       <c r="A362" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B362" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="C362" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="D362" s="2"/>
     </row>
     <row r="363">
       <c r="A363" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B363" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="C363" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="D363" s="2"/>
     </row>
     <row r="364">
       <c r="A364" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B364" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="C364" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="D364" s="2"/>
     </row>
     <row r="365">
       <c r="A365" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B365" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C365" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="D365" s="2"/>
     </row>
     <row r="366">
       <c r="A366" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B366" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="C366" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="D366" s="2"/>
     </row>
     <row r="367">
       <c r="A367" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B367" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="C367" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="D367" s="2"/>
     </row>
     <row r="368">
       <c r="A368" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B368" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="C368" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="D368" s="2"/>
     </row>
     <row r="369">
       <c r="A369" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B369" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C369" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="D369" s="2"/>
     </row>
     <row r="370">
       <c r="A370" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B370" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C370" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="D370" s="2"/>
     </row>
     <row r="371">
       <c r="A371" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B371" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C371" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="D371" s="2"/>
     </row>
     <row r="372">
       <c r="A372" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B372" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="C372" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="D372" s="2"/>
     </row>
     <row r="373">
       <c r="A373" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B373" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="C373" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="D373" s="2"/>
     </row>
     <row r="374">
       <c r="A374" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B374" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="C374" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="D374" s="2"/>
     </row>
     <row r="375">
       <c r="A375" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B375" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="C375" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="D375" s="2"/>
     </row>
     <row r="376">
       <c r="A376" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B376" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="C376" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="D376" s="2"/>
     </row>
     <row r="377">
       <c r="A377" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B377" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C377" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D377" s="2"/>
     </row>
     <row r="378">
       <c r="A378" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B378" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="C378" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="D378" s="2"/>
     </row>
     <row r="379">
       <c r="A379" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B379" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="C379" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="D379" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B380" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="C380" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D380" s="2"/>
     </row>
     <row r="381">
       <c r="A381" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B381" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="C381" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="D381" s="2"/>
     </row>
     <row r="382">
       <c r="A382" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B382" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C382" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="D382" s="2"/>
     </row>
     <row r="383">
       <c r="A383" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B383" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="C383" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="D383" s="2"/>
     </row>
     <row r="384">
       <c r="A384" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B384" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="C384" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D384" s="2"/>
     </row>
     <row r="385">
       <c r="A385" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B385" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="C385" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="D385" s="2"/>
     </row>
     <row r="386">
       <c r="A386" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B386" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="C386" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="D386" s="2"/>
     </row>
     <row r="387">
       <c r="A387" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B387" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="C387" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="D387" s="2"/>
     </row>
     <row r="388">
       <c r="A388" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B388" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="C388" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="D388" s="2"/>
     </row>
     <row r="389">
       <c r="A389" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B389" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="C389" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D389" s="2"/>
     </row>
     <row r="390">
       <c r="A390" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B390" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="C390" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="D390" s="2"/>
     </row>
     <row r="391">
       <c r="A391" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B391" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="C391" t="s" s="2">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="D391" s="2"/>
     </row>
     <row r="392">
       <c r="A392" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B392" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="C392" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="D392" s="2"/>
     </row>
     <row r="393">
       <c r="A393" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B393" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C393" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="D393" s="2"/>
     </row>
     <row r="394">
       <c r="A394" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B394" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="C394" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="D394" s="2"/>
     </row>
     <row r="395">
       <c r="A395" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B395" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="C395" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="D395" s="2"/>
     </row>
     <row r="396">
       <c r="A396" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B396" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="C396" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="D396" s="2"/>
     </row>
     <row r="397">
       <c r="A397" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B397" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="C397" t="s" s="2">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="D397" s="2"/>
     </row>
     <row r="398">
       <c r="A398" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B398" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C398" t="s" s="2">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="D398" s="2"/>
     </row>
     <row r="399">
       <c r="A399" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B399" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="C399" t="s" s="2">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="D399" s="2"/>
     </row>
     <row r="400">
       <c r="A400" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B400" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="C400" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="D400" s="2"/>
     </row>
     <row r="401">
       <c r="A401" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B401" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="C401" t="s" s="2">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="D401" s="2"/>
     </row>
     <row r="402">
       <c r="A402" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B402" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="C402" t="s" s="2">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="D402" s="2"/>
     </row>
     <row r="403">
       <c r="A403" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B403" t="s" s="2">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="C403" t="s" s="2">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="D403" s="2"/>
     </row>
     <row r="404">
       <c r="A404" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B404" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="C404" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="D404" s="2"/>
     </row>
     <row r="405">
       <c r="A405" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B405" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="C405" t="s" s="2">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="D405" s="2"/>
     </row>
     <row r="406">
       <c r="A406" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B406" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="C406" t="s" s="2">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="D406" s="2"/>
     </row>
     <row r="407">
       <c r="A407" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B407" t="s" s="2">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="C407" t="s" s="2">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="D407" s="2"/>
     </row>
     <row r="408">
       <c r="A408" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B408" t="s" s="2">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="C408" t="s" s="2">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="D408" s="2"/>
     </row>
     <row r="409">
       <c r="A409" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B409" t="s" s="2">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="C409" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="D409" s="2"/>
     </row>
     <row r="410">
       <c r="A410" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B410" t="s" s="2">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="C410" t="s" s="2">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="D410" s="2"/>
     </row>
     <row r="411">
       <c r="A411" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B411" t="s" s="2">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="C411" t="s" s="2">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="D411" s="2"/>
     </row>
     <row r="412">
       <c r="A412" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B412" t="s" s="2">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="C412" t="s" s="2">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="D412" s="2"/>
     </row>
     <row r="413">
       <c r="A413" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B413" t="s" s="2">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="C413" t="s" s="2">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="D413" s="2"/>
     </row>
     <row r="414">
       <c r="A414" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B414" t="s" s="2">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="C414" t="s" s="2">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="D414" s="2"/>
     </row>
     <row r="415">
       <c r="A415" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B415" t="s" s="2">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="C415" t="s" s="2">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="D415" s="2"/>
     </row>
     <row r="416">
       <c r="A416" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B416" t="s" s="2">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="C416" t="s" s="2">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="D416" s="2"/>
     </row>
     <row r="417">
       <c r="A417" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B417" t="s" s="2">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="C417" t="s" s="2">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="D417" s="2"/>
     </row>
     <row r="418">
       <c r="A418" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B418" t="s" s="2">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="C418" t="s" s="2">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="D418" s="2"/>
     </row>
     <row r="419">
       <c r="A419" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B419" t="s" s="2">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="C419" t="s" s="2">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="D419" s="2"/>
     </row>
     <row r="420">
       <c r="A420" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B420" t="s" s="2">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="C420" t="s" s="2">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="D420" s="2"/>
     </row>
     <row r="421">
       <c r="A421" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B421" t="s" s="2">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="C421" t="s" s="2">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="D421" s="2"/>
     </row>
     <row r="422">
       <c r="A422" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B422" t="s" s="2">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="C422" t="s" s="2">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="D422" s="2"/>
     </row>
     <row r="423">
       <c r="A423" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B423" t="s" s="2">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="C423" t="s" s="2">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="D423" t="s" s="2">
-        <v>901</v>
+        <v>902</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B424" t="s" s="2">
+        <v>903</v>
+      </c>
+      <c r="C424" t="s" s="2">
+        <v>904</v>
+      </c>
+      <c r="D424" t="s" s="2">
         <v>902</v>
-      </c>
-      <c r="C424" t="s" s="2">
-        <v>903</v>
-      </c>
-      <c r="D424" t="s" s="2">
-        <v>901</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B425" t="s" s="2">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="C425" t="s" s="2">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="D425" t="s" s="2">
-        <v>901</v>
+        <v>902</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B426" t="s" s="2">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="C426" t="s" s="2">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="D426" s="2"/>
     </row>

--- a/ig/DM_FINESS_New/CodeSystem-tre-r397-categorie-entite-geographique-exercice.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-tre-r397-categorie-entite-geographique-exercice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1360" uniqueCount="909">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1364" uniqueCount="913">
   <si>
     <t>Property</t>
   </si>
@@ -223,6 +223,18 @@
     <t>Date Concept was retired</t>
   </si>
   <si>
+    <t>specialisationRor</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#specialisationRor</t>
+  </si>
+  <si>
+    <t>Propriété permettant de spécifier les codes exclusifs appartenant au ROR</t>
+  </si>
+  <si>
+    <t>boolean</t>
+  </si>
+  <si>
     <t>Level</t>
   </si>
   <si>
@@ -241,49 +253,49 @@
     <t>Etablissements d'administration</t>
   </si>
   <si>
+    <t>1000</t>
+  </si>
+  <si>
+    <t>Etablissements Relevant de la Loi Hospitalière</t>
+  </si>
+  <si>
+    <t>2000</t>
+  </si>
+  <si>
+    <t>Autres Etablissements de Soins et Prévention</t>
+  </si>
+  <si>
+    <t>3000</t>
+  </si>
+  <si>
+    <t>Autres Etablissements à Caractère Sanitaire</t>
+  </si>
+  <si>
+    <t>4000</t>
+  </si>
+  <si>
+    <t>Etab.Serv.Soc.d'Accueil Hébergement Assistance Réadaptation</t>
+  </si>
+  <si>
+    <t>5000</t>
+  </si>
+  <si>
+    <t>Etablissements et Services Sociaux d'Aide à la Famille</t>
+  </si>
+  <si>
+    <t>6000</t>
+  </si>
+  <si>
+    <t>Etab.de Formation des Personnels Sanitaires et Sociaux</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>Etablissements d'Administration</t>
+  </si>
+  <si>
     <t>0110</t>
-  </si>
-  <si>
-    <t>Etablissements d'Administration</t>
-  </si>
-  <si>
-    <t>1000</t>
-  </si>
-  <si>
-    <t>Etablissements Relevant de la Loi Hospitalière</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>2000</t>
-  </si>
-  <si>
-    <t>Autres Etablissements de Soins et Prévention</t>
-  </si>
-  <si>
-    <t>3000</t>
-  </si>
-  <si>
-    <t>Autres Etablissements à Caractère Sanitaire</t>
-  </si>
-  <si>
-    <t>4000</t>
-  </si>
-  <si>
-    <t>Etab.Serv.Soc.d'Accueil Hébergement Assistance Réadaptation</t>
-  </si>
-  <si>
-    <t>5000</t>
-  </si>
-  <si>
-    <t>Etablissements et Services Sociaux d'Aide à la Famille</t>
-  </si>
-  <si>
-    <t>6000</t>
-  </si>
-  <si>
-    <t>Etab.de Formation des Personnels Sanitaires et Sociaux</t>
   </si>
   <si>
     <t>1100</t>
@@ -3046,7 +3058,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -3187,6 +3199,20 @@
       </c>
       <c r="D10" t="s" s="2">
         <v>53</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="C11" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="D11" t="s" s="2">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -3201,5123 +3227,5123 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B1" t="s" s="1">
         <v>35</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>71</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="D5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C8" t="s" s="2">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C9" t="s" s="2">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D21" s="2"/>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D22" s="2"/>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="D23" s="2"/>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D24" s="2"/>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D25" s="2"/>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D26" s="2"/>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D27" s="2"/>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="D28" s="2"/>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="D29" s="2"/>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="D30" s="2"/>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D31" s="2"/>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="D32" s="2"/>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D33" s="2"/>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="D34" s="2"/>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D35" s="2"/>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="D36" s="2"/>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D37" s="2"/>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D38" s="2"/>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="D39" s="2"/>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="D40" s="2"/>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D41" s="2"/>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="D42" s="2"/>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="D43" s="2"/>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="D44" s="2"/>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D45" s="2"/>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="D46" s="2"/>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="D47" s="2"/>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="D48" s="2"/>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D49" s="2"/>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="D50" s="2"/>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="D51" s="2"/>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="D52" s="2"/>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="D53" s="2"/>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="D54" s="2"/>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="D55" s="2"/>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D56" s="2"/>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D57" s="2"/>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="D58" s="2"/>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="D59" s="2"/>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="D60" s="2"/>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="D61" s="2"/>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="D62" s="2"/>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="D63" s="2"/>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="D64" s="2"/>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="D65" s="2"/>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D66" s="2"/>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="D67" s="2"/>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="D68" s="2"/>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="D69" s="2"/>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="D70" s="2"/>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="D71" s="2"/>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="D72" s="2"/>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="D73" s="2"/>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="D74" s="2"/>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="D75" s="2"/>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="D76" s="2"/>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="D77" s="2"/>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D78" s="2"/>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="D79" s="2"/>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="D80" s="2"/>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="D81" s="2"/>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C82" t="s" s="2">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="D82" s="2"/>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="C83" t="s" s="2">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="D83" s="2"/>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="D84" s="2"/>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="C85" t="s" s="2">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="D85" s="2"/>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="D86" s="2"/>
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="C87" t="s" s="2">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="D87" s="2"/>
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="D88" s="2"/>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="C89" t="s" s="2">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D89" s="2"/>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="D90" s="2"/>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="D91" s="2"/>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="C92" t="s" s="2">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="D92" s="2"/>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="D93" s="2"/>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="C94" t="s" s="2">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="D94" s="2"/>
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D95" s="2"/>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="D96" s="2"/>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="D97" s="2"/>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D98" s="2"/>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D99" s="2"/>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D100" s="2"/>
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="D101" s="2"/>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="C102" t="s" s="2">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D102" s="2"/>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="D103" s="2"/>
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D104" s="2"/>
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="D105" s="2"/>
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="D106" s="2"/>
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D107" s="2"/>
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D108" s="2"/>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="D109" s="2"/>
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="C110" t="s" s="2">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="D110" s="2"/>
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="D111" s="2"/>
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="D112" s="2"/>
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="C113" t="s" s="2">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="D113" s="2"/>
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="C114" t="s" s="2">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="D114" s="2"/>
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C115" t="s" s="2">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="D115" s="2"/>
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="C116" t="s" s="2">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="D116" s="2"/>
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="C117" t="s" s="2">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="D117" s="2"/>
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="C118" t="s" s="2">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="D118" s="2"/>
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="D119" s="2"/>
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="C120" t="s" s="2">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="D120" s="2"/>
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="C121" t="s" s="2">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="D121" s="2"/>
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="C122" t="s" s="2">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="D122" s="2"/>
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="C123" t="s" s="2">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="D123" s="2"/>
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="C124" t="s" s="2">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="D124" s="2"/>
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="C125" t="s" s="2">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="D125" s="2"/>
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="C126" t="s" s="2">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="D126" s="2"/>
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="C127" t="s" s="2">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="D127" s="2"/>
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="C128" t="s" s="2">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="D128" s="2"/>
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="C129" t="s" s="2">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="D129" s="2"/>
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="C130" t="s" s="2">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="D130" s="2"/>
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="C131" t="s" s="2">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="D131" s="2"/>
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="C132" t="s" s="2">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="D132" s="2"/>
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="C133" t="s" s="2">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="D133" s="2"/>
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="C134" t="s" s="2">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D134" s="2"/>
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="C135" t="s" s="2">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="D135" s="2"/>
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="C136" t="s" s="2">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="D136" s="2"/>
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="C137" t="s" s="2">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="D137" s="2"/>
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="C138" t="s" s="2">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="D138" s="2"/>
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="C139" t="s" s="2">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="D139" s="2"/>
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="C140" t="s" s="2">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="D140" s="2"/>
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="C141" t="s" s="2">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="D141" s="2"/>
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="C142" t="s" s="2">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="D142" s="2"/>
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="C143" t="s" s="2">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="D143" s="2"/>
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="C144" t="s" s="2">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="D144" s="2"/>
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="C145" t="s" s="2">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="D145" s="2"/>
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C146" t="s" s="2">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="D146" s="2"/>
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="C147" t="s" s="2">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="D147" s="2"/>
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="C148" t="s" s="2">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="D148" s="2"/>
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="C149" t="s" s="2">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="D149" s="2"/>
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="C150" t="s" s="2">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="D150" s="2"/>
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="C151" t="s" s="2">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="D151" s="2"/>
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="C152" t="s" s="2">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="D152" s="2"/>
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="C153" t="s" s="2">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="D153" s="2"/>
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="C154" t="s" s="2">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="D154" s="2"/>
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="C155" t="s" s="2">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="D155" s="2"/>
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="C156" t="s" s="2">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="D156" s="2"/>
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="C157" t="s" s="2">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="D157" s="2"/>
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C158" t="s" s="2">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="D158" s="2"/>
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="C159" t="s" s="2">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="D159" s="2"/>
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="C160" t="s" s="2">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="D160" s="2"/>
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="C161" t="s" s="2">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="D161" s="2"/>
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="C162" t="s" s="2">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="D162" s="2"/>
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="C163" t="s" s="2">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="D163" s="2"/>
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="C164" t="s" s="2">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="D164" s="2"/>
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="C165" t="s" s="2">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="D165" s="2"/>
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C166" t="s" s="2">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="D166" s="2"/>
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="C167" t="s" s="2">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="D167" s="2"/>
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="C168" t="s" s="2">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="D168" s="2"/>
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="C169" t="s" s="2">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D169" s="2"/>
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="C170" t="s" s="2">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="D170" s="2"/>
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="C171" t="s" s="2">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="D171" s="2"/>
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="C172" t="s" s="2">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="D172" s="2"/>
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="C173" t="s" s="2">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="D173" s="2"/>
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="C174" t="s" s="2">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="D174" s="2"/>
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="C175" t="s" s="2">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="D175" s="2"/>
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="C176" t="s" s="2">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="D176" s="2"/>
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="C177" t="s" s="2">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="D177" s="2"/>
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="C178" t="s" s="2">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="D178" s="2"/>
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="C179" t="s" s="2">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="D179" s="2"/>
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="C180" t="s" s="2">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="D180" s="2"/>
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="C181" t="s" s="2">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="D181" s="2"/>
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="C182" t="s" s="2">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="D182" s="2"/>
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="C183" t="s" s="2">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="D183" s="2"/>
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="C184" t="s" s="2">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="D184" s="2"/>
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="C185" t="s" s="2">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="D185" s="2"/>
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="C186" t="s" s="2">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="D186" s="2"/>
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="C187" t="s" s="2">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="D187" s="2"/>
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="C188" t="s" s="2">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="D188" s="2"/>
     </row>
     <row r="189">
       <c r="A189" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="C189" t="s" s="2">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="D189" s="2"/>
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="C190" t="s" s="2">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="D190" s="2"/>
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="C191" t="s" s="2">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="D191" s="2"/>
     </row>
     <row r="192">
       <c r="A192" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="C192" t="s" s="2">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="D192" s="2"/>
     </row>
     <row r="193">
       <c r="A193" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="C193" t="s" s="2">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="D193" s="2"/>
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="C194" t="s" s="2">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="D194" s="2"/>
     </row>
     <row r="195">
       <c r="A195" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="C195" t="s" s="2">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="D195" s="2"/>
     </row>
     <row r="196">
       <c r="A196" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="C196" t="s" s="2">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="D196" s="2"/>
     </row>
     <row r="197">
       <c r="A197" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="C197" t="s" s="2">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="D197" s="2"/>
     </row>
     <row r="198">
       <c r="A198" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="C198" t="s" s="2">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="D198" s="2"/>
     </row>
     <row r="199">
       <c r="A199" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="C199" t="s" s="2">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="D199" s="2"/>
     </row>
     <row r="200">
       <c r="A200" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="C200" t="s" s="2">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="D200" s="2"/>
     </row>
     <row r="201">
       <c r="A201" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="C201" t="s" s="2">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="D201" s="2"/>
     </row>
     <row r="202">
       <c r="A202" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="C202" t="s" s="2">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="D202" s="2"/>
     </row>
     <row r="203">
       <c r="A203" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="C203" t="s" s="2">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="D203" s="2"/>
     </row>
     <row r="204">
       <c r="A204" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="C204" t="s" s="2">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="D204" s="2"/>
     </row>
     <row r="205">
       <c r="A205" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="C205" t="s" s="2">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="D205" s="2"/>
     </row>
     <row r="206">
       <c r="A206" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="C206" t="s" s="2">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="D206" s="2"/>
     </row>
     <row r="207">
       <c r="A207" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="C207" t="s" s="2">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="D207" s="2"/>
     </row>
     <row r="208">
       <c r="A208" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="C208" t="s" s="2">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="D208" s="2"/>
     </row>
     <row r="209">
       <c r="A209" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="C209" t="s" s="2">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="D209" s="2"/>
     </row>
     <row r="210">
       <c r="A210" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="C210" t="s" s="2">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="D210" s="2"/>
     </row>
     <row r="211">
       <c r="A211" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="C211" t="s" s="2">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="D211" s="2"/>
     </row>
     <row r="212">
       <c r="A212" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="C212" t="s" s="2">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="D212" s="2"/>
     </row>
     <row r="213">
       <c r="A213" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="C213" t="s" s="2">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="D213" s="2"/>
     </row>
     <row r="214">
       <c r="A214" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="C214" t="s" s="2">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="D214" s="2"/>
     </row>
     <row r="215">
       <c r="A215" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="C215" t="s" s="2">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="D215" s="2"/>
     </row>
     <row r="216">
       <c r="A216" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="C216" t="s" s="2">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="D216" s="2"/>
     </row>
     <row r="217">
       <c r="A217" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="C217" t="s" s="2">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="D217" s="2"/>
     </row>
     <row r="218">
       <c r="A218" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="C218" t="s" s="2">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="D218" s="2"/>
     </row>
     <row r="219">
       <c r="A219" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="C219" t="s" s="2">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="D219" s="2"/>
     </row>
     <row r="220">
       <c r="A220" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="C220" t="s" s="2">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="D220" s="2"/>
     </row>
     <row r="221">
       <c r="A221" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="C221" t="s" s="2">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="D221" s="2"/>
     </row>
     <row r="222">
       <c r="A222" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="C222" t="s" s="2">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="D222" s="2"/>
     </row>
     <row r="223">
       <c r="A223" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="C223" t="s" s="2">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="D223" s="2"/>
     </row>
     <row r="224">
       <c r="A224" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="C224" t="s" s="2">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="D224" s="2"/>
     </row>
     <row r="225">
       <c r="A225" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="C225" t="s" s="2">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="D225" s="2"/>
     </row>
     <row r="226">
       <c r="A226" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="C226" t="s" s="2">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="D226" s="2"/>
     </row>
     <row r="227">
       <c r="A227" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="C227" t="s" s="2">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="D227" s="2"/>
     </row>
     <row r="228">
       <c r="A228" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="C228" t="s" s="2">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="D228" s="2"/>
     </row>
     <row r="229">
       <c r="A229" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="C229" t="s" s="2">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="D229" s="2"/>
     </row>
     <row r="230">
       <c r="A230" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="C230" t="s" s="2">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="D230" s="2"/>
     </row>
     <row r="231">
       <c r="A231" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="C231" t="s" s="2">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="D231" s="2"/>
     </row>
     <row r="232">
       <c r="A232" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="C232" t="s" s="2">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="D232" s="2"/>
     </row>
     <row r="233">
       <c r="A233" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="C233" t="s" s="2">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="D233" s="2"/>
     </row>
     <row r="234">
       <c r="A234" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="C234" t="s" s="2">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="D234" s="2"/>
     </row>
     <row r="235">
       <c r="A235" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="C235" t="s" s="2">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="D235" s="2"/>
     </row>
     <row r="236">
       <c r="A236" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="C236" t="s" s="2">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="D236" s="2"/>
     </row>
     <row r="237">
       <c r="A237" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="C237" t="s" s="2">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="D237" s="2"/>
     </row>
     <row r="238">
       <c r="A238" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="C238" t="s" s="2">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="D238" s="2"/>
     </row>
     <row r="239">
       <c r="A239" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="C239" t="s" s="2">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="D239" s="2"/>
     </row>
     <row r="240">
       <c r="A240" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="C240" t="s" s="2">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="D240" s="2"/>
     </row>
     <row r="241">
       <c r="A241" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="C241" t="s" s="2">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="D241" s="2"/>
     </row>
     <row r="242">
       <c r="A242" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="C242" t="s" s="2">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="D242" s="2"/>
     </row>
     <row r="243">
       <c r="A243" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="C243" t="s" s="2">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="D243" s="2"/>
     </row>
     <row r="244">
       <c r="A244" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="C244" t="s" s="2">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="D244" s="2"/>
     </row>
     <row r="245">
       <c r="A245" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="C245" t="s" s="2">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="D245" s="2"/>
     </row>
     <row r="246">
       <c r="A246" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="C246" t="s" s="2">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="D246" s="2"/>
     </row>
     <row r="247">
       <c r="A247" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B247" t="s" s="2">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="C247" t="s" s="2">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="D247" s="2"/>
     </row>
     <row r="248">
       <c r="A248" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B248" t="s" s="2">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="C248" t="s" s="2">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="D248" s="2"/>
     </row>
     <row r="249">
       <c r="A249" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B249" t="s" s="2">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="C249" t="s" s="2">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="D249" s="2"/>
     </row>
     <row r="250">
       <c r="A250" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B250" t="s" s="2">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="C250" t="s" s="2">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="D250" s="2"/>
     </row>
     <row r="251">
       <c r="A251" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B251" t="s" s="2">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="C251" t="s" s="2">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="D251" s="2"/>
     </row>
     <row r="252">
       <c r="A252" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B252" t="s" s="2">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="C252" t="s" s="2">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="D252" s="2"/>
     </row>
     <row r="253">
       <c r="A253" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B253" t="s" s="2">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="C253" t="s" s="2">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="D253" s="2"/>
     </row>
     <row r="254">
       <c r="A254" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B254" t="s" s="2">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="C254" t="s" s="2">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="D254" s="2"/>
     </row>
     <row r="255">
       <c r="A255" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B255" t="s" s="2">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="C255" t="s" s="2">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="D255" s="2"/>
     </row>
     <row r="256">
       <c r="A256" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B256" t="s" s="2">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="C256" t="s" s="2">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="D256" s="2"/>
     </row>
     <row r="257">
       <c r="A257" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B257" t="s" s="2">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="C257" t="s" s="2">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="D257" s="2"/>
     </row>
     <row r="258">
       <c r="A258" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B258" t="s" s="2">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="C258" t="s" s="2">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="D258" s="2"/>
     </row>
     <row r="259">
       <c r="A259" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B259" t="s" s="2">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="C259" t="s" s="2">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="D259" s="2"/>
     </row>
     <row r="260">
       <c r="A260" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B260" t="s" s="2">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="C260" t="s" s="2">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="D260" s="2"/>
     </row>
     <row r="261">
       <c r="A261" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B261" t="s" s="2">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="C261" t="s" s="2">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="D261" s="2"/>
     </row>
     <row r="262">
       <c r="A262" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B262" t="s" s="2">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="C262" t="s" s="2">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="D262" s="2"/>
     </row>
     <row r="263">
       <c r="A263" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B263" t="s" s="2">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="C263" t="s" s="2">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="D263" s="2"/>
     </row>
     <row r="264">
       <c r="A264" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B264" t="s" s="2">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="C264" t="s" s="2">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="D264" s="2"/>
     </row>
     <row r="265">
       <c r="A265" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B265" t="s" s="2">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="C265" t="s" s="2">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="D265" s="2"/>
     </row>
     <row r="266">
       <c r="A266" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B266" t="s" s="2">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="C266" t="s" s="2">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="D266" s="2"/>
     </row>
     <row r="267">
       <c r="A267" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B267" t="s" s="2">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="C267" t="s" s="2">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="D267" s="2"/>
     </row>
     <row r="268">
       <c r="A268" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B268" t="s" s="2">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="C268" t="s" s="2">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="D268" s="2"/>
     </row>
     <row r="269">
       <c r="A269" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B269" t="s" s="2">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="C269" t="s" s="2">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="D269" s="2"/>
     </row>
     <row r="270">
       <c r="A270" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B270" t="s" s="2">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="C270" t="s" s="2">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="D270" s="2"/>
     </row>
     <row r="271">
       <c r="A271" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B271" t="s" s="2">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="C271" t="s" s="2">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="D271" s="2"/>
     </row>
     <row r="272">
       <c r="A272" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B272" t="s" s="2">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="C272" t="s" s="2">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="D272" s="2"/>
     </row>
     <row r="273">
       <c r="A273" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B273" t="s" s="2">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="C273" t="s" s="2">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="D273" s="2"/>
     </row>
     <row r="274">
       <c r="A274" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B274" t="s" s="2">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="C274" t="s" s="2">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="D274" s="2"/>
     </row>
     <row r="275">
       <c r="A275" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B275" t="s" s="2">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="C275" t="s" s="2">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="D275" s="2"/>
     </row>
     <row r="276">
       <c r="A276" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B276" t="s" s="2">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="C276" t="s" s="2">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="D276" s="2"/>
     </row>
     <row r="277">
       <c r="A277" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B277" t="s" s="2">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="C277" t="s" s="2">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="D277" s="2"/>
     </row>
     <row r="278">
       <c r="A278" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B278" t="s" s="2">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="C278" t="s" s="2">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="D278" s="2"/>
     </row>
     <row r="279">
       <c r="A279" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B279" t="s" s="2">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="C279" t="s" s="2">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="D279" s="2"/>
     </row>
     <row r="280">
       <c r="A280" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B280" t="s" s="2">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="C280" t="s" s="2">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="D280" s="2"/>
     </row>
     <row r="281">
       <c r="A281" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B281" t="s" s="2">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="C281" t="s" s="2">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="D281" s="2"/>
     </row>
     <row r="282">
       <c r="A282" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B282" t="s" s="2">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="C282" t="s" s="2">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="D282" s="2"/>
     </row>
     <row r="283">
       <c r="A283" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B283" t="s" s="2">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="C283" t="s" s="2">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="D283" s="2"/>
     </row>
     <row r="284">
       <c r="A284" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B284" t="s" s="2">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="C284" t="s" s="2">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="D284" s="2"/>
     </row>
     <row r="285">
       <c r="A285" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B285" t="s" s="2">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="C285" t="s" s="2">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="D285" s="2"/>
     </row>
     <row r="286">
       <c r="A286" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B286" t="s" s="2">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="C286" t="s" s="2">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="D286" s="2"/>
     </row>
     <row r="287">
       <c r="A287" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B287" t="s" s="2">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="C287" t="s" s="2">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="D287" s="2"/>
     </row>
     <row r="288">
       <c r="A288" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B288" t="s" s="2">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="C288" t="s" s="2">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="D288" s="2"/>
     </row>
     <row r="289">
       <c r="A289" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B289" t="s" s="2">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="C289" t="s" s="2">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="D289" s="2"/>
     </row>
     <row r="290">
       <c r="A290" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B290" t="s" s="2">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="C290" t="s" s="2">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="D290" s="2"/>
     </row>
     <row r="291">
       <c r="A291" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B291" t="s" s="2">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="C291" t="s" s="2">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="D291" s="2"/>
     </row>
     <row r="292">
       <c r="A292" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B292" t="s" s="2">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="C292" t="s" s="2">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="D292" s="2"/>
     </row>
     <row r="293">
       <c r="A293" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B293" t="s" s="2">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="C293" t="s" s="2">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="D293" s="2"/>
     </row>
     <row r="294">
       <c r="A294" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B294" t="s" s="2">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="C294" t="s" s="2">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="D294" s="2"/>
     </row>
     <row r="295">
       <c r="A295" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B295" t="s" s="2">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="C295" t="s" s="2">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="D295" s="2"/>
     </row>
     <row r="296">
       <c r="A296" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B296" t="s" s="2">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="C296" t="s" s="2">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="D296" s="2"/>
     </row>
     <row r="297">
       <c r="A297" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B297" t="s" s="2">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="C297" t="s" s="2">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="D297" s="2"/>
     </row>
     <row r="298">
       <c r="A298" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B298" t="s" s="2">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="C298" t="s" s="2">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="D298" s="2"/>
     </row>
     <row r="299">
       <c r="A299" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B299" t="s" s="2">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="C299" t="s" s="2">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="D299" s="2"/>
     </row>
     <row r="300">
       <c r="A300" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B300" t="s" s="2">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="C300" t="s" s="2">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="D300" s="2"/>
     </row>
     <row r="301">
       <c r="A301" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B301" t="s" s="2">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C301" t="s" s="2">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="D301" s="2"/>
     </row>
     <row r="302">
       <c r="A302" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B302" t="s" s="2">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="C302" t="s" s="2">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="D302" s="2"/>
     </row>
     <row r="303">
       <c r="A303" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B303" t="s" s="2">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="C303" t="s" s="2">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="D303" s="2"/>
     </row>
     <row r="304">
       <c r="A304" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B304" t="s" s="2">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C304" t="s" s="2">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="D304" s="2"/>
     </row>
     <row r="305">
       <c r="A305" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B305" t="s" s="2">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="C305" t="s" s="2">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="D305" s="2"/>
     </row>
     <row r="306">
       <c r="A306" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B306" t="s" s="2">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="C306" t="s" s="2">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="D306" s="2"/>
     </row>
     <row r="307">
       <c r="A307" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B307" t="s" s="2">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="C307" t="s" s="2">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="D307" s="2"/>
     </row>
     <row r="308">
       <c r="A308" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B308" t="s" s="2">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="C308" t="s" s="2">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="D308" s="2"/>
     </row>
     <row r="309">
       <c r="A309" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B309" t="s" s="2">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="C309" t="s" s="2">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="D309" s="2"/>
     </row>
     <row r="310">
       <c r="A310" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B310" t="s" s="2">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="C310" t="s" s="2">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="D310" s="2"/>
     </row>
     <row r="311">
       <c r="A311" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B311" t="s" s="2">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="C311" t="s" s="2">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="D311" s="2"/>
     </row>
     <row r="312">
       <c r="A312" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B312" t="s" s="2">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="C312" t="s" s="2">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="D312" s="2"/>
     </row>
     <row r="313">
       <c r="A313" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B313" t="s" s="2">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="C313" t="s" s="2">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="D313" s="2"/>
     </row>
     <row r="314">
       <c r="A314" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B314" t="s" s="2">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="C314" t="s" s="2">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="D314" s="2"/>
     </row>
     <row r="315">
       <c r="A315" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B315" t="s" s="2">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="C315" t="s" s="2">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="D315" s="2"/>
     </row>
     <row r="316">
       <c r="A316" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B316" t="s" s="2">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="C316" t="s" s="2">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="D316" s="2"/>
     </row>
     <row r="317">
       <c r="A317" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B317" t="s" s="2">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="C317" t="s" s="2">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="D317" s="2"/>
     </row>
     <row r="318">
       <c r="A318" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B318" t="s" s="2">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="C318" t="s" s="2">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="D318" s="2"/>
     </row>
     <row r="319">
       <c r="A319" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B319" t="s" s="2">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="C319" t="s" s="2">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="D319" s="2"/>
     </row>
     <row r="320">
       <c r="A320" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B320" t="s" s="2">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="C320" t="s" s="2">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="D320" s="2"/>
     </row>
     <row r="321">
       <c r="A321" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B321" t="s" s="2">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="C321" t="s" s="2">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="D321" s="2"/>
     </row>
     <row r="322">
       <c r="A322" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B322" t="s" s="2">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="C322" t="s" s="2">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="D322" s="2"/>
     </row>
     <row r="323">
       <c r="A323" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B323" t="s" s="2">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="C323" t="s" s="2">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="D323" s="2"/>
     </row>
     <row r="324">
       <c r="A324" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B324" t="s" s="2">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="C324" t="s" s="2">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="D324" s="2"/>
     </row>
     <row r="325">
       <c r="A325" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B325" t="s" s="2">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="C325" t="s" s="2">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="D325" s="2"/>
     </row>
     <row r="326">
       <c r="A326" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B326" t="s" s="2">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="C326" t="s" s="2">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="D326" s="2"/>
     </row>
     <row r="327">
       <c r="A327" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B327" t="s" s="2">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="C327" t="s" s="2">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="D327" s="2"/>
     </row>
     <row r="328">
       <c r="A328" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B328" t="s" s="2">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="C328" t="s" s="2">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="D328" s="2"/>
     </row>
     <row r="329">
       <c r="A329" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B329" t="s" s="2">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="C329" t="s" s="2">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="D329" s="2"/>
     </row>
     <row r="330">
       <c r="A330" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B330" t="s" s="2">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="C330" t="s" s="2">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="D330" s="2"/>
     </row>
     <row r="331">
       <c r="A331" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B331" t="s" s="2">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="C331" t="s" s="2">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="D331" s="2"/>
     </row>
     <row r="332">
       <c r="A332" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B332" t="s" s="2">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="C332" t="s" s="2">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="D332" s="2"/>
     </row>
     <row r="333">
       <c r="A333" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B333" t="s" s="2">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="C333" t="s" s="2">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="D333" s="2"/>
     </row>
     <row r="334">
       <c r="A334" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B334" t="s" s="2">
-        <v>725</v>
+        <v>729</v>
       </c>
       <c r="C334" t="s" s="2">
-        <v>726</v>
+        <v>730</v>
       </c>
       <c r="D334" s="2"/>
     </row>
     <row r="335">
       <c r="A335" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B335" t="s" s="2">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="C335" t="s" s="2">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="D335" s="2"/>
     </row>
     <row r="336">
       <c r="A336" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B336" t="s" s="2">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="C336" t="s" s="2">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="D336" s="2"/>
     </row>
     <row r="337">
       <c r="A337" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B337" t="s" s="2">
-        <v>731</v>
+        <v>735</v>
       </c>
       <c r="C337" t="s" s="2">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="D337" s="2"/>
     </row>
     <row r="338">
       <c r="A338" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B338" t="s" s="2">
-        <v>733</v>
+        <v>737</v>
       </c>
       <c r="C338" t="s" s="2">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="D338" s="2"/>
     </row>
     <row r="339">
       <c r="A339" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B339" t="s" s="2">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="C339" t="s" s="2">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="D339" s="2"/>
     </row>
     <row r="340">
       <c r="A340" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B340" t="s" s="2">
-        <v>737</v>
+        <v>741</v>
       </c>
       <c r="C340" t="s" s="2">
-        <v>738</v>
+        <v>742</v>
       </c>
       <c r="D340" s="2"/>
     </row>
     <row r="341">
       <c r="A341" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B341" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C341" t="s" s="2">
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="D341" s="2"/>
     </row>
     <row r="342">
       <c r="A342" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B342" t="s" s="2">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="C342" t="s" s="2">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="D342" s="2"/>
     </row>
     <row r="343">
       <c r="A343" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B343" t="s" s="2">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="C343" t="s" s="2">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="D343" s="2"/>
     </row>
     <row r="344">
       <c r="A344" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B344" t="s" s="2">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="C344" t="s" s="2">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="D344" s="2"/>
     </row>
     <row r="345">
       <c r="A345" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B345" t="s" s="2">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="C345" t="s" s="2">
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="D345" s="2"/>
     </row>
     <row r="346">
       <c r="A346" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B346" t="s" s="2">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="C346" t="s" s="2">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="D346" s="2"/>
     </row>
     <row r="347">
       <c r="A347" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B347" t="s" s="2">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="C347" t="s" s="2">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="D347" s="2"/>
     </row>
     <row r="348">
       <c r="A348" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B348" t="s" s="2">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="C348" t="s" s="2">
-        <v>753</v>
+        <v>757</v>
       </c>
       <c r="D348" s="2"/>
     </row>
     <row r="349">
       <c r="A349" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B349" t="s" s="2">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="C349" t="s" s="2">
-        <v>755</v>
+        <v>759</v>
       </c>
       <c r="D349" s="2"/>
     </row>
     <row r="350">
       <c r="A350" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B350" t="s" s="2">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="C350" t="s" s="2">
-        <v>757</v>
+        <v>761</v>
       </c>
       <c r="D350" s="2"/>
     </row>
     <row r="351">
       <c r="A351" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B351" t="s" s="2">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="C351" t="s" s="2">
-        <v>759</v>
+        <v>763</v>
       </c>
       <c r="D351" s="2"/>
     </row>
     <row r="352">
       <c r="A352" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B352" t="s" s="2">
-        <v>760</v>
+        <v>764</v>
       </c>
       <c r="C352" t="s" s="2">
-        <v>761</v>
+        <v>765</v>
       </c>
       <c r="D352" s="2"/>
     </row>
     <row r="353">
       <c r="A353" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B353" t="s" s="2">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="C353" t="s" s="2">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="D353" s="2"/>
     </row>
     <row r="354">
       <c r="A354" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B354" t="s" s="2">
-        <v>764</v>
+        <v>768</v>
       </c>
       <c r="C354" t="s" s="2">
-        <v>765</v>
+        <v>769</v>
       </c>
       <c r="D354" s="2"/>
     </row>
     <row r="355">
       <c r="A355" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B355" t="s" s="2">
-        <v>766</v>
+        <v>770</v>
       </c>
       <c r="C355" t="s" s="2">
-        <v>767</v>
+        <v>771</v>
       </c>
       <c r="D355" s="2"/>
     </row>
     <row r="356">
       <c r="A356" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B356" t="s" s="2">
-        <v>768</v>
+        <v>772</v>
       </c>
       <c r="C356" t="s" s="2">
-        <v>769</v>
+        <v>773</v>
       </c>
       <c r="D356" s="2"/>
     </row>
     <row r="357">
       <c r="A357" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B357" t="s" s="2">
-        <v>770</v>
+        <v>774</v>
       </c>
       <c r="C357" t="s" s="2">
-        <v>771</v>
+        <v>775</v>
       </c>
       <c r="D357" s="2"/>
     </row>
     <row r="358">
       <c r="A358" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B358" t="s" s="2">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="C358" t="s" s="2">
-        <v>773</v>
+        <v>777</v>
       </c>
       <c r="D358" s="2"/>
     </row>
     <row r="359">
       <c r="A359" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B359" t="s" s="2">
-        <v>774</v>
+        <v>778</v>
       </c>
       <c r="C359" t="s" s="2">
-        <v>775</v>
+        <v>779</v>
       </c>
       <c r="D359" s="2"/>
     </row>
     <row r="360">
       <c r="A360" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B360" t="s" s="2">
-        <v>776</v>
+        <v>780</v>
       </c>
       <c r="C360" t="s" s="2">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="D360" s="2"/>
     </row>
     <row r="361">
       <c r="A361" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B361" t="s" s="2">
-        <v>778</v>
+        <v>782</v>
       </c>
       <c r="C361" t="s" s="2">
-        <v>779</v>
+        <v>783</v>
       </c>
       <c r="D361" s="2"/>
     </row>
     <row r="362">
       <c r="A362" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B362" t="s" s="2">
-        <v>780</v>
+        <v>784</v>
       </c>
       <c r="C362" t="s" s="2">
-        <v>781</v>
+        <v>785</v>
       </c>
       <c r="D362" s="2"/>
     </row>
     <row r="363">
       <c r="A363" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B363" t="s" s="2">
-        <v>782</v>
+        <v>786</v>
       </c>
       <c r="C363" t="s" s="2">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="D363" s="2"/>
     </row>
     <row r="364">
       <c r="A364" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B364" t="s" s="2">
-        <v>784</v>
+        <v>788</v>
       </c>
       <c r="C364" t="s" s="2">
-        <v>785</v>
+        <v>789</v>
       </c>
       <c r="D364" s="2"/>
     </row>
     <row r="365">
       <c r="A365" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B365" t="s" s="2">
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="C365" t="s" s="2">
-        <v>787</v>
+        <v>791</v>
       </c>
       <c r="D365" s="2"/>
     </row>
     <row r="366">
       <c r="A366" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B366" t="s" s="2">
-        <v>788</v>
+        <v>792</v>
       </c>
       <c r="C366" t="s" s="2">
-        <v>789</v>
+        <v>793</v>
       </c>
       <c r="D366" s="2"/>
     </row>
     <row r="367">
       <c r="A367" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B367" t="s" s="2">
-        <v>790</v>
+        <v>794</v>
       </c>
       <c r="C367" t="s" s="2">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="D367" s="2"/>
     </row>
     <row r="368">
       <c r="A368" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B368" t="s" s="2">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="C368" t="s" s="2">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="D368" s="2"/>
     </row>
     <row r="369">
       <c r="A369" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B369" t="s" s="2">
-        <v>794</v>
+        <v>798</v>
       </c>
       <c r="C369" t="s" s="2">
-        <v>795</v>
+        <v>799</v>
       </c>
       <c r="D369" s="2"/>
     </row>
     <row r="370">
       <c r="A370" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B370" t="s" s="2">
-        <v>796</v>
+        <v>800</v>
       </c>
       <c r="C370" t="s" s="2">
-        <v>797</v>
+        <v>801</v>
       </c>
       <c r="D370" s="2"/>
     </row>
     <row r="371">
       <c r="A371" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B371" t="s" s="2">
-        <v>798</v>
+        <v>802</v>
       </c>
       <c r="C371" t="s" s="2">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="D371" s="2"/>
     </row>
     <row r="372">
       <c r="A372" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B372" t="s" s="2">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="C372" t="s" s="2">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="D372" s="2"/>
     </row>
     <row r="373">
       <c r="A373" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B373" t="s" s="2">
-        <v>802</v>
+        <v>806</v>
       </c>
       <c r="C373" t="s" s="2">
-        <v>803</v>
+        <v>807</v>
       </c>
       <c r="D373" s="2"/>
     </row>
     <row r="374">
       <c r="A374" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B374" t="s" s="2">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="C374" t="s" s="2">
-        <v>805</v>
+        <v>809</v>
       </c>
       <c r="D374" s="2"/>
     </row>
     <row r="375">
       <c r="A375" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B375" t="s" s="2">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="C375" t="s" s="2">
-        <v>807</v>
+        <v>811</v>
       </c>
       <c r="D375" s="2"/>
     </row>
     <row r="376">
       <c r="A376" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B376" t="s" s="2">
-        <v>808</v>
+        <v>812</v>
       </c>
       <c r="C376" t="s" s="2">
-        <v>809</v>
+        <v>813</v>
       </c>
       <c r="D376" s="2"/>
     </row>
     <row r="377">
       <c r="A377" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B377" t="s" s="2">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="C377" t="s" s="2">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="D377" s="2"/>
     </row>
     <row r="378">
       <c r="A378" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B378" t="s" s="2">
-        <v>811</v>
+        <v>815</v>
       </c>
       <c r="C378" t="s" s="2">
-        <v>812</v>
+        <v>816</v>
       </c>
       <c r="D378" s="2"/>
     </row>
     <row r="379">
       <c r="A379" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B379" t="s" s="2">
-        <v>813</v>
+        <v>817</v>
       </c>
       <c r="C379" t="s" s="2">
-        <v>814</v>
+        <v>818</v>
       </c>
       <c r="D379" t="s" s="2">
-        <v>815</v>
+        <v>819</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B380" t="s" s="2">
-        <v>816</v>
+        <v>820</v>
       </c>
       <c r="C380" t="s" s="2">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D380" s="2"/>
     </row>
     <row r="381">
       <c r="A381" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B381" t="s" s="2">
-        <v>817</v>
+        <v>821</v>
       </c>
       <c r="C381" t="s" s="2">
-        <v>818</v>
+        <v>822</v>
       </c>
       <c r="D381" s="2"/>
     </row>
     <row r="382">
       <c r="A382" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B382" t="s" s="2">
-        <v>819</v>
+        <v>823</v>
       </c>
       <c r="C382" t="s" s="2">
-        <v>820</v>
+        <v>824</v>
       </c>
       <c r="D382" s="2"/>
     </row>
     <row r="383">
       <c r="A383" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B383" t="s" s="2">
-        <v>821</v>
+        <v>825</v>
       </c>
       <c r="C383" t="s" s="2">
-        <v>822</v>
+        <v>826</v>
       </c>
       <c r="D383" s="2"/>
     </row>
     <row r="384">
       <c r="A384" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B384" t="s" s="2">
-        <v>823</v>
+        <v>827</v>
       </c>
       <c r="C384" t="s" s="2">
-        <v>824</v>
+        <v>828</v>
       </c>
       <c r="D384" s="2"/>
     </row>
     <row r="385">
       <c r="A385" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B385" t="s" s="2">
-        <v>825</v>
+        <v>829</v>
       </c>
       <c r="C385" t="s" s="2">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="D385" s="2"/>
     </row>
     <row r="386">
       <c r="A386" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B386" t="s" s="2">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="C386" t="s" s="2">
-        <v>828</v>
+        <v>832</v>
       </c>
       <c r="D386" s="2"/>
     </row>
     <row r="387">
       <c r="A387" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B387" t="s" s="2">
-        <v>829</v>
+        <v>833</v>
       </c>
       <c r="C387" t="s" s="2">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="D387" s="2"/>
     </row>
     <row r="388">
       <c r="A388" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B388" t="s" s="2">
-        <v>831</v>
+        <v>835</v>
       </c>
       <c r="C388" t="s" s="2">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="D388" s="2"/>
     </row>
     <row r="389">
       <c r="A389" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B389" t="s" s="2">
-        <v>833</v>
+        <v>837</v>
       </c>
       <c r="C389" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="D389" s="2"/>
     </row>
     <row r="390">
       <c r="A390" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B390" t="s" s="2">
-        <v>834</v>
+        <v>838</v>
       </c>
       <c r="C390" t="s" s="2">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="D390" s="2"/>
     </row>
     <row r="391">
       <c r="A391" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B391" t="s" s="2">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="C391" t="s" s="2">
-        <v>837</v>
+        <v>841</v>
       </c>
       <c r="D391" s="2"/>
     </row>
     <row r="392">
       <c r="A392" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B392" t="s" s="2">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="C392" t="s" s="2">
-        <v>839</v>
+        <v>843</v>
       </c>
       <c r="D392" s="2"/>
     </row>
     <row r="393">
       <c r="A393" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B393" t="s" s="2">
-        <v>840</v>
+        <v>844</v>
       </c>
       <c r="C393" t="s" s="2">
-        <v>841</v>
+        <v>845</v>
       </c>
       <c r="D393" s="2"/>
     </row>
     <row r="394">
       <c r="A394" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B394" t="s" s="2">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="C394" t="s" s="2">
-        <v>843</v>
+        <v>847</v>
       </c>
       <c r="D394" s="2"/>
     </row>
     <row r="395">
       <c r="A395" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B395" t="s" s="2">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="C395" t="s" s="2">
-        <v>845</v>
+        <v>849</v>
       </c>
       <c r="D395" s="2"/>
     </row>
     <row r="396">
       <c r="A396" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B396" t="s" s="2">
-        <v>846</v>
+        <v>850</v>
       </c>
       <c r="C396" t="s" s="2">
-        <v>847</v>
+        <v>851</v>
       </c>
       <c r="D396" s="2"/>
     </row>
     <row r="397">
       <c r="A397" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B397" t="s" s="2">
-        <v>848</v>
+        <v>852</v>
       </c>
       <c r="C397" t="s" s="2">
-        <v>849</v>
+        <v>853</v>
       </c>
       <c r="D397" s="2"/>
     </row>
     <row r="398">
       <c r="A398" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B398" t="s" s="2">
-        <v>850</v>
+        <v>854</v>
       </c>
       <c r="C398" t="s" s="2">
-        <v>851</v>
+        <v>855</v>
       </c>
       <c r="D398" s="2"/>
     </row>
     <row r="399">
       <c r="A399" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B399" t="s" s="2">
-        <v>852</v>
+        <v>856</v>
       </c>
       <c r="C399" t="s" s="2">
-        <v>853</v>
+        <v>857</v>
       </c>
       <c r="D399" s="2"/>
     </row>
     <row r="400">
       <c r="A400" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B400" t="s" s="2">
-        <v>854</v>
+        <v>858</v>
       </c>
       <c r="C400" t="s" s="2">
-        <v>855</v>
+        <v>859</v>
       </c>
       <c r="D400" s="2"/>
     </row>
     <row r="401">
       <c r="A401" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B401" t="s" s="2">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="C401" t="s" s="2">
-        <v>857</v>
+        <v>861</v>
       </c>
       <c r="D401" s="2"/>
     </row>
     <row r="402">
       <c r="A402" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B402" t="s" s="2">
-        <v>858</v>
+        <v>862</v>
       </c>
       <c r="C402" t="s" s="2">
-        <v>859</v>
+        <v>863</v>
       </c>
       <c r="D402" s="2"/>
     </row>
     <row r="403">
       <c r="A403" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B403" t="s" s="2">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="C403" t="s" s="2">
-        <v>861</v>
+        <v>865</v>
       </c>
       <c r="D403" s="2"/>
     </row>
     <row r="404">
       <c r="A404" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B404" t="s" s="2">
-        <v>862</v>
+        <v>866</v>
       </c>
       <c r="C404" t="s" s="2">
-        <v>863</v>
+        <v>867</v>
       </c>
       <c r="D404" s="2"/>
     </row>
     <row r="405">
       <c r="A405" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B405" t="s" s="2">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="C405" t="s" s="2">
-        <v>865</v>
+        <v>869</v>
       </c>
       <c r="D405" s="2"/>
     </row>
     <row r="406">
       <c r="A406" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B406" t="s" s="2">
-        <v>866</v>
+        <v>870</v>
       </c>
       <c r="C406" t="s" s="2">
-        <v>867</v>
+        <v>871</v>
       </c>
       <c r="D406" s="2"/>
     </row>
     <row r="407">
       <c r="A407" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B407" t="s" s="2">
-        <v>868</v>
+        <v>872</v>
       </c>
       <c r="C407" t="s" s="2">
-        <v>869</v>
+        <v>873</v>
       </c>
       <c r="D407" s="2"/>
     </row>
     <row r="408">
       <c r="A408" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B408" t="s" s="2">
-        <v>870</v>
+        <v>874</v>
       </c>
       <c r="C408" t="s" s="2">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="D408" s="2"/>
     </row>
     <row r="409">
       <c r="A409" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B409" t="s" s="2">
-        <v>872</v>
+        <v>876</v>
       </c>
       <c r="C409" t="s" s="2">
-        <v>873</v>
+        <v>877</v>
       </c>
       <c r="D409" s="2"/>
     </row>
     <row r="410">
       <c r="A410" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B410" t="s" s="2">
-        <v>874</v>
+        <v>878</v>
       </c>
       <c r="C410" t="s" s="2">
-        <v>875</v>
+        <v>879</v>
       </c>
       <c r="D410" s="2"/>
     </row>
     <row r="411">
       <c r="A411" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B411" t="s" s="2">
-        <v>876</v>
+        <v>880</v>
       </c>
       <c r="C411" t="s" s="2">
-        <v>877</v>
+        <v>881</v>
       </c>
       <c r="D411" s="2"/>
     </row>
     <row r="412">
       <c r="A412" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B412" t="s" s="2">
-        <v>878</v>
+        <v>882</v>
       </c>
       <c r="C412" t="s" s="2">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="D412" s="2"/>
     </row>
     <row r="413">
       <c r="A413" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B413" t="s" s="2">
-        <v>880</v>
+        <v>884</v>
       </c>
       <c r="C413" t="s" s="2">
-        <v>881</v>
+        <v>885</v>
       </c>
       <c r="D413" s="2"/>
     </row>
     <row r="414">
       <c r="A414" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B414" t="s" s="2">
-        <v>882</v>
+        <v>886</v>
       </c>
       <c r="C414" t="s" s="2">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="D414" s="2"/>
     </row>
     <row r="415">
       <c r="A415" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B415" t="s" s="2">
-        <v>884</v>
+        <v>888</v>
       </c>
       <c r="C415" t="s" s="2">
-        <v>885</v>
+        <v>889</v>
       </c>
       <c r="D415" s="2"/>
     </row>
     <row r="416">
       <c r="A416" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B416" t="s" s="2">
-        <v>886</v>
+        <v>890</v>
       </c>
       <c r="C416" t="s" s="2">
-        <v>887</v>
+        <v>891</v>
       </c>
       <c r="D416" s="2"/>
     </row>
     <row r="417">
       <c r="A417" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B417" t="s" s="2">
-        <v>888</v>
+        <v>892</v>
       </c>
       <c r="C417" t="s" s="2">
-        <v>889</v>
+        <v>893</v>
       </c>
       <c r="D417" s="2"/>
     </row>
     <row r="418">
       <c r="A418" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B418" t="s" s="2">
-        <v>890</v>
+        <v>894</v>
       </c>
       <c r="C418" t="s" s="2">
-        <v>891</v>
+        <v>895</v>
       </c>
       <c r="D418" s="2"/>
     </row>
     <row r="419">
       <c r="A419" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B419" t="s" s="2">
-        <v>892</v>
+        <v>896</v>
       </c>
       <c r="C419" t="s" s="2">
-        <v>893</v>
+        <v>897</v>
       </c>
       <c r="D419" s="2"/>
     </row>
     <row r="420">
       <c r="A420" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B420" t="s" s="2">
-        <v>894</v>
+        <v>898</v>
       </c>
       <c r="C420" t="s" s="2">
-        <v>895</v>
+        <v>899</v>
       </c>
       <c r="D420" s="2"/>
     </row>
     <row r="421">
       <c r="A421" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B421" t="s" s="2">
-        <v>896</v>
+        <v>900</v>
       </c>
       <c r="C421" t="s" s="2">
-        <v>897</v>
+        <v>901</v>
       </c>
       <c r="D421" s="2"/>
     </row>
     <row r="422">
       <c r="A422" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B422" t="s" s="2">
-        <v>898</v>
+        <v>902</v>
       </c>
       <c r="C422" t="s" s="2">
-        <v>899</v>
+        <v>903</v>
       </c>
       <c r="D422" s="2"/>
     </row>
     <row r="423">
       <c r="A423" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B423" t="s" s="2">
-        <v>900</v>
+        <v>904</v>
       </c>
       <c r="C423" t="s" s="2">
-        <v>901</v>
+        <v>905</v>
       </c>
       <c r="D423" t="s" s="2">
-        <v>902</v>
+        <v>906</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B424" t="s" s="2">
-        <v>903</v>
+        <v>907</v>
       </c>
       <c r="C424" t="s" s="2">
-        <v>904</v>
+        <v>908</v>
       </c>
       <c r="D424" t="s" s="2">
-        <v>902</v>
+        <v>906</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B425" t="s" s="2">
-        <v>905</v>
+        <v>909</v>
       </c>
       <c r="C425" t="s" s="2">
+        <v>910</v>
+      </c>
+      <c r="D425" t="s" s="2">
         <v>906</v>
-      </c>
-      <c r="D425" t="s" s="2">
-        <v>902</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="s" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B426" t="s" s="2">
-        <v>907</v>
+        <v>911</v>
       </c>
       <c r="C426" t="s" s="2">
-        <v>908</v>
+        <v>912</v>
       </c>
       <c r="D426" s="2"/>
     </row>

--- a/ig/DM_FINESS_New/CodeSystem-tre-r397-categorie-entite-geographique-exercice.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-tre-r397-categorie-entite-geographique-exercice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1364" uniqueCount="913">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1364" uniqueCount="914">
   <si>
     <t>Property</t>
   </si>
@@ -47,6 +47,9 @@
   </si>
   <si>
     <t>Title</t>
+  </si>
+  <si>
+    <t>Tre R397 Categorie Entite Geographique Exercice</t>
   </si>
   <si>
     <t>Status</t>
@@ -2938,117 +2941,117 @@
         <v>10</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -3063,156 +3066,156 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="C6" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="D6" t="s" s="2">
         <v>54</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>55</v>
-      </c>
-      <c r="C6" t="s" s="2">
-        <v>56</v>
-      </c>
-      <c r="D6" t="s" s="2">
-        <v>53</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C8" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C9" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -3227,5123 +3230,5123 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C8" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C9" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B10" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="C10" t="s" s="2">
         <v>93</v>
-      </c>
-      <c r="C10" t="s" s="2">
-        <v>92</v>
       </c>
       <c r="D10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D21" s="2"/>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D22" s="2"/>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D23" s="2"/>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D24" s="2"/>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D25" s="2"/>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D26" s="2"/>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D27" s="2"/>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D28" s="2"/>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D29" s="2"/>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D30" s="2"/>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D31" s="2"/>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D32" s="2"/>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D33" s="2"/>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D34" s="2"/>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D35" s="2"/>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D36" s="2"/>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D37" s="2"/>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D38" s="2"/>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D39" s="2"/>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D40" s="2"/>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D41" s="2"/>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D42" s="2"/>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D43" s="2"/>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D44" s="2"/>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D45" s="2"/>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D46" s="2"/>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D47" s="2"/>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D48" s="2"/>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D49" s="2"/>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D50" s="2"/>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D51" s="2"/>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D52" s="2"/>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D53" s="2"/>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D54" s="2"/>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D55" s="2"/>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D56" s="2"/>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D57" s="2"/>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D58" s="2"/>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D59" s="2"/>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D60" s="2"/>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D61" s="2"/>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D62" s="2"/>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D63" s="2"/>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D64" s="2"/>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D65" s="2"/>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D66" s="2"/>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D67" s="2"/>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D68" s="2"/>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D69" s="2"/>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D70" s="2"/>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D71" s="2"/>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D72" s="2"/>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D73" s="2"/>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D74" s="2"/>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D75" s="2"/>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D76" s="2"/>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D77" s="2"/>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D78" s="2"/>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D79" s="2"/>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D80" s="2"/>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D81" s="2"/>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C82" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D82" s="2"/>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C83" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D83" s="2"/>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D84" s="2"/>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C85" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D85" s="2"/>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D86" s="2"/>
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C87" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D87" s="2"/>
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D88" s="2"/>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C89" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D89" s="2"/>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D90" s="2"/>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D91" s="2"/>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C92" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D92" s="2"/>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D93" s="2"/>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C94" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D94" s="2"/>
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D95" s="2"/>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D96" s="2"/>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D97" s="2"/>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D98" s="2"/>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D99" s="2"/>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D100" s="2"/>
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D101" s="2"/>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C102" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D102" s="2"/>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D103" s="2"/>
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D104" s="2"/>
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D105" s="2"/>
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D106" s="2"/>
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D107" s="2"/>
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D108" s="2"/>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D109" s="2"/>
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C110" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D110" s="2"/>
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D111" s="2"/>
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D112" s="2"/>
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C113" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D113" s="2"/>
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C114" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D114" s="2"/>
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C115" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D115" s="2"/>
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C116" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D116" s="2"/>
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C117" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D117" s="2"/>
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C118" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D118" s="2"/>
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D119" s="2"/>
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C120" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D120" s="2"/>
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C121" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D121" s="2"/>
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C122" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D122" s="2"/>
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C123" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D123" s="2"/>
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C124" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D124" s="2"/>
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C125" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D125" s="2"/>
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C126" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D126" s="2"/>
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C127" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D127" s="2"/>
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C128" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D128" s="2"/>
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C129" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D129" s="2"/>
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C130" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D130" s="2"/>
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C131" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D131" s="2"/>
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C132" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D132" s="2"/>
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C133" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D133" s="2"/>
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C134" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D134" s="2"/>
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C135" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D135" s="2"/>
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C136" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D136" s="2"/>
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C137" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D137" s="2"/>
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C138" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D138" s="2"/>
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C139" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D139" s="2"/>
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C140" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D140" s="2"/>
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C141" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D141" s="2"/>
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C142" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D142" s="2"/>
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C143" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D143" s="2"/>
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C144" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D144" s="2"/>
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C145" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D145" s="2"/>
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C146" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D146" s="2"/>
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C147" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D147" s="2"/>
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C148" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D148" s="2"/>
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C149" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D149" s="2"/>
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C150" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D150" s="2"/>
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C151" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D151" s="2"/>
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C152" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D152" s="2"/>
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C153" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D153" s="2"/>
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C154" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D154" s="2"/>
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C155" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D155" s="2"/>
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C156" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D156" s="2"/>
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C157" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D157" s="2"/>
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C158" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D158" s="2"/>
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C159" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D159" s="2"/>
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C160" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D160" s="2"/>
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C161" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D161" s="2"/>
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C162" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D162" s="2"/>
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C163" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D163" s="2"/>
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C164" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D164" s="2"/>
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C165" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D165" s="2"/>
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C166" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D166" s="2"/>
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C167" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D167" s="2"/>
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C168" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D168" s="2"/>
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C169" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D169" s="2"/>
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C170" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D170" s="2"/>
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C171" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D171" s="2"/>
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C172" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D172" s="2"/>
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C173" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D173" s="2"/>
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C174" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D174" s="2"/>
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C175" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D175" s="2"/>
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C176" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D176" s="2"/>
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C177" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D177" s="2"/>
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C178" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D178" s="2"/>
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C179" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D179" s="2"/>
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C180" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D180" s="2"/>
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C181" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D181" s="2"/>
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C182" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D182" s="2"/>
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C183" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D183" s="2"/>
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C184" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D184" s="2"/>
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C185" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D185" s="2"/>
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C186" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D186" s="2"/>
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C187" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D187" s="2"/>
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C188" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D188" s="2"/>
     </row>
     <row r="189">
       <c r="A189" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C189" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D189" s="2"/>
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C190" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D190" s="2"/>
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C191" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D191" s="2"/>
     </row>
     <row r="192">
       <c r="A192" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C192" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D192" s="2"/>
     </row>
     <row r="193">
       <c r="A193" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C193" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="D193" s="2"/>
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C194" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D194" s="2"/>
     </row>
     <row r="195">
       <c r="A195" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C195" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D195" s="2"/>
     </row>
     <row r="196">
       <c r="A196" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C196" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D196" s="2"/>
     </row>
     <row r="197">
       <c r="A197" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C197" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D197" s="2"/>
     </row>
     <row r="198">
       <c r="A198" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C198" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D198" s="2"/>
     </row>
     <row r="199">
       <c r="A199" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C199" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D199" s="2"/>
     </row>
     <row r="200">
       <c r="A200" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C200" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D200" s="2"/>
     </row>
     <row r="201">
       <c r="A201" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C201" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D201" s="2"/>
     </row>
     <row r="202">
       <c r="A202" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C202" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D202" s="2"/>
     </row>
     <row r="203">
       <c r="A203" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C203" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D203" s="2"/>
     </row>
     <row r="204">
       <c r="A204" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C204" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D204" s="2"/>
     </row>
     <row r="205">
       <c r="A205" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C205" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D205" s="2"/>
     </row>
     <row r="206">
       <c r="A206" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C206" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D206" s="2"/>
     </row>
     <row r="207">
       <c r="A207" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C207" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D207" s="2"/>
     </row>
     <row r="208">
       <c r="A208" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C208" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="D208" s="2"/>
     </row>
     <row r="209">
       <c r="A209" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C209" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D209" s="2"/>
     </row>
     <row r="210">
       <c r="A210" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C210" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D210" s="2"/>
     </row>
     <row r="211">
       <c r="A211" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C211" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="D211" s="2"/>
     </row>
     <row r="212">
       <c r="A212" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C212" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D212" s="2"/>
     </row>
     <row r="213">
       <c r="A213" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C213" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="D213" s="2"/>
     </row>
     <row r="214">
       <c r="A214" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C214" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D214" s="2"/>
     </row>
     <row r="215">
       <c r="A215" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C215" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D215" s="2"/>
     </row>
     <row r="216">
       <c r="A216" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C216" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D216" s="2"/>
     </row>
     <row r="217">
       <c r="A217" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C217" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D217" s="2"/>
     </row>
     <row r="218">
       <c r="A218" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C218" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D218" s="2"/>
     </row>
     <row r="219">
       <c r="A219" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C219" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="D219" s="2"/>
     </row>
     <row r="220">
       <c r="A220" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C220" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D220" s="2"/>
     </row>
     <row r="221">
       <c r="A221" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C221" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D221" s="2"/>
     </row>
     <row r="222">
       <c r="A222" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C222" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D222" s="2"/>
     </row>
     <row r="223">
       <c r="A223" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C223" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D223" s="2"/>
     </row>
     <row r="224">
       <c r="A224" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C224" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D224" s="2"/>
     </row>
     <row r="225">
       <c r="A225" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C225" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D225" s="2"/>
     </row>
     <row r="226">
       <c r="A226" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C226" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D226" s="2"/>
     </row>
     <row r="227">
       <c r="A227" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C227" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="D227" s="2"/>
     </row>
     <row r="228">
       <c r="A228" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C228" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D228" s="2"/>
     </row>
     <row r="229">
       <c r="A229" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C229" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D229" s="2"/>
     </row>
     <row r="230">
       <c r="A230" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C230" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D230" s="2"/>
     </row>
     <row r="231">
       <c r="A231" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C231" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D231" s="2"/>
     </row>
     <row r="232">
       <c r="A232" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C232" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D232" s="2"/>
     </row>
     <row r="233">
       <c r="A233" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C233" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D233" s="2"/>
     </row>
     <row r="234">
       <c r="A234" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C234" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="D234" s="2"/>
     </row>
     <row r="235">
       <c r="A235" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C235" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="D235" s="2"/>
     </row>
     <row r="236">
       <c r="A236" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C236" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D236" s="2"/>
     </row>
     <row r="237">
       <c r="A237" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C237" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="D237" s="2"/>
     </row>
     <row r="238">
       <c r="A238" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C238" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D238" s="2"/>
     </row>
     <row r="239">
       <c r="A239" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C239" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="D239" s="2"/>
     </row>
     <row r="240">
       <c r="A240" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C240" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D240" s="2"/>
     </row>
     <row r="241">
       <c r="A241" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C241" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D241" s="2"/>
     </row>
     <row r="242">
       <c r="A242" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C242" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="D242" s="2"/>
     </row>
     <row r="243">
       <c r="A243" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C243" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="D243" s="2"/>
     </row>
     <row r="244">
       <c r="A244" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C244" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D244" s="2"/>
     </row>
     <row r="245">
       <c r="A245" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C245" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="D245" s="2"/>
     </row>
     <row r="246">
       <c r="A246" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C246" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="D246" s="2"/>
     </row>
     <row r="247">
       <c r="A247" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B247" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C247" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D247" s="2"/>
     </row>
     <row r="248">
       <c r="A248" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B248" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C248" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="D248" s="2"/>
     </row>
     <row r="249">
       <c r="A249" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B249" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C249" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="D249" s="2"/>
     </row>
     <row r="250">
       <c r="A250" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B250" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C250" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D250" s="2"/>
     </row>
     <row r="251">
       <c r="A251" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B251" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C251" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="D251" s="2"/>
     </row>
     <row r="252">
       <c r="A252" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B252" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C252" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D252" s="2"/>
     </row>
     <row r="253">
       <c r="A253" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B253" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C253" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="D253" s="2"/>
     </row>
     <row r="254">
       <c r="A254" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B254" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C254" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="D254" s="2"/>
     </row>
     <row r="255">
       <c r="A255" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B255" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C255" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="D255" s="2"/>
     </row>
     <row r="256">
       <c r="A256" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B256" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C256" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="D256" s="2"/>
     </row>
     <row r="257">
       <c r="A257" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B257" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C257" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="D257" s="2"/>
     </row>
     <row r="258">
       <c r="A258" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B258" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C258" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="D258" s="2"/>
     </row>
     <row r="259">
       <c r="A259" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B259" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C259" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="D259" s="2"/>
     </row>
     <row r="260">
       <c r="A260" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B260" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C260" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="D260" s="2"/>
     </row>
     <row r="261">
       <c r="A261" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B261" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C261" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="D261" s="2"/>
     </row>
     <row r="262">
       <c r="A262" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B262" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C262" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D262" s="2"/>
     </row>
     <row r="263">
       <c r="A263" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B263" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C263" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="D263" s="2"/>
     </row>
     <row r="264">
       <c r="A264" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B264" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C264" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="D264" s="2"/>
     </row>
     <row r="265">
       <c r="A265" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B265" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C265" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="D265" s="2"/>
     </row>
     <row r="266">
       <c r="A266" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B266" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C266" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="D266" s="2"/>
     </row>
     <row r="267">
       <c r="A267" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B267" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C267" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D267" s="2"/>
     </row>
     <row r="268">
       <c r="A268" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B268" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C268" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="D268" s="2"/>
     </row>
     <row r="269">
       <c r="A269" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B269" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C269" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="D269" s="2"/>
     </row>
     <row r="270">
       <c r="A270" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B270" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C270" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="D270" s="2"/>
     </row>
     <row r="271">
       <c r="A271" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B271" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C271" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="D271" s="2"/>
     </row>
     <row r="272">
       <c r="A272" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B272" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C272" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="D272" s="2"/>
     </row>
     <row r="273">
       <c r="A273" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B273" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C273" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="D273" s="2"/>
     </row>
     <row r="274">
       <c r="A274" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B274" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C274" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="D274" s="2"/>
     </row>
     <row r="275">
       <c r="A275" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B275" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C275" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D275" s="2"/>
     </row>
     <row r="276">
       <c r="A276" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B276" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C276" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="D276" s="2"/>
     </row>
     <row r="277">
       <c r="A277" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B277" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C277" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="D277" s="2"/>
     </row>
     <row r="278">
       <c r="A278" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B278" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C278" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="D278" s="2"/>
     </row>
     <row r="279">
       <c r="A279" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B279" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C279" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="D279" s="2"/>
     </row>
     <row r="280">
       <c r="A280" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B280" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C280" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="D280" s="2"/>
     </row>
     <row r="281">
       <c r="A281" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B281" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C281" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="D281" s="2"/>
     </row>
     <row r="282">
       <c r="A282" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B282" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C282" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D282" s="2"/>
     </row>
     <row r="283">
       <c r="A283" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B283" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C283" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="D283" s="2"/>
     </row>
     <row r="284">
       <c r="A284" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B284" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C284" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="D284" s="2"/>
     </row>
     <row r="285">
       <c r="A285" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B285" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C285" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="D285" s="2"/>
     </row>
     <row r="286">
       <c r="A286" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B286" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C286" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="D286" s="2"/>
     </row>
     <row r="287">
       <c r="A287" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B287" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C287" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="D287" s="2"/>
     </row>
     <row r="288">
       <c r="A288" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B288" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C288" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="D288" s="2"/>
     </row>
     <row r="289">
       <c r="A289" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B289" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C289" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="D289" s="2"/>
     </row>
     <row r="290">
       <c r="A290" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B290" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C290" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="D290" s="2"/>
     </row>
     <row r="291">
       <c r="A291" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B291" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C291" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="D291" s="2"/>
     </row>
     <row r="292">
       <c r="A292" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B292" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C292" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="D292" s="2"/>
     </row>
     <row r="293">
       <c r="A293" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B293" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C293" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="D293" s="2"/>
     </row>
     <row r="294">
       <c r="A294" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B294" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C294" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="D294" s="2"/>
     </row>
     <row r="295">
       <c r="A295" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B295" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C295" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="D295" s="2"/>
     </row>
     <row r="296">
       <c r="A296" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B296" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C296" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="D296" s="2"/>
     </row>
     <row r="297">
       <c r="A297" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B297" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C297" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="D297" s="2"/>
     </row>
     <row r="298">
       <c r="A298" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B298" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C298" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="D298" s="2"/>
     </row>
     <row r="299">
       <c r="A299" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B299" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C299" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="D299" s="2"/>
     </row>
     <row r="300">
       <c r="A300" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B300" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C300" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="D300" s="2"/>
     </row>
     <row r="301">
       <c r="A301" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B301" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C301" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D301" s="2"/>
     </row>
     <row r="302">
       <c r="A302" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B302" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C302" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="D302" s="2"/>
     </row>
     <row r="303">
       <c r="A303" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B303" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="C303" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="D303" s="2"/>
     </row>
     <row r="304">
       <c r="A304" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B304" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C304" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="D304" s="2"/>
     </row>
     <row r="305">
       <c r="A305" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B305" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C305" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="D305" s="2"/>
     </row>
     <row r="306">
       <c r="A306" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B306" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C306" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="D306" s="2"/>
     </row>
     <row r="307">
       <c r="A307" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B307" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C307" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="D307" s="2"/>
     </row>
     <row r="308">
       <c r="A308" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B308" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C308" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="D308" s="2"/>
     </row>
     <row r="309">
       <c r="A309" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B309" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C309" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="D309" s="2"/>
     </row>
     <row r="310">
       <c r="A310" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B310" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C310" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="D310" s="2"/>
     </row>
     <row r="311">
       <c r="A311" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B311" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C311" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="D311" s="2"/>
     </row>
     <row r="312">
       <c r="A312" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B312" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C312" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D312" s="2"/>
     </row>
     <row r="313">
       <c r="A313" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B313" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C313" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="D313" s="2"/>
     </row>
     <row r="314">
       <c r="A314" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B314" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C314" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="D314" s="2"/>
     </row>
     <row r="315">
       <c r="A315" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B315" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C315" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="D315" s="2"/>
     </row>
     <row r="316">
       <c r="A316" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B316" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C316" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="D316" s="2"/>
     </row>
     <row r="317">
       <c r="A317" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B317" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C317" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="D317" s="2"/>
     </row>
     <row r="318">
       <c r="A318" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B318" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C318" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="D318" s="2"/>
     </row>
     <row r="319">
       <c r="A319" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B319" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="C319" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="D319" s="2"/>
     </row>
     <row r="320">
       <c r="A320" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B320" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C320" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="D320" s="2"/>
     </row>
     <row r="321">
       <c r="A321" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B321" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="C321" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="D321" s="2"/>
     </row>
     <row r="322">
       <c r="A322" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B322" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="C322" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="D322" s="2"/>
     </row>
     <row r="323">
       <c r="A323" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B323" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="C323" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="D323" s="2"/>
     </row>
     <row r="324">
       <c r="A324" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B324" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C324" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="D324" s="2"/>
     </row>
     <row r="325">
       <c r="A325" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B325" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C325" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="D325" s="2"/>
     </row>
     <row r="326">
       <c r="A326" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B326" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="C326" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="D326" s="2"/>
     </row>
     <row r="327">
       <c r="A327" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B327" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="C327" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="D327" s="2"/>
     </row>
     <row r="328">
       <c r="A328" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B328" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="C328" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="D328" s="2"/>
     </row>
     <row r="329">
       <c r="A329" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B329" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C329" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="D329" s="2"/>
     </row>
     <row r="330">
       <c r="A330" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B330" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C330" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="D330" s="2"/>
     </row>
     <row r="331">
       <c r="A331" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B331" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C331" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="D331" s="2"/>
     </row>
     <row r="332">
       <c r="A332" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B332" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="C332" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="D332" s="2"/>
     </row>
     <row r="333">
       <c r="A333" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B333" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="C333" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="D333" s="2"/>
     </row>
     <row r="334">
       <c r="A334" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B334" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C334" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D334" s="2"/>
     </row>
     <row r="335">
       <c r="A335" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B335" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C335" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="D335" s="2"/>
     </row>
     <row r="336">
       <c r="A336" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B336" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C336" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="D336" s="2"/>
     </row>
     <row r="337">
       <c r="A337" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B337" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="C337" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="D337" s="2"/>
     </row>
     <row r="338">
       <c r="A338" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B338" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="C338" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="D338" s="2"/>
     </row>
     <row r="339">
       <c r="A339" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B339" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="C339" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="D339" s="2"/>
     </row>
     <row r="340">
       <c r="A340" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B340" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="C340" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="D340" s="2"/>
     </row>
     <row r="341">
       <c r="A341" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B341" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C341" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="D341" s="2"/>
     </row>
     <row r="342">
       <c r="A342" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B342" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="C342" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="D342" s="2"/>
     </row>
     <row r="343">
       <c r="A343" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B343" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="C343" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="D343" s="2"/>
     </row>
     <row r="344">
       <c r="A344" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B344" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="C344" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="D344" s="2"/>
     </row>
     <row r="345">
       <c r="A345" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B345" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="C345" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="D345" s="2"/>
     </row>
     <row r="346">
       <c r="A346" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B346" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C346" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="D346" s="2"/>
     </row>
     <row r="347">
       <c r="A347" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B347" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="C347" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="D347" s="2"/>
     </row>
     <row r="348">
       <c r="A348" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B348" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="C348" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="D348" s="2"/>
     </row>
     <row r="349">
       <c r="A349" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B349" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="C349" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="D349" s="2"/>
     </row>
     <row r="350">
       <c r="A350" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B350" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="C350" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="D350" s="2"/>
     </row>
     <row r="351">
       <c r="A351" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B351" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="C351" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="D351" s="2"/>
     </row>
     <row r="352">
       <c r="A352" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B352" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="C352" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="D352" s="2"/>
     </row>
     <row r="353">
       <c r="A353" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B353" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C353" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D353" s="2"/>
     </row>
     <row r="354">
       <c r="A354" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B354" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="C354" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="D354" s="2"/>
     </row>
     <row r="355">
       <c r="A355" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B355" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="C355" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="D355" s="2"/>
     </row>
     <row r="356">
       <c r="A356" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B356" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="C356" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="D356" s="2"/>
     </row>
     <row r="357">
       <c r="A357" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B357" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="C357" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="D357" s="2"/>
     </row>
     <row r="358">
       <c r="A358" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B358" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="C358" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="D358" s="2"/>
     </row>
     <row r="359">
       <c r="A359" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B359" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="C359" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="D359" s="2"/>
     </row>
     <row r="360">
       <c r="A360" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B360" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="C360" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="D360" s="2"/>
     </row>
     <row r="361">
       <c r="A361" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B361" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="C361" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="D361" s="2"/>
     </row>
     <row r="362">
       <c r="A362" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B362" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="C362" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="D362" s="2"/>
     </row>
     <row r="363">
       <c r="A363" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B363" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="C363" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="D363" s="2"/>
     </row>
     <row r="364">
       <c r="A364" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B364" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="C364" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="D364" s="2"/>
     </row>
     <row r="365">
       <c r="A365" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B365" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C365" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="D365" s="2"/>
     </row>
     <row r="366">
       <c r="A366" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B366" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="C366" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="D366" s="2"/>
     </row>
     <row r="367">
       <c r="A367" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B367" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="C367" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="D367" s="2"/>
     </row>
     <row r="368">
       <c r="A368" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B368" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="C368" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="D368" s="2"/>
     </row>
     <row r="369">
       <c r="A369" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B369" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="C369" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="D369" s="2"/>
     </row>
     <row r="370">
       <c r="A370" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B370" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="C370" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="D370" s="2"/>
     </row>
     <row r="371">
       <c r="A371" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B371" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="C371" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="D371" s="2"/>
     </row>
     <row r="372">
       <c r="A372" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B372" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="C372" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="D372" s="2"/>
     </row>
     <row r="373">
       <c r="A373" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B373" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C373" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="D373" s="2"/>
     </row>
     <row r="374">
       <c r="A374" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B374" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="C374" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="D374" s="2"/>
     </row>
     <row r="375">
       <c r="A375" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B375" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="C375" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="D375" s="2"/>
     </row>
     <row r="376">
       <c r="A376" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B376" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="C376" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="D376" s="2"/>
     </row>
     <row r="377">
       <c r="A377" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B377" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="C377" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D377" s="2"/>
     </row>
     <row r="378">
       <c r="A378" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B378" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="C378" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="D378" s="2"/>
     </row>
     <row r="379">
       <c r="A379" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B379" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="C379" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="D379" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B380" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="C380" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D380" s="2"/>
     </row>
     <row r="381">
       <c r="A381" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B381" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C381" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="D381" s="2"/>
     </row>
     <row r="382">
       <c r="A382" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B382" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="C382" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="D382" s="2"/>
     </row>
     <row r="383">
       <c r="A383" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B383" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="C383" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="D383" s="2"/>
     </row>
     <row r="384">
       <c r="A384" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B384" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="C384" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="D384" s="2"/>
     </row>
     <row r="385">
       <c r="A385" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B385" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="C385" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="D385" s="2"/>
     </row>
     <row r="386">
       <c r="A386" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B386" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="C386" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="D386" s="2"/>
     </row>
     <row r="387">
       <c r="A387" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B387" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="C387" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="D387" s="2"/>
     </row>
     <row r="388">
       <c r="A388" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B388" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="C388" t="s" s="2">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="D388" s="2"/>
     </row>
     <row r="389">
       <c r="A389" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B389" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="C389" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D389" s="2"/>
     </row>
     <row r="390">
       <c r="A390" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B390" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="C390" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="D390" s="2"/>
     </row>
     <row r="391">
       <c r="A391" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B391" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="C391" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="D391" s="2"/>
     </row>
     <row r="392">
       <c r="A392" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B392" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="C392" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="D392" s="2"/>
     </row>
     <row r="393">
       <c r="A393" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B393" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="C393" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="D393" s="2"/>
     </row>
     <row r="394">
       <c r="A394" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B394" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="C394" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="D394" s="2"/>
     </row>
     <row r="395">
       <c r="A395" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B395" t="s" s="2">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="C395" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="D395" s="2"/>
     </row>
     <row r="396">
       <c r="A396" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B396" t="s" s="2">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="C396" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="D396" s="2"/>
     </row>
     <row r="397">
       <c r="A397" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B397" t="s" s="2">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="C397" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="D397" s="2"/>
     </row>
     <row r="398">
       <c r="A398" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B398" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="C398" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="D398" s="2"/>
     </row>
     <row r="399">
       <c r="A399" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B399" t="s" s="2">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="C399" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="D399" s="2"/>
     </row>
     <row r="400">
       <c r="A400" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B400" t="s" s="2">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="C400" t="s" s="2">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="D400" s="2"/>
     </row>
     <row r="401">
       <c r="A401" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B401" t="s" s="2">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="C401" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="D401" s="2"/>
     </row>
     <row r="402">
       <c r="A402" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B402" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="C402" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="D402" s="2"/>
     </row>
     <row r="403">
       <c r="A403" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B403" t="s" s="2">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="C403" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="D403" s="2"/>
     </row>
     <row r="404">
       <c r="A404" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B404" t="s" s="2">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C404" t="s" s="2">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="D404" s="2"/>
     </row>
     <row r="405">
       <c r="A405" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B405" t="s" s="2">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="C405" t="s" s="2">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="D405" s="2"/>
     </row>
     <row r="406">
       <c r="A406" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B406" t="s" s="2">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="C406" t="s" s="2">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="D406" s="2"/>
     </row>
     <row r="407">
       <c r="A407" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B407" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="C407" t="s" s="2">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="D407" s="2"/>
     </row>
     <row r="408">
       <c r="A408" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B408" t="s" s="2">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C408" t="s" s="2">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="D408" s="2"/>
     </row>
     <row r="409">
       <c r="A409" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B409" t="s" s="2">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="C409" t="s" s="2">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="D409" s="2"/>
     </row>
     <row r="410">
       <c r="A410" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B410" t="s" s="2">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="C410" t="s" s="2">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="D410" s="2"/>
     </row>
     <row r="411">
       <c r="A411" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B411" t="s" s="2">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="C411" t="s" s="2">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="D411" s="2"/>
     </row>
     <row r="412">
       <c r="A412" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B412" t="s" s="2">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="C412" t="s" s="2">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="D412" s="2"/>
     </row>
     <row r="413">
       <c r="A413" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B413" t="s" s="2">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="C413" t="s" s="2">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="D413" s="2"/>
     </row>
     <row r="414">
       <c r="A414" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B414" t="s" s="2">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="C414" t="s" s="2">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="D414" s="2"/>
     </row>
     <row r="415">
       <c r="A415" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B415" t="s" s="2">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="C415" t="s" s="2">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="D415" s="2"/>
     </row>
     <row r="416">
       <c r="A416" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B416" t="s" s="2">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="C416" t="s" s="2">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="D416" s="2"/>
     </row>
     <row r="417">
       <c r="A417" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B417" t="s" s="2">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="C417" t="s" s="2">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="D417" s="2"/>
     </row>
     <row r="418">
       <c r="A418" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B418" t="s" s="2">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="C418" t="s" s="2">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="D418" s="2"/>
     </row>
     <row r="419">
       <c r="A419" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B419" t="s" s="2">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="C419" t="s" s="2">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="D419" s="2"/>
     </row>
     <row r="420">
       <c r="A420" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B420" t="s" s="2">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="C420" t="s" s="2">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="D420" s="2"/>
     </row>
     <row r="421">
       <c r="A421" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B421" t="s" s="2">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="C421" t="s" s="2">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="D421" s="2"/>
     </row>
     <row r="422">
       <c r="A422" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B422" t="s" s="2">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="C422" t="s" s="2">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="D422" s="2"/>
     </row>
     <row r="423">
       <c r="A423" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B423" t="s" s="2">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="C423" t="s" s="2">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="D423" t="s" s="2">
-        <v>906</v>
+        <v>907</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B424" t="s" s="2">
+        <v>908</v>
+      </c>
+      <c r="C424" t="s" s="2">
+        <v>909</v>
+      </c>
+      <c r="D424" t="s" s="2">
         <v>907</v>
-      </c>
-      <c r="C424" t="s" s="2">
-        <v>908</v>
-      </c>
-      <c r="D424" t="s" s="2">
-        <v>906</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B425" t="s" s="2">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="C425" t="s" s="2">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="D425" t="s" s="2">
-        <v>906</v>
+        <v>907</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B426" t="s" s="2">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="C426" t="s" s="2">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="D426" s="2"/>
     </row>

--- a/ig/DM_FINESS_New/CodeSystem-tre-r397-categorie-entite-geographique-exercice.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-tre-r397-categorie-entite-geographique-exercice.xlsx
@@ -292,13 +292,13 @@
     <t>Etab.de Formation des Personnels Sanitaires et Sociaux</t>
   </si>
   <si>
+    <t>0110</t>
+  </si>
+  <si>
+    <t>Etablissements d'Administration</t>
+  </si>
+  <si>
     <t>110</t>
-  </si>
-  <si>
-    <t>Etablissements d'Administration</t>
-  </si>
-  <si>
-    <t>0110</t>
   </si>
   <si>
     <t>1100</t>

--- a/ig/DM_FINESS_New/CodeSystem-tre-r397-categorie-entite-geographique-exercice.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-tre-r397-categorie-entite-geographique-exercice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1364" uniqueCount="914">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1363" uniqueCount="913">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250922120000</t>
+    <t>20251222120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-25T12:00:00+01:00</t>
+    <t>2025-12-22T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -92,9 +92,6 @@
   </si>
   <si>
     <t>Value Set (all codes)</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r397-categorie-entite-geographique-exercice?vs</t>
   </si>
   <si>
     <t>Hierarchy</t>
@@ -3008,50 +3005,48 @@
       <c r="A15" t="s" s="2">
         <v>25</v>
       </c>
-      <c r="B15" t="s" s="2">
-        <v>26</v>
-      </c>
+      <c r="B15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="B16" t="s" s="2">
         <v>27</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>28</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B19" t="s" s="2">
         <v>31</v>
-      </c>
-      <c r="B19" t="s" s="2">
-        <v>32</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B21" t="s" s="2">
         <v>34</v>
-      </c>
-      <c r="B21" t="s" s="2">
-        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -3066,156 +3061,156 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="B1" t="s" s="1">
         <v>36</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>37</v>
       </c>
       <c r="C1" t="s" s="1">
         <v>20</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B2" t="s" s="2">
         <v>39</v>
       </c>
-      <c r="B2" t="s" s="2">
+      <c r="C2" t="s" s="2">
         <v>40</v>
       </c>
-      <c r="C2" t="s" s="2">
+      <c r="D2" t="s" s="2">
         <v>41</v>
-      </c>
-      <c r="D2" t="s" s="2">
-        <v>42</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B3" t="s" s="2">
         <v>43</v>
       </c>
-      <c r="B3" t="s" s="2">
+      <c r="C3" t="s" s="2">
         <v>44</v>
       </c>
-      <c r="C3" t="s" s="2">
+      <c r="D3" t="s" s="2">
         <v>45</v>
-      </c>
-      <c r="D3" t="s" s="2">
-        <v>46</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B4" t="s" s="2">
         <v>47</v>
       </c>
-      <c r="B4" t="s" s="2">
+      <c r="C4" t="s" s="2">
         <v>48</v>
       </c>
-      <c r="C4" t="s" s="2">
+      <c r="D4" t="s" s="2">
         <v>49</v>
-      </c>
-      <c r="D4" t="s" s="2">
-        <v>50</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B5" t="s" s="2">
         <v>51</v>
       </c>
-      <c r="B5" t="s" s="2">
+      <c r="C5" t="s" s="2">
         <v>52</v>
       </c>
-      <c r="C5" t="s" s="2">
+      <c r="D5" t="s" s="2">
         <v>53</v>
-      </c>
-      <c r="D5" t="s" s="2">
-        <v>54</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="B6" t="s" s="2">
         <v>55</v>
       </c>
-      <c r="B6" t="s" s="2">
+      <c r="C6" t="s" s="2">
         <v>56</v>
       </c>
-      <c r="C6" t="s" s="2">
-        <v>57</v>
-      </c>
       <c r="D6" t="s" s="2">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B7" t="s" s="2">
         <v>58</v>
       </c>
-      <c r="B7" t="s" s="2">
+      <c r="C7" t="s" s="2">
         <v>59</v>
       </c>
-      <c r="C7" t="s" s="2">
-        <v>60</v>
-      </c>
       <c r="D7" t="s" s="2">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="B8" t="s" s="2">
         <v>61</v>
       </c>
-      <c r="B8" t="s" s="2">
+      <c r="C8" t="s" s="2">
         <v>62</v>
       </c>
-      <c r="C8" t="s" s="2">
-        <v>63</v>
-      </c>
       <c r="D8" t="s" s="2">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="B9" t="s" s="2">
         <v>64</v>
       </c>
-      <c r="B9" t="s" s="2">
+      <c r="C9" t="s" s="2">
         <v>65</v>
       </c>
-      <c r="C9" t="s" s="2">
-        <v>66</v>
-      </c>
       <c r="D9" t="s" s="2">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="B10" t="s" s="2">
         <v>67</v>
       </c>
-      <c r="B10" t="s" s="2">
+      <c r="C10" t="s" s="2">
         <v>68</v>
       </c>
-      <c r="C10" t="s" s="2">
-        <v>69</v>
-      </c>
       <c r="D10" t="s" s="2">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="B11" t="s" s="2">
         <v>70</v>
       </c>
-      <c r="B11" t="s" s="2">
+      <c r="C11" t="s" s="2">
         <v>71</v>
       </c>
-      <c r="C11" t="s" s="2">
+      <c r="D11" t="s" s="2">
         <v>72</v>
-      </c>
-      <c r="D11" t="s" s="2">
-        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -3230,5123 +3225,5123 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
+        <v>73</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="C1" t="s" s="1">
         <v>74</v>
       </c>
-      <c r="B1" t="s" s="1">
-        <v>36</v>
-      </c>
-      <c r="C1" t="s" s="1">
+      <c r="D1" t="s" s="1">
         <v>75</v>
-      </c>
-      <c r="D1" t="s" s="1">
-        <v>76</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="B2" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="B2" t="s" s="2">
+      <c r="C2" t="s" s="2">
         <v>78</v>
-      </c>
-      <c r="C2" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="D2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B3" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="C3" t="s" s="2">
         <v>80</v>
-      </c>
-      <c r="C3" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="D3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B4" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="C4" t="s" s="2">
         <v>82</v>
-      </c>
-      <c r="C4" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="D4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B5" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="C5" t="s" s="2">
         <v>84</v>
-      </c>
-      <c r="C5" t="s" s="2">
-        <v>85</v>
       </c>
       <c r="D5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B6" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="C6" t="s" s="2">
         <v>86</v>
-      </c>
-      <c r="C6" t="s" s="2">
-        <v>87</v>
       </c>
       <c r="D6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B7" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="C7" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="C7" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="D7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B8" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="C8" t="s" s="2">
         <v>90</v>
-      </c>
-      <c r="C8" t="s" s="2">
-        <v>91</v>
       </c>
       <c r="D8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B9" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="C9" t="s" s="2">
         <v>92</v>
-      </c>
-      <c r="C9" t="s" s="2">
-        <v>93</v>
       </c>
       <c r="D9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B11" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="C11" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="C11" t="s" s="2">
-        <v>96</v>
       </c>
       <c r="D11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B12" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="C12" t="s" s="2">
         <v>97</v>
-      </c>
-      <c r="C12" t="s" s="2">
-        <v>98</v>
       </c>
       <c r="D12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B13" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="C13" t="s" s="2">
         <v>99</v>
-      </c>
-      <c r="C13" t="s" s="2">
-        <v>100</v>
       </c>
       <c r="D13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B15" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="C15" t="s" s="2">
         <v>102</v>
-      </c>
-      <c r="C15" t="s" s="2">
-        <v>103</v>
       </c>
       <c r="D15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B16" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="C16" t="s" s="2">
         <v>104</v>
-      </c>
-      <c r="C16" t="s" s="2">
-        <v>105</v>
       </c>
       <c r="D16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B18" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="C18" t="s" s="2">
         <v>107</v>
-      </c>
-      <c r="C18" t="s" s="2">
-        <v>108</v>
       </c>
       <c r="D18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B19" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="C19" t="s" s="2">
         <v>109</v>
-      </c>
-      <c r="C19" t="s" s="2">
-        <v>110</v>
       </c>
       <c r="D19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B20" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="C20" t="s" s="2">
         <v>111</v>
-      </c>
-      <c r="C20" t="s" s="2">
-        <v>112</v>
       </c>
       <c r="D20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B21" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="C21" t="s" s="2">
         <v>113</v>
-      </c>
-      <c r="C21" t="s" s="2">
-        <v>114</v>
       </c>
       <c r="D21" s="2"/>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B22" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="C22" t="s" s="2">
         <v>115</v>
-      </c>
-      <c r="C22" t="s" s="2">
-        <v>116</v>
       </c>
       <c r="D22" s="2"/>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B23" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="C23" t="s" s="2">
         <v>117</v>
-      </c>
-      <c r="C23" t="s" s="2">
-        <v>118</v>
       </c>
       <c r="D23" s="2"/>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D24" s="2"/>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B25" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="C25" t="s" s="2">
         <v>120</v>
-      </c>
-      <c r="C25" t="s" s="2">
-        <v>121</v>
       </c>
       <c r="D25" s="2"/>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B26" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="C26" t="s" s="2">
         <v>122</v>
-      </c>
-      <c r="C26" t="s" s="2">
-        <v>123</v>
       </c>
       <c r="D26" s="2"/>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B27" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="C27" t="s" s="2">
         <v>124</v>
-      </c>
-      <c r="C27" t="s" s="2">
-        <v>125</v>
       </c>
       <c r="D27" s="2"/>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D28" s="2"/>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B29" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="C29" t="s" s="2">
         <v>127</v>
-      </c>
-      <c r="C29" t="s" s="2">
-        <v>128</v>
       </c>
       <c r="D29" s="2"/>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B30" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="C30" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="C30" t="s" s="2">
-        <v>130</v>
       </c>
       <c r="D30" s="2"/>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B31" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="C31" t="s" s="2">
         <v>131</v>
-      </c>
-      <c r="C31" t="s" s="2">
-        <v>132</v>
       </c>
       <c r="D31" s="2"/>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B32" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="C32" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="C32" t="s" s="2">
-        <v>134</v>
       </c>
       <c r="D32" s="2"/>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B33" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="C33" t="s" s="2">
         <v>135</v>
-      </c>
-      <c r="C33" t="s" s="2">
-        <v>136</v>
       </c>
       <c r="D33" s="2"/>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B34" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="C34" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="C34" t="s" s="2">
-        <v>138</v>
       </c>
       <c r="D34" s="2"/>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B35" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="C35" t="s" s="2">
         <v>139</v>
-      </c>
-      <c r="C35" t="s" s="2">
-        <v>140</v>
       </c>
       <c r="D35" s="2"/>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B36" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="C36" t="s" s="2">
         <v>141</v>
-      </c>
-      <c r="C36" t="s" s="2">
-        <v>142</v>
       </c>
       <c r="D36" s="2"/>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B37" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="C37" t="s" s="2">
         <v>143</v>
-      </c>
-      <c r="C37" t="s" s="2">
-        <v>144</v>
       </c>
       <c r="D37" s="2"/>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B38" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="C38" t="s" s="2">
         <v>145</v>
-      </c>
-      <c r="C38" t="s" s="2">
-        <v>146</v>
       </c>
       <c r="D38" s="2"/>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B39" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="C39" t="s" s="2">
         <v>147</v>
-      </c>
-      <c r="C39" t="s" s="2">
-        <v>148</v>
       </c>
       <c r="D39" s="2"/>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B40" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="C40" t="s" s="2">
         <v>149</v>
-      </c>
-      <c r="C40" t="s" s="2">
-        <v>150</v>
       </c>
       <c r="D40" s="2"/>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B41" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="C41" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="C41" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="D41" s="2"/>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B42" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="C42" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="C42" t="s" s="2">
-        <v>154</v>
       </c>
       <c r="D42" s="2"/>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B43" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="C43" t="s" s="2">
         <v>155</v>
-      </c>
-      <c r="C43" t="s" s="2">
-        <v>156</v>
       </c>
       <c r="D43" s="2"/>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B44" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="C44" t="s" s="2">
         <v>157</v>
-      </c>
-      <c r="C44" t="s" s="2">
-        <v>158</v>
       </c>
       <c r="D44" s="2"/>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D45" s="2"/>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B46" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="C46" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="C46" t="s" s="2">
-        <v>161</v>
       </c>
       <c r="D46" s="2"/>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B47" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="C47" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="C47" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="D47" s="2"/>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B48" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="C48" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="C48" t="s" s="2">
-        <v>165</v>
       </c>
       <c r="D48" s="2"/>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B49" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="C49" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="C49" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="D49" s="2"/>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B50" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="C50" t="s" s="2">
         <v>168</v>
-      </c>
-      <c r="C50" t="s" s="2">
-        <v>169</v>
       </c>
       <c r="D50" s="2"/>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B51" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="C51" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="C51" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="D51" s="2"/>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B52" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="C52" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="C52" t="s" s="2">
-        <v>173</v>
       </c>
       <c r="D52" s="2"/>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B53" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="C53" t="s" s="2">
         <v>174</v>
-      </c>
-      <c r="C53" t="s" s="2">
-        <v>175</v>
       </c>
       <c r="D53" s="2"/>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B54" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="C54" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="C54" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="D54" s="2"/>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B55" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="C55" t="s" s="2">
         <v>178</v>
-      </c>
-      <c r="C55" t="s" s="2">
-        <v>179</v>
       </c>
       <c r="D55" s="2"/>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D56" s="2"/>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D57" s="2"/>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B58" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="C58" t="s" s="2">
         <v>182</v>
-      </c>
-      <c r="C58" t="s" s="2">
-        <v>183</v>
       </c>
       <c r="D58" s="2"/>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B59" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="C59" t="s" s="2">
         <v>184</v>
-      </c>
-      <c r="C59" t="s" s="2">
-        <v>185</v>
       </c>
       <c r="D59" s="2"/>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B60" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="C60" t="s" s="2">
         <v>186</v>
-      </c>
-      <c r="C60" t="s" s="2">
-        <v>187</v>
       </c>
       <c r="D60" s="2"/>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B61" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="C61" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="C61" t="s" s="2">
-        <v>189</v>
       </c>
       <c r="D61" s="2"/>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B62" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="C62" t="s" s="2">
         <v>190</v>
-      </c>
-      <c r="C62" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="D62" s="2"/>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B63" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="C63" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="C63" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="D63" s="2"/>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B64" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="C64" t="s" s="2">
         <v>194</v>
-      </c>
-      <c r="C64" t="s" s="2">
-        <v>195</v>
       </c>
       <c r="D64" s="2"/>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B65" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="C65" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="C65" t="s" s="2">
-        <v>197</v>
       </c>
       <c r="D65" s="2"/>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B66" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="C66" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="C66" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="D66" s="2"/>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B67" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="C67" t="s" s="2">
         <v>200</v>
-      </c>
-      <c r="C67" t="s" s="2">
-        <v>201</v>
       </c>
       <c r="D67" s="2"/>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B68" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="C68" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="C68" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="D68" s="2"/>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B69" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="C69" t="s" s="2">
         <v>204</v>
-      </c>
-      <c r="C69" t="s" s="2">
-        <v>205</v>
       </c>
       <c r="D69" s="2"/>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B70" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="C70" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="C70" t="s" s="2">
-        <v>207</v>
       </c>
       <c r="D70" s="2"/>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B71" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="C71" t="s" s="2">
         <v>208</v>
-      </c>
-      <c r="C71" t="s" s="2">
-        <v>209</v>
       </c>
       <c r="D71" s="2"/>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B72" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="C72" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="C72" t="s" s="2">
-        <v>211</v>
       </c>
       <c r="D72" s="2"/>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B73" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="C73" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="C73" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="D73" s="2"/>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B74" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="C74" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="C74" t="s" s="2">
-        <v>215</v>
       </c>
       <c r="D74" s="2"/>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B75" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="C75" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="C75" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="D75" s="2"/>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B76" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="C76" t="s" s="2">
         <v>218</v>
-      </c>
-      <c r="C76" t="s" s="2">
-        <v>219</v>
       </c>
       <c r="D76" s="2"/>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B77" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="C77" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="C77" t="s" s="2">
-        <v>221</v>
       </c>
       <c r="D77" s="2"/>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B78" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="C78" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="C78" t="s" s="2">
-        <v>223</v>
       </c>
       <c r="D78" s="2"/>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B79" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="C79" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="C79" t="s" s="2">
-        <v>225</v>
       </c>
       <c r="D79" s="2"/>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B80" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="C80" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="C80" t="s" s="2">
-        <v>227</v>
       </c>
       <c r="D80" s="2"/>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B81" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="C81" t="s" s="2">
         <v>228</v>
-      </c>
-      <c r="C81" t="s" s="2">
-        <v>229</v>
       </c>
       <c r="D81" s="2"/>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B82" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="C82" t="s" s="2">
         <v>230</v>
-      </c>
-      <c r="C82" t="s" s="2">
-        <v>231</v>
       </c>
       <c r="D82" s="2"/>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B83" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="C83" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="C83" t="s" s="2">
-        <v>233</v>
       </c>
       <c r="D83" s="2"/>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B84" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="C84" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="C84" t="s" s="2">
-        <v>235</v>
       </c>
       <c r="D84" s="2"/>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B85" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="C85" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="C85" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="D85" s="2"/>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B86" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="C86" t="s" s="2">
         <v>238</v>
-      </c>
-      <c r="C86" t="s" s="2">
-        <v>239</v>
       </c>
       <c r="D86" s="2"/>
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B87" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="C87" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="C87" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="D87" s="2"/>
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B88" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="C88" t="s" s="2">
         <v>242</v>
-      </c>
-      <c r="C88" t="s" s="2">
-        <v>243</v>
       </c>
       <c r="D88" s="2"/>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B89" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="C89" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="C89" t="s" s="2">
-        <v>245</v>
       </c>
       <c r="D89" s="2"/>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B90" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="C90" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="C90" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="D90" s="2"/>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B91" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="C91" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="C91" t="s" s="2">
-        <v>249</v>
       </c>
       <c r="D91" s="2"/>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B92" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="C92" t="s" s="2">
         <v>250</v>
-      </c>
-      <c r="C92" t="s" s="2">
-        <v>251</v>
       </c>
       <c r="D92" s="2"/>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B93" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="C93" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="C93" t="s" s="2">
-        <v>253</v>
       </c>
       <c r="D93" s="2"/>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B94" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="C94" t="s" s="2">
         <v>254</v>
-      </c>
-      <c r="C94" t="s" s="2">
-        <v>255</v>
       </c>
       <c r="D94" s="2"/>
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B95" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="C95" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="C95" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="D95" s="2"/>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B96" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="C96" t="s" s="2">
         <v>258</v>
-      </c>
-      <c r="C96" t="s" s="2">
-        <v>259</v>
       </c>
       <c r="D96" s="2"/>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B97" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="C97" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="C97" t="s" s="2">
-        <v>261</v>
       </c>
       <c r="D97" s="2"/>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B98" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="C98" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="C98" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="D98" s="2"/>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B99" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="C99" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="C99" t="s" s="2">
-        <v>265</v>
       </c>
       <c r="D99" s="2"/>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B100" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="C100" t="s" s="2">
         <v>266</v>
-      </c>
-      <c r="C100" t="s" s="2">
-        <v>267</v>
       </c>
       <c r="D100" s="2"/>
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B101" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="C101" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="C101" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="D101" s="2"/>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B102" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="C102" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="C102" t="s" s="2">
-        <v>271</v>
       </c>
       <c r="D102" s="2"/>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B103" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="C103" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="C103" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="D103" s="2"/>
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D104" s="2"/>
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B105" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="C105" t="s" s="2">
         <v>275</v>
-      </c>
-      <c r="C105" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="D105" s="2"/>
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B106" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="C106" t="s" s="2">
         <v>277</v>
-      </c>
-      <c r="C106" t="s" s="2">
-        <v>278</v>
       </c>
       <c r="D106" s="2"/>
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D107" s="2"/>
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D108" s="2"/>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B109" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="C109" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="C109" t="s" s="2">
-        <v>282</v>
       </c>
       <c r="D109" s="2"/>
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B110" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="C110" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="C110" t="s" s="2">
-        <v>284</v>
       </c>
       <c r="D110" s="2"/>
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B111" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="C111" t="s" s="2">
         <v>285</v>
-      </c>
-      <c r="C111" t="s" s="2">
-        <v>286</v>
       </c>
       <c r="D111" s="2"/>
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B112" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="C112" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="C112" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="D112" s="2"/>
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B113" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="C113" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="C113" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="D113" s="2"/>
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B114" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="C114" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="C114" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="D114" s="2"/>
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B115" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="C115" t="s" s="2">
         <v>293</v>
-      </c>
-      <c r="C115" t="s" s="2">
-        <v>294</v>
       </c>
       <c r="D115" s="2"/>
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B116" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="C116" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="C116" t="s" s="2">
-        <v>296</v>
       </c>
       <c r="D116" s="2"/>
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B117" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="C117" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="C117" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="D117" s="2"/>
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B118" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="C118" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="C118" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="D118" s="2"/>
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B119" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="C119" t="s" s="2">
         <v>301</v>
-      </c>
-      <c r="C119" t="s" s="2">
-        <v>302</v>
       </c>
       <c r="D119" s="2"/>
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B120" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="C120" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="C120" t="s" s="2">
-        <v>304</v>
       </c>
       <c r="D120" s="2"/>
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B121" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="C121" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="C121" t="s" s="2">
-        <v>306</v>
       </c>
       <c r="D121" s="2"/>
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B122" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="C122" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="C122" t="s" s="2">
-        <v>308</v>
       </c>
       <c r="D122" s="2"/>
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B123" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="C123" t="s" s="2">
         <v>309</v>
-      </c>
-      <c r="C123" t="s" s="2">
-        <v>310</v>
       </c>
       <c r="D123" s="2"/>
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B124" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="C124" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="C124" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="D124" s="2"/>
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B125" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="C125" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="C125" t="s" s="2">
-        <v>314</v>
       </c>
       <c r="D125" s="2"/>
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B126" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="C126" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="C126" t="s" s="2">
-        <v>316</v>
       </c>
       <c r="D126" s="2"/>
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B127" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="C127" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="C127" t="s" s="2">
-        <v>318</v>
       </c>
       <c r="D127" s="2"/>
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B128" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="C128" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="C128" t="s" s="2">
-        <v>320</v>
       </c>
       <c r="D128" s="2"/>
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B129" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="C129" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="C129" t="s" s="2">
-        <v>322</v>
       </c>
       <c r="D129" s="2"/>
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B130" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="C130" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="C130" t="s" s="2">
-        <v>324</v>
       </c>
       <c r="D130" s="2"/>
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B131" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="C131" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="C131" t="s" s="2">
-        <v>326</v>
       </c>
       <c r="D131" s="2"/>
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B132" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="C132" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="C132" t="s" s="2">
-        <v>328</v>
       </c>
       <c r="D132" s="2"/>
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B133" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="C133" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="C133" t="s" s="2">
-        <v>330</v>
       </c>
       <c r="D133" s="2"/>
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B134" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="C134" t="s" s="2">
         <v>331</v>
-      </c>
-      <c r="C134" t="s" s="2">
-        <v>332</v>
       </c>
       <c r="D134" s="2"/>
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B135" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="C135" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="C135" t="s" s="2">
-        <v>334</v>
       </c>
       <c r="D135" s="2"/>
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B136" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="C136" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="C136" t="s" s="2">
-        <v>336</v>
       </c>
       <c r="D136" s="2"/>
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B137" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="C137" t="s" s="2">
         <v>337</v>
-      </c>
-      <c r="C137" t="s" s="2">
-        <v>338</v>
       </c>
       <c r="D137" s="2"/>
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B138" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="C138" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="C138" t="s" s="2">
-        <v>340</v>
       </c>
       <c r="D138" s="2"/>
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B139" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="C139" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="C139" t="s" s="2">
-        <v>342</v>
       </c>
       <c r="D139" s="2"/>
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B140" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="C140" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="C140" t="s" s="2">
-        <v>344</v>
       </c>
       <c r="D140" s="2"/>
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B141" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="C141" t="s" s="2">
         <v>345</v>
-      </c>
-      <c r="C141" t="s" s="2">
-        <v>346</v>
       </c>
       <c r="D141" s="2"/>
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B142" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="C142" t="s" s="2">
         <v>347</v>
-      </c>
-      <c r="C142" t="s" s="2">
-        <v>348</v>
       </c>
       <c r="D142" s="2"/>
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B143" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="C143" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="C143" t="s" s="2">
-        <v>350</v>
       </c>
       <c r="D143" s="2"/>
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B144" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="C144" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="C144" t="s" s="2">
-        <v>352</v>
       </c>
       <c r="D144" s="2"/>
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B145" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="C145" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="C145" t="s" s="2">
-        <v>354</v>
       </c>
       <c r="D145" s="2"/>
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B146" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="C146" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="C146" t="s" s="2">
-        <v>356</v>
       </c>
       <c r="D146" s="2"/>
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B147" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="C147" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="C147" t="s" s="2">
-        <v>358</v>
       </c>
       <c r="D147" s="2"/>
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B148" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="C148" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="C148" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="D148" s="2"/>
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B149" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="C149" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="C149" t="s" s="2">
-        <v>362</v>
       </c>
       <c r="D149" s="2"/>
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B150" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="C150" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="C150" t="s" s="2">
-        <v>364</v>
       </c>
       <c r="D150" s="2"/>
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B151" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="C151" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="C151" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="D151" s="2"/>
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B152" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="C152" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="C152" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="D152" s="2"/>
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B153" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="C153" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="C153" t="s" s="2">
-        <v>370</v>
       </c>
       <c r="D153" s="2"/>
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B154" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="C154" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="C154" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="D154" s="2"/>
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B155" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="C155" t="s" s="2">
         <v>373</v>
-      </c>
-      <c r="C155" t="s" s="2">
-        <v>374</v>
       </c>
       <c r="D155" s="2"/>
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B156" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="C156" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="C156" t="s" s="2">
-        <v>376</v>
       </c>
       <c r="D156" s="2"/>
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B157" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="C157" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="C157" t="s" s="2">
-        <v>378</v>
       </c>
       <c r="D157" s="2"/>
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B158" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="C158" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="C158" t="s" s="2">
-        <v>380</v>
       </c>
       <c r="D158" s="2"/>
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B159" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="C159" t="s" s="2">
         <v>381</v>
-      </c>
-      <c r="C159" t="s" s="2">
-        <v>382</v>
       </c>
       <c r="D159" s="2"/>
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B160" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="C160" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="C160" t="s" s="2">
-        <v>384</v>
       </c>
       <c r="D160" s="2"/>
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B161" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="C161" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="C161" t="s" s="2">
-        <v>386</v>
       </c>
       <c r="D161" s="2"/>
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B162" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="C162" t="s" s="2">
         <v>387</v>
-      </c>
-      <c r="C162" t="s" s="2">
-        <v>388</v>
       </c>
       <c r="D162" s="2"/>
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B163" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="C163" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="C163" t="s" s="2">
-        <v>390</v>
       </c>
       <c r="D163" s="2"/>
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B164" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="C164" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="C164" t="s" s="2">
-        <v>392</v>
       </c>
       <c r="D164" s="2"/>
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B165" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="C165" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="C165" t="s" s="2">
-        <v>394</v>
       </c>
       <c r="D165" s="2"/>
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B166" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="C166" t="s" s="2">
         <v>395</v>
-      </c>
-      <c r="C166" t="s" s="2">
-        <v>396</v>
       </c>
       <c r="D166" s="2"/>
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B167" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="C167" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="C167" t="s" s="2">
-        <v>398</v>
       </c>
       <c r="D167" s="2"/>
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B168" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="C168" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="C168" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="D168" s="2"/>
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B169" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="C169" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="C169" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="D169" s="2"/>
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B170" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="C170" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="C170" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="D170" s="2"/>
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B171" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="C171" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="C171" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="D171" s="2"/>
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B172" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="C172" t="s" s="2">
         <v>407</v>
-      </c>
-      <c r="C172" t="s" s="2">
-        <v>408</v>
       </c>
       <c r="D172" s="2"/>
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B173" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="C173" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="C173" t="s" s="2">
-        <v>410</v>
       </c>
       <c r="D173" s="2"/>
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B174" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="C174" t="s" s="2">
         <v>411</v>
-      </c>
-      <c r="C174" t="s" s="2">
-        <v>412</v>
       </c>
       <c r="D174" s="2"/>
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B175" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="C175" t="s" s="2">
         <v>413</v>
-      </c>
-      <c r="C175" t="s" s="2">
-        <v>414</v>
       </c>
       <c r="D175" s="2"/>
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B176" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="C176" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="C176" t="s" s="2">
-        <v>416</v>
       </c>
       <c r="D176" s="2"/>
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B177" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="C177" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="C177" t="s" s="2">
-        <v>418</v>
       </c>
       <c r="D177" s="2"/>
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B178" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="C178" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="C178" t="s" s="2">
-        <v>420</v>
       </c>
       <c r="D178" s="2"/>
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B179" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="C179" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="C179" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="D179" s="2"/>
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B180" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="C180" t="s" s="2">
         <v>423</v>
-      </c>
-      <c r="C180" t="s" s="2">
-        <v>424</v>
       </c>
       <c r="D180" s="2"/>
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B181" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="C181" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="C181" t="s" s="2">
-        <v>426</v>
       </c>
       <c r="D181" s="2"/>
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B182" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="C182" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="C182" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="D182" s="2"/>
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B183" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="C183" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="C183" t="s" s="2">
-        <v>430</v>
       </c>
       <c r="D183" s="2"/>
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B184" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="C184" t="s" s="2">
         <v>431</v>
-      </c>
-      <c r="C184" t="s" s="2">
-        <v>432</v>
       </c>
       <c r="D184" s="2"/>
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B185" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="C185" t="s" s="2">
         <v>433</v>
-      </c>
-      <c r="C185" t="s" s="2">
-        <v>434</v>
       </c>
       <c r="D185" s="2"/>
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B186" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="C186" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="C186" t="s" s="2">
-        <v>436</v>
       </c>
       <c r="D186" s="2"/>
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B187" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="C187" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="C187" t="s" s="2">
-        <v>438</v>
       </c>
       <c r="D187" s="2"/>
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B188" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="C188" t="s" s="2">
         <v>439</v>
-      </c>
-      <c r="C188" t="s" s="2">
-        <v>440</v>
       </c>
       <c r="D188" s="2"/>
     </row>
     <row r="189">
       <c r="A189" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B189" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="C189" t="s" s="2">
         <v>441</v>
-      </c>
-      <c r="C189" t="s" s="2">
-        <v>442</v>
       </c>
       <c r="D189" s="2"/>
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B190" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="C190" t="s" s="2">
         <v>443</v>
-      </c>
-      <c r="C190" t="s" s="2">
-        <v>444</v>
       </c>
       <c r="D190" s="2"/>
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B191" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="C191" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="C191" t="s" s="2">
-        <v>446</v>
       </c>
       <c r="D191" s="2"/>
     </row>
     <row r="192">
       <c r="A192" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B192" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="C192" t="s" s="2">
         <v>447</v>
-      </c>
-      <c r="C192" t="s" s="2">
-        <v>448</v>
       </c>
       <c r="D192" s="2"/>
     </row>
     <row r="193">
       <c r="A193" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B193" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="C193" t="s" s="2">
         <v>449</v>
-      </c>
-      <c r="C193" t="s" s="2">
-        <v>450</v>
       </c>
       <c r="D193" s="2"/>
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B194" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="C194" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="C194" t="s" s="2">
-        <v>452</v>
       </c>
       <c r="D194" s="2"/>
     </row>
     <row r="195">
       <c r="A195" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B195" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="C195" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="C195" t="s" s="2">
-        <v>454</v>
       </c>
       <c r="D195" s="2"/>
     </row>
     <row r="196">
       <c r="A196" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B196" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="C196" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="C196" t="s" s="2">
-        <v>456</v>
       </c>
       <c r="D196" s="2"/>
     </row>
     <row r="197">
       <c r="A197" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B197" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="C197" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="C197" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="D197" s="2"/>
     </row>
     <row r="198">
       <c r="A198" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B198" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="C198" t="s" s="2">
         <v>459</v>
-      </c>
-      <c r="C198" t="s" s="2">
-        <v>460</v>
       </c>
       <c r="D198" s="2"/>
     </row>
     <row r="199">
       <c r="A199" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B199" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="C199" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="C199" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="D199" s="2"/>
     </row>
     <row r="200">
       <c r="A200" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B200" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="C200" t="s" s="2">
         <v>463</v>
-      </c>
-      <c r="C200" t="s" s="2">
-        <v>464</v>
       </c>
       <c r="D200" s="2"/>
     </row>
     <row r="201">
       <c r="A201" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B201" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="C201" t="s" s="2">
         <v>465</v>
-      </c>
-      <c r="C201" t="s" s="2">
-        <v>466</v>
       </c>
       <c r="D201" s="2"/>
     </row>
     <row r="202">
       <c r="A202" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B202" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="C202" t="s" s="2">
         <v>467</v>
-      </c>
-      <c r="C202" t="s" s="2">
-        <v>468</v>
       </c>
       <c r="D202" s="2"/>
     </row>
     <row r="203">
       <c r="A203" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B203" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="C203" t="s" s="2">
         <v>469</v>
-      </c>
-      <c r="C203" t="s" s="2">
-        <v>470</v>
       </c>
       <c r="D203" s="2"/>
     </row>
     <row r="204">
       <c r="A204" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B204" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="C204" t="s" s="2">
         <v>471</v>
-      </c>
-      <c r="C204" t="s" s="2">
-        <v>472</v>
       </c>
       <c r="D204" s="2"/>
     </row>
     <row r="205">
       <c r="A205" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B205" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="C205" t="s" s="2">
         <v>473</v>
-      </c>
-      <c r="C205" t="s" s="2">
-        <v>474</v>
       </c>
       <c r="D205" s="2"/>
     </row>
     <row r="206">
       <c r="A206" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B206" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="C206" t="s" s="2">
         <v>475</v>
-      </c>
-      <c r="C206" t="s" s="2">
-        <v>476</v>
       </c>
       <c r="D206" s="2"/>
     </row>
     <row r="207">
       <c r="A207" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B207" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="C207" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="C207" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="D207" s="2"/>
     </row>
     <row r="208">
       <c r="A208" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B208" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="C208" t="s" s="2">
         <v>479</v>
-      </c>
-      <c r="C208" t="s" s="2">
-        <v>480</v>
       </c>
       <c r="D208" s="2"/>
     </row>
     <row r="209">
       <c r="A209" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B209" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="C209" t="s" s="2">
         <v>481</v>
-      </c>
-      <c r="C209" t="s" s="2">
-        <v>482</v>
       </c>
       <c r="D209" s="2"/>
     </row>
     <row r="210">
       <c r="A210" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B210" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="C210" t="s" s="2">
         <v>483</v>
-      </c>
-      <c r="C210" t="s" s="2">
-        <v>484</v>
       </c>
       <c r="D210" s="2"/>
     </row>
     <row r="211">
       <c r="A211" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B211" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="C211" t="s" s="2">
         <v>485</v>
-      </c>
-      <c r="C211" t="s" s="2">
-        <v>486</v>
       </c>
       <c r="D211" s="2"/>
     </row>
     <row r="212">
       <c r="A212" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B212" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="C212" t="s" s="2">
         <v>487</v>
-      </c>
-      <c r="C212" t="s" s="2">
-        <v>488</v>
       </c>
       <c r="D212" s="2"/>
     </row>
     <row r="213">
       <c r="A213" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B213" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="C213" t="s" s="2">
         <v>489</v>
-      </c>
-      <c r="C213" t="s" s="2">
-        <v>490</v>
       </c>
       <c r="D213" s="2"/>
     </row>
     <row r="214">
       <c r="A214" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B214" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="C214" t="s" s="2">
         <v>491</v>
-      </c>
-      <c r="C214" t="s" s="2">
-        <v>492</v>
       </c>
       <c r="D214" s="2"/>
     </row>
     <row r="215">
       <c r="A215" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B215" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="C215" t="s" s="2">
         <v>493</v>
-      </c>
-      <c r="C215" t="s" s="2">
-        <v>494</v>
       </c>
       <c r="D215" s="2"/>
     </row>
     <row r="216">
       <c r="A216" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B216" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="C216" t="s" s="2">
         <v>495</v>
-      </c>
-      <c r="C216" t="s" s="2">
-        <v>496</v>
       </c>
       <c r="D216" s="2"/>
     </row>
     <row r="217">
       <c r="A217" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B217" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="C217" t="s" s="2">
         <v>497</v>
-      </c>
-      <c r="C217" t="s" s="2">
-        <v>498</v>
       </c>
       <c r="D217" s="2"/>
     </row>
     <row r="218">
       <c r="A218" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B218" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="C218" t="s" s="2">
         <v>499</v>
-      </c>
-      <c r="C218" t="s" s="2">
-        <v>500</v>
       </c>
       <c r="D218" s="2"/>
     </row>
     <row r="219">
       <c r="A219" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B219" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="C219" t="s" s="2">
         <v>501</v>
-      </c>
-      <c r="C219" t="s" s="2">
-        <v>502</v>
       </c>
       <c r="D219" s="2"/>
     </row>
     <row r="220">
       <c r="A220" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B220" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="C220" t="s" s="2">
         <v>503</v>
-      </c>
-      <c r="C220" t="s" s="2">
-        <v>504</v>
       </c>
       <c r="D220" s="2"/>
     </row>
     <row r="221">
       <c r="A221" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B221" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="C221" t="s" s="2">
         <v>505</v>
-      </c>
-      <c r="C221" t="s" s="2">
-        <v>506</v>
       </c>
       <c r="D221" s="2"/>
     </row>
     <row r="222">
       <c r="A222" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B222" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="C222" t="s" s="2">
         <v>507</v>
-      </c>
-      <c r="C222" t="s" s="2">
-        <v>508</v>
       </c>
       <c r="D222" s="2"/>
     </row>
     <row r="223">
       <c r="A223" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B223" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="C223" t="s" s="2">
         <v>509</v>
-      </c>
-      <c r="C223" t="s" s="2">
-        <v>510</v>
       </c>
       <c r="D223" s="2"/>
     </row>
     <row r="224">
       <c r="A224" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B224" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="C224" t="s" s="2">
         <v>511</v>
-      </c>
-      <c r="C224" t="s" s="2">
-        <v>512</v>
       </c>
       <c r="D224" s="2"/>
     </row>
     <row r="225">
       <c r="A225" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B225" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="C225" t="s" s="2">
         <v>513</v>
-      </c>
-      <c r="C225" t="s" s="2">
-        <v>514</v>
       </c>
       <c r="D225" s="2"/>
     </row>
     <row r="226">
       <c r="A226" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B226" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="C226" t="s" s="2">
         <v>515</v>
-      </c>
-      <c r="C226" t="s" s="2">
-        <v>516</v>
       </c>
       <c r="D226" s="2"/>
     </row>
     <row r="227">
       <c r="A227" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B227" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="C227" t="s" s="2">
         <v>517</v>
-      </c>
-      <c r="C227" t="s" s="2">
-        <v>518</v>
       </c>
       <c r="D227" s="2"/>
     </row>
     <row r="228">
       <c r="A228" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B228" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="C228" t="s" s="2">
         <v>519</v>
-      </c>
-      <c r="C228" t="s" s="2">
-        <v>520</v>
       </c>
       <c r="D228" s="2"/>
     </row>
     <row r="229">
       <c r="A229" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B229" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="C229" t="s" s="2">
         <v>521</v>
-      </c>
-      <c r="C229" t="s" s="2">
-        <v>522</v>
       </c>
       <c r="D229" s="2"/>
     </row>
     <row r="230">
       <c r="A230" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B230" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="C230" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="C230" t="s" s="2">
-        <v>524</v>
       </c>
       <c r="D230" s="2"/>
     </row>
     <row r="231">
       <c r="A231" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B231" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="C231" t="s" s="2">
         <v>525</v>
-      </c>
-      <c r="C231" t="s" s="2">
-        <v>526</v>
       </c>
       <c r="D231" s="2"/>
     </row>
     <row r="232">
       <c r="A232" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B232" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="C232" t="s" s="2">
         <v>527</v>
-      </c>
-      <c r="C232" t="s" s="2">
-        <v>528</v>
       </c>
       <c r="D232" s="2"/>
     </row>
     <row r="233">
       <c r="A233" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B233" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="C233" t="s" s="2">
         <v>529</v>
-      </c>
-      <c r="C233" t="s" s="2">
-        <v>530</v>
       </c>
       <c r="D233" s="2"/>
     </row>
     <row r="234">
       <c r="A234" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B234" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="C234" t="s" s="2">
         <v>531</v>
-      </c>
-      <c r="C234" t="s" s="2">
-        <v>532</v>
       </c>
       <c r="D234" s="2"/>
     </row>
     <row r="235">
       <c r="A235" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B235" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="C235" t="s" s="2">
         <v>533</v>
-      </c>
-      <c r="C235" t="s" s="2">
-        <v>534</v>
       </c>
       <c r="D235" s="2"/>
     </row>
     <row r="236">
       <c r="A236" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B236" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="C236" t="s" s="2">
         <v>535</v>
-      </c>
-      <c r="C236" t="s" s="2">
-        <v>536</v>
       </c>
       <c r="D236" s="2"/>
     </row>
     <row r="237">
       <c r="A237" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B237" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="C237" t="s" s="2">
         <v>537</v>
-      </c>
-      <c r="C237" t="s" s="2">
-        <v>538</v>
       </c>
       <c r="D237" s="2"/>
     </row>
     <row r="238">
       <c r="A238" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B238" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="C238" t="s" s="2">
         <v>539</v>
-      </c>
-      <c r="C238" t="s" s="2">
-        <v>540</v>
       </c>
       <c r="D238" s="2"/>
     </row>
     <row r="239">
       <c r="A239" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B239" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="C239" t="s" s="2">
         <v>541</v>
-      </c>
-      <c r="C239" t="s" s="2">
-        <v>542</v>
       </c>
       <c r="D239" s="2"/>
     </row>
     <row r="240">
       <c r="A240" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B240" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="C240" t="s" s="2">
         <v>543</v>
-      </c>
-      <c r="C240" t="s" s="2">
-        <v>544</v>
       </c>
       <c r="D240" s="2"/>
     </row>
     <row r="241">
       <c r="A241" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B241" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="C241" t="s" s="2">
         <v>545</v>
-      </c>
-      <c r="C241" t="s" s="2">
-        <v>546</v>
       </c>
       <c r="D241" s="2"/>
     </row>
     <row r="242">
       <c r="A242" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B242" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="C242" t="s" s="2">
         <v>547</v>
-      </c>
-      <c r="C242" t="s" s="2">
-        <v>548</v>
       </c>
       <c r="D242" s="2"/>
     </row>
     <row r="243">
       <c r="A243" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B243" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="C243" t="s" s="2">
         <v>549</v>
-      </c>
-      <c r="C243" t="s" s="2">
-        <v>550</v>
       </c>
       <c r="D243" s="2"/>
     </row>
     <row r="244">
       <c r="A244" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B244" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="C244" t="s" s="2">
         <v>551</v>
-      </c>
-      <c r="C244" t="s" s="2">
-        <v>552</v>
       </c>
       <c r="D244" s="2"/>
     </row>
     <row r="245">
       <c r="A245" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B245" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="C245" t="s" s="2">
         <v>553</v>
-      </c>
-      <c r="C245" t="s" s="2">
-        <v>554</v>
       </c>
       <c r="D245" s="2"/>
     </row>
     <row r="246">
       <c r="A246" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B246" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="C246" t="s" s="2">
         <v>555</v>
-      </c>
-      <c r="C246" t="s" s="2">
-        <v>556</v>
       </c>
       <c r="D246" s="2"/>
     </row>
     <row r="247">
       <c r="A247" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B247" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="C247" t="s" s="2">
         <v>557</v>
-      </c>
-      <c r="C247" t="s" s="2">
-        <v>558</v>
       </c>
       <c r="D247" s="2"/>
     </row>
     <row r="248">
       <c r="A248" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B248" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="C248" t="s" s="2">
         <v>559</v>
-      </c>
-      <c r="C248" t="s" s="2">
-        <v>560</v>
       </c>
       <c r="D248" s="2"/>
     </row>
     <row r="249">
       <c r="A249" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B249" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="C249" t="s" s="2">
         <v>561</v>
-      </c>
-      <c r="C249" t="s" s="2">
-        <v>562</v>
       </c>
       <c r="D249" s="2"/>
     </row>
     <row r="250">
       <c r="A250" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B250" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="C250" t="s" s="2">
         <v>563</v>
-      </c>
-      <c r="C250" t="s" s="2">
-        <v>564</v>
       </c>
       <c r="D250" s="2"/>
     </row>
     <row r="251">
       <c r="A251" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B251" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="C251" t="s" s="2">
         <v>565</v>
-      </c>
-      <c r="C251" t="s" s="2">
-        <v>566</v>
       </c>
       <c r="D251" s="2"/>
     </row>
     <row r="252">
       <c r="A252" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B252" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="C252" t="s" s="2">
         <v>567</v>
-      </c>
-      <c r="C252" t="s" s="2">
-        <v>568</v>
       </c>
       <c r="D252" s="2"/>
     </row>
     <row r="253">
       <c r="A253" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B253" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="C253" t="s" s="2">
         <v>569</v>
-      </c>
-      <c r="C253" t="s" s="2">
-        <v>570</v>
       </c>
       <c r="D253" s="2"/>
     </row>
     <row r="254">
       <c r="A254" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B254" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="C254" t="s" s="2">
         <v>571</v>
-      </c>
-      <c r="C254" t="s" s="2">
-        <v>572</v>
       </c>
       <c r="D254" s="2"/>
     </row>
     <row r="255">
       <c r="A255" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B255" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="C255" t="s" s="2">
         <v>573</v>
-      </c>
-      <c r="C255" t="s" s="2">
-        <v>574</v>
       </c>
       <c r="D255" s="2"/>
     </row>
     <row r="256">
       <c r="A256" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B256" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="C256" t="s" s="2">
         <v>575</v>
-      </c>
-      <c r="C256" t="s" s="2">
-        <v>576</v>
       </c>
       <c r="D256" s="2"/>
     </row>
     <row r="257">
       <c r="A257" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B257" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="C257" t="s" s="2">
         <v>577</v>
-      </c>
-      <c r="C257" t="s" s="2">
-        <v>578</v>
       </c>
       <c r="D257" s="2"/>
     </row>
     <row r="258">
       <c r="A258" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B258" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="C258" t="s" s="2">
         <v>579</v>
-      </c>
-      <c r="C258" t="s" s="2">
-        <v>580</v>
       </c>
       <c r="D258" s="2"/>
     </row>
     <row r="259">
       <c r="A259" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B259" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="C259" t="s" s="2">
         <v>581</v>
-      </c>
-      <c r="C259" t="s" s="2">
-        <v>582</v>
       </c>
       <c r="D259" s="2"/>
     </row>
     <row r="260">
       <c r="A260" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B260" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="C260" t="s" s="2">
         <v>583</v>
-      </c>
-      <c r="C260" t="s" s="2">
-        <v>584</v>
       </c>
       <c r="D260" s="2"/>
     </row>
     <row r="261">
       <c r="A261" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B261" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="C261" t="s" s="2">
         <v>585</v>
-      </c>
-      <c r="C261" t="s" s="2">
-        <v>586</v>
       </c>
       <c r="D261" s="2"/>
     </row>
     <row r="262">
       <c r="A262" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B262" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="C262" t="s" s="2">
         <v>587</v>
-      </c>
-      <c r="C262" t="s" s="2">
-        <v>588</v>
       </c>
       <c r="D262" s="2"/>
     </row>
     <row r="263">
       <c r="A263" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B263" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="C263" t="s" s="2">
         <v>589</v>
-      </c>
-      <c r="C263" t="s" s="2">
-        <v>590</v>
       </c>
       <c r="D263" s="2"/>
     </row>
     <row r="264">
       <c r="A264" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B264" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="C264" t="s" s="2">
         <v>591</v>
-      </c>
-      <c r="C264" t="s" s="2">
-        <v>592</v>
       </c>
       <c r="D264" s="2"/>
     </row>
     <row r="265">
       <c r="A265" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B265" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="C265" t="s" s="2">
         <v>593</v>
-      </c>
-      <c r="C265" t="s" s="2">
-        <v>594</v>
       </c>
       <c r="D265" s="2"/>
     </row>
     <row r="266">
       <c r="A266" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B266" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="C266" t="s" s="2">
         <v>595</v>
-      </c>
-      <c r="C266" t="s" s="2">
-        <v>596</v>
       </c>
       <c r="D266" s="2"/>
     </row>
     <row r="267">
       <c r="A267" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B267" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="C267" t="s" s="2">
         <v>597</v>
-      </c>
-      <c r="C267" t="s" s="2">
-        <v>598</v>
       </c>
       <c r="D267" s="2"/>
     </row>
     <row r="268">
       <c r="A268" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B268" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="C268" t="s" s="2">
         <v>599</v>
-      </c>
-      <c r="C268" t="s" s="2">
-        <v>600</v>
       </c>
       <c r="D268" s="2"/>
     </row>
     <row r="269">
       <c r="A269" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B269" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="C269" t="s" s="2">
         <v>601</v>
-      </c>
-      <c r="C269" t="s" s="2">
-        <v>602</v>
       </c>
       <c r="D269" s="2"/>
     </row>
     <row r="270">
       <c r="A270" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B270" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="C270" t="s" s="2">
         <v>603</v>
-      </c>
-      <c r="C270" t="s" s="2">
-        <v>604</v>
       </c>
       <c r="D270" s="2"/>
     </row>
     <row r="271">
       <c r="A271" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B271" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="C271" t="s" s="2">
         <v>605</v>
-      </c>
-      <c r="C271" t="s" s="2">
-        <v>606</v>
       </c>
       <c r="D271" s="2"/>
     </row>
     <row r="272">
       <c r="A272" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B272" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="C272" t="s" s="2">
         <v>607</v>
-      </c>
-      <c r="C272" t="s" s="2">
-        <v>608</v>
       </c>
       <c r="D272" s="2"/>
     </row>
     <row r="273">
       <c r="A273" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B273" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="C273" t="s" s="2">
         <v>609</v>
-      </c>
-      <c r="C273" t="s" s="2">
-        <v>610</v>
       </c>
       <c r="D273" s="2"/>
     </row>
     <row r="274">
       <c r="A274" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B274" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="C274" t="s" s="2">
         <v>611</v>
-      </c>
-      <c r="C274" t="s" s="2">
-        <v>612</v>
       </c>
       <c r="D274" s="2"/>
     </row>
     <row r="275">
       <c r="A275" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B275" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C275" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D275" s="2"/>
     </row>
     <row r="276">
       <c r="A276" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B276" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="C276" t="s" s="2">
         <v>614</v>
-      </c>
-      <c r="C276" t="s" s="2">
-        <v>615</v>
       </c>
       <c r="D276" s="2"/>
     </row>
     <row r="277">
       <c r="A277" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B277" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="C277" t="s" s="2">
         <v>616</v>
-      </c>
-      <c r="C277" t="s" s="2">
-        <v>617</v>
       </c>
       <c r="D277" s="2"/>
     </row>
     <row r="278">
       <c r="A278" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B278" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="C278" t="s" s="2">
         <v>618</v>
-      </c>
-      <c r="C278" t="s" s="2">
-        <v>619</v>
       </c>
       <c r="D278" s="2"/>
     </row>
     <row r="279">
       <c r="A279" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B279" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="C279" t="s" s="2">
         <v>620</v>
-      </c>
-      <c r="C279" t="s" s="2">
-        <v>621</v>
       </c>
       <c r="D279" s="2"/>
     </row>
     <row r="280">
       <c r="A280" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B280" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="C280" t="s" s="2">
         <v>622</v>
-      </c>
-      <c r="C280" t="s" s="2">
-        <v>623</v>
       </c>
       <c r="D280" s="2"/>
     </row>
     <row r="281">
       <c r="A281" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B281" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="C281" t="s" s="2">
         <v>624</v>
-      </c>
-      <c r="C281" t="s" s="2">
-        <v>625</v>
       </c>
       <c r="D281" s="2"/>
     </row>
     <row r="282">
       <c r="A282" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B282" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="C282" t="s" s="2">
         <v>626</v>
-      </c>
-      <c r="C282" t="s" s="2">
-        <v>627</v>
       </c>
       <c r="D282" s="2"/>
     </row>
     <row r="283">
       <c r="A283" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B283" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="C283" t="s" s="2">
         <v>628</v>
-      </c>
-      <c r="C283" t="s" s="2">
-        <v>629</v>
       </c>
       <c r="D283" s="2"/>
     </row>
     <row r="284">
       <c r="A284" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B284" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="C284" t="s" s="2">
         <v>630</v>
-      </c>
-      <c r="C284" t="s" s="2">
-        <v>631</v>
       </c>
       <c r="D284" s="2"/>
     </row>
     <row r="285">
       <c r="A285" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B285" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="C285" t="s" s="2">
         <v>632</v>
-      </c>
-      <c r="C285" t="s" s="2">
-        <v>633</v>
       </c>
       <c r="D285" s="2"/>
     </row>
     <row r="286">
       <c r="A286" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B286" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="C286" t="s" s="2">
         <v>634</v>
-      </c>
-      <c r="C286" t="s" s="2">
-        <v>635</v>
       </c>
       <c r="D286" s="2"/>
     </row>
     <row r="287">
       <c r="A287" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B287" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="C287" t="s" s="2">
         <v>636</v>
-      </c>
-      <c r="C287" t="s" s="2">
-        <v>637</v>
       </c>
       <c r="D287" s="2"/>
     </row>
     <row r="288">
       <c r="A288" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B288" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="C288" t="s" s="2">
         <v>638</v>
-      </c>
-      <c r="C288" t="s" s="2">
-        <v>639</v>
       </c>
       <c r="D288" s="2"/>
     </row>
     <row r="289">
       <c r="A289" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B289" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="C289" t="s" s="2">
         <v>640</v>
-      </c>
-      <c r="C289" t="s" s="2">
-        <v>641</v>
       </c>
       <c r="D289" s="2"/>
     </row>
     <row r="290">
       <c r="A290" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B290" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="C290" t="s" s="2">
         <v>642</v>
-      </c>
-      <c r="C290" t="s" s="2">
-        <v>643</v>
       </c>
       <c r="D290" s="2"/>
     </row>
     <row r="291">
       <c r="A291" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B291" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="C291" t="s" s="2">
         <v>644</v>
-      </c>
-      <c r="C291" t="s" s="2">
-        <v>645</v>
       </c>
       <c r="D291" s="2"/>
     </row>
     <row r="292">
       <c r="A292" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B292" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="C292" t="s" s="2">
         <v>646</v>
-      </c>
-      <c r="C292" t="s" s="2">
-        <v>647</v>
       </c>
       <c r="D292" s="2"/>
     </row>
     <row r="293">
       <c r="A293" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B293" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="C293" t="s" s="2">
         <v>648</v>
-      </c>
-      <c r="C293" t="s" s="2">
-        <v>649</v>
       </c>
       <c r="D293" s="2"/>
     </row>
     <row r="294">
       <c r="A294" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B294" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="C294" t="s" s="2">
         <v>650</v>
-      </c>
-      <c r="C294" t="s" s="2">
-        <v>651</v>
       </c>
       <c r="D294" s="2"/>
     </row>
     <row r="295">
       <c r="A295" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B295" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="C295" t="s" s="2">
         <v>652</v>
-      </c>
-      <c r="C295" t="s" s="2">
-        <v>653</v>
       </c>
       <c r="D295" s="2"/>
     </row>
     <row r="296">
       <c r="A296" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B296" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="C296" t="s" s="2">
         <v>654</v>
-      </c>
-      <c r="C296" t="s" s="2">
-        <v>655</v>
       </c>
       <c r="D296" s="2"/>
     </row>
     <row r="297">
       <c r="A297" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B297" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="C297" t="s" s="2">
         <v>656</v>
-      </c>
-      <c r="C297" t="s" s="2">
-        <v>657</v>
       </c>
       <c r="D297" s="2"/>
     </row>
     <row r="298">
       <c r="A298" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B298" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="C298" t="s" s="2">
         <v>658</v>
-      </c>
-      <c r="C298" t="s" s="2">
-        <v>659</v>
       </c>
       <c r="D298" s="2"/>
     </row>
     <row r="299">
       <c r="A299" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B299" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="C299" t="s" s="2">
         <v>660</v>
-      </c>
-      <c r="C299" t="s" s="2">
-        <v>661</v>
       </c>
       <c r="D299" s="2"/>
     </row>
     <row r="300">
       <c r="A300" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B300" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="C300" t="s" s="2">
         <v>662</v>
-      </c>
-      <c r="C300" t="s" s="2">
-        <v>663</v>
       </c>
       <c r="D300" s="2"/>
     </row>
     <row r="301">
       <c r="A301" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B301" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="C301" t="s" s="2">
         <v>664</v>
-      </c>
-      <c r="C301" t="s" s="2">
-        <v>665</v>
       </c>
       <c r="D301" s="2"/>
     </row>
     <row r="302">
       <c r="A302" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B302" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="C302" t="s" s="2">
         <v>666</v>
-      </c>
-      <c r="C302" t="s" s="2">
-        <v>667</v>
       </c>
       <c r="D302" s="2"/>
     </row>
     <row r="303">
       <c r="A303" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B303" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="C303" t="s" s="2">
         <v>668</v>
-      </c>
-      <c r="C303" t="s" s="2">
-        <v>669</v>
       </c>
       <c r="D303" s="2"/>
     </row>
     <row r="304">
       <c r="A304" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B304" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="C304" t="s" s="2">
         <v>670</v>
-      </c>
-      <c r="C304" t="s" s="2">
-        <v>671</v>
       </c>
       <c r="D304" s="2"/>
     </row>
     <row r="305">
       <c r="A305" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B305" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="C305" t="s" s="2">
         <v>672</v>
-      </c>
-      <c r="C305" t="s" s="2">
-        <v>673</v>
       </c>
       <c r="D305" s="2"/>
     </row>
     <row r="306">
       <c r="A306" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B306" t="s" s="2">
+        <v>673</v>
+      </c>
+      <c r="C306" t="s" s="2">
         <v>674</v>
-      </c>
-      <c r="C306" t="s" s="2">
-        <v>675</v>
       </c>
       <c r="D306" s="2"/>
     </row>
     <row r="307">
       <c r="A307" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B307" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="C307" t="s" s="2">
         <v>676</v>
-      </c>
-      <c r="C307" t="s" s="2">
-        <v>677</v>
       </c>
       <c r="D307" s="2"/>
     </row>
     <row r="308">
       <c r="A308" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B308" t="s" s="2">
+        <v>677</v>
+      </c>
+      <c r="C308" t="s" s="2">
         <v>678</v>
-      </c>
-      <c r="C308" t="s" s="2">
-        <v>679</v>
       </c>
       <c r="D308" s="2"/>
     </row>
     <row r="309">
       <c r="A309" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B309" t="s" s="2">
+        <v>679</v>
+      </c>
+      <c r="C309" t="s" s="2">
         <v>680</v>
-      </c>
-      <c r="C309" t="s" s="2">
-        <v>681</v>
       </c>
       <c r="D309" s="2"/>
     </row>
     <row r="310">
       <c r="A310" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B310" t="s" s="2">
+        <v>681</v>
+      </c>
+      <c r="C310" t="s" s="2">
         <v>682</v>
-      </c>
-      <c r="C310" t="s" s="2">
-        <v>683</v>
       </c>
       <c r="D310" s="2"/>
     </row>
     <row r="311">
       <c r="A311" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B311" t="s" s="2">
+        <v>683</v>
+      </c>
+      <c r="C311" t="s" s="2">
         <v>684</v>
-      </c>
-      <c r="C311" t="s" s="2">
-        <v>685</v>
       </c>
       <c r="D311" s="2"/>
     </row>
     <row r="312">
       <c r="A312" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B312" t="s" s="2">
+        <v>685</v>
+      </c>
+      <c r="C312" t="s" s="2">
         <v>686</v>
-      </c>
-      <c r="C312" t="s" s="2">
-        <v>687</v>
       </c>
       <c r="D312" s="2"/>
     </row>
     <row r="313">
       <c r="A313" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B313" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="C313" t="s" s="2">
         <v>688</v>
-      </c>
-      <c r="C313" t="s" s="2">
-        <v>689</v>
       </c>
       <c r="D313" s="2"/>
     </row>
     <row r="314">
       <c r="A314" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B314" t="s" s="2">
+        <v>689</v>
+      </c>
+      <c r="C314" t="s" s="2">
         <v>690</v>
-      </c>
-      <c r="C314" t="s" s="2">
-        <v>691</v>
       </c>
       <c r="D314" s="2"/>
     </row>
     <row r="315">
       <c r="A315" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B315" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="C315" t="s" s="2">
         <v>692</v>
-      </c>
-      <c r="C315" t="s" s="2">
-        <v>693</v>
       </c>
       <c r="D315" s="2"/>
     </row>
     <row r="316">
       <c r="A316" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B316" t="s" s="2">
+        <v>693</v>
+      </c>
+      <c r="C316" t="s" s="2">
         <v>694</v>
-      </c>
-      <c r="C316" t="s" s="2">
-        <v>695</v>
       </c>
       <c r="D316" s="2"/>
     </row>
     <row r="317">
       <c r="A317" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B317" t="s" s="2">
+        <v>695</v>
+      </c>
+      <c r="C317" t="s" s="2">
         <v>696</v>
-      </c>
-      <c r="C317" t="s" s="2">
-        <v>697</v>
       </c>
       <c r="D317" s="2"/>
     </row>
     <row r="318">
       <c r="A318" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B318" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="C318" t="s" s="2">
         <v>698</v>
-      </c>
-      <c r="C318" t="s" s="2">
-        <v>699</v>
       </c>
       <c r="D318" s="2"/>
     </row>
     <row r="319">
       <c r="A319" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B319" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="C319" t="s" s="2">
         <v>700</v>
-      </c>
-      <c r="C319" t="s" s="2">
-        <v>701</v>
       </c>
       <c r="D319" s="2"/>
     </row>
     <row r="320">
       <c r="A320" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B320" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="C320" t="s" s="2">
         <v>702</v>
-      </c>
-      <c r="C320" t="s" s="2">
-        <v>703</v>
       </c>
       <c r="D320" s="2"/>
     </row>
     <row r="321">
       <c r="A321" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B321" t="s" s="2">
+        <v>703</v>
+      </c>
+      <c r="C321" t="s" s="2">
         <v>704</v>
-      </c>
-      <c r="C321" t="s" s="2">
-        <v>705</v>
       </c>
       <c r="D321" s="2"/>
     </row>
     <row r="322">
       <c r="A322" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B322" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="C322" t="s" s="2">
         <v>706</v>
-      </c>
-      <c r="C322" t="s" s="2">
-        <v>707</v>
       </c>
       <c r="D322" s="2"/>
     </row>
     <row r="323">
       <c r="A323" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B323" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="C323" t="s" s="2">
         <v>708</v>
-      </c>
-      <c r="C323" t="s" s="2">
-        <v>709</v>
       </c>
       <c r="D323" s="2"/>
     </row>
     <row r="324">
       <c r="A324" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B324" t="s" s="2">
+        <v>709</v>
+      </c>
+      <c r="C324" t="s" s="2">
         <v>710</v>
-      </c>
-      <c r="C324" t="s" s="2">
-        <v>711</v>
       </c>
       <c r="D324" s="2"/>
     </row>
     <row r="325">
       <c r="A325" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B325" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="C325" t="s" s="2">
         <v>712</v>
-      </c>
-      <c r="C325" t="s" s="2">
-        <v>713</v>
       </c>
       <c r="D325" s="2"/>
     </row>
     <row r="326">
       <c r="A326" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B326" t="s" s="2">
+        <v>713</v>
+      </c>
+      <c r="C326" t="s" s="2">
         <v>714</v>
-      </c>
-      <c r="C326" t="s" s="2">
-        <v>715</v>
       </c>
       <c r="D326" s="2"/>
     </row>
     <row r="327">
       <c r="A327" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B327" t="s" s="2">
+        <v>715</v>
+      </c>
+      <c r="C327" t="s" s="2">
         <v>716</v>
-      </c>
-      <c r="C327" t="s" s="2">
-        <v>717</v>
       </c>
       <c r="D327" s="2"/>
     </row>
     <row r="328">
       <c r="A328" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B328" t="s" s="2">
+        <v>717</v>
+      </c>
+      <c r="C328" t="s" s="2">
         <v>718</v>
-      </c>
-      <c r="C328" t="s" s="2">
-        <v>719</v>
       </c>
       <c r="D328" s="2"/>
     </row>
     <row r="329">
       <c r="A329" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B329" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="C329" t="s" s="2">
         <v>720</v>
-      </c>
-      <c r="C329" t="s" s="2">
-        <v>721</v>
       </c>
       <c r="D329" s="2"/>
     </row>
     <row r="330">
       <c r="A330" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B330" t="s" s="2">
+        <v>721</v>
+      </c>
+      <c r="C330" t="s" s="2">
         <v>722</v>
-      </c>
-      <c r="C330" t="s" s="2">
-        <v>723</v>
       </c>
       <c r="D330" s="2"/>
     </row>
     <row r="331">
       <c r="A331" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B331" t="s" s="2">
+        <v>723</v>
+      </c>
+      <c r="C331" t="s" s="2">
         <v>724</v>
-      </c>
-      <c r="C331" t="s" s="2">
-        <v>725</v>
       </c>
       <c r="D331" s="2"/>
     </row>
     <row r="332">
       <c r="A332" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B332" t="s" s="2">
+        <v>725</v>
+      </c>
+      <c r="C332" t="s" s="2">
         <v>726</v>
-      </c>
-      <c r="C332" t="s" s="2">
-        <v>727</v>
       </c>
       <c r="D332" s="2"/>
     </row>
     <row r="333">
       <c r="A333" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B333" t="s" s="2">
+        <v>727</v>
+      </c>
+      <c r="C333" t="s" s="2">
         <v>728</v>
-      </c>
-      <c r="C333" t="s" s="2">
-        <v>729</v>
       </c>
       <c r="D333" s="2"/>
     </row>
     <row r="334">
       <c r="A334" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B334" t="s" s="2">
+        <v>729</v>
+      </c>
+      <c r="C334" t="s" s="2">
         <v>730</v>
-      </c>
-      <c r="C334" t="s" s="2">
-        <v>731</v>
       </c>
       <c r="D334" s="2"/>
     </row>
     <row r="335">
       <c r="A335" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B335" t="s" s="2">
+        <v>731</v>
+      </c>
+      <c r="C335" t="s" s="2">
         <v>732</v>
-      </c>
-      <c r="C335" t="s" s="2">
-        <v>733</v>
       </c>
       <c r="D335" s="2"/>
     </row>
     <row r="336">
       <c r="A336" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B336" t="s" s="2">
+        <v>733</v>
+      </c>
+      <c r="C336" t="s" s="2">
         <v>734</v>
-      </c>
-      <c r="C336" t="s" s="2">
-        <v>735</v>
       </c>
       <c r="D336" s="2"/>
     </row>
     <row r="337">
       <c r="A337" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B337" t="s" s="2">
+        <v>735</v>
+      </c>
+      <c r="C337" t="s" s="2">
         <v>736</v>
-      </c>
-      <c r="C337" t="s" s="2">
-        <v>737</v>
       </c>
       <c r="D337" s="2"/>
     </row>
     <row r="338">
       <c r="A338" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B338" t="s" s="2">
+        <v>737</v>
+      </c>
+      <c r="C338" t="s" s="2">
         <v>738</v>
-      </c>
-      <c r="C338" t="s" s="2">
-        <v>739</v>
       </c>
       <c r="D338" s="2"/>
     </row>
     <row r="339">
       <c r="A339" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B339" t="s" s="2">
+        <v>739</v>
+      </c>
+      <c r="C339" t="s" s="2">
         <v>740</v>
-      </c>
-      <c r="C339" t="s" s="2">
-        <v>741</v>
       </c>
       <c r="D339" s="2"/>
     </row>
     <row r="340">
       <c r="A340" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B340" t="s" s="2">
+        <v>741</v>
+      </c>
+      <c r="C340" t="s" s="2">
         <v>742</v>
-      </c>
-      <c r="C340" t="s" s="2">
-        <v>743</v>
       </c>
       <c r="D340" s="2"/>
     </row>
     <row r="341">
       <c r="A341" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B341" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C341" t="s" s="2">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="D341" s="2"/>
     </row>
     <row r="342">
       <c r="A342" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B342" t="s" s="2">
+        <v>744</v>
+      </c>
+      <c r="C342" t="s" s="2">
         <v>745</v>
-      </c>
-      <c r="C342" t="s" s="2">
-        <v>746</v>
       </c>
       <c r="D342" s="2"/>
     </row>
     <row r="343">
       <c r="A343" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B343" t="s" s="2">
+        <v>746</v>
+      </c>
+      <c r="C343" t="s" s="2">
         <v>747</v>
-      </c>
-      <c r="C343" t="s" s="2">
-        <v>748</v>
       </c>
       <c r="D343" s="2"/>
     </row>
     <row r="344">
       <c r="A344" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B344" t="s" s="2">
+        <v>748</v>
+      </c>
+      <c r="C344" t="s" s="2">
         <v>749</v>
-      </c>
-      <c r="C344" t="s" s="2">
-        <v>750</v>
       </c>
       <c r="D344" s="2"/>
     </row>
     <row r="345">
       <c r="A345" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B345" t="s" s="2">
+        <v>750</v>
+      </c>
+      <c r="C345" t="s" s="2">
         <v>751</v>
-      </c>
-      <c r="C345" t="s" s="2">
-        <v>752</v>
       </c>
       <c r="D345" s="2"/>
     </row>
     <row r="346">
       <c r="A346" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B346" t="s" s="2">
+        <v>752</v>
+      </c>
+      <c r="C346" t="s" s="2">
         <v>753</v>
-      </c>
-      <c r="C346" t="s" s="2">
-        <v>754</v>
       </c>
       <c r="D346" s="2"/>
     </row>
     <row r="347">
       <c r="A347" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B347" t="s" s="2">
+        <v>754</v>
+      </c>
+      <c r="C347" t="s" s="2">
         <v>755</v>
-      </c>
-      <c r="C347" t="s" s="2">
-        <v>756</v>
       </c>
       <c r="D347" s="2"/>
     </row>
     <row r="348">
       <c r="A348" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B348" t="s" s="2">
+        <v>756</v>
+      </c>
+      <c r="C348" t="s" s="2">
         <v>757</v>
-      </c>
-      <c r="C348" t="s" s="2">
-        <v>758</v>
       </c>
       <c r="D348" s="2"/>
     </row>
     <row r="349">
       <c r="A349" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B349" t="s" s="2">
+        <v>758</v>
+      </c>
+      <c r="C349" t="s" s="2">
         <v>759</v>
-      </c>
-      <c r="C349" t="s" s="2">
-        <v>760</v>
       </c>
       <c r="D349" s="2"/>
     </row>
     <row r="350">
       <c r="A350" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B350" t="s" s="2">
+        <v>760</v>
+      </c>
+      <c r="C350" t="s" s="2">
         <v>761</v>
-      </c>
-      <c r="C350" t="s" s="2">
-        <v>762</v>
       </c>
       <c r="D350" s="2"/>
     </row>
     <row r="351">
       <c r="A351" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B351" t="s" s="2">
+        <v>762</v>
+      </c>
+      <c r="C351" t="s" s="2">
         <v>763</v>
-      </c>
-      <c r="C351" t="s" s="2">
-        <v>764</v>
       </c>
       <c r="D351" s="2"/>
     </row>
     <row r="352">
       <c r="A352" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B352" t="s" s="2">
+        <v>764</v>
+      </c>
+      <c r="C352" t="s" s="2">
         <v>765</v>
-      </c>
-      <c r="C352" t="s" s="2">
-        <v>766</v>
       </c>
       <c r="D352" s="2"/>
     </row>
     <row r="353">
       <c r="A353" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B353" t="s" s="2">
+        <v>766</v>
+      </c>
+      <c r="C353" t="s" s="2">
         <v>767</v>
-      </c>
-      <c r="C353" t="s" s="2">
-        <v>768</v>
       </c>
       <c r="D353" s="2"/>
     </row>
     <row r="354">
       <c r="A354" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B354" t="s" s="2">
+        <v>768</v>
+      </c>
+      <c r="C354" t="s" s="2">
         <v>769</v>
-      </c>
-      <c r="C354" t="s" s="2">
-        <v>770</v>
       </c>
       <c r="D354" s="2"/>
     </row>
     <row r="355">
       <c r="A355" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B355" t="s" s="2">
+        <v>770</v>
+      </c>
+      <c r="C355" t="s" s="2">
         <v>771</v>
-      </c>
-      <c r="C355" t="s" s="2">
-        <v>772</v>
       </c>
       <c r="D355" s="2"/>
     </row>
     <row r="356">
       <c r="A356" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B356" t="s" s="2">
+        <v>772</v>
+      </c>
+      <c r="C356" t="s" s="2">
         <v>773</v>
-      </c>
-      <c r="C356" t="s" s="2">
-        <v>774</v>
       </c>
       <c r="D356" s="2"/>
     </row>
     <row r="357">
       <c r="A357" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B357" t="s" s="2">
+        <v>774</v>
+      </c>
+      <c r="C357" t="s" s="2">
         <v>775</v>
-      </c>
-      <c r="C357" t="s" s="2">
-        <v>776</v>
       </c>
       <c r="D357" s="2"/>
     </row>
     <row r="358">
       <c r="A358" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B358" t="s" s="2">
+        <v>776</v>
+      </c>
+      <c r="C358" t="s" s="2">
         <v>777</v>
-      </c>
-      <c r="C358" t="s" s="2">
-        <v>778</v>
       </c>
       <c r="D358" s="2"/>
     </row>
     <row r="359">
       <c r="A359" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B359" t="s" s="2">
+        <v>778</v>
+      </c>
+      <c r="C359" t="s" s="2">
         <v>779</v>
-      </c>
-      <c r="C359" t="s" s="2">
-        <v>780</v>
       </c>
       <c r="D359" s="2"/>
     </row>
     <row r="360">
       <c r="A360" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B360" t="s" s="2">
+        <v>780</v>
+      </c>
+      <c r="C360" t="s" s="2">
         <v>781</v>
-      </c>
-      <c r="C360" t="s" s="2">
-        <v>782</v>
       </c>
       <c r="D360" s="2"/>
     </row>
     <row r="361">
       <c r="A361" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B361" t="s" s="2">
+        <v>782</v>
+      </c>
+      <c r="C361" t="s" s="2">
         <v>783</v>
-      </c>
-      <c r="C361" t="s" s="2">
-        <v>784</v>
       </c>
       <c r="D361" s="2"/>
     </row>
     <row r="362">
       <c r="A362" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B362" t="s" s="2">
+        <v>784</v>
+      </c>
+      <c r="C362" t="s" s="2">
         <v>785</v>
-      </c>
-      <c r="C362" t="s" s="2">
-        <v>786</v>
       </c>
       <c r="D362" s="2"/>
     </row>
     <row r="363">
       <c r="A363" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B363" t="s" s="2">
+        <v>786</v>
+      </c>
+      <c r="C363" t="s" s="2">
         <v>787</v>
-      </c>
-      <c r="C363" t="s" s="2">
-        <v>788</v>
       </c>
       <c r="D363" s="2"/>
     </row>
     <row r="364">
       <c r="A364" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B364" t="s" s="2">
+        <v>788</v>
+      </c>
+      <c r="C364" t="s" s="2">
         <v>789</v>
-      </c>
-      <c r="C364" t="s" s="2">
-        <v>790</v>
       </c>
       <c r="D364" s="2"/>
     </row>
     <row r="365">
       <c r="A365" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B365" t="s" s="2">
+        <v>790</v>
+      </c>
+      <c r="C365" t="s" s="2">
         <v>791</v>
-      </c>
-      <c r="C365" t="s" s="2">
-        <v>792</v>
       </c>
       <c r="D365" s="2"/>
     </row>
     <row r="366">
       <c r="A366" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B366" t="s" s="2">
+        <v>792</v>
+      </c>
+      <c r="C366" t="s" s="2">
         <v>793</v>
-      </c>
-      <c r="C366" t="s" s="2">
-        <v>794</v>
       </c>
       <c r="D366" s="2"/>
     </row>
     <row r="367">
       <c r="A367" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B367" t="s" s="2">
+        <v>794</v>
+      </c>
+      <c r="C367" t="s" s="2">
         <v>795</v>
-      </c>
-      <c r="C367" t="s" s="2">
-        <v>796</v>
       </c>
       <c r="D367" s="2"/>
     </row>
     <row r="368">
       <c r="A368" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B368" t="s" s="2">
+        <v>796</v>
+      </c>
+      <c r="C368" t="s" s="2">
         <v>797</v>
-      </c>
-      <c r="C368" t="s" s="2">
-        <v>798</v>
       </c>
       <c r="D368" s="2"/>
     </row>
     <row r="369">
       <c r="A369" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B369" t="s" s="2">
+        <v>798</v>
+      </c>
+      <c r="C369" t="s" s="2">
         <v>799</v>
-      </c>
-      <c r="C369" t="s" s="2">
-        <v>800</v>
       </c>
       <c r="D369" s="2"/>
     </row>
     <row r="370">
       <c r="A370" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B370" t="s" s="2">
+        <v>800</v>
+      </c>
+      <c r="C370" t="s" s="2">
         <v>801</v>
-      </c>
-      <c r="C370" t="s" s="2">
-        <v>802</v>
       </c>
       <c r="D370" s="2"/>
     </row>
     <row r="371">
       <c r="A371" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B371" t="s" s="2">
+        <v>802</v>
+      </c>
+      <c r="C371" t="s" s="2">
         <v>803</v>
-      </c>
-      <c r="C371" t="s" s="2">
-        <v>804</v>
       </c>
       <c r="D371" s="2"/>
     </row>
     <row r="372">
       <c r="A372" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B372" t="s" s="2">
+        <v>804</v>
+      </c>
+      <c r="C372" t="s" s="2">
         <v>805</v>
-      </c>
-      <c r="C372" t="s" s="2">
-        <v>806</v>
       </c>
       <c r="D372" s="2"/>
     </row>
     <row r="373">
       <c r="A373" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B373" t="s" s="2">
+        <v>806</v>
+      </c>
+      <c r="C373" t="s" s="2">
         <v>807</v>
-      </c>
-      <c r="C373" t="s" s="2">
-        <v>808</v>
       </c>
       <c r="D373" s="2"/>
     </row>
     <row r="374">
       <c r="A374" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B374" t="s" s="2">
+        <v>808</v>
+      </c>
+      <c r="C374" t="s" s="2">
         <v>809</v>
-      </c>
-      <c r="C374" t="s" s="2">
-        <v>810</v>
       </c>
       <c r="D374" s="2"/>
     </row>
     <row r="375">
       <c r="A375" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B375" t="s" s="2">
+        <v>810</v>
+      </c>
+      <c r="C375" t="s" s="2">
         <v>811</v>
-      </c>
-      <c r="C375" t="s" s="2">
-        <v>812</v>
       </c>
       <c r="D375" s="2"/>
     </row>
     <row r="376">
       <c r="A376" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B376" t="s" s="2">
+        <v>812</v>
+      </c>
+      <c r="C376" t="s" s="2">
         <v>813</v>
-      </c>
-      <c r="C376" t="s" s="2">
-        <v>814</v>
       </c>
       <c r="D376" s="2"/>
     </row>
     <row r="377">
       <c r="A377" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B377" t="s" s="2">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="C377" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D377" s="2"/>
     </row>
     <row r="378">
       <c r="A378" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B378" t="s" s="2">
+        <v>815</v>
+      </c>
+      <c r="C378" t="s" s="2">
         <v>816</v>
-      </c>
-      <c r="C378" t="s" s="2">
-        <v>817</v>
       </c>
       <c r="D378" s="2"/>
     </row>
     <row r="379">
       <c r="A379" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B379" t="s" s="2">
+        <v>817</v>
+      </c>
+      <c r="C379" t="s" s="2">
         <v>818</v>
       </c>
-      <c r="C379" t="s" s="2">
+      <c r="D379" t="s" s="2">
         <v>819</v>
-      </c>
-      <c r="D379" t="s" s="2">
-        <v>820</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B380" t="s" s="2">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="C380" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D380" s="2"/>
     </row>
     <row r="381">
       <c r="A381" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B381" t="s" s="2">
+        <v>821</v>
+      </c>
+      <c r="C381" t="s" s="2">
         <v>822</v>
-      </c>
-      <c r="C381" t="s" s="2">
-        <v>823</v>
       </c>
       <c r="D381" s="2"/>
     </row>
     <row r="382">
       <c r="A382" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B382" t="s" s="2">
+        <v>823</v>
+      </c>
+      <c r="C382" t="s" s="2">
         <v>824</v>
-      </c>
-      <c r="C382" t="s" s="2">
-        <v>825</v>
       </c>
       <c r="D382" s="2"/>
     </row>
     <row r="383">
       <c r="A383" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B383" t="s" s="2">
+        <v>825</v>
+      </c>
+      <c r="C383" t="s" s="2">
         <v>826</v>
-      </c>
-      <c r="C383" t="s" s="2">
-        <v>827</v>
       </c>
       <c r="D383" s="2"/>
     </row>
     <row r="384">
       <c r="A384" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B384" t="s" s="2">
+        <v>827</v>
+      </c>
+      <c r="C384" t="s" s="2">
         <v>828</v>
-      </c>
-      <c r="C384" t="s" s="2">
-        <v>829</v>
       </c>
       <c r="D384" s="2"/>
     </row>
     <row r="385">
       <c r="A385" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B385" t="s" s="2">
+        <v>829</v>
+      </c>
+      <c r="C385" t="s" s="2">
         <v>830</v>
-      </c>
-      <c r="C385" t="s" s="2">
-        <v>831</v>
       </c>
       <c r="D385" s="2"/>
     </row>
     <row r="386">
       <c r="A386" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B386" t="s" s="2">
+        <v>831</v>
+      </c>
+      <c r="C386" t="s" s="2">
         <v>832</v>
-      </c>
-      <c r="C386" t="s" s="2">
-        <v>833</v>
       </c>
       <c r="D386" s="2"/>
     </row>
     <row r="387">
       <c r="A387" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B387" t="s" s="2">
+        <v>833</v>
+      </c>
+      <c r="C387" t="s" s="2">
         <v>834</v>
-      </c>
-      <c r="C387" t="s" s="2">
-        <v>835</v>
       </c>
       <c r="D387" s="2"/>
     </row>
     <row r="388">
       <c r="A388" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B388" t="s" s="2">
+        <v>835</v>
+      </c>
+      <c r="C388" t="s" s="2">
         <v>836</v>
-      </c>
-      <c r="C388" t="s" s="2">
-        <v>837</v>
       </c>
       <c r="D388" s="2"/>
     </row>
     <row r="389">
       <c r="A389" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B389" t="s" s="2">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C389" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D389" s="2"/>
     </row>
     <row r="390">
       <c r="A390" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B390" t="s" s="2">
+        <v>838</v>
+      </c>
+      <c r="C390" t="s" s="2">
         <v>839</v>
-      </c>
-      <c r="C390" t="s" s="2">
-        <v>840</v>
       </c>
       <c r="D390" s="2"/>
     </row>
     <row r="391">
       <c r="A391" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B391" t="s" s="2">
+        <v>840</v>
+      </c>
+      <c r="C391" t="s" s="2">
         <v>841</v>
-      </c>
-      <c r="C391" t="s" s="2">
-        <v>842</v>
       </c>
       <c r="D391" s="2"/>
     </row>
     <row r="392">
       <c r="A392" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B392" t="s" s="2">
+        <v>842</v>
+      </c>
+      <c r="C392" t="s" s="2">
         <v>843</v>
-      </c>
-      <c r="C392" t="s" s="2">
-        <v>844</v>
       </c>
       <c r="D392" s="2"/>
     </row>
     <row r="393">
       <c r="A393" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B393" t="s" s="2">
+        <v>844</v>
+      </c>
+      <c r="C393" t="s" s="2">
         <v>845</v>
-      </c>
-      <c r="C393" t="s" s="2">
-        <v>846</v>
       </c>
       <c r="D393" s="2"/>
     </row>
     <row r="394">
       <c r="A394" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B394" t="s" s="2">
+        <v>846</v>
+      </c>
+      <c r="C394" t="s" s="2">
         <v>847</v>
-      </c>
-      <c r="C394" t="s" s="2">
-        <v>848</v>
       </c>
       <c r="D394" s="2"/>
     </row>
     <row r="395">
       <c r="A395" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B395" t="s" s="2">
+        <v>848</v>
+      </c>
+      <c r="C395" t="s" s="2">
         <v>849</v>
-      </c>
-      <c r="C395" t="s" s="2">
-        <v>850</v>
       </c>
       <c r="D395" s="2"/>
     </row>
     <row r="396">
       <c r="A396" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B396" t="s" s="2">
+        <v>850</v>
+      </c>
+      <c r="C396" t="s" s="2">
         <v>851</v>
-      </c>
-      <c r="C396" t="s" s="2">
-        <v>852</v>
       </c>
       <c r="D396" s="2"/>
     </row>
     <row r="397">
       <c r="A397" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B397" t="s" s="2">
+        <v>852</v>
+      </c>
+      <c r="C397" t="s" s="2">
         <v>853</v>
-      </c>
-      <c r="C397" t="s" s="2">
-        <v>854</v>
       </c>
       <c r="D397" s="2"/>
     </row>
     <row r="398">
       <c r="A398" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B398" t="s" s="2">
+        <v>854</v>
+      </c>
+      <c r="C398" t="s" s="2">
         <v>855</v>
-      </c>
-      <c r="C398" t="s" s="2">
-        <v>856</v>
       </c>
       <c r="D398" s="2"/>
     </row>
     <row r="399">
       <c r="A399" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B399" t="s" s="2">
+        <v>856</v>
+      </c>
+      <c r="C399" t="s" s="2">
         <v>857</v>
-      </c>
-      <c r="C399" t="s" s="2">
-        <v>858</v>
       </c>
       <c r="D399" s="2"/>
     </row>
     <row r="400">
       <c r="A400" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B400" t="s" s="2">
+        <v>858</v>
+      </c>
+      <c r="C400" t="s" s="2">
         <v>859</v>
-      </c>
-      <c r="C400" t="s" s="2">
-        <v>860</v>
       </c>
       <c r="D400" s="2"/>
     </row>
     <row r="401">
       <c r="A401" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B401" t="s" s="2">
+        <v>860</v>
+      </c>
+      <c r="C401" t="s" s="2">
         <v>861</v>
-      </c>
-      <c r="C401" t="s" s="2">
-        <v>862</v>
       </c>
       <c r="D401" s="2"/>
     </row>
     <row r="402">
       <c r="A402" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B402" t="s" s="2">
+        <v>862</v>
+      </c>
+      <c r="C402" t="s" s="2">
         <v>863</v>
-      </c>
-      <c r="C402" t="s" s="2">
-        <v>864</v>
       </c>
       <c r="D402" s="2"/>
     </row>
     <row r="403">
       <c r="A403" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B403" t="s" s="2">
+        <v>864</v>
+      </c>
+      <c r="C403" t="s" s="2">
         <v>865</v>
-      </c>
-      <c r="C403" t="s" s="2">
-        <v>866</v>
       </c>
       <c r="D403" s="2"/>
     </row>
     <row r="404">
       <c r="A404" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B404" t="s" s="2">
+        <v>866</v>
+      </c>
+      <c r="C404" t="s" s="2">
         <v>867</v>
-      </c>
-      <c r="C404" t="s" s="2">
-        <v>868</v>
       </c>
       <c r="D404" s="2"/>
     </row>
     <row r="405">
       <c r="A405" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B405" t="s" s="2">
+        <v>868</v>
+      </c>
+      <c r="C405" t="s" s="2">
         <v>869</v>
-      </c>
-      <c r="C405" t="s" s="2">
-        <v>870</v>
       </c>
       <c r="D405" s="2"/>
     </row>
     <row r="406">
       <c r="A406" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B406" t="s" s="2">
+        <v>870</v>
+      </c>
+      <c r="C406" t="s" s="2">
         <v>871</v>
-      </c>
-      <c r="C406" t="s" s="2">
-        <v>872</v>
       </c>
       <c r="D406" s="2"/>
     </row>
     <row r="407">
       <c r="A407" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B407" t="s" s="2">
+        <v>872</v>
+      </c>
+      <c r="C407" t="s" s="2">
         <v>873</v>
-      </c>
-      <c r="C407" t="s" s="2">
-        <v>874</v>
       </c>
       <c r="D407" s="2"/>
     </row>
     <row r="408">
       <c r="A408" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B408" t="s" s="2">
+        <v>874</v>
+      </c>
+      <c r="C408" t="s" s="2">
         <v>875</v>
-      </c>
-      <c r="C408" t="s" s="2">
-        <v>876</v>
       </c>
       <c r="D408" s="2"/>
     </row>
     <row r="409">
       <c r="A409" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B409" t="s" s="2">
+        <v>876</v>
+      </c>
+      <c r="C409" t="s" s="2">
         <v>877</v>
-      </c>
-      <c r="C409" t="s" s="2">
-        <v>878</v>
       </c>
       <c r="D409" s="2"/>
     </row>
     <row r="410">
       <c r="A410" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B410" t="s" s="2">
+        <v>878</v>
+      </c>
+      <c r="C410" t="s" s="2">
         <v>879</v>
-      </c>
-      <c r="C410" t="s" s="2">
-        <v>880</v>
       </c>
       <c r="D410" s="2"/>
     </row>
     <row r="411">
       <c r="A411" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B411" t="s" s="2">
+        <v>880</v>
+      </c>
+      <c r="C411" t="s" s="2">
         <v>881</v>
-      </c>
-      <c r="C411" t="s" s="2">
-        <v>882</v>
       </c>
       <c r="D411" s="2"/>
     </row>
     <row r="412">
       <c r="A412" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B412" t="s" s="2">
+        <v>882</v>
+      </c>
+      <c r="C412" t="s" s="2">
         <v>883</v>
-      </c>
-      <c r="C412" t="s" s="2">
-        <v>884</v>
       </c>
       <c r="D412" s="2"/>
     </row>
     <row r="413">
       <c r="A413" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B413" t="s" s="2">
+        <v>884</v>
+      </c>
+      <c r="C413" t="s" s="2">
         <v>885</v>
-      </c>
-      <c r="C413" t="s" s="2">
-        <v>886</v>
       </c>
       <c r="D413" s="2"/>
     </row>
     <row r="414">
       <c r="A414" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B414" t="s" s="2">
+        <v>886</v>
+      </c>
+      <c r="C414" t="s" s="2">
         <v>887</v>
-      </c>
-      <c r="C414" t="s" s="2">
-        <v>888</v>
       </c>
       <c r="D414" s="2"/>
     </row>
     <row r="415">
       <c r="A415" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B415" t="s" s="2">
+        <v>888</v>
+      </c>
+      <c r="C415" t="s" s="2">
         <v>889</v>
-      </c>
-      <c r="C415" t="s" s="2">
-        <v>890</v>
       </c>
       <c r="D415" s="2"/>
     </row>
     <row r="416">
       <c r="A416" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B416" t="s" s="2">
+        <v>890</v>
+      </c>
+      <c r="C416" t="s" s="2">
         <v>891</v>
-      </c>
-      <c r="C416" t="s" s="2">
-        <v>892</v>
       </c>
       <c r="D416" s="2"/>
     </row>
     <row r="417">
       <c r="A417" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B417" t="s" s="2">
+        <v>892</v>
+      </c>
+      <c r="C417" t="s" s="2">
         <v>893</v>
-      </c>
-      <c r="C417" t="s" s="2">
-        <v>894</v>
       </c>
       <c r="D417" s="2"/>
     </row>
     <row r="418">
       <c r="A418" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B418" t="s" s="2">
+        <v>894</v>
+      </c>
+      <c r="C418" t="s" s="2">
         <v>895</v>
-      </c>
-      <c r="C418" t="s" s="2">
-        <v>896</v>
       </c>
       <c r="D418" s="2"/>
     </row>
     <row r="419">
       <c r="A419" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B419" t="s" s="2">
+        <v>896</v>
+      </c>
+      <c r="C419" t="s" s="2">
         <v>897</v>
-      </c>
-      <c r="C419" t="s" s="2">
-        <v>898</v>
       </c>
       <c r="D419" s="2"/>
     </row>
     <row r="420">
       <c r="A420" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B420" t="s" s="2">
+        <v>898</v>
+      </c>
+      <c r="C420" t="s" s="2">
         <v>899</v>
-      </c>
-      <c r="C420" t="s" s="2">
-        <v>900</v>
       </c>
       <c r="D420" s="2"/>
     </row>
     <row r="421">
       <c r="A421" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B421" t="s" s="2">
+        <v>900</v>
+      </c>
+      <c r="C421" t="s" s="2">
         <v>901</v>
-      </c>
-      <c r="C421" t="s" s="2">
-        <v>902</v>
       </c>
       <c r="D421" s="2"/>
     </row>
     <row r="422">
       <c r="A422" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B422" t="s" s="2">
+        <v>902</v>
+      </c>
+      <c r="C422" t="s" s="2">
         <v>903</v>
-      </c>
-      <c r="C422" t="s" s="2">
-        <v>904</v>
       </c>
       <c r="D422" s="2"/>
     </row>
     <row r="423">
       <c r="A423" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B423" t="s" s="2">
+        <v>904</v>
+      </c>
+      <c r="C423" t="s" s="2">
         <v>905</v>
       </c>
-      <c r="C423" t="s" s="2">
+      <c r="D423" t="s" s="2">
         <v>906</v>
-      </c>
-      <c r="D423" t="s" s="2">
-        <v>907</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B424" t="s" s="2">
+        <v>907</v>
+      </c>
+      <c r="C424" t="s" s="2">
         <v>908</v>
       </c>
-      <c r="C424" t="s" s="2">
-        <v>909</v>
-      </c>
       <c r="D424" t="s" s="2">
-        <v>907</v>
+        <v>906</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B425" t="s" s="2">
+        <v>909</v>
+      </c>
+      <c r="C425" t="s" s="2">
         <v>910</v>
       </c>
-      <c r="C425" t="s" s="2">
-        <v>911</v>
-      </c>
       <c r="D425" t="s" s="2">
-        <v>907</v>
+        <v>906</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B426" t="s" s="2">
+        <v>911</v>
+      </c>
+      <c r="C426" t="s" s="2">
         <v>912</v>
-      </c>
-      <c r="C426" t="s" s="2">
-        <v>913</v>
       </c>
       <c r="D426" s="2"/>
     </row>

--- a/ig/DM_FINESS_New/CodeSystem-tre-r397-categorie-entite-geographique-exercice.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-tre-r397-categorie-entite-geographique-exercice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1363" uniqueCount="913">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1367" uniqueCount="916">
   <si>
     <t>Property</t>
   </si>
@@ -118,2139 +118,2139 @@
     <t>Count</t>
   </si>
   <si>
+    <t>426</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Uri</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>niveau</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#niveau</t>
+  </si>
+  <si>
+    <t>Permet d'indiquer le niveau hiérarchique du code</t>
+  </si>
+  <si>
+    <t>integer</t>
+  </si>
+  <si>
+    <t>parent</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/concept-properties#parent</t>
+  </si>
+  <si>
+    <t>An immediate parent of the concept in the hierarchy</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>domaine</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#domaine</t>
+  </si>
+  <si>
+    <t>Domaine de la categorie d etablissement</t>
+  </si>
+  <si>
+    <t>Coding</t>
+  </si>
+  <si>
+    <t>dateValid</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateValid</t>
+  </si>
+  <si>
+    <t>date de validité d'un code concept</t>
+  </si>
+  <si>
+    <t>dateTime</t>
+  </si>
+  <si>
+    <t>dateMaj</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateMaj</t>
+  </si>
+  <si>
+    <t>Date de mise à jour d'un code concept</t>
+  </si>
+  <si>
+    <t>dateFin</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateFin</t>
+  </si>
+  <si>
+    <t>Date de fin d'exploitation d'un code concept</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/concept-properties#status</t>
+  </si>
+  <si>
+    <t>A property that indicates the status of the concept.</t>
+  </si>
+  <si>
+    <t>deprecationDate</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/concept-properties#deprecationDate</t>
+  </si>
+  <si>
+    <t>Date Concept was deprecated</t>
+  </si>
+  <si>
+    <t>retirementDate</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/concept-properties#retirementDate</t>
+  </si>
+  <si>
+    <t>Date Concept was retired</t>
+  </si>
+  <si>
+    <t>specialisationRor</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#specialisationRor</t>
+  </si>
+  <si>
+    <t>Propriété permettant de spécifier les codes exclusifs appartenant au ROR</t>
+  </si>
+  <si>
+    <t>boolean</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>Display</t>
+  </si>
+  <si>
+    <t>Definition</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>0100</t>
+  </si>
+  <si>
+    <t>Etablissements d'administration</t>
+  </si>
+  <si>
+    <t>1000</t>
+  </si>
+  <si>
+    <t>Etablissements Relevant de la Loi Hospitalière</t>
+  </si>
+  <si>
+    <t>2000</t>
+  </si>
+  <si>
+    <t>Autres Etablissements de Soins et Prévention</t>
+  </si>
+  <si>
+    <t>3000</t>
+  </si>
+  <si>
+    <t>Autres Etablissements à Caractère Sanitaire</t>
+  </si>
+  <si>
+    <t>4000</t>
+  </si>
+  <si>
+    <t>Etab.Serv.Soc.d'Accueil Hébergement Assistance Réadaptation</t>
+  </si>
+  <si>
+    <t>5000</t>
+  </si>
+  <si>
+    <t>Etablissements et Services Sociaux d'Aide à la Famille</t>
+  </si>
+  <si>
+    <t>6000</t>
+  </si>
+  <si>
+    <t>Etab.de Formation des Personnels Sanitaires et Sociaux</t>
+  </si>
+  <si>
+    <t>0110</t>
+  </si>
+  <si>
+    <t>Etablissements d'Administration</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>1100</t>
+  </si>
+  <si>
+    <t>Etablissements Hospitaliers</t>
+  </si>
+  <si>
+    <t>1200</t>
+  </si>
+  <si>
+    <t>Autres Etablissements Relevant de la Loi Hospitalière</t>
+  </si>
+  <si>
+    <t>2100</t>
+  </si>
+  <si>
+    <t>Cabinets Libéraux</t>
+  </si>
+  <si>
+    <t>2200</t>
+  </si>
+  <si>
+    <t>3100</t>
+  </si>
+  <si>
+    <t>Laboratoires de Biologie Médicale</t>
+  </si>
+  <si>
+    <t>3200</t>
+  </si>
+  <si>
+    <t>Commerce de Biens à Usage Médicaux</t>
+  </si>
+  <si>
+    <t>3400</t>
+  </si>
+  <si>
+    <t>4100</t>
+  </si>
+  <si>
+    <t>Etab.et Serv.pour l'Enfance et la Jeunesse Handicapée</t>
+  </si>
+  <si>
+    <t>4200</t>
+  </si>
+  <si>
+    <t>Etablissements ou Classes d'Enseignement Spécial</t>
+  </si>
+  <si>
+    <t>4300</t>
+  </si>
+  <si>
+    <t>Etablissements et Services pour Adultes Handicapés</t>
+  </si>
+  <si>
+    <t>4400</t>
+  </si>
+  <si>
+    <t>Etablissements et Services pour Personnes Agées</t>
+  </si>
+  <si>
+    <t>4500</t>
+  </si>
+  <si>
+    <t>Etab.et Serv.Sociaux Concourant à la Protection de l'Enfance</t>
+  </si>
+  <si>
+    <t>4600</t>
+  </si>
+  <si>
+    <t>Autres Etab. Accueil, Hébergement, Réadaptation et Services</t>
+  </si>
+  <si>
+    <t>5100</t>
+  </si>
+  <si>
+    <t>6100</t>
+  </si>
+  <si>
+    <t>Etablissements de Formation des Personnels Sanitaires</t>
+  </si>
+  <si>
+    <t>6200</t>
+  </si>
+  <si>
+    <t>Etablissements de Formation des Personnels Sociaux</t>
+  </si>
+  <si>
+    <t>6300</t>
+  </si>
+  <si>
+    <t>Etablissements de Formation Polyvalente</t>
+  </si>
+  <si>
+    <t>0101</t>
+  </si>
+  <si>
+    <t>1101</t>
+  </si>
+  <si>
+    <t>Centres Hospitaliers Régionaux</t>
+  </si>
+  <si>
+    <t>1102</t>
+  </si>
+  <si>
+    <t>Centres Hospitaliers</t>
+  </si>
+  <si>
+    <t>1103</t>
+  </si>
+  <si>
+    <t>Centres Hospitaliers Spécialisés Lutte Maladies Mentales</t>
+  </si>
+  <si>
+    <t>1104</t>
+  </si>
+  <si>
+    <t>Centres de Lutte contre le Cancer</t>
+  </si>
+  <si>
+    <t>1106</t>
+  </si>
+  <si>
+    <t>Hôpitaux Locaux</t>
+  </si>
+  <si>
+    <t>1107</t>
+  </si>
+  <si>
+    <t>Etablissements de santé privé autorisés en SSR</t>
+  </si>
+  <si>
+    <t>1108</t>
+  </si>
+  <si>
+    <t>Centre de Moyen et de Long Séjour</t>
+  </si>
+  <si>
+    <t>1109</t>
+  </si>
+  <si>
+    <t>Etablissements de Soins de Longue Durée</t>
+  </si>
+  <si>
+    <t>1110</t>
+  </si>
+  <si>
+    <t>Etablissements de Soins de Courte Durée</t>
+  </si>
+  <si>
+    <t>1111</t>
+  </si>
+  <si>
+    <t>Autres Etablissements de Lutte contre les Maladies Mentales</t>
+  </si>
+  <si>
+    <t>1112</t>
+  </si>
+  <si>
+    <t>Etablissements d'Enfants à Caractère Sanitaire</t>
+  </si>
+  <si>
+    <t>1113</t>
+  </si>
+  <si>
+    <t>Etablissements de Lutte contre l'Alcoolisme</t>
+  </si>
+  <si>
+    <t>1201</t>
+  </si>
+  <si>
+    <t>Traitements et Soins à Domicile</t>
+  </si>
+  <si>
+    <t>1202</t>
+  </si>
+  <si>
+    <t>Santé Mentale</t>
+  </si>
+  <si>
+    <t>1203</t>
+  </si>
+  <si>
+    <t>Dialyse ambulatoire</t>
+  </si>
+  <si>
+    <t>1204</t>
+  </si>
+  <si>
+    <t>Urgence et Réanimation</t>
+  </si>
+  <si>
+    <t>1205</t>
+  </si>
+  <si>
+    <t>2101</t>
+  </si>
+  <si>
+    <t>Cabinets Libéraux de Médecins</t>
+  </si>
+  <si>
+    <t>2102</t>
+  </si>
+  <si>
+    <t>Cabinet de Groupe</t>
+  </si>
+  <si>
+    <t>2103</t>
+  </si>
+  <si>
+    <t>Autres structures d'exercice libéral</t>
+  </si>
+  <si>
+    <t>2105</t>
+  </si>
+  <si>
+    <t>Cabinet d'Auxiliaires Médicaux</t>
+  </si>
+  <si>
+    <t>2201</t>
+  </si>
+  <si>
+    <t>Dispensaires ou Centres de Soins</t>
+  </si>
+  <si>
+    <t>2202</t>
+  </si>
+  <si>
+    <t>Etablissements de PMI et de Planification Familiale</t>
+  </si>
+  <si>
+    <t>2203</t>
+  </si>
+  <si>
+    <t>Etablissements de Soins Dentaires</t>
+  </si>
+  <si>
+    <t>2204</t>
+  </si>
+  <si>
+    <t>Etablissements ne relevant pas de la Loi Hospitalière</t>
+  </si>
+  <si>
+    <t>2205</t>
+  </si>
+  <si>
+    <t>Etab.de soins relevant du service de santé des armées</t>
+  </si>
+  <si>
+    <t>2206</t>
+  </si>
+  <si>
+    <t>Centres de Santé</t>
+  </si>
+  <si>
+    <t>3101</t>
+  </si>
+  <si>
+    <t>3201</t>
+  </si>
+  <si>
+    <t>3202</t>
+  </si>
+  <si>
+    <t>Commerce de Biens Médicaux</t>
+  </si>
+  <si>
+    <t>3401</t>
+  </si>
+  <si>
+    <t>Transfusion Sanguine</t>
+  </si>
+  <si>
+    <t>3402</t>
+  </si>
+  <si>
+    <t>Conservation et Stockage d'autres Produits Humains</t>
+  </si>
+  <si>
+    <t>3403</t>
+  </si>
+  <si>
+    <t>Centre Antipoison</t>
+  </si>
+  <si>
+    <t>3404</t>
+  </si>
+  <si>
+    <t>Service d'Ambulances</t>
+  </si>
+  <si>
+    <t>3405</t>
+  </si>
+  <si>
+    <t>Installations autonomes de chirurgie esthétique</t>
+  </si>
+  <si>
+    <t>3406</t>
+  </si>
+  <si>
+    <t>Maisons de Naissance</t>
+  </si>
+  <si>
+    <t>3407</t>
+  </si>
+  <si>
+    <t>Etablissements Expérimentaux en Santé</t>
+  </si>
+  <si>
+    <t>3408</t>
+  </si>
+  <si>
+    <t>Centre de ressources transverse</t>
+  </si>
+  <si>
+    <t>3409</t>
+  </si>
+  <si>
+    <t>Services de Prévention et de Santé au Travail (SPST)</t>
+  </si>
+  <si>
+    <t>3410</t>
+  </si>
+  <si>
+    <t>Services d'incendie et de secours</t>
+  </si>
+  <si>
+    <t>4101</t>
+  </si>
+  <si>
+    <t>Etab.Educ.Spéciale pour Déficients Mentaux et Handicapés</t>
+  </si>
+  <si>
+    <t>4102</t>
+  </si>
+  <si>
+    <t>Etab.Educ Spéciale pour Enfants Trouble Conduite et Comport</t>
+  </si>
+  <si>
+    <t>4103</t>
+  </si>
+  <si>
+    <t>Etablissements d'Education Spéciale pour Handicapés Moteurs</t>
+  </si>
+  <si>
+    <t>4104</t>
+  </si>
+  <si>
+    <t>Etab.Education Spéciale pour Déficients Sensoriels</t>
+  </si>
+  <si>
+    <t>4105</t>
+  </si>
+  <si>
+    <t>Etablissements et Services Hébergement Enfants Handicapés</t>
+  </si>
+  <si>
+    <t>4106</t>
+  </si>
+  <si>
+    <t>Services à Domicile ou Ambulatoires pour Handicapés</t>
+  </si>
+  <si>
+    <t>4107</t>
+  </si>
+  <si>
+    <t>Etab. Expérimentaux en Faveur de l'Enfance Handicapée</t>
+  </si>
+  <si>
+    <t>4201</t>
+  </si>
+  <si>
+    <t>Etablissements ou Classes de Pré-Élémentaire et Élémentaire</t>
+  </si>
+  <si>
+    <t>4202</t>
+  </si>
+  <si>
+    <t>Etablissements d'Enseignement Secondaire</t>
+  </si>
+  <si>
+    <t>4301</t>
+  </si>
+  <si>
+    <t>Etab. et Services d'Hébergement pour Adultes Handicapés</t>
+  </si>
+  <si>
+    <t>4302</t>
+  </si>
+  <si>
+    <t>Etab.et Services de Travail Protégé pour Adultes Handicapés</t>
+  </si>
+  <si>
+    <t>4303</t>
+  </si>
+  <si>
+    <t>Etab.et Services de Réinsertion Prof pour Adultes Handicapés</t>
+  </si>
+  <si>
+    <t>4304</t>
+  </si>
+  <si>
+    <t>Etab.Expérimentaux en Faveur des Adultes Handicapés</t>
+  </si>
+  <si>
+    <t>4305</t>
+  </si>
+  <si>
+    <t>Services de Maintien à Domicile pour Handicapés</t>
+  </si>
+  <si>
+    <t>4401</t>
+  </si>
+  <si>
+    <t>Etablissements d'Hébergement pour Personnes Âgées</t>
+  </si>
+  <si>
+    <t>4402</t>
+  </si>
+  <si>
+    <t>Services de Maintien à Domicile pour Personnes Âgées</t>
+  </si>
+  <si>
+    <t>4403</t>
+  </si>
+  <si>
+    <t>Services Sociaux en Faveur des Personnes Âgées</t>
+  </si>
+  <si>
+    <t>4404</t>
+  </si>
+  <si>
+    <t>Etablissements Expérimentaux en Faveur des Personnes Âgées</t>
+  </si>
+  <si>
+    <t>4501</t>
+  </si>
+  <si>
+    <t>Etablissements de l'Aide Sociale à l'Enfance</t>
+  </si>
+  <si>
+    <t>4502</t>
+  </si>
+  <si>
+    <t>Etab.et Services du Ministère de la Justice pour Mineurs</t>
+  </si>
+  <si>
+    <t>4504</t>
+  </si>
+  <si>
+    <t>Services Concourant à la Protection de l'Enfance</t>
+  </si>
+  <si>
+    <t>4505</t>
+  </si>
+  <si>
+    <t>Etab. Expérimentaux en Faveur de l'Enfance Protégée</t>
+  </si>
+  <si>
+    <t>4601</t>
+  </si>
+  <si>
+    <t>Etablissements pour Adultes et Familles en Difficulté</t>
+  </si>
+  <si>
+    <t>4602</t>
+  </si>
+  <si>
+    <t>Autres Etablissements Sociaux d'Hébergement et d'Accueil</t>
+  </si>
+  <si>
+    <t>4603</t>
+  </si>
+  <si>
+    <t>Etablissements Expérimentaux en Faveur des Adultes</t>
+  </si>
+  <si>
+    <t>4604</t>
+  </si>
+  <si>
+    <t>Autres Etablissements médico-sociaux</t>
+  </si>
+  <si>
+    <t>4605</t>
+  </si>
+  <si>
+    <t>Etablissements et services multi-clientèles</t>
+  </si>
+  <si>
+    <t>4606</t>
+  </si>
+  <si>
+    <t>Centres de ressources</t>
+  </si>
+  <si>
+    <t>4607</t>
+  </si>
+  <si>
+    <t>Logements en Structure Collective</t>
+  </si>
+  <si>
+    <t>4608</t>
+  </si>
+  <si>
+    <t>Protection des majeurs</t>
+  </si>
+  <si>
+    <t>4609</t>
+  </si>
+  <si>
+    <t>Centres prestataires de services pr personnes cérébro-lésées</t>
+  </si>
+  <si>
+    <t>5101</t>
+  </si>
+  <si>
+    <t>Etablissements Garde d'Enfants d'Age pré-Scolaire</t>
+  </si>
+  <si>
+    <t>5102</t>
+  </si>
+  <si>
+    <t>Etablissements d'Hébergement pour Enfants d'Age Scolaire</t>
+  </si>
+  <si>
+    <t>5103</t>
+  </si>
+  <si>
+    <t>Etablissements Sociaux pour Loisirs et Vacances</t>
+  </si>
+  <si>
+    <t>5104</t>
+  </si>
+  <si>
+    <t>Etablissements ou Services Divers d'Aide à la Famille</t>
+  </si>
+  <si>
+    <t>6101</t>
+  </si>
+  <si>
+    <t>6102</t>
+  </si>
+  <si>
+    <t>Etablissements de Formation des Personnels Techniques</t>
+  </si>
+  <si>
+    <t>6103</t>
+  </si>
+  <si>
+    <t>Autres Etablissements de Formation des Personnels Techniques</t>
+  </si>
+  <si>
+    <t>6201</t>
+  </si>
+  <si>
+    <t>6301</t>
+  </si>
+  <si>
+    <t>001</t>
+  </si>
+  <si>
+    <t>Autres lits de m.R.</t>
+  </si>
+  <si>
+    <t>002</t>
+  </si>
+  <si>
+    <t>Autres places de l-f.</t>
+  </si>
+  <si>
+    <t>003</t>
+  </si>
+  <si>
+    <t>Autres lits de l-s</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>Centre Hospitalier Régional (C.H.R.)</t>
+  </si>
+  <si>
+    <t>106</t>
+  </si>
+  <si>
+    <t>Centre hospitalier, ex Hôpital local</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>Etablissement de Convalescence et de Repos</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>Etablissement de santé privé autorisé en SSR</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>Centre de Convalescence Cure ou Réadaptation</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>Hôpital des armées</t>
+  </si>
+  <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t>Etablissement de Soins du Service de Santé des Armées</t>
+  </si>
+  <si>
+    <t>119</t>
+  </si>
+  <si>
+    <t>Maison de Régime</t>
+  </si>
+  <si>
+    <t>122</t>
+  </si>
+  <si>
+    <t>Etablissement Soins Obstétriques Chirurgico-Gynécologiques</t>
+  </si>
+  <si>
+    <t>124</t>
+  </si>
+  <si>
+    <t>Centre de Santé</t>
+  </si>
+  <si>
+    <t>125</t>
+  </si>
+  <si>
+    <t>Centre de Santé Dentaire</t>
+  </si>
+  <si>
+    <t>126</t>
+  </si>
+  <si>
+    <t>Etablissement Thermal</t>
+  </si>
+  <si>
+    <t>127</t>
+  </si>
+  <si>
+    <t>Hospitalisation à Domicile</t>
+  </si>
+  <si>
+    <t>128</t>
+  </si>
+  <si>
+    <t>Etablissement de Soins Chirurgicaux</t>
+  </si>
+  <si>
+    <t>129</t>
+  </si>
+  <si>
+    <t>Etablissement de Soins Médicaux</t>
+  </si>
+  <si>
+    <t>130</t>
+  </si>
+  <si>
+    <t>Centre de Soins Médicaux</t>
+  </si>
+  <si>
+    <t>131</t>
+  </si>
+  <si>
+    <t>Centre de Lutte Contre Cancer</t>
+  </si>
+  <si>
+    <t>132</t>
+  </si>
+  <si>
+    <t>Etablissement de Transfusion Sanguine</t>
+  </si>
+  <si>
+    <t>135</t>
+  </si>
+  <si>
+    <t>Etablissement Réadaptation Fonctionnelle</t>
+  </si>
+  <si>
+    <t>136</t>
+  </si>
+  <si>
+    <t>Banque de Sperme</t>
+  </si>
+  <si>
+    <t>137</t>
+  </si>
+  <si>
+    <t>Banque d'Organes</t>
+  </si>
+  <si>
+    <t>138</t>
+  </si>
+  <si>
+    <t>Centre de Dialyse Périodique</t>
+  </si>
+  <si>
+    <t>139</t>
+  </si>
+  <si>
+    <t>Centre de Dialyse et d'entraînement à la Dialyse</t>
+  </si>
+  <si>
+    <t>140</t>
+  </si>
+  <si>
+    <t>Centre d'Entraînement à la Dialyse</t>
+  </si>
+  <si>
+    <t>141</t>
+  </si>
+  <si>
+    <t>Centre de dialyse</t>
+  </si>
+  <si>
+    <t>142</t>
+  </si>
+  <si>
+    <t>Dispensaire Antituberculeux</t>
+  </si>
+  <si>
+    <t>143</t>
+  </si>
+  <si>
+    <t>Centre de Vaccination BCG</t>
+  </si>
+  <si>
+    <t>144</t>
+  </si>
+  <si>
+    <t>Etablissement de Lutte Contre la Tuberculose</t>
+  </si>
+  <si>
+    <t>146</t>
+  </si>
+  <si>
+    <t>Structure d'Alternative à la dialyse en centre</t>
+  </si>
+  <si>
+    <t>156</t>
+  </si>
+  <si>
+    <t>Centre Médico-Psychologique (C.M.P.)</t>
+  </si>
+  <si>
+    <t>157</t>
+  </si>
+  <si>
+    <t>Centre de Postcure</t>
+  </si>
+  <si>
+    <t>159</t>
+  </si>
+  <si>
+    <t>Centre Parental</t>
+  </si>
+  <si>
+    <t>160</t>
+  </si>
+  <si>
+    <t>Centre de Soins Spécifiques pour Toxicomanes (C.S.S.T.)</t>
+  </si>
+  <si>
+    <t>161</t>
+  </si>
+  <si>
+    <t>Maison de Santé pour Maladies Mentales</t>
+  </si>
+  <si>
+    <t>162</t>
+  </si>
+  <si>
+    <t>Centre de Cure Ambulatoire en Alcoologie (C.C.A.A.)</t>
+  </si>
+  <si>
+    <t>163</t>
+  </si>
+  <si>
+    <t>Maison d'Enfants à Caractère Sanitaire Temporaire</t>
+  </si>
+  <si>
+    <t>164</t>
+  </si>
+  <si>
+    <t>Etablissements Expérimentaux Accueil de la Petite Enfance</t>
+  </si>
+  <si>
+    <t>165</t>
+  </si>
+  <si>
+    <t>Appartement de Coordination Thérapeutique (A.C.T.)</t>
+  </si>
+  <si>
+    <t>166</t>
+  </si>
+  <si>
+    <t>Etablissement d'Accueil Mère-Enfant</t>
+  </si>
+  <si>
+    <t>167</t>
+  </si>
+  <si>
+    <t>Crèche Collective</t>
+  </si>
+  <si>
+    <t>168</t>
+  </si>
+  <si>
+    <t>Service Accueil Familial pour la Petite Enfance</t>
+  </si>
+  <si>
+    <t>169</t>
+  </si>
+  <si>
+    <t>Crèche Multi Accueil Collectif et Familial</t>
+  </si>
+  <si>
+    <t>170</t>
+  </si>
+  <si>
+    <t>Halte Garderie</t>
+  </si>
+  <si>
+    <t>171</t>
+  </si>
+  <si>
+    <t>Garderie et Jardin d'Enfants</t>
+  </si>
+  <si>
+    <t>172</t>
+  </si>
+  <si>
+    <t>Pouponnière à Caractère Social</t>
+  </si>
+  <si>
+    <t>173</t>
+  </si>
+  <si>
+    <t>Pouponnière à Caractère Sanitaire</t>
+  </si>
+  <si>
+    <t>174</t>
+  </si>
+  <si>
+    <t>Etablissement d'Accueil Collectif Régulier et Occasionnel</t>
+  </si>
+  <si>
+    <t>175</t>
+  </si>
+  <si>
+    <t>Foyer de l'Enfance</t>
+  </si>
+  <si>
+    <t>176</t>
+  </si>
+  <si>
+    <t>Village d'Enfants</t>
+  </si>
+  <si>
+    <t>177</t>
+  </si>
+  <si>
+    <t>Maison d'Enfants à Caractère Social</t>
+  </si>
+  <si>
+    <t>178</t>
+  </si>
+  <si>
+    <t>Ctre.Accueil- Accomp.Réduc.Risq.Usag. Drogues (C.A.A.R.U.D.)</t>
+  </si>
+  <si>
+    <t>179</t>
+  </si>
+  <si>
+    <t>Maison d'Enfants à Caractère Sanitaire Permanente</t>
+  </si>
+  <si>
+    <t>180</t>
+  </si>
+  <si>
+    <t>Lits Halte Soins Santé (L.H.S.S.)</t>
+  </si>
+  <si>
+    <t>181</t>
+  </si>
+  <si>
+    <t>Maison Familiale de Vacances</t>
+  </si>
+  <si>
+    <t>182</t>
+  </si>
+  <si>
+    <t>Service d'Éducation Spéciale et de Soins à Domicile</t>
+  </si>
+  <si>
+    <t>183</t>
+  </si>
+  <si>
+    <t>Institut Médico-Educatif (I.M.E.)</t>
+  </si>
+  <si>
+    <t>184</t>
+  </si>
+  <si>
+    <t>Institut Médico-Pédagogique (I.M.P.)</t>
+  </si>
+  <si>
+    <t>185</t>
+  </si>
+  <si>
+    <t>Institut Médico-Professionnel (I.M.Pro.)</t>
+  </si>
+  <si>
+    <t>186</t>
+  </si>
+  <si>
+    <t>Institut Thérapeutique Éducatif et Pédagogique (I.T.E.P.)</t>
+  </si>
+  <si>
+    <t>188</t>
+  </si>
+  <si>
+    <t>Etablissement pour Enfants ou Adolescents Polyhandicapés</t>
+  </si>
+  <si>
+    <t>189</t>
+  </si>
+  <si>
+    <t>Centre Médico-Psycho-Pédagogique (C.M.P.P.)</t>
+  </si>
+  <si>
+    <t>190</t>
+  </si>
+  <si>
+    <t>Centre Action Médico-Sociale Précoce (C.A.M.S.P.)</t>
+  </si>
+  <si>
+    <t>191</t>
+  </si>
+  <si>
+    <t>Etablissement pour Déficients Moteurs Cérébraux</t>
+  </si>
+  <si>
+    <t>192</t>
+  </si>
+  <si>
+    <t>Institut d'éducation motrice</t>
+  </si>
+  <si>
+    <t>193</t>
+  </si>
+  <si>
+    <t>Etablissement pour Déficients Moteurs et Moteurs Cérébraux</t>
+  </si>
+  <si>
+    <t>194</t>
+  </si>
+  <si>
+    <t>Institut pour Déficients Visuels</t>
+  </si>
+  <si>
+    <t>195</t>
+  </si>
+  <si>
+    <t>Institut pour Déficients Auditifs</t>
+  </si>
+  <si>
+    <t>196</t>
+  </si>
+  <si>
+    <t>Institut d'Education Sensorielle Sourd-Aveugle</t>
+  </si>
+  <si>
+    <t>197</t>
+  </si>
+  <si>
+    <t>Centre soins accompagnement prévention addictologie (CSAPA)</t>
+  </si>
+  <si>
+    <t>198</t>
+  </si>
+  <si>
+    <t>Établissement et Service de Préorientation</t>
+  </si>
+  <si>
+    <t>199</t>
+  </si>
+  <si>
+    <t>Hospice</t>
+  </si>
+  <si>
+    <t>200</t>
+  </si>
+  <si>
+    <t>Maison de Retraite</t>
+  </si>
+  <si>
+    <t>202</t>
+  </si>
+  <si>
+    <t>Résidences autonomie</t>
+  </si>
+  <si>
+    <t>205</t>
+  </si>
+  <si>
+    <t>Foyer Club Restaurant</t>
+  </si>
+  <si>
+    <t>207</t>
+  </si>
+  <si>
+    <t>Centre de Jour pour Personnes Agées</t>
+  </si>
+  <si>
+    <t>208</t>
+  </si>
+  <si>
+    <t>Service d'Aide Ménagère à Domicile</t>
+  </si>
+  <si>
+    <t>209</t>
+  </si>
+  <si>
+    <t>Service autonomie aide et soins (SAAS)</t>
+  </si>
+  <si>
+    <t>212</t>
+  </si>
+  <si>
+    <t>Alarme Médico-Sociale</t>
+  </si>
+  <si>
+    <t>213</t>
+  </si>
+  <si>
+    <t>Lits d'Accueil Médicalisés (L.A.M.)</t>
+  </si>
+  <si>
+    <t>214</t>
+  </si>
+  <si>
+    <t>Centre Hébergement &amp; Réinsertion Sociale (C.H.R.S.)</t>
+  </si>
+  <si>
+    <t>215</t>
+  </si>
+  <si>
+    <t>Maison Relai</t>
+  </si>
+  <si>
+    <t>216</t>
+  </si>
+  <si>
+    <t>Résidence Hôtelière à Vocation Sociale (R.H.V.S)</t>
+  </si>
+  <si>
+    <t>217</t>
+  </si>
+  <si>
+    <t>Cité de Transit</t>
+  </si>
+  <si>
+    <t>218</t>
+  </si>
+  <si>
+    <t>Aire Station Nomades</t>
+  </si>
+  <si>
+    <t>219</t>
+  </si>
+  <si>
+    <t>Autre Centre d'Accueil</t>
+  </si>
+  <si>
+    <t>220</t>
+  </si>
+  <si>
+    <t>Centre Social</t>
+  </si>
+  <si>
+    <t>221</t>
+  </si>
+  <si>
+    <t>Bureau d'Aide Psychologique Universitaire (B.A.P.U.)</t>
+  </si>
+  <si>
+    <t>223</t>
+  </si>
+  <si>
+    <t>Protection Maternelle et Infantile (P.M.I.)</t>
+  </si>
+  <si>
+    <t>224</t>
+  </si>
+  <si>
+    <t>Etablissement de Consultation Pré et Post-natale</t>
+  </si>
+  <si>
+    <t>225</t>
+  </si>
+  <si>
+    <t>Consultations de Nourrissons</t>
+  </si>
+  <si>
+    <t>228</t>
+  </si>
+  <si>
+    <t>Centre de Santé Sexuelle</t>
+  </si>
+  <si>
+    <t>229</t>
+  </si>
+  <si>
+    <t>Consultation Problèmes naissance</t>
+  </si>
+  <si>
+    <t>230</t>
+  </si>
+  <si>
+    <t>Etablissement Consultation Protection Infantile</t>
+  </si>
+  <si>
+    <t>231</t>
+  </si>
+  <si>
+    <t>Etablissement Information Consultation Conseil Familial</t>
+  </si>
+  <si>
+    <t>233</t>
+  </si>
+  <si>
+    <t>Lactarium</t>
+  </si>
+  <si>
+    <t>236</t>
+  </si>
+  <si>
+    <t>Centre Placement Familial Socio-Educatif (C.P.F.S.E.)</t>
+  </si>
+  <si>
+    <t>237</t>
+  </si>
+  <si>
+    <t>Centre de Placement Familial Spécialisé</t>
+  </si>
+  <si>
+    <t>238</t>
+  </si>
+  <si>
+    <t>Centre d'Accueil Familial Spécialisé</t>
+  </si>
+  <si>
+    <t>241</t>
+  </si>
+  <si>
+    <t>Établissement de Placement</t>
+  </si>
+  <si>
+    <t>242</t>
+  </si>
+  <si>
+    <t>Service d’Activité de Jour</t>
+  </si>
+  <si>
+    <t>246</t>
+  </si>
+  <si>
+    <t>Etablissement et Service d'Aide par le Travail (E.S.A.T.)</t>
+  </si>
+  <si>
+    <t>247</t>
+  </si>
+  <si>
+    <t>Entreprise adaptée</t>
+  </si>
+  <si>
+    <t>249</t>
+  </si>
+  <si>
+    <t>Établissement et Service de Réadaptation Professionnelle</t>
+  </si>
+  <si>
+    <t>250</t>
+  </si>
+  <si>
+    <t>Centre Réentrainement au travail</t>
+  </si>
+  <si>
+    <t>251</t>
+  </si>
+  <si>
+    <t>Maison Vacances pour Handicapés</t>
+  </si>
+  <si>
+    <t>252</t>
+  </si>
+  <si>
+    <t>Foyer Hébergement Adultes Handicapés</t>
+  </si>
+  <si>
+    <t>253</t>
+  </si>
+  <si>
+    <t>Foyer d'Accueil Polyvalent pour Adultes Handicapés</t>
+  </si>
+  <si>
+    <t>255</t>
+  </si>
+  <si>
+    <t>Maison d'Accueil Spécialisée (M.A.S.)</t>
+  </si>
+  <si>
+    <t>256</t>
+  </si>
+  <si>
+    <t>Foyer Travailleurs Migrants non transformé en Résidence Soc.</t>
+  </si>
+  <si>
+    <t>257</t>
+  </si>
+  <si>
+    <t>Foyers de jeunes travailleurs</t>
+  </si>
+  <si>
+    <t>258</t>
+  </si>
+  <si>
+    <t>Maisons Relais - Pensions de Famille</t>
+  </si>
+  <si>
+    <t>259</t>
+  </si>
+  <si>
+    <t>Autres résidences sociales</t>
+  </si>
+  <si>
+    <t>261</t>
+  </si>
+  <si>
+    <t>D.D.A.S.S.</t>
+  </si>
+  <si>
+    <t>262</t>
+  </si>
+  <si>
+    <t>Etablissement Régional d'Enseignement Adapté</t>
+  </si>
+  <si>
+    <t>265</t>
+  </si>
+  <si>
+    <t>Section Education Spéciale Classe Atelier</t>
+  </si>
+  <si>
+    <t>266</t>
+  </si>
+  <si>
+    <t>Dispensaire Antivénérien</t>
+  </si>
+  <si>
+    <t>267</t>
+  </si>
+  <si>
+    <t>Dispensaire Antihansénien</t>
+  </si>
+  <si>
+    <t>268</t>
+  </si>
+  <si>
+    <t>Centre Médico-Scolaire</t>
+  </si>
+  <si>
+    <t>269</t>
+  </si>
+  <si>
+    <t>Centre de Médecine Universitaire</t>
+  </si>
+  <si>
+    <t>270</t>
+  </si>
+  <si>
+    <t>Centre de Médecine Sportive</t>
+  </si>
+  <si>
+    <t>271</t>
+  </si>
+  <si>
+    <t>Maison d'accueil Hospitalière</t>
+  </si>
+  <si>
+    <t>272</t>
+  </si>
+  <si>
+    <t>Ecole d'ambulanciers</t>
+  </si>
+  <si>
+    <t>273</t>
+  </si>
+  <si>
+    <t>Institut de formation en soins infirmiers (I.F.S.I.)</t>
+  </si>
+  <si>
+    <t>274</t>
+  </si>
+  <si>
+    <t>Ecole de sages_femmes</t>
+  </si>
+  <si>
+    <t>275</t>
+  </si>
+  <si>
+    <t>Ecole de masseurs-kinésithérapeutes</t>
+  </si>
+  <si>
+    <t>276</t>
+  </si>
+  <si>
+    <t>Ecole de laborantins d'analyses médicales</t>
+  </si>
+  <si>
+    <t>277</t>
+  </si>
+  <si>
+    <t>Ecole de péricultrices</t>
+  </si>
+  <si>
+    <t>278</t>
+  </si>
+  <si>
+    <t>Etablissement de formation polyvalent</t>
+  </si>
+  <si>
+    <t>279</t>
+  </si>
+  <si>
+    <t>Ecole de service social</t>
+  </si>
+  <si>
+    <t>280</t>
+  </si>
+  <si>
+    <t>Ecole d'éducateurs spécialisés</t>
+  </si>
+  <si>
+    <t>281</t>
+  </si>
+  <si>
+    <t>Centre de formation d'aides soignants</t>
+  </si>
+  <si>
+    <t>282</t>
+  </si>
+  <si>
+    <t>Ecole de pédicures-podologues</t>
+  </si>
+  <si>
+    <t>283</t>
+  </si>
+  <si>
+    <t>Ecole de manipulateurs d'électro-radiologie</t>
+  </si>
+  <si>
+    <t>284</t>
+  </si>
+  <si>
+    <t>Ecole de travailleuses familiales</t>
+  </si>
+  <si>
+    <t>285</t>
+  </si>
+  <si>
+    <t>Centres de Loisirs sans Hébergement</t>
+  </si>
+  <si>
+    <t>286</t>
+  </si>
+  <si>
+    <t>Club Equipe de Prévention</t>
+  </si>
+  <si>
+    <t>289</t>
+  </si>
+  <si>
+    <t>Centre de Soins Infirmiers</t>
+  </si>
+  <si>
+    <t>292</t>
+  </si>
+  <si>
+    <t>Centre Hospitalier Spécialisé lutte Maladies Mentales</t>
+  </si>
+  <si>
+    <t>294</t>
+  </si>
+  <si>
+    <t>Centre de Consultations Cancer</t>
+  </si>
+  <si>
+    <t>295</t>
+  </si>
+  <si>
+    <t>Service AEMO et AED</t>
+  </si>
+  <si>
+    <t>297</t>
+  </si>
+  <si>
+    <t>Dispensaire Polyvalent</t>
+  </si>
+  <si>
+    <t>300</t>
+  </si>
+  <si>
+    <t>Ecoles Formant aux Professions Sanitaires</t>
+  </si>
+  <si>
+    <t>303</t>
+  </si>
+  <si>
+    <t>Ecole de conseillers en économie sociale et familiale</t>
+  </si>
+  <si>
+    <t>304</t>
+  </si>
+  <si>
+    <t>Ecole d'ergothérapeutes</t>
+  </si>
+  <si>
+    <t>305</t>
+  </si>
+  <si>
+    <t>Ecole de psycho-motriciens</t>
+  </si>
+  <si>
+    <t>306</t>
+  </si>
+  <si>
+    <t>Ecole d'infirmiers anesthésistes</t>
+  </si>
+  <si>
+    <t>307</t>
+  </si>
+  <si>
+    <t>Ecole d'infirmiers de bloc opératoire</t>
+  </si>
+  <si>
+    <t>308</t>
+  </si>
+  <si>
+    <t>Centre de formation professionnelle de secteur psychiatrique</t>
+  </si>
+  <si>
+    <t>309</t>
+  </si>
+  <si>
+    <t>Ecole de cadres infirmiers</t>
+  </si>
+  <si>
+    <t>310</t>
+  </si>
+  <si>
+    <t>Ecole de cadres de secteur psychiatrique</t>
+  </si>
+  <si>
+    <t>311</t>
+  </si>
+  <si>
+    <t>Ecole de cadres de masseurs-kinésithérapeutes</t>
+  </si>
+  <si>
+    <t>312</t>
+  </si>
+  <si>
+    <t>Ecole de cadres de manipulateurs d'électro-radiologie</t>
+  </si>
+  <si>
+    <t>313</t>
+  </si>
+  <si>
+    <t>Ecole d'éducateurs de jeunes enfants</t>
+  </si>
+  <si>
+    <t>314</t>
+  </si>
+  <si>
+    <t>Ecole d'éducateurs techniques spécialisés</t>
+  </si>
+  <si>
+    <t>315</t>
+  </si>
+  <si>
+    <t>Ecole de moniteurs-éducateurs</t>
+  </si>
+  <si>
+    <t>316</t>
+  </si>
+  <si>
+    <t>Ecole d'aides médico-psychologiques</t>
+  </si>
+  <si>
+    <t>317</t>
+  </si>
+  <si>
+    <t>Ecole d'animateurs socio-éducatifs</t>
+  </si>
+  <si>
+    <t>319</t>
+  </si>
+  <si>
+    <t>Inst. régional de formation des travailleurs sociaux</t>
+  </si>
+  <si>
+    <t>320</t>
+  </si>
+  <si>
+    <t>S.A.M.U. et Centre 15</t>
+  </si>
+  <si>
+    <t>321</t>
+  </si>
+  <si>
+    <t>Unité Mobile Hospitalière</t>
+  </si>
+  <si>
+    <t>322</t>
+  </si>
+  <si>
+    <t>Centre Rég.Informatiq.Hospit.</t>
+  </si>
+  <si>
+    <t>324</t>
+  </si>
+  <si>
+    <t>Logement Foyer non Spécialisé</t>
+  </si>
+  <si>
+    <t>326</t>
+  </si>
+  <si>
+    <t>Ecole de cadres</t>
+  </si>
+  <si>
+    <t>327</t>
+  </si>
+  <si>
+    <t>328</t>
+  </si>
+  <si>
+    <t>Centre Consultation Soins Dentaire</t>
+  </si>
+  <si>
+    <t>329</t>
+  </si>
+  <si>
+    <t>Sectorisation Psychiatrique</t>
+  </si>
+  <si>
+    <t>330</t>
+  </si>
+  <si>
+    <t>Ecoles Formant aux Professions Sociales</t>
+  </si>
+  <si>
+    <t>340</t>
+  </si>
+  <si>
+    <t>Service mandataire judiciaire à la protection des majeurs</t>
+  </si>
+  <si>
+    <t>341</t>
+  </si>
+  <si>
+    <t>Service dédié mesures d'accompagnement social personnalisé</t>
+  </si>
+  <si>
+    <t>342</t>
+  </si>
+  <si>
+    <t>Service d'information et de soutien aux tuteurs familiaux</t>
+  </si>
+  <si>
+    <t>343</t>
+  </si>
+  <si>
+    <t>Equipe Préparation et Suite Reclassement (EPSR)</t>
+  </si>
+  <si>
+    <t>344</t>
+  </si>
+  <si>
+    <t>Service délégué aux prestations familiales</t>
+  </si>
+  <si>
+    <t>345</t>
+  </si>
+  <si>
+    <t>Service Tutelle Prestation Sociale</t>
+  </si>
+  <si>
+    <t>346</t>
+  </si>
+  <si>
+    <t>Service de Travailleuses Familiales</t>
+  </si>
+  <si>
+    <t>347</t>
+  </si>
+  <si>
+    <t>Centre d'Examens de Santé</t>
+  </si>
+  <si>
+    <t>349</t>
+  </si>
+  <si>
+    <t>Ecole de cadres de sages-femmes</t>
+  </si>
+  <si>
+    <t>350</t>
+  </si>
+  <si>
+    <t>Centre de formation d'auxiliaires de puériculture</t>
+  </si>
+  <si>
+    <t>352</t>
+  </si>
+  <si>
+    <t>Centre de Psychothérapie</t>
+  </si>
+  <si>
+    <t>353</t>
+  </si>
+  <si>
+    <t>Hôpital de Jour Spécialités Médicales</t>
+  </si>
+  <si>
+    <t>354</t>
+  </si>
+  <si>
+    <t>Service de Soins Infirmiers A Domicile (S.S.I.A.D)</t>
+  </si>
+  <si>
+    <t>355</t>
+  </si>
+  <si>
+    <t>Centre Hospitalier (C.H.)</t>
+  </si>
+  <si>
+    <t>357</t>
+  </si>
+  <si>
+    <t>Association Aide aux Insuffisants Respiratoires</t>
+  </si>
+  <si>
+    <t>359</t>
+  </si>
+  <si>
+    <t>Centre Circonscription Sanitaire et Sociale</t>
+  </si>
+  <si>
+    <t>361</t>
+  </si>
+  <si>
+    <t>Centre de Cure Médicale</t>
+  </si>
+  <si>
+    <t>362</t>
+  </si>
+  <si>
+    <t>Etablissement de Soins Longue Durée</t>
+  </si>
+  <si>
+    <t>363</t>
+  </si>
+  <si>
+    <t>Centre moyen et long séjour</t>
+  </si>
+  <si>
+    <t>365</t>
+  </si>
+  <si>
+    <t>Etablissement de Soins Pluridisciplinaire</t>
+  </si>
+  <si>
+    <t>366</t>
+  </si>
+  <si>
+    <t>Atelier Thérapeutique</t>
+  </si>
+  <si>
+    <t>367</t>
+  </si>
+  <si>
+    <t>Maison d'Enfants non Conventionnée ni Habilitée</t>
+  </si>
+  <si>
+    <t>368</t>
+  </si>
+  <si>
+    <t>Service de Repas à Domicile</t>
+  </si>
+  <si>
+    <t>369</t>
+  </si>
+  <si>
+    <t>Centre Adaptation Vie Active (C.A.V.A.)</t>
+  </si>
+  <si>
+    <t>370</t>
+  </si>
+  <si>
+    <t>Etablissement Expérimental pour personnes handicapées</t>
+  </si>
+  <si>
+    <t>371</t>
+  </si>
+  <si>
+    <t>Service Action Socio-Educative pour Familles en difficulté</t>
+  </si>
+  <si>
+    <t>373</t>
+  </si>
+  <si>
+    <t>Centre de formation supérieure des travailleurs sociaux</t>
+  </si>
+  <si>
+    <t>374</t>
+  </si>
+  <si>
+    <t>Ecole Nationale Santé Publique (E.N.S.P.)</t>
+  </si>
+  <si>
+    <t>375</t>
+  </si>
+  <si>
+    <t>Classe d'Adaptation</t>
+  </si>
+  <si>
+    <t>376</t>
+  </si>
+  <si>
+    <t>Classe Spéciale Ecole Primaire</t>
+  </si>
+  <si>
+    <t>377</t>
+  </si>
+  <si>
+    <t>Etablissement Expérimental pour Enfance Handicapée</t>
+  </si>
+  <si>
+    <t>378</t>
+  </si>
+  <si>
+    <t>Etablissement Expérimental Enfance Protégée</t>
+  </si>
+  <si>
+    <t>379</t>
+  </si>
+  <si>
+    <t>Etablissement Expérimental pour Adultes Handicapés</t>
+  </si>
+  <si>
+    <t>380</t>
+  </si>
+  <si>
+    <t>Etablissement Expérimental Autres Adultes</t>
+  </si>
+  <si>
+    <t>381</t>
+  </si>
+  <si>
+    <t>Etablissement Expérimental pour Personnes Agées</t>
+  </si>
+  <si>
+    <t>382</t>
+  </si>
+  <si>
+    <t>Foyer de Vie pour Adultes Handicapés</t>
+  </si>
+  <si>
+    <t>386</t>
+  </si>
+  <si>
+    <t>Ecole Secondaire Spéciale</t>
+  </si>
+  <si>
+    <t>390</t>
+  </si>
+  <si>
+    <t>Etablissement d'Accueil Temporaire d'Enfants Handicapés</t>
+  </si>
+  <si>
+    <t>393</t>
+  </si>
+  <si>
+    <t>Autre résidence But lucratif pr personnes Âgées</t>
+  </si>
+  <si>
+    <t>394</t>
+  </si>
+  <si>
+    <t>Etablissement d'Accueil Temporaire pour Personnes Agées</t>
+  </si>
+  <si>
+    <t>395</t>
+  </si>
+  <si>
+    <t>Etablissement d'Accueil Temporaire pour Adultes Handicapés</t>
+  </si>
+  <si>
+    <t>396</t>
+  </si>
+  <si>
+    <t>Foyer Hébergement Enfants et Adolescents Handicapés</t>
+  </si>
+  <si>
+    <t>397</t>
+  </si>
+  <si>
+    <t>Service Auxiliaire de Vie pour Handicapés</t>
+  </si>
+  <si>
+    <t>398</t>
+  </si>
+  <si>
+    <t>Crèche Parentale</t>
+  </si>
+  <si>
+    <t>399</t>
+  </si>
+  <si>
+    <t>Halte Garderie Parentale</t>
+  </si>
+  <si>
+    <t>400</t>
+  </si>
+  <si>
+    <t>Centre de Services pour Associations</t>
+  </si>
+  <si>
+    <t>401</t>
+  </si>
+  <si>
+    <t>D.R.A.S.S.</t>
+  </si>
+  <si>
+    <t>402</t>
+  </si>
+  <si>
+    <t>Jardin d'Enfants Spécialisé</t>
+  </si>
+  <si>
+    <t>403</t>
+  </si>
+  <si>
+    <t>Service Social Spécialisé ou Polyvalent de Catégorie</t>
+  </si>
+  <si>
+    <t>404</t>
+  </si>
+  <si>
+    <t>Etablissement Acc.Collect.Parental Régulier &amp; Occasionnel</t>
+  </si>
+  <si>
+    <t>405</t>
+  </si>
+  <si>
+    <t>Service Social Polyvalent de Secteur</t>
+  </si>
+  <si>
+    <t>411</t>
+  </si>
+  <si>
+    <t>Intermédiaire de Placement Social</t>
+  </si>
+  <si>
+    <t>412</t>
+  </si>
+  <si>
+    <t>Appartement Thérapeutique</t>
+  </si>
+  <si>
+    <t>413</t>
+  </si>
+  <si>
+    <t>C.E.C.O.S</t>
+  </si>
+  <si>
+    <t>414</t>
+  </si>
+  <si>
+    <t>Centre Anti Poison</t>
+  </si>
+  <si>
+    <t>415</t>
+  </si>
+  <si>
+    <t>Service Médico-Psychologique Régional (S.M.P.R.)</t>
+  </si>
+  <si>
+    <t>418</t>
+  </si>
+  <si>
+    <t>Service d'Enquêtes Sociales (S.E.S.)</t>
+  </si>
+  <si>
+    <t>419</t>
+  </si>
+  <si>
+    <t>Centre d'Accueil Toxicomanes</t>
+  </si>
+  <si>
+    <t>420</t>
+  </si>
+  <si>
+    <t>Entreprise d'Insertion</t>
+  </si>
+  <si>
+    <t>421</t>
+  </si>
+  <si>
+    <t>Centre d'enseignement aux secours d'urgence</t>
+  </si>
+  <si>
+    <t>422</t>
+  </si>
+  <si>
+    <t>Traitements Spécialisés à Domicile</t>
+  </si>
+  <si>
+    <t>423</t>
+  </si>
+  <si>
+    <t>Ecole des cadres de laborantins d'analyses médicales</t>
+  </si>
+  <si>
     <t>425</t>
   </si>
   <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>Uri</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>niveau</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/concept-properties#niveau</t>
-  </si>
-  <si>
-    <t>Permet d'indiquer le niveau hiérarchique du code</t>
-  </si>
-  <si>
-    <t>integer</t>
-  </si>
-  <si>
-    <t>parent</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/concept-properties#parent</t>
-  </si>
-  <si>
-    <t>An immediate parent of the concept in the hierarchy</t>
-  </si>
-  <si>
-    <t>code</t>
-  </si>
-  <si>
-    <t>domaine</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/concept-properties#domaine</t>
-  </si>
-  <si>
-    <t>Domaine de la categorie d etablissement</t>
-  </si>
-  <si>
-    <t>Coding</t>
-  </si>
-  <si>
-    <t>dateValid</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateValid</t>
-  </si>
-  <si>
-    <t>date de validité d'un code concept</t>
-  </si>
-  <si>
-    <t>dateTime</t>
-  </si>
-  <si>
-    <t>dateMaj</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateMaj</t>
-  </si>
-  <si>
-    <t>Date de mise à jour d'un code concept</t>
-  </si>
-  <si>
-    <t>dateFin</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateFin</t>
-  </si>
-  <si>
-    <t>Date de fin d'exploitation d'un code concept</t>
-  </si>
-  <si>
-    <t>status</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/concept-properties#status</t>
-  </si>
-  <si>
-    <t>A property that indicates the status of the concept.</t>
-  </si>
-  <si>
-    <t>deprecationDate</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/concept-properties#deprecationDate</t>
-  </si>
-  <si>
-    <t>Date Concept was deprecated</t>
-  </si>
-  <si>
-    <t>retirementDate</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/concept-properties#retirementDate</t>
-  </si>
-  <si>
-    <t>Date Concept was retired</t>
-  </si>
-  <si>
-    <t>specialisationRor</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/concept-properties#specialisationRor</t>
-  </si>
-  <si>
-    <t>Propriété permettant de spécifier les codes exclusifs appartenant au ROR</t>
-  </si>
-  <si>
-    <t>boolean</t>
-  </si>
-  <si>
-    <t>Level</t>
-  </si>
-  <si>
-    <t>Display</t>
-  </si>
-  <si>
-    <t>Definition</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>0100</t>
-  </si>
-  <si>
-    <t>Etablissements d'administration</t>
-  </si>
-  <si>
-    <t>1000</t>
-  </si>
-  <si>
-    <t>Etablissements Relevant de la Loi Hospitalière</t>
-  </si>
-  <si>
-    <t>2000</t>
-  </si>
-  <si>
-    <t>Autres Etablissements de Soins et Prévention</t>
-  </si>
-  <si>
-    <t>3000</t>
-  </si>
-  <si>
-    <t>Autres Etablissements à Caractère Sanitaire</t>
-  </si>
-  <si>
-    <t>4000</t>
-  </si>
-  <si>
-    <t>Etab.Serv.Soc.d'Accueil Hébergement Assistance Réadaptation</t>
-  </si>
-  <si>
-    <t>5000</t>
-  </si>
-  <si>
-    <t>Etablissements et Services Sociaux d'Aide à la Famille</t>
-  </si>
-  <si>
-    <t>6000</t>
-  </si>
-  <si>
-    <t>Etab.de Formation des Personnels Sanitaires et Sociaux</t>
-  </si>
-  <si>
-    <t>0110</t>
-  </si>
-  <si>
-    <t>Etablissements d'Administration</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>1100</t>
-  </si>
-  <si>
-    <t>Etablissements Hospitaliers</t>
-  </si>
-  <si>
-    <t>1200</t>
-  </si>
-  <si>
-    <t>Autres Etablissements Relevant de la Loi Hospitalière</t>
-  </si>
-  <si>
-    <t>2100</t>
-  </si>
-  <si>
-    <t>Cabinets Libéraux</t>
-  </si>
-  <si>
-    <t>2200</t>
-  </si>
-  <si>
-    <t>3100</t>
-  </si>
-  <si>
-    <t>Laboratoires de Biologie Médicale</t>
-  </si>
-  <si>
-    <t>3200</t>
-  </si>
-  <si>
-    <t>Commerce de Biens à Usage Médicaux</t>
-  </si>
-  <si>
-    <t>3400</t>
-  </si>
-  <si>
-    <t>4100</t>
-  </si>
-  <si>
-    <t>Etab.et Serv.pour l'Enfance et la Jeunesse Handicapée</t>
-  </si>
-  <si>
-    <t>4200</t>
-  </si>
-  <si>
-    <t>Etablissements ou Classes d'Enseignement Spécial</t>
-  </si>
-  <si>
-    <t>4300</t>
-  </si>
-  <si>
-    <t>Etablissements et Services pour Adultes Handicapés</t>
-  </si>
-  <si>
-    <t>4400</t>
-  </si>
-  <si>
-    <t>Etablissements et Services pour Personnes Agées</t>
-  </si>
-  <si>
-    <t>4500</t>
-  </si>
-  <si>
-    <t>Etab.et Serv.Sociaux Concourant à la Protection de l'Enfance</t>
-  </si>
-  <si>
-    <t>4600</t>
-  </si>
-  <si>
-    <t>Autres Etab. Accueil, Hébergement, Réadaptation et Services</t>
-  </si>
-  <si>
-    <t>5100</t>
-  </si>
-  <si>
-    <t>6100</t>
-  </si>
-  <si>
-    <t>Etablissements de Formation des Personnels Sanitaires</t>
-  </si>
-  <si>
-    <t>6200</t>
-  </si>
-  <si>
-    <t>Etablissements de Formation des Personnels Sociaux</t>
-  </si>
-  <si>
-    <t>6300</t>
-  </si>
-  <si>
-    <t>Etablissements de Formation Polyvalente</t>
-  </si>
-  <si>
-    <t>0101</t>
-  </si>
-  <si>
-    <t>1101</t>
-  </si>
-  <si>
-    <t>Centres Hospitaliers Régionaux</t>
-  </si>
-  <si>
-    <t>1102</t>
-  </si>
-  <si>
-    <t>Centres Hospitaliers</t>
-  </si>
-  <si>
-    <t>1103</t>
-  </si>
-  <si>
-    <t>Centres Hospitaliers Spécialisés Lutte Maladies Mentales</t>
-  </si>
-  <si>
-    <t>1104</t>
-  </si>
-  <si>
-    <t>Centres de Lutte contre le Cancer</t>
-  </si>
-  <si>
-    <t>1106</t>
-  </si>
-  <si>
-    <t>Hôpitaux Locaux</t>
-  </si>
-  <si>
-    <t>1107</t>
-  </si>
-  <si>
-    <t>Etablissements de santé privé autorisés en SSR</t>
-  </si>
-  <si>
-    <t>1108</t>
-  </si>
-  <si>
-    <t>Centre de Moyen et de Long Séjour</t>
-  </si>
-  <si>
-    <t>1109</t>
-  </si>
-  <si>
-    <t>Etablissements de Soins de Longue Durée</t>
-  </si>
-  <si>
-    <t>1110</t>
-  </si>
-  <si>
-    <t>Etablissements de Soins de Courte Durée</t>
-  </si>
-  <si>
-    <t>1111</t>
-  </si>
-  <si>
-    <t>Autres Etablissements de Lutte contre les Maladies Mentales</t>
-  </si>
-  <si>
-    <t>1112</t>
-  </si>
-  <si>
-    <t>Etablissements d'Enfants à Caractère Sanitaire</t>
-  </si>
-  <si>
-    <t>1113</t>
-  </si>
-  <si>
-    <t>Etablissements de Lutte contre l'Alcoolisme</t>
-  </si>
-  <si>
-    <t>1201</t>
-  </si>
-  <si>
-    <t>Traitements et Soins à Domicile</t>
-  </si>
-  <si>
-    <t>1202</t>
-  </si>
-  <si>
-    <t>Santé Mentale</t>
-  </si>
-  <si>
-    <t>1203</t>
-  </si>
-  <si>
-    <t>Dialyse ambulatoire</t>
-  </si>
-  <si>
-    <t>1204</t>
-  </si>
-  <si>
-    <t>Urgence et Réanimation</t>
-  </si>
-  <si>
-    <t>1205</t>
-  </si>
-  <si>
-    <t>2101</t>
-  </si>
-  <si>
-    <t>Cabinets Libéraux de Médecins</t>
-  </si>
-  <si>
-    <t>2102</t>
-  </si>
-  <si>
-    <t>Cabinet de Groupe</t>
-  </si>
-  <si>
-    <t>2103</t>
-  </si>
-  <si>
-    <t>Autres structures d'exercice libéral</t>
-  </si>
-  <si>
-    <t>2105</t>
-  </si>
-  <si>
-    <t>Cabinet d'Auxiliaires Médicaux</t>
-  </si>
-  <si>
-    <t>2201</t>
-  </si>
-  <si>
-    <t>Dispensaires ou Centres de Soins</t>
-  </si>
-  <si>
-    <t>2202</t>
-  </si>
-  <si>
-    <t>Etablissements de PMI et de Planification Familiale</t>
-  </si>
-  <si>
-    <t>2203</t>
-  </si>
-  <si>
-    <t>Etablissements de Soins Dentaires</t>
-  </si>
-  <si>
-    <t>2204</t>
-  </si>
-  <si>
-    <t>Etablissements ne relevant pas de la Loi Hospitalière</t>
-  </si>
-  <si>
-    <t>2205</t>
-  </si>
-  <si>
-    <t>Etab.de soins relevant du service de santé des armées</t>
-  </si>
-  <si>
-    <t>2206</t>
-  </si>
-  <si>
-    <t>Centres de Santé</t>
-  </si>
-  <si>
-    <t>3101</t>
-  </si>
-  <si>
-    <t>3201</t>
-  </si>
-  <si>
-    <t>3202</t>
-  </si>
-  <si>
-    <t>Commerce de Biens Médicaux</t>
-  </si>
-  <si>
-    <t>3401</t>
-  </si>
-  <si>
-    <t>Transfusion Sanguine</t>
-  </si>
-  <si>
-    <t>3402</t>
-  </si>
-  <si>
-    <t>Conservation et Stockage d'autres Produits Humains</t>
-  </si>
-  <si>
-    <t>3403</t>
-  </si>
-  <si>
-    <t>Centre Antipoison</t>
-  </si>
-  <si>
-    <t>3404</t>
-  </si>
-  <si>
-    <t>Service d'Ambulances</t>
-  </si>
-  <si>
-    <t>3405</t>
-  </si>
-  <si>
-    <t>Installations autonomes de chirurgie esthétique</t>
-  </si>
-  <si>
-    <t>3406</t>
-  </si>
-  <si>
-    <t>Maisons de Naissance</t>
-  </si>
-  <si>
-    <t>3407</t>
-  </si>
-  <si>
-    <t>Etablissements Expérimentaux en Santé</t>
-  </si>
-  <si>
-    <t>3408</t>
-  </si>
-  <si>
-    <t>Centre de ressources transverse</t>
-  </si>
-  <si>
-    <t>3409</t>
-  </si>
-  <si>
-    <t>Services de Prévention et de Santé au Travail (SPST)</t>
-  </si>
-  <si>
-    <t>3410</t>
-  </si>
-  <si>
-    <t>Services d'incendie et de secours</t>
-  </si>
-  <si>
-    <t>4101</t>
-  </si>
-  <si>
-    <t>Etab.Educ.Spéciale pour Déficients Mentaux et Handicapés</t>
-  </si>
-  <si>
-    <t>4102</t>
-  </si>
-  <si>
-    <t>Etab.Educ Spéciale pour Enfants Trouble Conduite et Comport</t>
-  </si>
-  <si>
-    <t>4103</t>
-  </si>
-  <si>
-    <t>Etablissements d'Education Spéciale pour Handicapés Moteurs</t>
-  </si>
-  <si>
-    <t>4104</t>
-  </si>
-  <si>
-    <t>Etab.Education Spéciale pour Déficients Sensoriels</t>
-  </si>
-  <si>
-    <t>4105</t>
-  </si>
-  <si>
-    <t>Etablissements et Services Hébergement Enfants Handicapés</t>
-  </si>
-  <si>
-    <t>4106</t>
-  </si>
-  <si>
-    <t>Services à Domicile ou Ambulatoires pour Handicapés</t>
-  </si>
-  <si>
-    <t>4107</t>
-  </si>
-  <si>
-    <t>Etab. Expérimentaux en Faveur de l'Enfance Handicapée</t>
-  </si>
-  <si>
-    <t>4201</t>
-  </si>
-  <si>
-    <t>Etablissements ou Classes de Pré-Élémentaire et Élémentaire</t>
-  </si>
-  <si>
-    <t>4202</t>
-  </si>
-  <si>
-    <t>Etablissements d'Enseignement Secondaire</t>
-  </si>
-  <si>
-    <t>4301</t>
-  </si>
-  <si>
-    <t>Etab. et Services d'Hébergement pour Adultes Handicapés</t>
-  </si>
-  <si>
-    <t>4302</t>
-  </si>
-  <si>
-    <t>Etab.et Services de Travail Protégé pour Adultes Handicapés</t>
-  </si>
-  <si>
-    <t>4303</t>
-  </si>
-  <si>
-    <t>Etab.et Services de Réinsertion Prof pour Adultes Handicapés</t>
-  </si>
-  <si>
-    <t>4304</t>
-  </si>
-  <si>
-    <t>Etab.Expérimentaux en Faveur des Adultes Handicapés</t>
-  </si>
-  <si>
-    <t>4305</t>
-  </si>
-  <si>
-    <t>Services de Maintien à Domicile pour Handicapés</t>
-  </si>
-  <si>
-    <t>4401</t>
-  </si>
-  <si>
-    <t>Etablissements d'Hébergement pour Personnes Âgées</t>
-  </si>
-  <si>
-    <t>4402</t>
-  </si>
-  <si>
-    <t>Services de Maintien à Domicile pour Personnes Âgées</t>
-  </si>
-  <si>
-    <t>4403</t>
-  </si>
-  <si>
-    <t>Services Sociaux en Faveur des Personnes Âgées</t>
-  </si>
-  <si>
-    <t>4404</t>
-  </si>
-  <si>
-    <t>Etablissements Expérimentaux en Faveur des Personnes Âgées</t>
-  </si>
-  <si>
-    <t>4501</t>
-  </si>
-  <si>
-    <t>Etablissements de l'Aide Sociale à l'Enfance</t>
-  </si>
-  <si>
-    <t>4502</t>
-  </si>
-  <si>
-    <t>Etab.et Services du Ministère de la Justice pour Mineurs</t>
-  </si>
-  <si>
-    <t>4504</t>
-  </si>
-  <si>
-    <t>Services Concourant à la Protection de l'Enfance</t>
-  </si>
-  <si>
-    <t>4505</t>
-  </si>
-  <si>
-    <t>Etab. Expérimentaux en Faveur de l'Enfance Protégée</t>
-  </si>
-  <si>
-    <t>4601</t>
-  </si>
-  <si>
-    <t>Etablissements pour Adultes et Familles en Difficulté</t>
-  </si>
-  <si>
-    <t>4602</t>
-  </si>
-  <si>
-    <t>Autres Etablissements Sociaux d'Hébergement et d'Accueil</t>
-  </si>
-  <si>
-    <t>4603</t>
-  </si>
-  <si>
-    <t>Etablissements Expérimentaux en Faveur des Adultes</t>
-  </si>
-  <si>
-    <t>4604</t>
-  </si>
-  <si>
-    <t>Autres Etablissements médico-sociaux</t>
-  </si>
-  <si>
-    <t>4605</t>
-  </si>
-  <si>
-    <t>Etablissements et services multi-clientèles</t>
-  </si>
-  <si>
-    <t>4606</t>
-  </si>
-  <si>
-    <t>Centres de ressources</t>
-  </si>
-  <si>
-    <t>4607</t>
-  </si>
-  <si>
-    <t>Logements en Structure Collective</t>
-  </si>
-  <si>
-    <t>4608</t>
-  </si>
-  <si>
-    <t>Protection des majeurs</t>
-  </si>
-  <si>
-    <t>4609</t>
-  </si>
-  <si>
-    <t>Centres prestataires de services pr personnes cérébro-lésées</t>
-  </si>
-  <si>
-    <t>5101</t>
-  </si>
-  <si>
-    <t>Etablissements Garde d'Enfants d'Age pré-Scolaire</t>
-  </si>
-  <si>
-    <t>5102</t>
-  </si>
-  <si>
-    <t>Etablissements d'Hébergement pour Enfants d'Age Scolaire</t>
-  </si>
-  <si>
-    <t>5103</t>
-  </si>
-  <si>
-    <t>Etablissements Sociaux pour Loisirs et Vacances</t>
-  </si>
-  <si>
-    <t>5104</t>
-  </si>
-  <si>
-    <t>Etablissements ou Services Divers d'Aide à la Famille</t>
-  </si>
-  <si>
-    <t>6101</t>
-  </si>
-  <si>
-    <t>6102</t>
-  </si>
-  <si>
-    <t>Etablissements de Formation des Personnels Techniques</t>
-  </si>
-  <si>
-    <t>6103</t>
-  </si>
-  <si>
-    <t>Autres Etablissements de Formation des Personnels Techniques</t>
-  </si>
-  <si>
-    <t>6201</t>
-  </si>
-  <si>
-    <t>6301</t>
-  </si>
-  <si>
-    <t>001</t>
-  </si>
-  <si>
-    <t>Autres lits de m.R.</t>
-  </si>
-  <si>
-    <t>002</t>
-  </si>
-  <si>
-    <t>Autres places de l-f.</t>
-  </si>
-  <si>
-    <t>003</t>
-  </si>
-  <si>
-    <t>Autres lits de l-s</t>
-  </si>
-  <si>
-    <t>101</t>
-  </si>
-  <si>
-    <t>Centre Hospitalier Régional (C.H.R.)</t>
-  </si>
-  <si>
-    <t>106</t>
-  </si>
-  <si>
-    <t>Centre hospitalier, ex Hôpital local</t>
-  </si>
-  <si>
-    <t>108</t>
-  </si>
-  <si>
-    <t>Etablissement de Convalescence et de Repos</t>
-  </si>
-  <si>
-    <t>109</t>
-  </si>
-  <si>
-    <t>Etablissement de santé privé autorisé en SSR</t>
-  </si>
-  <si>
-    <t>112</t>
-  </si>
-  <si>
-    <t>Centre de Convalescence Cure ou Réadaptation</t>
-  </si>
-  <si>
-    <t>114</t>
-  </si>
-  <si>
-    <t>Hôpital des armées</t>
-  </si>
-  <si>
-    <t>115</t>
-  </si>
-  <si>
-    <t>Etablissement de Soins du Service de Santé des Armées</t>
-  </si>
-  <si>
-    <t>119</t>
-  </si>
-  <si>
-    <t>Maison de Régime</t>
-  </si>
-  <si>
-    <t>122</t>
-  </si>
-  <si>
-    <t>Etablissement Soins Obstétriques Chirurgico-Gynécologiques</t>
-  </si>
-  <si>
-    <t>124</t>
-  </si>
-  <si>
-    <t>Centre de Santé</t>
-  </si>
-  <si>
-    <t>125</t>
-  </si>
-  <si>
-    <t>Centre de Santé Dentaire</t>
-  </si>
-  <si>
-    <t>126</t>
-  </si>
-  <si>
-    <t>Etablissement Thermal</t>
-  </si>
-  <si>
-    <t>127</t>
-  </si>
-  <si>
-    <t>Hospitalisation à Domicile</t>
-  </si>
-  <si>
-    <t>128</t>
-  </si>
-  <si>
-    <t>Etablissement de Soins Chirurgicaux</t>
-  </si>
-  <si>
-    <t>129</t>
-  </si>
-  <si>
-    <t>Etablissement de Soins Médicaux</t>
-  </si>
-  <si>
-    <t>130</t>
-  </si>
-  <si>
-    <t>Centre de Soins Médicaux</t>
-  </si>
-  <si>
-    <t>131</t>
-  </si>
-  <si>
-    <t>Centre de Lutte Contre Cancer</t>
-  </si>
-  <si>
-    <t>132</t>
-  </si>
-  <si>
-    <t>Etablissement de Transfusion Sanguine</t>
-  </si>
-  <si>
-    <t>135</t>
-  </si>
-  <si>
-    <t>Etablissement Réadaptation Fonctionnelle</t>
-  </si>
-  <si>
-    <t>136</t>
-  </si>
-  <si>
-    <t>Banque de Sperme</t>
-  </si>
-  <si>
-    <t>137</t>
-  </si>
-  <si>
-    <t>Banque d'Organes</t>
-  </si>
-  <si>
-    <t>138</t>
-  </si>
-  <si>
-    <t>Centre de Dialyse Périodique</t>
-  </si>
-  <si>
-    <t>139</t>
-  </si>
-  <si>
-    <t>Centre de Dialyse et d'entraînement à la Dialyse</t>
-  </si>
-  <si>
-    <t>140</t>
-  </si>
-  <si>
-    <t>Centre d'Entraînement à la Dialyse</t>
-  </si>
-  <si>
-    <t>141</t>
-  </si>
-  <si>
-    <t>Centre de dialyse</t>
-  </si>
-  <si>
-    <t>142</t>
-  </si>
-  <si>
-    <t>Dispensaire Antituberculeux</t>
-  </si>
-  <si>
-    <t>143</t>
-  </si>
-  <si>
-    <t>Centre de Vaccination BCG</t>
-  </si>
-  <si>
-    <t>144</t>
-  </si>
-  <si>
-    <t>Etablissement de Lutte Contre la Tuberculose</t>
-  </si>
-  <si>
-    <t>146</t>
-  </si>
-  <si>
-    <t>Structure d'Alternative à la dialyse en centre</t>
-  </si>
-  <si>
-    <t>156</t>
-  </si>
-  <si>
-    <t>Centre Médico-Psychologique (C.M.P.)</t>
-  </si>
-  <si>
-    <t>157</t>
-  </si>
-  <si>
-    <t>Centre de Postcure</t>
-  </si>
-  <si>
-    <t>159</t>
-  </si>
-  <si>
-    <t>Centre Parental</t>
-  </si>
-  <si>
-    <t>160</t>
-  </si>
-  <si>
-    <t>Centre de Soins Spécifiques pour Toxicomanes (C.S.S.T.)</t>
-  </si>
-  <si>
-    <t>161</t>
-  </si>
-  <si>
-    <t>Maison de Santé pour Maladies Mentales</t>
-  </si>
-  <si>
-    <t>162</t>
-  </si>
-  <si>
-    <t>Centre de Cure Ambulatoire en Alcoologie (C.C.A.A.)</t>
-  </si>
-  <si>
-    <t>163</t>
-  </si>
-  <si>
-    <t>Maison d'Enfants à Caractère Sanitaire Temporaire</t>
-  </si>
-  <si>
-    <t>164</t>
-  </si>
-  <si>
-    <t>Etablissements Expérimentaux Accueil de la Petite Enfance</t>
-  </si>
-  <si>
-    <t>165</t>
-  </si>
-  <si>
-    <t>Appartement de Coordination Thérapeutique (A.C.T.)</t>
-  </si>
-  <si>
-    <t>166</t>
-  </si>
-  <si>
-    <t>Etablissement d'Accueil Mère-Enfant</t>
-  </si>
-  <si>
-    <t>167</t>
-  </si>
-  <si>
-    <t>Crèche Collective</t>
-  </si>
-  <si>
-    <t>168</t>
-  </si>
-  <si>
-    <t>Service Accueil Familial pour la Petite Enfance</t>
-  </si>
-  <si>
-    <t>169</t>
-  </si>
-  <si>
-    <t>Crèche Multi Accueil Collectif et Familial</t>
-  </si>
-  <si>
-    <t>170</t>
-  </si>
-  <si>
-    <t>Halte Garderie</t>
-  </si>
-  <si>
-    <t>171</t>
-  </si>
-  <si>
-    <t>Garderie et Jardin d'Enfants</t>
-  </si>
-  <si>
-    <t>172</t>
-  </si>
-  <si>
-    <t>Pouponnière à Caractère Social</t>
-  </si>
-  <si>
-    <t>173</t>
-  </si>
-  <si>
-    <t>Pouponnière à Caractère Sanitaire</t>
-  </si>
-  <si>
-    <t>174</t>
-  </si>
-  <si>
-    <t>Etablissement d'Accueil Collectif Régulier et Occasionnel</t>
-  </si>
-  <si>
-    <t>175</t>
-  </si>
-  <si>
-    <t>Foyer de l'Enfance</t>
-  </si>
-  <si>
-    <t>176</t>
-  </si>
-  <si>
-    <t>Village d'Enfants</t>
-  </si>
-  <si>
-    <t>177</t>
-  </si>
-  <si>
-    <t>Maison d'Enfants à Caractère Social</t>
-  </si>
-  <si>
-    <t>178</t>
-  </si>
-  <si>
-    <t>Ctre.Accueil- Accomp.Réduc.Risq.Usag. Drogues (C.A.A.R.U.D.)</t>
-  </si>
-  <si>
-    <t>179</t>
-  </si>
-  <si>
-    <t>Maison d'Enfants à Caractère Sanitaire Permanente</t>
-  </si>
-  <si>
-    <t>180</t>
-  </si>
-  <si>
-    <t>Lits Halte Soins Santé (L.H.S.S.)</t>
-  </si>
-  <si>
-    <t>181</t>
-  </si>
-  <si>
-    <t>Maison Familiale de Vacances</t>
-  </si>
-  <si>
-    <t>182</t>
-  </si>
-  <si>
-    <t>Service d'Éducation Spéciale et de Soins à Domicile</t>
-  </si>
-  <si>
-    <t>183</t>
-  </si>
-  <si>
-    <t>Institut Médico-Educatif (I.M.E.)</t>
-  </si>
-  <si>
-    <t>184</t>
-  </si>
-  <si>
-    <t>Institut Médico-Pédagogique (I.M.P.)</t>
-  </si>
-  <si>
-    <t>185</t>
-  </si>
-  <si>
-    <t>Institut Médico-Professionnel (I.M.Pro.)</t>
-  </si>
-  <si>
-    <t>186</t>
-  </si>
-  <si>
-    <t>Institut Thérapeutique Éducatif et Pédagogique (I.T.E.P.)</t>
-  </si>
-  <si>
-    <t>188</t>
-  </si>
-  <si>
-    <t>Etablissement pour Enfants ou Adolescents Polyhandicapés</t>
-  </si>
-  <si>
-    <t>189</t>
-  </si>
-  <si>
-    <t>Centre Médico-Psycho-Pédagogique (C.M.P.P.)</t>
-  </si>
-  <si>
-    <t>190</t>
-  </si>
-  <si>
-    <t>Centre Action Médico-Sociale Précoce (C.A.M.S.P.)</t>
-  </si>
-  <si>
-    <t>191</t>
-  </si>
-  <si>
-    <t>Etablissement pour Déficients Moteurs Cérébraux</t>
-  </si>
-  <si>
-    <t>192</t>
-  </si>
-  <si>
-    <t>Institut d'éducation motrice</t>
-  </si>
-  <si>
-    <t>193</t>
-  </si>
-  <si>
-    <t>Etablissement pour Déficients Moteurs et Moteurs Cérébraux</t>
-  </si>
-  <si>
-    <t>194</t>
-  </si>
-  <si>
-    <t>Institut pour Déficients Visuels</t>
-  </si>
-  <si>
-    <t>195</t>
-  </si>
-  <si>
-    <t>Institut pour Déficients Auditifs</t>
-  </si>
-  <si>
-    <t>196</t>
-  </si>
-  <si>
-    <t>Institut d'Education Sensorielle Sourd-Aveugle</t>
-  </si>
-  <si>
-    <t>197</t>
-  </si>
-  <si>
-    <t>Centre soins accompagnement prévention addictologie (CSAPA)</t>
-  </si>
-  <si>
-    <t>198</t>
-  </si>
-  <si>
-    <t>Établissement et Service de Préorientation</t>
-  </si>
-  <si>
-    <t>199</t>
-  </si>
-  <si>
-    <t>Hospice</t>
-  </si>
-  <si>
-    <t>200</t>
-  </si>
-  <si>
-    <t>Maison de Retraite</t>
-  </si>
-  <si>
-    <t>202</t>
-  </si>
-  <si>
-    <t>Résidences autonomie</t>
-  </si>
-  <si>
-    <t>205</t>
-  </si>
-  <si>
-    <t>Foyer Club Restaurant</t>
-  </si>
-  <si>
-    <t>207</t>
-  </si>
-  <si>
-    <t>Centre de Jour pour Personnes Agées</t>
-  </si>
-  <si>
-    <t>208</t>
-  </si>
-  <si>
-    <t>Service d'Aide Ménagère à Domicile</t>
-  </si>
-  <si>
-    <t>209</t>
-  </si>
-  <si>
-    <t>Service autonomie aide et soins (SAAS)</t>
-  </si>
-  <si>
-    <t>212</t>
-  </si>
-  <si>
-    <t>Alarme Médico-Sociale</t>
-  </si>
-  <si>
-    <t>213</t>
-  </si>
-  <si>
-    <t>Lits d'Accueil Médicalisés (L.A.M.)</t>
-  </si>
-  <si>
-    <t>214</t>
-  </si>
-  <si>
-    <t>Centre Hébergement &amp; Réinsertion Sociale (C.H.R.S.)</t>
-  </si>
-  <si>
-    <t>215</t>
-  </si>
-  <si>
-    <t>Maison Relai</t>
-  </si>
-  <si>
-    <t>216</t>
-  </si>
-  <si>
-    <t>Résidence Hôtelière à Vocation Sociale (R.H.V.S)</t>
-  </si>
-  <si>
-    <t>217</t>
-  </si>
-  <si>
-    <t>Cité de Transit</t>
-  </si>
-  <si>
-    <t>218</t>
-  </si>
-  <si>
-    <t>Aire Station Nomades</t>
-  </si>
-  <si>
-    <t>219</t>
-  </si>
-  <si>
-    <t>Autre Centre d'Accueil</t>
-  </si>
-  <si>
-    <t>220</t>
-  </si>
-  <si>
-    <t>Centre Social</t>
-  </si>
-  <si>
-    <t>221</t>
-  </si>
-  <si>
-    <t>Bureau d'Aide Psychologique Universitaire (B.A.P.U.)</t>
-  </si>
-  <si>
-    <t>223</t>
-  </si>
-  <si>
-    <t>Protection Maternelle et Infantile (P.M.I.)</t>
-  </si>
-  <si>
-    <t>224</t>
-  </si>
-  <si>
-    <t>Etablissement de Consultation Pré et Post-natale</t>
-  </si>
-  <si>
-    <t>225</t>
-  </si>
-  <si>
-    <t>Consultations de Nourrissons</t>
-  </si>
-  <si>
-    <t>228</t>
-  </si>
-  <si>
-    <t>Centre de Santé Sexuelle</t>
-  </si>
-  <si>
-    <t>229</t>
-  </si>
-  <si>
-    <t>Consultation Problèmes naissance</t>
-  </si>
-  <si>
-    <t>230</t>
-  </si>
-  <si>
-    <t>Etablissement Consultation Protection Infantile</t>
-  </si>
-  <si>
-    <t>231</t>
-  </si>
-  <si>
-    <t>Etablissement Information Consultation Conseil Familial</t>
-  </si>
-  <si>
-    <t>233</t>
-  </si>
-  <si>
-    <t>Lactarium</t>
-  </si>
-  <si>
-    <t>236</t>
-  </si>
-  <si>
-    <t>Centre Placement Familial Socio-Educatif (C.P.F.S.E.)</t>
-  </si>
-  <si>
-    <t>237</t>
-  </si>
-  <si>
-    <t>Centre de Placement Familial Spécialisé</t>
-  </si>
-  <si>
-    <t>238</t>
-  </si>
-  <si>
-    <t>Centre d'Accueil Familial Spécialisé</t>
-  </si>
-  <si>
-    <t>241</t>
-  </si>
-  <si>
-    <t>Établissement de Placement</t>
-  </si>
-  <si>
-    <t>242</t>
-  </si>
-  <si>
-    <t>Service d’Activité de Jour</t>
-  </si>
-  <si>
-    <t>246</t>
-  </si>
-  <si>
-    <t>Etablissement et Service d'Aide par le Travail (E.S.A.T.)</t>
-  </si>
-  <si>
-    <t>247</t>
-  </si>
-  <si>
-    <t>Entreprise adaptée</t>
-  </si>
-  <si>
-    <t>249</t>
-  </si>
-  <si>
-    <t>Établissement et Service de Réadaptation Professionnelle</t>
-  </si>
-  <si>
-    <t>250</t>
-  </si>
-  <si>
-    <t>Centre Réentrainement au travail</t>
-  </si>
-  <si>
-    <t>251</t>
-  </si>
-  <si>
-    <t>Maison Vacances pour Handicapés</t>
-  </si>
-  <si>
-    <t>252</t>
-  </si>
-  <si>
-    <t>Foyer Hébergement Adultes Handicapés</t>
-  </si>
-  <si>
-    <t>253</t>
-  </si>
-  <si>
-    <t>Foyer d'Accueil Polyvalent pour Adultes Handicapés</t>
-  </si>
-  <si>
-    <t>255</t>
-  </si>
-  <si>
-    <t>Maison d'Accueil Spécialisée (M.A.S.)</t>
-  </si>
-  <si>
-    <t>256</t>
-  </si>
-  <si>
-    <t>Foyer Travailleurs Migrants non transformé en Résidence Soc.</t>
-  </si>
-  <si>
-    <t>257</t>
-  </si>
-  <si>
-    <t>Foyers de jeunes travailleurs</t>
-  </si>
-  <si>
-    <t>258</t>
-  </si>
-  <si>
-    <t>Maisons Relais - Pensions de Famille</t>
-  </si>
-  <si>
-    <t>259</t>
-  </si>
-  <si>
-    <t>Autres résidences sociales</t>
-  </si>
-  <si>
-    <t>261</t>
-  </si>
-  <si>
-    <t>D.D.A.S.S.</t>
-  </si>
-  <si>
-    <t>262</t>
-  </si>
-  <si>
-    <t>Etablissement Régional d'Enseignement Adapté</t>
-  </si>
-  <si>
-    <t>265</t>
-  </si>
-  <si>
-    <t>Section Education Spéciale Classe Atelier</t>
-  </si>
-  <si>
-    <t>266</t>
-  </si>
-  <si>
-    <t>Dispensaire Antivénérien</t>
-  </si>
-  <si>
-    <t>267</t>
-  </si>
-  <si>
-    <t>Dispensaire Antihansénien</t>
-  </si>
-  <si>
-    <t>268</t>
-  </si>
-  <si>
-    <t>Centre Médico-Scolaire</t>
-  </si>
-  <si>
-    <t>269</t>
-  </si>
-  <si>
-    <t>Centre de Médecine Universitaire</t>
-  </si>
-  <si>
-    <t>270</t>
-  </si>
-  <si>
-    <t>Centre de Médecine Sportive</t>
-  </si>
-  <si>
-    <t>271</t>
-  </si>
-  <si>
-    <t>Maison d'accueil Hospitalière</t>
-  </si>
-  <si>
-    <t>272</t>
-  </si>
-  <si>
-    <t>Ecole d'ambulanciers</t>
-  </si>
-  <si>
-    <t>273</t>
-  </si>
-  <si>
-    <t>Institut de formation en soins infirmiers (I.F.S.I.)</t>
-  </si>
-  <si>
-    <t>274</t>
-  </si>
-  <si>
-    <t>Ecole de sages_femmes</t>
-  </si>
-  <si>
-    <t>275</t>
-  </si>
-  <si>
-    <t>Ecole de masseurs-kinésithérapeutes</t>
-  </si>
-  <si>
-    <t>276</t>
-  </si>
-  <si>
-    <t>Ecole de laborantins d'analyses médicales</t>
-  </si>
-  <si>
-    <t>277</t>
-  </si>
-  <si>
-    <t>Ecole de péricultrices</t>
-  </si>
-  <si>
-    <t>278</t>
-  </si>
-  <si>
-    <t>Etablissement de formation polyvalent</t>
-  </si>
-  <si>
-    <t>279</t>
-  </si>
-  <si>
-    <t>Ecole de service social</t>
-  </si>
-  <si>
-    <t>280</t>
-  </si>
-  <si>
-    <t>Ecole d'éducateurs spécialisés</t>
-  </si>
-  <si>
-    <t>281</t>
-  </si>
-  <si>
-    <t>Centre de formation d'aides soignants</t>
-  </si>
-  <si>
-    <t>282</t>
-  </si>
-  <si>
-    <t>Ecole de pédicures-podologues</t>
-  </si>
-  <si>
-    <t>283</t>
-  </si>
-  <si>
-    <t>Ecole de manipulateurs d'électro-radiologie</t>
-  </si>
-  <si>
-    <t>284</t>
-  </si>
-  <si>
-    <t>Ecole de travailleuses familiales</t>
-  </si>
-  <si>
-    <t>285</t>
-  </si>
-  <si>
-    <t>Centres de Loisirs sans Hébergement</t>
-  </si>
-  <si>
-    <t>286</t>
-  </si>
-  <si>
-    <t>Club Equipe de Prévention</t>
-  </si>
-  <si>
-    <t>289</t>
-  </si>
-  <si>
-    <t>Centre de Soins Infirmiers</t>
-  </si>
-  <si>
-    <t>292</t>
-  </si>
-  <si>
-    <t>Centre Hospitalier Spécialisé lutte Maladies Mentales</t>
-  </si>
-  <si>
-    <t>294</t>
-  </si>
-  <si>
-    <t>Centre de Consultations Cancer</t>
-  </si>
-  <si>
-    <t>295</t>
-  </si>
-  <si>
-    <t>Service AEMO et AED</t>
-  </si>
-  <si>
-    <t>297</t>
-  </si>
-  <si>
-    <t>Dispensaire Polyvalent</t>
-  </si>
-  <si>
-    <t>300</t>
-  </si>
-  <si>
-    <t>Ecoles Formant aux Professions Sanitaires</t>
-  </si>
-  <si>
-    <t>303</t>
-  </si>
-  <si>
-    <t>Ecole de conseillers en économie sociale et familiale</t>
-  </si>
-  <si>
-    <t>304</t>
-  </si>
-  <si>
-    <t>Ecole d'ergothérapeutes</t>
-  </si>
-  <si>
-    <t>305</t>
-  </si>
-  <si>
-    <t>Ecole de psycho-motriciens</t>
-  </si>
-  <si>
-    <t>306</t>
-  </si>
-  <si>
-    <t>Ecole d'infirmiers anesthésistes</t>
-  </si>
-  <si>
-    <t>307</t>
-  </si>
-  <si>
-    <t>Ecole d'infirmiers de bloc opératoire</t>
-  </si>
-  <si>
-    <t>308</t>
-  </si>
-  <si>
-    <t>Centre de formation professionnelle de secteur psychiatrique</t>
-  </si>
-  <si>
-    <t>309</t>
-  </si>
-  <si>
-    <t>Ecole de cadres infirmiers</t>
-  </si>
-  <si>
-    <t>310</t>
-  </si>
-  <si>
-    <t>Ecole de cadres de secteur psychiatrique</t>
-  </si>
-  <si>
-    <t>311</t>
-  </si>
-  <si>
-    <t>Ecole de cadres de masseurs-kinésithérapeutes</t>
-  </si>
-  <si>
-    <t>312</t>
-  </si>
-  <si>
-    <t>Ecole de cadres de manipulateurs d'électro-radiologie</t>
-  </si>
-  <si>
-    <t>313</t>
-  </si>
-  <si>
-    <t>Ecole d'éducateurs de jeunes enfants</t>
-  </si>
-  <si>
-    <t>314</t>
-  </si>
-  <si>
-    <t>Ecole d'éducateurs techniques spécialisés</t>
-  </si>
-  <si>
-    <t>315</t>
-  </si>
-  <si>
-    <t>Ecole de moniteurs-éducateurs</t>
-  </si>
-  <si>
-    <t>316</t>
-  </si>
-  <si>
-    <t>Ecole d'aides médico-psychologiques</t>
-  </si>
-  <si>
-    <t>317</t>
-  </si>
-  <si>
-    <t>Ecole d'animateurs socio-éducatifs</t>
-  </si>
-  <si>
-    <t>319</t>
-  </si>
-  <si>
-    <t>Inst. régional de formation des travailleurs sociaux</t>
-  </si>
-  <si>
-    <t>320</t>
-  </si>
-  <si>
-    <t>S.A.M.U. et Centre 15</t>
-  </si>
-  <si>
-    <t>321</t>
-  </si>
-  <si>
-    <t>Unité Mobile Hospitalière</t>
-  </si>
-  <si>
-    <t>322</t>
-  </si>
-  <si>
-    <t>Centre Rég.Informatiq.Hospit.</t>
-  </si>
-  <si>
-    <t>324</t>
-  </si>
-  <si>
-    <t>Logement Foyer non Spécialisé</t>
-  </si>
-  <si>
-    <t>326</t>
-  </si>
-  <si>
-    <t>Ecole de cadres</t>
-  </si>
-  <si>
-    <t>327</t>
-  </si>
-  <si>
-    <t>328</t>
-  </si>
-  <si>
-    <t>Centre Consultation Soins Dentaire</t>
-  </si>
-  <si>
-    <t>329</t>
-  </si>
-  <si>
-    <t>Sectorisation Psychiatrique</t>
-  </si>
-  <si>
-    <t>330</t>
-  </si>
-  <si>
-    <t>Ecoles Formant aux Professions Sociales</t>
-  </si>
-  <si>
-    <t>340</t>
-  </si>
-  <si>
-    <t>Service mandataire judiciaire à la protection des majeurs</t>
-  </si>
-  <si>
-    <t>341</t>
-  </si>
-  <si>
-    <t>Service dédié mesures d'accompagnement social personnalisé</t>
-  </si>
-  <si>
-    <t>342</t>
-  </si>
-  <si>
-    <t>Service d'information et de soutien aux tuteurs familiaux</t>
-  </si>
-  <si>
-    <t>343</t>
-  </si>
-  <si>
-    <t>Equipe Préparation et Suite Reclassement (EPSR)</t>
-  </si>
-  <si>
-    <t>344</t>
-  </si>
-  <si>
-    <t>Service délégué aux prestations familiales</t>
-  </si>
-  <si>
-    <t>345</t>
-  </si>
-  <si>
-    <t>Service Tutelle Prestation Sociale</t>
-  </si>
-  <si>
-    <t>346</t>
-  </si>
-  <si>
-    <t>Service de Travailleuses Familiales</t>
-  </si>
-  <si>
-    <t>347</t>
-  </si>
-  <si>
-    <t>Centre d'Examens de Santé</t>
-  </si>
-  <si>
-    <t>349</t>
-  </si>
-  <si>
-    <t>Ecole de cadres de sages-femmes</t>
-  </si>
-  <si>
-    <t>350</t>
-  </si>
-  <si>
-    <t>Centre de formation d'auxiliaires de puériculture</t>
-  </si>
-  <si>
-    <t>352</t>
-  </si>
-  <si>
-    <t>Centre de Psychothérapie</t>
-  </si>
-  <si>
-    <t>353</t>
-  </si>
-  <si>
-    <t>Hôpital de Jour Spécialités Médicales</t>
-  </si>
-  <si>
-    <t>354</t>
-  </si>
-  <si>
-    <t>Service de Soins Infirmiers A Domicile (S.S.I.A.D)</t>
-  </si>
-  <si>
-    <t>355</t>
-  </si>
-  <si>
-    <t>Centre Hospitalier (C.H.)</t>
-  </si>
-  <si>
-    <t>357</t>
-  </si>
-  <si>
-    <t>Association Aide aux Insuffisants Respiratoires</t>
-  </si>
-  <si>
-    <t>359</t>
-  </si>
-  <si>
-    <t>Centre Circonscription Sanitaire et Sociale</t>
-  </si>
-  <si>
-    <t>361</t>
-  </si>
-  <si>
-    <t>Centre de Cure Médicale</t>
-  </si>
-  <si>
-    <t>362</t>
-  </si>
-  <si>
-    <t>Etablissement de Soins Longue Durée</t>
-  </si>
-  <si>
-    <t>363</t>
-  </si>
-  <si>
-    <t>Centre moyen et long séjour</t>
-  </si>
-  <si>
-    <t>365</t>
-  </si>
-  <si>
-    <t>Etablissement de Soins Pluridisciplinaire</t>
-  </si>
-  <si>
-    <t>366</t>
-  </si>
-  <si>
-    <t>Atelier Thérapeutique</t>
-  </si>
-  <si>
-    <t>367</t>
-  </si>
-  <si>
-    <t>Maison d'Enfants non Conventionnée ni Habilitée</t>
-  </si>
-  <si>
-    <t>368</t>
-  </si>
-  <si>
-    <t>Service de Repas à Domicile</t>
-  </si>
-  <si>
-    <t>369</t>
-  </si>
-  <si>
-    <t>Centre Adaptation Vie Active (C.A.V.A.)</t>
-  </si>
-  <si>
-    <t>370</t>
-  </si>
-  <si>
-    <t>Etablissement Expérimental pour personnes handicapées</t>
-  </si>
-  <si>
-    <t>371</t>
-  </si>
-  <si>
-    <t>Service Action Socio-Educative pour Familles en difficulté</t>
-  </si>
-  <si>
-    <t>373</t>
-  </si>
-  <si>
-    <t>Centre de formation supérieure des travailleurs sociaux</t>
-  </si>
-  <si>
-    <t>374</t>
-  </si>
-  <si>
-    <t>Ecole Nationale Santé Publique (E.N.S.P.)</t>
-  </si>
-  <si>
-    <t>375</t>
-  </si>
-  <si>
-    <t>Classe d'Adaptation</t>
-  </si>
-  <si>
-    <t>376</t>
-  </si>
-  <si>
-    <t>Classe Spéciale Ecole Primaire</t>
-  </si>
-  <si>
-    <t>377</t>
-  </si>
-  <si>
-    <t>Etablissement Expérimental pour Enfance Handicapée</t>
-  </si>
-  <si>
-    <t>378</t>
-  </si>
-  <si>
-    <t>Etablissement Expérimental Enfance Protégée</t>
-  </si>
-  <si>
-    <t>379</t>
-  </si>
-  <si>
-    <t>Etablissement Expérimental pour Adultes Handicapés</t>
-  </si>
-  <si>
-    <t>380</t>
-  </si>
-  <si>
-    <t>Etablissement Expérimental Autres Adultes</t>
-  </si>
-  <si>
-    <t>381</t>
-  </si>
-  <si>
-    <t>Etablissement Expérimental pour Personnes Agées</t>
-  </si>
-  <si>
-    <t>382</t>
-  </si>
-  <si>
-    <t>Foyer de Vie pour Adultes Handicapés</t>
-  </si>
-  <si>
-    <t>386</t>
-  </si>
-  <si>
-    <t>Ecole Secondaire Spéciale</t>
-  </si>
-  <si>
-    <t>390</t>
-  </si>
-  <si>
-    <t>Etablissement d'Accueil Temporaire d'Enfants Handicapés</t>
-  </si>
-  <si>
-    <t>393</t>
-  </si>
-  <si>
-    <t>Autre résidence But lucratif pr personnes Âgées</t>
-  </si>
-  <si>
-    <t>394</t>
-  </si>
-  <si>
-    <t>Etablissement d'Accueil Temporaire pour Personnes Agées</t>
-  </si>
-  <si>
-    <t>395</t>
-  </si>
-  <si>
-    <t>Etablissement d'Accueil Temporaire pour Adultes Handicapés</t>
-  </si>
-  <si>
-    <t>396</t>
-  </si>
-  <si>
-    <t>Foyer Hébergement Enfants et Adolescents Handicapés</t>
-  </si>
-  <si>
-    <t>397</t>
-  </si>
-  <si>
-    <t>Service Auxiliaire de Vie pour Handicapés</t>
-  </si>
-  <si>
-    <t>398</t>
-  </si>
-  <si>
-    <t>Crèche Parentale</t>
-  </si>
-  <si>
-    <t>399</t>
-  </si>
-  <si>
-    <t>Halte Garderie Parentale</t>
-  </si>
-  <si>
-    <t>400</t>
-  </si>
-  <si>
-    <t>Centre de Services pour Associations</t>
-  </si>
-  <si>
-    <t>401</t>
-  </si>
-  <si>
-    <t>D.R.A.S.S.</t>
-  </si>
-  <si>
-    <t>402</t>
-  </si>
-  <si>
-    <t>Jardin d'Enfants Spécialisé</t>
-  </si>
-  <si>
-    <t>403</t>
-  </si>
-  <si>
-    <t>Service Social Spécialisé ou Polyvalent de Catégorie</t>
-  </si>
-  <si>
-    <t>404</t>
-  </si>
-  <si>
-    <t>Etablissement Acc.Collect.Parental Régulier &amp; Occasionnel</t>
-  </si>
-  <si>
-    <t>405</t>
-  </si>
-  <si>
-    <t>Service Social Polyvalent de Secteur</t>
-  </si>
-  <si>
-    <t>411</t>
-  </si>
-  <si>
-    <t>Intermédiaire de Placement Social</t>
-  </si>
-  <si>
-    <t>412</t>
-  </si>
-  <si>
-    <t>Appartement Thérapeutique</t>
-  </si>
-  <si>
-    <t>413</t>
-  </si>
-  <si>
-    <t>C.E.C.O.S</t>
-  </si>
-  <si>
-    <t>414</t>
-  </si>
-  <si>
-    <t>Centre Anti Poison</t>
-  </si>
-  <si>
-    <t>415</t>
-  </si>
-  <si>
-    <t>Service Médico-Psychologique Régional (S.M.P.R.)</t>
-  </si>
-  <si>
-    <t>418</t>
-  </si>
-  <si>
-    <t>Service d'Enquêtes Sociales (S.E.S.)</t>
-  </si>
-  <si>
-    <t>419</t>
-  </si>
-  <si>
-    <t>Centre d'Accueil Toxicomanes</t>
-  </si>
-  <si>
-    <t>420</t>
-  </si>
-  <si>
-    <t>Entreprise d'Insertion</t>
-  </si>
-  <si>
-    <t>421</t>
-  </si>
-  <si>
-    <t>Centre d'enseignement aux secours d'urgence</t>
-  </si>
-  <si>
-    <t>422</t>
-  </si>
-  <si>
-    <t>Traitements Spécialisés à Domicile</t>
-  </si>
-  <si>
-    <t>423</t>
-  </si>
-  <si>
-    <t>Ecole des cadres de laborantins d'analyses médicales</t>
-  </si>
-  <si>
     <t>Centre d'Accueil Thérapeutique à temps partiel (C.A.T.T.P.)</t>
   </si>
   <si>
-    <t>426</t>
-  </si>
-  <si>
     <t>Syndicat Inter Hospitalier (S.I.H.)</t>
   </si>
   <si>
@@ -2753,6 +2753,15 @@
   </si>
   <si>
     <t>Espace Santé Jeunes (ESJ)</t>
+  </si>
+  <si>
+    <t>704</t>
+  </si>
+  <si>
+    <t>Autre service territorial</t>
+  </si>
+  <si>
+    <t>Points locaux d'information dédiés aux personnes âgées. Ces services peuvent être rattachés à des CCAS ( Centre Communaux d'Action Sociale)</t>
   </si>
 </sst>
 </file>
@@ -3220,7 +3229,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D426"/>
+  <dimension ref="A1:D427"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -7310,10 +7319,10 @@
         <v>76</v>
       </c>
       <c r="B341" t="s" s="2">
-        <v>34</v>
+        <v>743</v>
       </c>
       <c r="C341" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="D341" s="2"/>
     </row>
@@ -7322,7 +7331,7 @@
         <v>76</v>
       </c>
       <c r="B342" t="s" s="2">
-        <v>744</v>
+        <v>34</v>
       </c>
       <c r="C342" t="s" s="2">
         <v>745</v>
@@ -8344,6 +8353,20 @@
         <v>912</v>
       </c>
       <c r="D426" s="2"/>
+    </row>
+    <row r="427">
+      <c r="A427" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="B427" t="s" s="2">
+        <v>913</v>
+      </c>
+      <c r="C427" t="s" s="2">
+        <v>914</v>
+      </c>
+      <c r="D427" t="s" s="2">
+        <v>915</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/ig/DM_FINESS_New/CodeSystem-tre-r397-categorie-entite-geographique-exercice.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-tre-r397-categorie-entite-geographique-exercice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1367" uniqueCount="916">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1375" uniqueCount="922">
   <si>
     <t>Property</t>
   </si>
@@ -233,6 +233,24 @@
   </si>
   <si>
     <t>boolean</t>
+  </si>
+  <si>
+    <t>ror</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#ror</t>
+  </si>
+  <si>
+    <t>Permet de définir les codes concepts uilisés par le ROR</t>
+  </si>
+  <si>
+    <t>cisis</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#cisis</t>
+  </si>
+  <si>
+    <t>Permet de définir les codes concepts uilisés par le CISIS</t>
   </si>
   <si>
     <t>Level</t>
@@ -3065,7 +3083,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -3219,6 +3237,34 @@
         <v>71</v>
       </c>
       <c r="D11" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="C12" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="D12" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="C13" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="D13" t="s" s="2">
         <v>72</v>
       </c>
     </row>
@@ -3234,5138 +3280,5138 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="B1" t="s" s="1">
         <v>35</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>75</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="D2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="D3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="D4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="D5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="D6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="D7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="C8" t="s" s="2">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C9" t="s" s="2">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="D9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="D10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="D11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="D12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="D13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="D14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="D15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="D16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="D17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="D18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="D19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="D20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="D21" s="2"/>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="D22" s="2"/>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="D23" s="2"/>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="D24" s="2"/>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="D25" s="2"/>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="D26" s="2"/>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="D27" s="2"/>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="D28" s="2"/>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="D29" s="2"/>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="D30" s="2"/>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="D31" s="2"/>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="D32" s="2"/>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="D33" s="2"/>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="D34" s="2"/>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="D35" s="2"/>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="D36" s="2"/>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="D37" s="2"/>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="D38" s="2"/>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="D39" s="2"/>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="D40" s="2"/>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="D41" s="2"/>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="D42" s="2"/>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="D43" s="2"/>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="D44" s="2"/>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="D45" s="2"/>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="D46" s="2"/>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="D47" s="2"/>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="D48" s="2"/>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="D49" s="2"/>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="D50" s="2"/>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="D51" s="2"/>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="D52" s="2"/>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="D53" s="2"/>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="D54" s="2"/>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="D55" s="2"/>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="D56" s="2"/>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="D57" s="2"/>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="D58" s="2"/>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="D59" s="2"/>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="D60" s="2"/>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="D61" s="2"/>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="D62" s="2"/>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="D63" s="2"/>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="D64" s="2"/>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="D65" s="2"/>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="D66" s="2"/>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="D67" s="2"/>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="D68" s="2"/>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="D69" s="2"/>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="D70" s="2"/>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="D71" s="2"/>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="D72" s="2"/>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D73" s="2"/>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="D74" s="2"/>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D75" s="2"/>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="D76" s="2"/>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="D77" s="2"/>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="D78" s="2"/>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="D79" s="2"/>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="D80" s="2"/>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="D81" s="2"/>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="C82" t="s" s="2">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="D82" s="2"/>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="C83" t="s" s="2">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D83" s="2"/>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="D84" s="2"/>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="C85" t="s" s="2">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="D85" s="2"/>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="D86" s="2"/>
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="C87" t="s" s="2">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="D87" s="2"/>
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="D88" s="2"/>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="C89" t="s" s="2">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="D89" s="2"/>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="D90" s="2"/>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="D91" s="2"/>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="C92" t="s" s="2">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="D92" s="2"/>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="D93" s="2"/>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="C94" t="s" s="2">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="D94" s="2"/>
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="D95" s="2"/>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="D96" s="2"/>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="D97" s="2"/>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="D98" s="2"/>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="D99" s="2"/>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D100" s="2"/>
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="D101" s="2"/>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="C102" t="s" s="2">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="D102" s="2"/>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="D103" s="2"/>
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="D104" s="2"/>
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="D105" s="2"/>
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="D106" s="2"/>
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="D107" s="2"/>
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="D108" s="2"/>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="D109" s="2"/>
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="C110" t="s" s="2">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="D110" s="2"/>
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D111" s="2"/>
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="D112" s="2"/>
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="C113" t="s" s="2">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="D113" s="2"/>
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="C114" t="s" s="2">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="D114" s="2"/>
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="C115" t="s" s="2">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="D115" s="2"/>
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="C116" t="s" s="2">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="D116" s="2"/>
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="C117" t="s" s="2">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="D117" s="2"/>
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="C118" t="s" s="2">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="D118" s="2"/>
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="D119" s="2"/>
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="C120" t="s" s="2">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="D120" s="2"/>
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="C121" t="s" s="2">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="D121" s="2"/>
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="C122" t="s" s="2">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="D122" s="2"/>
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="C123" t="s" s="2">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="D123" s="2"/>
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="C124" t="s" s="2">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="D124" s="2"/>
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="C125" t="s" s="2">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="D125" s="2"/>
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="C126" t="s" s="2">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="D126" s="2"/>
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="C127" t="s" s="2">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="D127" s="2"/>
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="C128" t="s" s="2">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="D128" s="2"/>
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="C129" t="s" s="2">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="D129" s="2"/>
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="C130" t="s" s="2">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="D130" s="2"/>
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="C131" t="s" s="2">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="D131" s="2"/>
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="C132" t="s" s="2">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="D132" s="2"/>
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="C133" t="s" s="2">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="D133" s="2"/>
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="C134" t="s" s="2">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="D134" s="2"/>
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="C135" t="s" s="2">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="D135" s="2"/>
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="C136" t="s" s="2">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="D136" s="2"/>
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="C137" t="s" s="2">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="D137" s="2"/>
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="C138" t="s" s="2">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="D138" s="2"/>
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="C139" t="s" s="2">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="D139" s="2"/>
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="C140" t="s" s="2">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="D140" s="2"/>
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="C141" t="s" s="2">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="D141" s="2"/>
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="C142" t="s" s="2">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="D142" s="2"/>
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="C143" t="s" s="2">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="D143" s="2"/>
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="C144" t="s" s="2">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="D144" s="2"/>
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="C145" t="s" s="2">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="D145" s="2"/>
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="C146" t="s" s="2">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="D146" s="2"/>
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="C147" t="s" s="2">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="D147" s="2"/>
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="C148" t="s" s="2">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="D148" s="2"/>
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="C149" t="s" s="2">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="D149" s="2"/>
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="C150" t="s" s="2">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="D150" s="2"/>
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="C151" t="s" s="2">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="D151" s="2"/>
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="C152" t="s" s="2">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="D152" s="2"/>
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="C153" t="s" s="2">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="D153" s="2"/>
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="C154" t="s" s="2">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="D154" s="2"/>
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="C155" t="s" s="2">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="D155" s="2"/>
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="C156" t="s" s="2">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="D156" s="2"/>
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="C157" t="s" s="2">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="D157" s="2"/>
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="C158" t="s" s="2">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="D158" s="2"/>
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="C159" t="s" s="2">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="D159" s="2"/>
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="C160" t="s" s="2">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="D160" s="2"/>
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="C161" t="s" s="2">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="D161" s="2"/>
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="C162" t="s" s="2">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="D162" s="2"/>
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="C163" t="s" s="2">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="D163" s="2"/>
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="C164" t="s" s="2">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="D164" s="2"/>
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="C165" t="s" s="2">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="D165" s="2"/>
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="C166" t="s" s="2">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="D166" s="2"/>
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="C167" t="s" s="2">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="D167" s="2"/>
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="C168" t="s" s="2">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="D168" s="2"/>
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="C169" t="s" s="2">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="D169" s="2"/>
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="C170" t="s" s="2">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="D170" s="2"/>
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="C171" t="s" s="2">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="D171" s="2"/>
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="C172" t="s" s="2">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="D172" s="2"/>
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="C173" t="s" s="2">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="D173" s="2"/>
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="C174" t="s" s="2">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="D174" s="2"/>
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="C175" t="s" s="2">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="D175" s="2"/>
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="C176" t="s" s="2">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="D176" s="2"/>
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="C177" t="s" s="2">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="D177" s="2"/>
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="C178" t="s" s="2">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="D178" s="2"/>
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="C179" t="s" s="2">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="D179" s="2"/>
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="C180" t="s" s="2">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="D180" s="2"/>
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C181" t="s" s="2">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="D181" s="2"/>
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="C182" t="s" s="2">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="D182" s="2"/>
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="C183" t="s" s="2">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="D183" s="2"/>
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="C184" t="s" s="2">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="D184" s="2"/>
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="C185" t="s" s="2">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="D185" s="2"/>
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="C186" t="s" s="2">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="D186" s="2"/>
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="C187" t="s" s="2">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="D187" s="2"/>
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="C188" t="s" s="2">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="D188" s="2"/>
     </row>
     <row r="189">
       <c r="A189" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C189" t="s" s="2">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="D189" s="2"/>
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="C190" t="s" s="2">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="D190" s="2"/>
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="C191" t="s" s="2">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="D191" s="2"/>
     </row>
     <row r="192">
       <c r="A192" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="C192" t="s" s="2">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="D192" s="2"/>
     </row>
     <row r="193">
       <c r="A193" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="C193" t="s" s="2">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D193" s="2"/>
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="C194" t="s" s="2">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="D194" s="2"/>
     </row>
     <row r="195">
       <c r="A195" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="C195" t="s" s="2">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="D195" s="2"/>
     </row>
     <row r="196">
       <c r="A196" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="C196" t="s" s="2">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="D196" s="2"/>
     </row>
     <row r="197">
       <c r="A197" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="C197" t="s" s="2">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="D197" s="2"/>
     </row>
     <row r="198">
       <c r="A198" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="C198" t="s" s="2">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="D198" s="2"/>
     </row>
     <row r="199">
       <c r="A199" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="C199" t="s" s="2">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="D199" s="2"/>
     </row>
     <row r="200">
       <c r="A200" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="C200" t="s" s="2">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="D200" s="2"/>
     </row>
     <row r="201">
       <c r="A201" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="C201" t="s" s="2">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="D201" s="2"/>
     </row>
     <row r="202">
       <c r="A202" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="C202" t="s" s="2">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="D202" s="2"/>
     </row>
     <row r="203">
       <c r="A203" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="C203" t="s" s="2">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="D203" s="2"/>
     </row>
     <row r="204">
       <c r="A204" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="C204" t="s" s="2">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="D204" s="2"/>
     </row>
     <row r="205">
       <c r="A205" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="C205" t="s" s="2">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="D205" s="2"/>
     </row>
     <row r="206">
       <c r="A206" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="C206" t="s" s="2">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="D206" s="2"/>
     </row>
     <row r="207">
       <c r="A207" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="C207" t="s" s="2">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="D207" s="2"/>
     </row>
     <row r="208">
       <c r="A208" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="C208" t="s" s="2">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="D208" s="2"/>
     </row>
     <row r="209">
       <c r="A209" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="C209" t="s" s="2">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="D209" s="2"/>
     </row>
     <row r="210">
       <c r="A210" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="C210" t="s" s="2">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="D210" s="2"/>
     </row>
     <row r="211">
       <c r="A211" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="C211" t="s" s="2">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="D211" s="2"/>
     </row>
     <row r="212">
       <c r="A212" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="C212" t="s" s="2">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="D212" s="2"/>
     </row>
     <row r="213">
       <c r="A213" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="C213" t="s" s="2">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="D213" s="2"/>
     </row>
     <row r="214">
       <c r="A214" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="C214" t="s" s="2">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="D214" s="2"/>
     </row>
     <row r="215">
       <c r="A215" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="C215" t="s" s="2">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="D215" s="2"/>
     </row>
     <row r="216">
       <c r="A216" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="C216" t="s" s="2">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="D216" s="2"/>
     </row>
     <row r="217">
       <c r="A217" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="C217" t="s" s="2">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D217" s="2"/>
     </row>
     <row r="218">
       <c r="A218" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="C218" t="s" s="2">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="D218" s="2"/>
     </row>
     <row r="219">
       <c r="A219" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="C219" t="s" s="2">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="D219" s="2"/>
     </row>
     <row r="220">
       <c r="A220" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="C220" t="s" s="2">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="D220" s="2"/>
     </row>
     <row r="221">
       <c r="A221" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="C221" t="s" s="2">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="D221" s="2"/>
     </row>
     <row r="222">
       <c r="A222" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="C222" t="s" s="2">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="D222" s="2"/>
     </row>
     <row r="223">
       <c r="A223" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="C223" t="s" s="2">
-        <v>509</v>
+        <v>515</v>
       </c>
       <c r="D223" s="2"/>
     </row>
     <row r="224">
       <c r="A224" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="C224" t="s" s="2">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="D224" s="2"/>
     </row>
     <row r="225">
       <c r="A225" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="C225" t="s" s="2">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="D225" s="2"/>
     </row>
     <row r="226">
       <c r="A226" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="C226" t="s" s="2">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="D226" s="2"/>
     </row>
     <row r="227">
       <c r="A227" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="C227" t="s" s="2">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="D227" s="2"/>
     </row>
     <row r="228">
       <c r="A228" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="C228" t="s" s="2">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="D228" s="2"/>
     </row>
     <row r="229">
       <c r="A229" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="C229" t="s" s="2">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="D229" s="2"/>
     </row>
     <row r="230">
       <c r="A230" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="C230" t="s" s="2">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="D230" s="2"/>
     </row>
     <row r="231">
       <c r="A231" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="C231" t="s" s="2">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="D231" s="2"/>
     </row>
     <row r="232">
       <c r="A232" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="C232" t="s" s="2">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="D232" s="2"/>
     </row>
     <row r="233">
       <c r="A233" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="C233" t="s" s="2">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="D233" s="2"/>
     </row>
     <row r="234">
       <c r="A234" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="C234" t="s" s="2">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="D234" s="2"/>
     </row>
     <row r="235">
       <c r="A235" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="C235" t="s" s="2">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="D235" s="2"/>
     </row>
     <row r="236">
       <c r="A236" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="C236" t="s" s="2">
-        <v>535</v>
+        <v>541</v>
       </c>
       <c r="D236" s="2"/>
     </row>
     <row r="237">
       <c r="A237" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="C237" t="s" s="2">
-        <v>537</v>
+        <v>543</v>
       </c>
       <c r="D237" s="2"/>
     </row>
     <row r="238">
       <c r="A238" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>538</v>
+        <v>544</v>
       </c>
       <c r="C238" t="s" s="2">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="D238" s="2"/>
     </row>
     <row r="239">
       <c r="A239" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="C239" t="s" s="2">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="D239" s="2"/>
     </row>
     <row r="240">
       <c r="A240" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="C240" t="s" s="2">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="D240" s="2"/>
     </row>
     <row r="241">
       <c r="A241" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="C241" t="s" s="2">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="D241" s="2"/>
     </row>
     <row r="242">
       <c r="A242" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>546</v>
+        <v>552</v>
       </c>
       <c r="C242" t="s" s="2">
-        <v>547</v>
+        <v>553</v>
       </c>
       <c r="D242" s="2"/>
     </row>
     <row r="243">
       <c r="A243" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="C243" t="s" s="2">
-        <v>549</v>
+        <v>555</v>
       </c>
       <c r="D243" s="2"/>
     </row>
     <row r="244">
       <c r="A244" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="C244" t="s" s="2">
-        <v>551</v>
+        <v>557</v>
       </c>
       <c r="D244" s="2"/>
     </row>
     <row r="245">
       <c r="A245" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="C245" t="s" s="2">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="D245" s="2"/>
     </row>
     <row r="246">
       <c r="A246" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="C246" t="s" s="2">
-        <v>555</v>
+        <v>561</v>
       </c>
       <c r="D246" s="2"/>
     </row>
     <row r="247">
       <c r="A247" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B247" t="s" s="2">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="C247" t="s" s="2">
-        <v>557</v>
+        <v>563</v>
       </c>
       <c r="D247" s="2"/>
     </row>
     <row r="248">
       <c r="A248" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B248" t="s" s="2">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="C248" t="s" s="2">
-        <v>559</v>
+        <v>565</v>
       </c>
       <c r="D248" s="2"/>
     </row>
     <row r="249">
       <c r="A249" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B249" t="s" s="2">
-        <v>560</v>
+        <v>566</v>
       </c>
       <c r="C249" t="s" s="2">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="D249" s="2"/>
     </row>
     <row r="250">
       <c r="A250" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B250" t="s" s="2">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="C250" t="s" s="2">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="D250" s="2"/>
     </row>
     <row r="251">
       <c r="A251" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B251" t="s" s="2">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="C251" t="s" s="2">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="D251" s="2"/>
     </row>
     <row r="252">
       <c r="A252" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B252" t="s" s="2">
-        <v>566</v>
+        <v>572</v>
       </c>
       <c r="C252" t="s" s="2">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="D252" s="2"/>
     </row>
     <row r="253">
       <c r="A253" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B253" t="s" s="2">
-        <v>568</v>
+        <v>574</v>
       </c>
       <c r="C253" t="s" s="2">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="D253" s="2"/>
     </row>
     <row r="254">
       <c r="A254" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B254" t="s" s="2">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="C254" t="s" s="2">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="D254" s="2"/>
     </row>
     <row r="255">
       <c r="A255" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B255" t="s" s="2">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="C255" t="s" s="2">
-        <v>573</v>
+        <v>579</v>
       </c>
       <c r="D255" s="2"/>
     </row>
     <row r="256">
       <c r="A256" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B256" t="s" s="2">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="C256" t="s" s="2">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="D256" s="2"/>
     </row>
     <row r="257">
       <c r="A257" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B257" t="s" s="2">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="C257" t="s" s="2">
-        <v>577</v>
+        <v>583</v>
       </c>
       <c r="D257" s="2"/>
     </row>
     <row r="258">
       <c r="A258" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B258" t="s" s="2">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="C258" t="s" s="2">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c r="D258" s="2"/>
     </row>
     <row r="259">
       <c r="A259" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B259" t="s" s="2">
-        <v>580</v>
+        <v>586</v>
       </c>
       <c r="C259" t="s" s="2">
-        <v>581</v>
+        <v>587</v>
       </c>
       <c r="D259" s="2"/>
     </row>
     <row r="260">
       <c r="A260" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B260" t="s" s="2">
-        <v>582</v>
+        <v>588</v>
       </c>
       <c r="C260" t="s" s="2">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="D260" s="2"/>
     </row>
     <row r="261">
       <c r="A261" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B261" t="s" s="2">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="C261" t="s" s="2">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="D261" s="2"/>
     </row>
     <row r="262">
       <c r="A262" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B262" t="s" s="2">
-        <v>586</v>
+        <v>592</v>
       </c>
       <c r="C262" t="s" s="2">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="D262" s="2"/>
     </row>
     <row r="263">
       <c r="A263" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B263" t="s" s="2">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="C263" t="s" s="2">
-        <v>589</v>
+        <v>595</v>
       </c>
       <c r="D263" s="2"/>
     </row>
     <row r="264">
       <c r="A264" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B264" t="s" s="2">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="C264" t="s" s="2">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="D264" s="2"/>
     </row>
     <row r="265">
       <c r="A265" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B265" t="s" s="2">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="C265" t="s" s="2">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="D265" s="2"/>
     </row>
     <row r="266">
       <c r="A266" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B266" t="s" s="2">
-        <v>594</v>
+        <v>600</v>
       </c>
       <c r="C266" t="s" s="2">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="D266" s="2"/>
     </row>
     <row r="267">
       <c r="A267" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B267" t="s" s="2">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C267" t="s" s="2">
-        <v>597</v>
+        <v>603</v>
       </c>
       <c r="D267" s="2"/>
     </row>
     <row r="268">
       <c r="A268" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B268" t="s" s="2">
-        <v>598</v>
+        <v>604</v>
       </c>
       <c r="C268" t="s" s="2">
-        <v>599</v>
+        <v>605</v>
       </c>
       <c r="D268" s="2"/>
     </row>
     <row r="269">
       <c r="A269" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B269" t="s" s="2">
-        <v>600</v>
+        <v>606</v>
       </c>
       <c r="C269" t="s" s="2">
-        <v>601</v>
+        <v>607</v>
       </c>
       <c r="D269" s="2"/>
     </row>
     <row r="270">
       <c r="A270" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B270" t="s" s="2">
-        <v>602</v>
+        <v>608</v>
       </c>
       <c r="C270" t="s" s="2">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="D270" s="2"/>
     </row>
     <row r="271">
       <c r="A271" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B271" t="s" s="2">
-        <v>604</v>
+        <v>610</v>
       </c>
       <c r="C271" t="s" s="2">
-        <v>605</v>
+        <v>611</v>
       </c>
       <c r="D271" s="2"/>
     </row>
     <row r="272">
       <c r="A272" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B272" t="s" s="2">
-        <v>606</v>
+        <v>612</v>
       </c>
       <c r="C272" t="s" s="2">
-        <v>607</v>
+        <v>613</v>
       </c>
       <c r="D272" s="2"/>
     </row>
     <row r="273">
       <c r="A273" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B273" t="s" s="2">
-        <v>608</v>
+        <v>614</v>
       </c>
       <c r="C273" t="s" s="2">
-        <v>609</v>
+        <v>615</v>
       </c>
       <c r="D273" s="2"/>
     </row>
     <row r="274">
       <c r="A274" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B274" t="s" s="2">
-        <v>610</v>
+        <v>616</v>
       </c>
       <c r="C274" t="s" s="2">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="D274" s="2"/>
     </row>
     <row r="275">
       <c r="A275" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B275" t="s" s="2">
-        <v>612</v>
+        <v>618</v>
       </c>
       <c r="C275" t="s" s="2">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="D275" s="2"/>
     </row>
     <row r="276">
       <c r="A276" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B276" t="s" s="2">
-        <v>613</v>
+        <v>619</v>
       </c>
       <c r="C276" t="s" s="2">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="D276" s="2"/>
     </row>
     <row r="277">
       <c r="A277" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B277" t="s" s="2">
-        <v>615</v>
+        <v>621</v>
       </c>
       <c r="C277" t="s" s="2">
-        <v>616</v>
+        <v>622</v>
       </c>
       <c r="D277" s="2"/>
     </row>
     <row r="278">
       <c r="A278" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B278" t="s" s="2">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="C278" t="s" s="2">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="D278" s="2"/>
     </row>
     <row r="279">
       <c r="A279" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B279" t="s" s="2">
-        <v>619</v>
+        <v>625</v>
       </c>
       <c r="C279" t="s" s="2">
-        <v>620</v>
+        <v>626</v>
       </c>
       <c r="D279" s="2"/>
     </row>
     <row r="280">
       <c r="A280" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B280" t="s" s="2">
-        <v>621</v>
+        <v>627</v>
       </c>
       <c r="C280" t="s" s="2">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="D280" s="2"/>
     </row>
     <row r="281">
       <c r="A281" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B281" t="s" s="2">
-        <v>623</v>
+        <v>629</v>
       </c>
       <c r="C281" t="s" s="2">
-        <v>624</v>
+        <v>630</v>
       </c>
       <c r="D281" s="2"/>
     </row>
     <row r="282">
       <c r="A282" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B282" t="s" s="2">
-        <v>625</v>
+        <v>631</v>
       </c>
       <c r="C282" t="s" s="2">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="D282" s="2"/>
     </row>
     <row r="283">
       <c r="A283" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B283" t="s" s="2">
-        <v>627</v>
+        <v>633</v>
       </c>
       <c r="C283" t="s" s="2">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="D283" s="2"/>
     </row>
     <row r="284">
       <c r="A284" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B284" t="s" s="2">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="C284" t="s" s="2">
-        <v>630</v>
+        <v>636</v>
       </c>
       <c r="D284" s="2"/>
     </row>
     <row r="285">
       <c r="A285" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B285" t="s" s="2">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="C285" t="s" s="2">
-        <v>632</v>
+        <v>638</v>
       </c>
       <c r="D285" s="2"/>
     </row>
     <row r="286">
       <c r="A286" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B286" t="s" s="2">
-        <v>633</v>
+        <v>639</v>
       </c>
       <c r="C286" t="s" s="2">
-        <v>634</v>
+        <v>640</v>
       </c>
       <c r="D286" s="2"/>
     </row>
     <row r="287">
       <c r="A287" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B287" t="s" s="2">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="C287" t="s" s="2">
-        <v>636</v>
+        <v>642</v>
       </c>
       <c r="D287" s="2"/>
     </row>
     <row r="288">
       <c r="A288" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B288" t="s" s="2">
-        <v>637</v>
+        <v>643</v>
       </c>
       <c r="C288" t="s" s="2">
-        <v>638</v>
+        <v>644</v>
       </c>
       <c r="D288" s="2"/>
     </row>
     <row r="289">
       <c r="A289" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B289" t="s" s="2">
-        <v>639</v>
+        <v>645</v>
       </c>
       <c r="C289" t="s" s="2">
-        <v>640</v>
+        <v>646</v>
       </c>
       <c r="D289" s="2"/>
     </row>
     <row r="290">
       <c r="A290" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B290" t="s" s="2">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="C290" t="s" s="2">
-        <v>642</v>
+        <v>648</v>
       </c>
       <c r="D290" s="2"/>
     </row>
     <row r="291">
       <c r="A291" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B291" t="s" s="2">
-        <v>643</v>
+        <v>649</v>
       </c>
       <c r="C291" t="s" s="2">
-        <v>644</v>
+        <v>650</v>
       </c>
       <c r="D291" s="2"/>
     </row>
     <row r="292">
       <c r="A292" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B292" t="s" s="2">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="C292" t="s" s="2">
-        <v>646</v>
+        <v>652</v>
       </c>
       <c r="D292" s="2"/>
     </row>
     <row r="293">
       <c r="A293" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B293" t="s" s="2">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="C293" t="s" s="2">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="D293" s="2"/>
     </row>
     <row r="294">
       <c r="A294" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B294" t="s" s="2">
-        <v>649</v>
+        <v>655</v>
       </c>
       <c r="C294" t="s" s="2">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="D294" s="2"/>
     </row>
     <row r="295">
       <c r="A295" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B295" t="s" s="2">
-        <v>651</v>
+        <v>657</v>
       </c>
       <c r="C295" t="s" s="2">
-        <v>652</v>
+        <v>658</v>
       </c>
       <c r="D295" s="2"/>
     </row>
     <row r="296">
       <c r="A296" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B296" t="s" s="2">
-        <v>653</v>
+        <v>659</v>
       </c>
       <c r="C296" t="s" s="2">
-        <v>654</v>
+        <v>660</v>
       </c>
       <c r="D296" s="2"/>
     </row>
     <row r="297">
       <c r="A297" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B297" t="s" s="2">
-        <v>655</v>
+        <v>661</v>
       </c>
       <c r="C297" t="s" s="2">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="D297" s="2"/>
     </row>
     <row r="298">
       <c r="A298" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B298" t="s" s="2">
-        <v>657</v>
+        <v>663</v>
       </c>
       <c r="C298" t="s" s="2">
-        <v>658</v>
+        <v>664</v>
       </c>
       <c r="D298" s="2"/>
     </row>
     <row r="299">
       <c r="A299" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B299" t="s" s="2">
-        <v>659</v>
+        <v>665</v>
       </c>
       <c r="C299" t="s" s="2">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="D299" s="2"/>
     </row>
     <row r="300">
       <c r="A300" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B300" t="s" s="2">
-        <v>661</v>
+        <v>667</v>
       </c>
       <c r="C300" t="s" s="2">
-        <v>662</v>
+        <v>668</v>
       </c>
       <c r="D300" s="2"/>
     </row>
     <row r="301">
       <c r="A301" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B301" t="s" s="2">
-        <v>663</v>
+        <v>669</v>
       </c>
       <c r="C301" t="s" s="2">
-        <v>664</v>
+        <v>670</v>
       </c>
       <c r="D301" s="2"/>
     </row>
     <row r="302">
       <c r="A302" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B302" t="s" s="2">
-        <v>665</v>
+        <v>671</v>
       </c>
       <c r="C302" t="s" s="2">
-        <v>666</v>
+        <v>672</v>
       </c>
       <c r="D302" s="2"/>
     </row>
     <row r="303">
       <c r="A303" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B303" t="s" s="2">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="C303" t="s" s="2">
-        <v>668</v>
+        <v>674</v>
       </c>
       <c r="D303" s="2"/>
     </row>
     <row r="304">
       <c r="A304" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B304" t="s" s="2">
-        <v>669</v>
+        <v>675</v>
       </c>
       <c r="C304" t="s" s="2">
-        <v>670</v>
+        <v>676</v>
       </c>
       <c r="D304" s="2"/>
     </row>
     <row r="305">
       <c r="A305" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B305" t="s" s="2">
-        <v>671</v>
+        <v>677</v>
       </c>
       <c r="C305" t="s" s="2">
-        <v>672</v>
+        <v>678</v>
       </c>
       <c r="D305" s="2"/>
     </row>
     <row r="306">
       <c r="A306" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B306" t="s" s="2">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="C306" t="s" s="2">
-        <v>674</v>
+        <v>680</v>
       </c>
       <c r="D306" s="2"/>
     </row>
     <row r="307">
       <c r="A307" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B307" t="s" s="2">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="C307" t="s" s="2">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="D307" s="2"/>
     </row>
     <row r="308">
       <c r="A308" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B308" t="s" s="2">
-        <v>677</v>
+        <v>683</v>
       </c>
       <c r="C308" t="s" s="2">
-        <v>678</v>
+        <v>684</v>
       </c>
       <c r="D308" s="2"/>
     </row>
     <row r="309">
       <c r="A309" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B309" t="s" s="2">
-        <v>679</v>
+        <v>685</v>
       </c>
       <c r="C309" t="s" s="2">
-        <v>680</v>
+        <v>686</v>
       </c>
       <c r="D309" s="2"/>
     </row>
     <row r="310">
       <c r="A310" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B310" t="s" s="2">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="C310" t="s" s="2">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="D310" s="2"/>
     </row>
     <row r="311">
       <c r="A311" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B311" t="s" s="2">
-        <v>683</v>
+        <v>689</v>
       </c>
       <c r="C311" t="s" s="2">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="D311" s="2"/>
     </row>
     <row r="312">
       <c r="A312" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B312" t="s" s="2">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="C312" t="s" s="2">
-        <v>686</v>
+        <v>692</v>
       </c>
       <c r="D312" s="2"/>
     </row>
     <row r="313">
       <c r="A313" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B313" t="s" s="2">
-        <v>687</v>
+        <v>693</v>
       </c>
       <c r="C313" t="s" s="2">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="D313" s="2"/>
     </row>
     <row r="314">
       <c r="A314" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B314" t="s" s="2">
-        <v>689</v>
+        <v>695</v>
       </c>
       <c r="C314" t="s" s="2">
-        <v>690</v>
+        <v>696</v>
       </c>
       <c r="D314" s="2"/>
     </row>
     <row r="315">
       <c r="A315" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B315" t="s" s="2">
-        <v>691</v>
+        <v>697</v>
       </c>
       <c r="C315" t="s" s="2">
-        <v>692</v>
+        <v>698</v>
       </c>
       <c r="D315" s="2"/>
     </row>
     <row r="316">
       <c r="A316" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B316" t="s" s="2">
-        <v>693</v>
+        <v>699</v>
       </c>
       <c r="C316" t="s" s="2">
-        <v>694</v>
+        <v>700</v>
       </c>
       <c r="D316" s="2"/>
     </row>
     <row r="317">
       <c r="A317" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B317" t="s" s="2">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="C317" t="s" s="2">
-        <v>696</v>
+        <v>702</v>
       </c>
       <c r="D317" s="2"/>
     </row>
     <row r="318">
       <c r="A318" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B318" t="s" s="2">
-        <v>697</v>
+        <v>703</v>
       </c>
       <c r="C318" t="s" s="2">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="D318" s="2"/>
     </row>
     <row r="319">
       <c r="A319" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B319" t="s" s="2">
-        <v>699</v>
+        <v>705</v>
       </c>
       <c r="C319" t="s" s="2">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="D319" s="2"/>
     </row>
     <row r="320">
       <c r="A320" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B320" t="s" s="2">
-        <v>701</v>
+        <v>707</v>
       </c>
       <c r="C320" t="s" s="2">
-        <v>702</v>
+        <v>708</v>
       </c>
       <c r="D320" s="2"/>
     </row>
     <row r="321">
       <c r="A321" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B321" t="s" s="2">
-        <v>703</v>
+        <v>709</v>
       </c>
       <c r="C321" t="s" s="2">
-        <v>704</v>
+        <v>710</v>
       </c>
       <c r="D321" s="2"/>
     </row>
     <row r="322">
       <c r="A322" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B322" t="s" s="2">
-        <v>705</v>
+        <v>711</v>
       </c>
       <c r="C322" t="s" s="2">
-        <v>706</v>
+        <v>712</v>
       </c>
       <c r="D322" s="2"/>
     </row>
     <row r="323">
       <c r="A323" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B323" t="s" s="2">
-        <v>707</v>
+        <v>713</v>
       </c>
       <c r="C323" t="s" s="2">
-        <v>708</v>
+        <v>714</v>
       </c>
       <c r="D323" s="2"/>
     </row>
     <row r="324">
       <c r="A324" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B324" t="s" s="2">
-        <v>709</v>
+        <v>715</v>
       </c>
       <c r="C324" t="s" s="2">
-        <v>710</v>
+        <v>716</v>
       </c>
       <c r="D324" s="2"/>
     </row>
     <row r="325">
       <c r="A325" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B325" t="s" s="2">
-        <v>711</v>
+        <v>717</v>
       </c>
       <c r="C325" t="s" s="2">
-        <v>712</v>
+        <v>718</v>
       </c>
       <c r="D325" s="2"/>
     </row>
     <row r="326">
       <c r="A326" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B326" t="s" s="2">
-        <v>713</v>
+        <v>719</v>
       </c>
       <c r="C326" t="s" s="2">
-        <v>714</v>
+        <v>720</v>
       </c>
       <c r="D326" s="2"/>
     </row>
     <row r="327">
       <c r="A327" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B327" t="s" s="2">
-        <v>715</v>
+        <v>721</v>
       </c>
       <c r="C327" t="s" s="2">
-        <v>716</v>
+        <v>722</v>
       </c>
       <c r="D327" s="2"/>
     </row>
     <row r="328">
       <c r="A328" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B328" t="s" s="2">
-        <v>717</v>
+        <v>723</v>
       </c>
       <c r="C328" t="s" s="2">
-        <v>718</v>
+        <v>724</v>
       </c>
       <c r="D328" s="2"/>
     </row>
     <row r="329">
       <c r="A329" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B329" t="s" s="2">
-        <v>719</v>
+        <v>725</v>
       </c>
       <c r="C329" t="s" s="2">
-        <v>720</v>
+        <v>726</v>
       </c>
       <c r="D329" s="2"/>
     </row>
     <row r="330">
       <c r="A330" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B330" t="s" s="2">
-        <v>721</v>
+        <v>727</v>
       </c>
       <c r="C330" t="s" s="2">
-        <v>722</v>
+        <v>728</v>
       </c>
       <c r="D330" s="2"/>
     </row>
     <row r="331">
       <c r="A331" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B331" t="s" s="2">
-        <v>723</v>
+        <v>729</v>
       </c>
       <c r="C331" t="s" s="2">
-        <v>724</v>
+        <v>730</v>
       </c>
       <c r="D331" s="2"/>
     </row>
     <row r="332">
       <c r="A332" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B332" t="s" s="2">
-        <v>725</v>
+        <v>731</v>
       </c>
       <c r="C332" t="s" s="2">
-        <v>726</v>
+        <v>732</v>
       </c>
       <c r="D332" s="2"/>
     </row>
     <row r="333">
       <c r="A333" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B333" t="s" s="2">
-        <v>727</v>
+        <v>733</v>
       </c>
       <c r="C333" t="s" s="2">
-        <v>728</v>
+        <v>734</v>
       </c>
       <c r="D333" s="2"/>
     </row>
     <row r="334">
       <c r="A334" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B334" t="s" s="2">
-        <v>729</v>
+        <v>735</v>
       </c>
       <c r="C334" t="s" s="2">
-        <v>730</v>
+        <v>736</v>
       </c>
       <c r="D334" s="2"/>
     </row>
     <row r="335">
       <c r="A335" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B335" t="s" s="2">
-        <v>731</v>
+        <v>737</v>
       </c>
       <c r="C335" t="s" s="2">
-        <v>732</v>
+        <v>738</v>
       </c>
       <c r="D335" s="2"/>
     </row>
     <row r="336">
       <c r="A336" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B336" t="s" s="2">
-        <v>733</v>
+        <v>739</v>
       </c>
       <c r="C336" t="s" s="2">
-        <v>734</v>
+        <v>740</v>
       </c>
       <c r="D336" s="2"/>
     </row>
     <row r="337">
       <c r="A337" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B337" t="s" s="2">
-        <v>735</v>
+        <v>741</v>
       </c>
       <c r="C337" t="s" s="2">
-        <v>736</v>
+        <v>742</v>
       </c>
       <c r="D337" s="2"/>
     </row>
     <row r="338">
       <c r="A338" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B338" t="s" s="2">
-        <v>737</v>
+        <v>743</v>
       </c>
       <c r="C338" t="s" s="2">
-        <v>738</v>
+        <v>744</v>
       </c>
       <c r="D338" s="2"/>
     </row>
     <row r="339">
       <c r="A339" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B339" t="s" s="2">
-        <v>739</v>
+        <v>745</v>
       </c>
       <c r="C339" t="s" s="2">
-        <v>740</v>
+        <v>746</v>
       </c>
       <c r="D339" s="2"/>
     </row>
     <row r="340">
       <c r="A340" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B340" t="s" s="2">
-        <v>741</v>
+        <v>747</v>
       </c>
       <c r="C340" t="s" s="2">
-        <v>742</v>
+        <v>748</v>
       </c>
       <c r="D340" s="2"/>
     </row>
     <row r="341">
       <c r="A341" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B341" t="s" s="2">
-        <v>743</v>
+        <v>749</v>
       </c>
       <c r="C341" t="s" s="2">
-        <v>744</v>
+        <v>750</v>
       </c>
       <c r="D341" s="2"/>
     </row>
     <row r="342">
       <c r="A342" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B342" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C342" t="s" s="2">
-        <v>745</v>
+        <v>751</v>
       </c>
       <c r="D342" s="2"/>
     </row>
     <row r="343">
       <c r="A343" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B343" t="s" s="2">
-        <v>746</v>
+        <v>752</v>
       </c>
       <c r="C343" t="s" s="2">
-        <v>747</v>
+        <v>753</v>
       </c>
       <c r="D343" s="2"/>
     </row>
     <row r="344">
       <c r="A344" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B344" t="s" s="2">
-        <v>748</v>
+        <v>754</v>
       </c>
       <c r="C344" t="s" s="2">
-        <v>749</v>
+        <v>755</v>
       </c>
       <c r="D344" s="2"/>
     </row>
     <row r="345">
       <c r="A345" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B345" t="s" s="2">
-        <v>750</v>
+        <v>756</v>
       </c>
       <c r="C345" t="s" s="2">
-        <v>751</v>
+        <v>757</v>
       </c>
       <c r="D345" s="2"/>
     </row>
     <row r="346">
       <c r="A346" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B346" t="s" s="2">
-        <v>752</v>
+        <v>758</v>
       </c>
       <c r="C346" t="s" s="2">
-        <v>753</v>
+        <v>759</v>
       </c>
       <c r="D346" s="2"/>
     </row>
     <row r="347">
       <c r="A347" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B347" t="s" s="2">
-        <v>754</v>
+        <v>760</v>
       </c>
       <c r="C347" t="s" s="2">
-        <v>755</v>
+        <v>761</v>
       </c>
       <c r="D347" s="2"/>
     </row>
     <row r="348">
       <c r="A348" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B348" t="s" s="2">
-        <v>756</v>
+        <v>762</v>
       </c>
       <c r="C348" t="s" s="2">
-        <v>757</v>
+        <v>763</v>
       </c>
       <c r="D348" s="2"/>
     </row>
     <row r="349">
       <c r="A349" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B349" t="s" s="2">
-        <v>758</v>
+        <v>764</v>
       </c>
       <c r="C349" t="s" s="2">
-        <v>759</v>
+        <v>765</v>
       </c>
       <c r="D349" s="2"/>
     </row>
     <row r="350">
       <c r="A350" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B350" t="s" s="2">
-        <v>760</v>
+        <v>766</v>
       </c>
       <c r="C350" t="s" s="2">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="D350" s="2"/>
     </row>
     <row r="351">
       <c r="A351" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B351" t="s" s="2">
-        <v>762</v>
+        <v>768</v>
       </c>
       <c r="C351" t="s" s="2">
-        <v>763</v>
+        <v>769</v>
       </c>
       <c r="D351" s="2"/>
     </row>
     <row r="352">
       <c r="A352" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B352" t="s" s="2">
-        <v>764</v>
+        <v>770</v>
       </c>
       <c r="C352" t="s" s="2">
-        <v>765</v>
+        <v>771</v>
       </c>
       <c r="D352" s="2"/>
     </row>
     <row r="353">
       <c r="A353" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B353" t="s" s="2">
-        <v>766</v>
+        <v>772</v>
       </c>
       <c r="C353" t="s" s="2">
-        <v>767</v>
+        <v>773</v>
       </c>
       <c r="D353" s="2"/>
     </row>
     <row r="354">
       <c r="A354" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B354" t="s" s="2">
-        <v>768</v>
+        <v>774</v>
       </c>
       <c r="C354" t="s" s="2">
-        <v>769</v>
+        <v>775</v>
       </c>
       <c r="D354" s="2"/>
     </row>
     <row r="355">
       <c r="A355" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B355" t="s" s="2">
-        <v>770</v>
+        <v>776</v>
       </c>
       <c r="C355" t="s" s="2">
-        <v>771</v>
+        <v>777</v>
       </c>
       <c r="D355" s="2"/>
     </row>
     <row r="356">
       <c r="A356" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B356" t="s" s="2">
-        <v>772</v>
+        <v>778</v>
       </c>
       <c r="C356" t="s" s="2">
-        <v>773</v>
+        <v>779</v>
       </c>
       <c r="D356" s="2"/>
     </row>
     <row r="357">
       <c r="A357" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B357" t="s" s="2">
-        <v>774</v>
+        <v>780</v>
       </c>
       <c r="C357" t="s" s="2">
-        <v>775</v>
+        <v>781</v>
       </c>
       <c r="D357" s="2"/>
     </row>
     <row r="358">
       <c r="A358" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B358" t="s" s="2">
-        <v>776</v>
+        <v>782</v>
       </c>
       <c r="C358" t="s" s="2">
-        <v>777</v>
+        <v>783</v>
       </c>
       <c r="D358" s="2"/>
     </row>
     <row r="359">
       <c r="A359" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B359" t="s" s="2">
-        <v>778</v>
+        <v>784</v>
       </c>
       <c r="C359" t="s" s="2">
-        <v>779</v>
+        <v>785</v>
       </c>
       <c r="D359" s="2"/>
     </row>
     <row r="360">
       <c r="A360" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B360" t="s" s="2">
-        <v>780</v>
+        <v>786</v>
       </c>
       <c r="C360" t="s" s="2">
-        <v>781</v>
+        <v>787</v>
       </c>
       <c r="D360" s="2"/>
     </row>
     <row r="361">
       <c r="A361" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B361" t="s" s="2">
-        <v>782</v>
+        <v>788</v>
       </c>
       <c r="C361" t="s" s="2">
-        <v>783</v>
+        <v>789</v>
       </c>
       <c r="D361" s="2"/>
     </row>
     <row r="362">
       <c r="A362" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B362" t="s" s="2">
-        <v>784</v>
+        <v>790</v>
       </c>
       <c r="C362" t="s" s="2">
-        <v>785</v>
+        <v>791</v>
       </c>
       <c r="D362" s="2"/>
     </row>
     <row r="363">
       <c r="A363" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B363" t="s" s="2">
-        <v>786</v>
+        <v>792</v>
       </c>
       <c r="C363" t="s" s="2">
-        <v>787</v>
+        <v>793</v>
       </c>
       <c r="D363" s="2"/>
     </row>
     <row r="364">
       <c r="A364" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B364" t="s" s="2">
-        <v>788</v>
+        <v>794</v>
       </c>
       <c r="C364" t="s" s="2">
-        <v>789</v>
+        <v>795</v>
       </c>
       <c r="D364" s="2"/>
     </row>
     <row r="365">
       <c r="A365" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B365" t="s" s="2">
-        <v>790</v>
+        <v>796</v>
       </c>
       <c r="C365" t="s" s="2">
-        <v>791</v>
+        <v>797</v>
       </c>
       <c r="D365" s="2"/>
     </row>
     <row r="366">
       <c r="A366" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B366" t="s" s="2">
-        <v>792</v>
+        <v>798</v>
       </c>
       <c r="C366" t="s" s="2">
-        <v>793</v>
+        <v>799</v>
       </c>
       <c r="D366" s="2"/>
     </row>
     <row r="367">
       <c r="A367" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B367" t="s" s="2">
-        <v>794</v>
+        <v>800</v>
       </c>
       <c r="C367" t="s" s="2">
-        <v>795</v>
+        <v>801</v>
       </c>
       <c r="D367" s="2"/>
     </row>
     <row r="368">
       <c r="A368" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B368" t="s" s="2">
-        <v>796</v>
+        <v>802</v>
       </c>
       <c r="C368" t="s" s="2">
-        <v>797</v>
+        <v>803</v>
       </c>
       <c r="D368" s="2"/>
     </row>
     <row r="369">
       <c r="A369" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B369" t="s" s="2">
-        <v>798</v>
+        <v>804</v>
       </c>
       <c r="C369" t="s" s="2">
-        <v>799</v>
+        <v>805</v>
       </c>
       <c r="D369" s="2"/>
     </row>
     <row r="370">
       <c r="A370" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B370" t="s" s="2">
-        <v>800</v>
+        <v>806</v>
       </c>
       <c r="C370" t="s" s="2">
-        <v>801</v>
+        <v>807</v>
       </c>
       <c r="D370" s="2"/>
     </row>
     <row r="371">
       <c r="A371" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B371" t="s" s="2">
-        <v>802</v>
+        <v>808</v>
       </c>
       <c r="C371" t="s" s="2">
-        <v>803</v>
+        <v>809</v>
       </c>
       <c r="D371" s="2"/>
     </row>
     <row r="372">
       <c r="A372" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B372" t="s" s="2">
-        <v>804</v>
+        <v>810</v>
       </c>
       <c r="C372" t="s" s="2">
-        <v>805</v>
+        <v>811</v>
       </c>
       <c r="D372" s="2"/>
     </row>
     <row r="373">
       <c r="A373" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B373" t="s" s="2">
-        <v>806</v>
+        <v>812</v>
       </c>
       <c r="C373" t="s" s="2">
-        <v>807</v>
+        <v>813</v>
       </c>
       <c r="D373" s="2"/>
     </row>
     <row r="374">
       <c r="A374" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B374" t="s" s="2">
-        <v>808</v>
+        <v>814</v>
       </c>
       <c r="C374" t="s" s="2">
-        <v>809</v>
+        <v>815</v>
       </c>
       <c r="D374" s="2"/>
     </row>
     <row r="375">
       <c r="A375" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B375" t="s" s="2">
-        <v>810</v>
+        <v>816</v>
       </c>
       <c r="C375" t="s" s="2">
-        <v>811</v>
+        <v>817</v>
       </c>
       <c r="D375" s="2"/>
     </row>
     <row r="376">
       <c r="A376" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B376" t="s" s="2">
-        <v>812</v>
+        <v>818</v>
       </c>
       <c r="C376" t="s" s="2">
-        <v>813</v>
+        <v>819</v>
       </c>
       <c r="D376" s="2"/>
     </row>
     <row r="377">
       <c r="A377" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B377" t="s" s="2">
-        <v>814</v>
+        <v>820</v>
       </c>
       <c r="C377" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="D377" s="2"/>
     </row>
     <row r="378">
       <c r="A378" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B378" t="s" s="2">
-        <v>815</v>
+        <v>821</v>
       </c>
       <c r="C378" t="s" s="2">
-        <v>816</v>
+        <v>822</v>
       </c>
       <c r="D378" s="2"/>
     </row>
     <row r="379">
       <c r="A379" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B379" t="s" s="2">
-        <v>817</v>
+        <v>823</v>
       </c>
       <c r="C379" t="s" s="2">
-        <v>818</v>
+        <v>824</v>
       </c>
       <c r="D379" t="s" s="2">
-        <v>819</v>
+        <v>825</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B380" t="s" s="2">
-        <v>820</v>
+        <v>826</v>
       </c>
       <c r="C380" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="D380" s="2"/>
     </row>
     <row r="381">
       <c r="A381" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B381" t="s" s="2">
-        <v>821</v>
+        <v>827</v>
       </c>
       <c r="C381" t="s" s="2">
-        <v>822</v>
+        <v>828</v>
       </c>
       <c r="D381" s="2"/>
     </row>
     <row r="382">
       <c r="A382" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B382" t="s" s="2">
-        <v>823</v>
+        <v>829</v>
       </c>
       <c r="C382" t="s" s="2">
-        <v>824</v>
+        <v>830</v>
       </c>
       <c r="D382" s="2"/>
     </row>
     <row r="383">
       <c r="A383" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B383" t="s" s="2">
-        <v>825</v>
+        <v>831</v>
       </c>
       <c r="C383" t="s" s="2">
-        <v>826</v>
+        <v>832</v>
       </c>
       <c r="D383" s="2"/>
     </row>
     <row r="384">
       <c r="A384" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B384" t="s" s="2">
-        <v>827</v>
+        <v>833</v>
       </c>
       <c r="C384" t="s" s="2">
-        <v>828</v>
+        <v>834</v>
       </c>
       <c r="D384" s="2"/>
     </row>
     <row r="385">
       <c r="A385" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B385" t="s" s="2">
-        <v>829</v>
+        <v>835</v>
       </c>
       <c r="C385" t="s" s="2">
-        <v>830</v>
+        <v>836</v>
       </c>
       <c r="D385" s="2"/>
     </row>
     <row r="386">
       <c r="A386" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B386" t="s" s="2">
-        <v>831</v>
+        <v>837</v>
       </c>
       <c r="C386" t="s" s="2">
-        <v>832</v>
+        <v>838</v>
       </c>
       <c r="D386" s="2"/>
     </row>
     <row r="387">
       <c r="A387" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B387" t="s" s="2">
-        <v>833</v>
+        <v>839</v>
       </c>
       <c r="C387" t="s" s="2">
-        <v>834</v>
+        <v>840</v>
       </c>
       <c r="D387" s="2"/>
     </row>
     <row r="388">
       <c r="A388" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B388" t="s" s="2">
-        <v>835</v>
+        <v>841</v>
       </c>
       <c r="C388" t="s" s="2">
-        <v>836</v>
+        <v>842</v>
       </c>
       <c r="D388" s="2"/>
     </row>
     <row r="389">
       <c r="A389" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B389" t="s" s="2">
-        <v>837</v>
+        <v>843</v>
       </c>
       <c r="C389" t="s" s="2">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="D389" s="2"/>
     </row>
     <row r="390">
       <c r="A390" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B390" t="s" s="2">
-        <v>838</v>
+        <v>844</v>
       </c>
       <c r="C390" t="s" s="2">
-        <v>839</v>
+        <v>845</v>
       </c>
       <c r="D390" s="2"/>
     </row>
     <row r="391">
       <c r="A391" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B391" t="s" s="2">
-        <v>840</v>
+        <v>846</v>
       </c>
       <c r="C391" t="s" s="2">
-        <v>841</v>
+        <v>847</v>
       </c>
       <c r="D391" s="2"/>
     </row>
     <row r="392">
       <c r="A392" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B392" t="s" s="2">
-        <v>842</v>
+        <v>848</v>
       </c>
       <c r="C392" t="s" s="2">
-        <v>843</v>
+        <v>849</v>
       </c>
       <c r="D392" s="2"/>
     </row>
     <row r="393">
       <c r="A393" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B393" t="s" s="2">
-        <v>844</v>
+        <v>850</v>
       </c>
       <c r="C393" t="s" s="2">
-        <v>845</v>
+        <v>851</v>
       </c>
       <c r="D393" s="2"/>
     </row>
     <row r="394">
       <c r="A394" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B394" t="s" s="2">
-        <v>846</v>
+        <v>852</v>
       </c>
       <c r="C394" t="s" s="2">
-        <v>847</v>
+        <v>853</v>
       </c>
       <c r="D394" s="2"/>
     </row>
     <row r="395">
       <c r="A395" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B395" t="s" s="2">
-        <v>848</v>
+        <v>854</v>
       </c>
       <c r="C395" t="s" s="2">
-        <v>849</v>
+        <v>855</v>
       </c>
       <c r="D395" s="2"/>
     </row>
     <row r="396">
       <c r="A396" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B396" t="s" s="2">
-        <v>850</v>
+        <v>856</v>
       </c>
       <c r="C396" t="s" s="2">
-        <v>851</v>
+        <v>857</v>
       </c>
       <c r="D396" s="2"/>
     </row>
     <row r="397">
       <c r="A397" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B397" t="s" s="2">
-        <v>852</v>
+        <v>858</v>
       </c>
       <c r="C397" t="s" s="2">
-        <v>853</v>
+        <v>859</v>
       </c>
       <c r="D397" s="2"/>
     </row>
     <row r="398">
       <c r="A398" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B398" t="s" s="2">
-        <v>854</v>
+        <v>860</v>
       </c>
       <c r="C398" t="s" s="2">
-        <v>855</v>
+        <v>861</v>
       </c>
       <c r="D398" s="2"/>
     </row>
     <row r="399">
       <c r="A399" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B399" t="s" s="2">
-        <v>856</v>
+        <v>862</v>
       </c>
       <c r="C399" t="s" s="2">
-        <v>857</v>
+        <v>863</v>
       </c>
       <c r="D399" s="2"/>
     </row>
     <row r="400">
       <c r="A400" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B400" t="s" s="2">
-        <v>858</v>
+        <v>864</v>
       </c>
       <c r="C400" t="s" s="2">
-        <v>859</v>
+        <v>865</v>
       </c>
       <c r="D400" s="2"/>
     </row>
     <row r="401">
       <c r="A401" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B401" t="s" s="2">
-        <v>860</v>
+        <v>866</v>
       </c>
       <c r="C401" t="s" s="2">
-        <v>861</v>
+        <v>867</v>
       </c>
       <c r="D401" s="2"/>
     </row>
     <row r="402">
       <c r="A402" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B402" t="s" s="2">
-        <v>862</v>
+        <v>868</v>
       </c>
       <c r="C402" t="s" s="2">
-        <v>863</v>
+        <v>869</v>
       </c>
       <c r="D402" s="2"/>
     </row>
     <row r="403">
       <c r="A403" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B403" t="s" s="2">
-        <v>864</v>
+        <v>870</v>
       </c>
       <c r="C403" t="s" s="2">
-        <v>865</v>
+        <v>871</v>
       </c>
       <c r="D403" s="2"/>
     </row>
     <row r="404">
       <c r="A404" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B404" t="s" s="2">
-        <v>866</v>
+        <v>872</v>
       </c>
       <c r="C404" t="s" s="2">
-        <v>867</v>
+        <v>873</v>
       </c>
       <c r="D404" s="2"/>
     </row>
     <row r="405">
       <c r="A405" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B405" t="s" s="2">
-        <v>868</v>
+        <v>874</v>
       </c>
       <c r="C405" t="s" s="2">
-        <v>869</v>
+        <v>875</v>
       </c>
       <c r="D405" s="2"/>
     </row>
     <row r="406">
       <c r="A406" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B406" t="s" s="2">
-        <v>870</v>
+        <v>876</v>
       </c>
       <c r="C406" t="s" s="2">
-        <v>871</v>
+        <v>877</v>
       </c>
       <c r="D406" s="2"/>
     </row>
     <row r="407">
       <c r="A407" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B407" t="s" s="2">
-        <v>872</v>
+        <v>878</v>
       </c>
       <c r="C407" t="s" s="2">
-        <v>873</v>
+        <v>879</v>
       </c>
       <c r="D407" s="2"/>
     </row>
     <row r="408">
       <c r="A408" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B408" t="s" s="2">
-        <v>874</v>
+        <v>880</v>
       </c>
       <c r="C408" t="s" s="2">
-        <v>875</v>
+        <v>881</v>
       </c>
       <c r="D408" s="2"/>
     </row>
     <row r="409">
       <c r="A409" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B409" t="s" s="2">
-        <v>876</v>
+        <v>882</v>
       </c>
       <c r="C409" t="s" s="2">
-        <v>877</v>
+        <v>883</v>
       </c>
       <c r="D409" s="2"/>
     </row>
     <row r="410">
       <c r="A410" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B410" t="s" s="2">
-        <v>878</v>
+        <v>884</v>
       </c>
       <c r="C410" t="s" s="2">
-        <v>879</v>
+        <v>885</v>
       </c>
       <c r="D410" s="2"/>
     </row>
     <row r="411">
       <c r="A411" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B411" t="s" s="2">
-        <v>880</v>
+        <v>886</v>
       </c>
       <c r="C411" t="s" s="2">
-        <v>881</v>
+        <v>887</v>
       </c>
       <c r="D411" s="2"/>
     </row>
     <row r="412">
       <c r="A412" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B412" t="s" s="2">
-        <v>882</v>
+        <v>888</v>
       </c>
       <c r="C412" t="s" s="2">
-        <v>883</v>
+        <v>889</v>
       </c>
       <c r="D412" s="2"/>
     </row>
     <row r="413">
       <c r="A413" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B413" t="s" s="2">
-        <v>884</v>
+        <v>890</v>
       </c>
       <c r="C413" t="s" s="2">
-        <v>885</v>
+        <v>891</v>
       </c>
       <c r="D413" s="2"/>
     </row>
     <row r="414">
       <c r="A414" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B414" t="s" s="2">
-        <v>886</v>
+        <v>892</v>
       </c>
       <c r="C414" t="s" s="2">
-        <v>887</v>
+        <v>893</v>
       </c>
       <c r="D414" s="2"/>
     </row>
     <row r="415">
       <c r="A415" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B415" t="s" s="2">
-        <v>888</v>
+        <v>894</v>
       </c>
       <c r="C415" t="s" s="2">
-        <v>889</v>
+        <v>895</v>
       </c>
       <c r="D415" s="2"/>
     </row>
     <row r="416">
       <c r="A416" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B416" t="s" s="2">
-        <v>890</v>
+        <v>896</v>
       </c>
       <c r="C416" t="s" s="2">
-        <v>891</v>
+        <v>897</v>
       </c>
       <c r="D416" s="2"/>
     </row>
     <row r="417">
       <c r="A417" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B417" t="s" s="2">
-        <v>892</v>
+        <v>898</v>
       </c>
       <c r="C417" t="s" s="2">
-        <v>893</v>
+        <v>899</v>
       </c>
       <c r="D417" s="2"/>
     </row>
     <row r="418">
       <c r="A418" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B418" t="s" s="2">
-        <v>894</v>
+        <v>900</v>
       </c>
       <c r="C418" t="s" s="2">
-        <v>895</v>
+        <v>901</v>
       </c>
       <c r="D418" s="2"/>
     </row>
     <row r="419">
       <c r="A419" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B419" t="s" s="2">
-        <v>896</v>
+        <v>902</v>
       </c>
       <c r="C419" t="s" s="2">
-        <v>897</v>
+        <v>903</v>
       </c>
       <c r="D419" s="2"/>
     </row>
     <row r="420">
       <c r="A420" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B420" t="s" s="2">
-        <v>898</v>
+        <v>904</v>
       </c>
       <c r="C420" t="s" s="2">
-        <v>899</v>
+        <v>905</v>
       </c>
       <c r="D420" s="2"/>
     </row>
     <row r="421">
       <c r="A421" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B421" t="s" s="2">
-        <v>900</v>
+        <v>906</v>
       </c>
       <c r="C421" t="s" s="2">
-        <v>901</v>
+        <v>907</v>
       </c>
       <c r="D421" s="2"/>
     </row>
     <row r="422">
       <c r="A422" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B422" t="s" s="2">
-        <v>902</v>
+        <v>908</v>
       </c>
       <c r="C422" t="s" s="2">
-        <v>903</v>
+        <v>909</v>
       </c>
       <c r="D422" s="2"/>
     </row>
     <row r="423">
       <c r="A423" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B423" t="s" s="2">
-        <v>904</v>
+        <v>910</v>
       </c>
       <c r="C423" t="s" s="2">
-        <v>905</v>
+        <v>911</v>
       </c>
       <c r="D423" t="s" s="2">
-        <v>906</v>
+        <v>912</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B424" t="s" s="2">
-        <v>907</v>
+        <v>913</v>
       </c>
       <c r="C424" t="s" s="2">
-        <v>908</v>
+        <v>914</v>
       </c>
       <c r="D424" t="s" s="2">
-        <v>906</v>
+        <v>912</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B425" t="s" s="2">
-        <v>909</v>
+        <v>915</v>
       </c>
       <c r="C425" t="s" s="2">
-        <v>910</v>
+        <v>916</v>
       </c>
       <c r="D425" t="s" s="2">
-        <v>906</v>
+        <v>912</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B426" t="s" s="2">
-        <v>911</v>
+        <v>917</v>
       </c>
       <c r="C426" t="s" s="2">
-        <v>912</v>
+        <v>918</v>
       </c>
       <c r="D426" s="2"/>
     </row>
     <row r="427">
       <c r="A427" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B427" t="s" s="2">
-        <v>913</v>
+        <v>919</v>
       </c>
       <c r="C427" t="s" s="2">
-        <v>914</v>
+        <v>920</v>
       </c>
       <c r="D427" t="s" s="2">
-        <v>915</v>
+        <v>921</v>
       </c>
     </row>
   </sheetData>

--- a/ig/DM_FINESS_New/CodeSystem-tre-r397-categorie-entite-geographique-exercice.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-tre-r397-categorie-entite-geographique-exercice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1375" uniqueCount="922">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1379" uniqueCount="925">
   <si>
     <t>Property</t>
   </si>
@@ -251,6 +251,15 @@
   </si>
   <si>
     <t>Permet de définir les codes concepts uilisés par le CISIS</t>
+  </si>
+  <si>
+    <t>rass</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#rass</t>
+  </si>
+  <si>
+    <t>Permet de définir les codes concepts uilisés par le RASS</t>
   </si>
   <si>
     <t>Level</t>
@@ -3083,7 +3092,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -3265,6 +3274,20 @@
         <v>78</v>
       </c>
       <c r="D13" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="C14" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="D14" t="s" s="2">
         <v>72</v>
       </c>
     </row>
@@ -3280,5138 +3303,5138 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B1" t="s" s="1">
         <v>35</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C8" t="s" s="2">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C9" t="s" s="2">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D21" s="2"/>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D22" s="2"/>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D23" s="2"/>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D24" s="2"/>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D25" s="2"/>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D26" s="2"/>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D27" s="2"/>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D28" s="2"/>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D29" s="2"/>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D30" s="2"/>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D31" s="2"/>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D32" s="2"/>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D33" s="2"/>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="D34" s="2"/>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D35" s="2"/>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D36" s="2"/>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D37" s="2"/>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D38" s="2"/>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D39" s="2"/>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D40" s="2"/>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D41" s="2"/>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D42" s="2"/>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="D43" s="2"/>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="D44" s="2"/>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D45" s="2"/>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="D46" s="2"/>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="D47" s="2"/>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="D48" s="2"/>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="D49" s="2"/>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D50" s="2"/>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D51" s="2"/>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D52" s="2"/>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="D53" s="2"/>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="D54" s="2"/>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D55" s="2"/>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D56" s="2"/>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D57" s="2"/>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="D58" s="2"/>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="D59" s="2"/>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="D60" s="2"/>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="D61" s="2"/>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="D62" s="2"/>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="D63" s="2"/>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="D64" s="2"/>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="D65" s="2"/>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="D66" s="2"/>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D67" s="2"/>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D68" s="2"/>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="D69" s="2"/>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D70" s="2"/>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="D71" s="2"/>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="D72" s="2"/>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="D73" s="2"/>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="D74" s="2"/>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="D75" s="2"/>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D76" s="2"/>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D77" s="2"/>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="D78" s="2"/>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D79" s="2"/>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="D80" s="2"/>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="D81" s="2"/>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C82" t="s" s="2">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D82" s="2"/>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C83" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="D83" s="2"/>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="D84" s="2"/>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C85" t="s" s="2">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D85" s="2"/>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="D86" s="2"/>
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C87" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="D87" s="2"/>
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D88" s="2"/>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C89" t="s" s="2">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="D89" s="2"/>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D90" s="2"/>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="D91" s="2"/>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C92" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="D92" s="2"/>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="D93" s="2"/>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C94" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="D94" s="2"/>
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D95" s="2"/>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="D96" s="2"/>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="D97" s="2"/>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="D98" s="2"/>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="D99" s="2"/>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="D100" s="2"/>
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="D101" s="2"/>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C102" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="D102" s="2"/>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="D103" s="2"/>
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D104" s="2"/>
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="D105" s="2"/>
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D106" s="2"/>
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D107" s="2"/>
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D108" s="2"/>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="D109" s="2"/>
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="C110" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="D110" s="2"/>
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="D111" s="2"/>
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D112" s="2"/>
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="C113" t="s" s="2">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="D113" s="2"/>
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C114" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="D114" s="2"/>
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="C115" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="D115" s="2"/>
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="C116" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="D116" s="2"/>
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="C117" t="s" s="2">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="D117" s="2"/>
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C118" t="s" s="2">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="D118" s="2"/>
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="D119" s="2"/>
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="C120" t="s" s="2">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="D120" s="2"/>
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="C121" t="s" s="2">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="D121" s="2"/>
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="C122" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="D122" s="2"/>
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C123" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="D123" s="2"/>
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="C124" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="D124" s="2"/>
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="C125" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="D125" s="2"/>
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="C126" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D126" s="2"/>
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="C127" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="D127" s="2"/>
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="C128" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="D128" s="2"/>
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="C129" t="s" s="2">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="D129" s="2"/>
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C130" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="D130" s="2"/>
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="C131" t="s" s="2">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="D131" s="2"/>
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C132" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="D132" s="2"/>
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C133" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="D133" s="2"/>
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="C134" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="D134" s="2"/>
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="C135" t="s" s="2">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="D135" s="2"/>
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="C136" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="D136" s="2"/>
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="C137" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="D137" s="2"/>
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C138" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="D138" s="2"/>
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="C139" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="D139" s="2"/>
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C140" t="s" s="2">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="D140" s="2"/>
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="C141" t="s" s="2">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="D141" s="2"/>
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="C142" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="D142" s="2"/>
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="C143" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="D143" s="2"/>
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="C144" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="D144" s="2"/>
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="C145" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="D145" s="2"/>
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="C146" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="D146" s="2"/>
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="C147" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="D147" s="2"/>
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="C148" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="D148" s="2"/>
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="C149" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="D149" s="2"/>
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="C150" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="D150" s="2"/>
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="C151" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="D151" s="2"/>
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="C152" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="D152" s="2"/>
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C153" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="D153" s="2"/>
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="C154" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="D154" s="2"/>
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="C155" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="D155" s="2"/>
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="C156" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="D156" s="2"/>
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="C157" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="D157" s="2"/>
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="C158" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="D158" s="2"/>
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="C159" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="D159" s="2"/>
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="C160" t="s" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="D160" s="2"/>
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="C161" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="D161" s="2"/>
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="C162" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="D162" s="2"/>
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="C163" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="D163" s="2"/>
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="C164" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="D164" s="2"/>
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="C165" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="D165" s="2"/>
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="C166" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="D166" s="2"/>
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="C167" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="D167" s="2"/>
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="C168" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="D168" s="2"/>
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="C169" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="D169" s="2"/>
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="C170" t="s" s="2">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="D170" s="2"/>
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="C171" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="D171" s="2"/>
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C172" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="D172" s="2"/>
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C173" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="D173" s="2"/>
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C174" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="D174" s="2"/>
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C175" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="D175" s="2"/>
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C176" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="D176" s="2"/>
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="C177" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="D177" s="2"/>
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="C178" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="D178" s="2"/>
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="C179" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="D179" s="2"/>
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C180" t="s" s="2">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="D180" s="2"/>
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="C181" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="D181" s="2"/>
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="C182" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="D182" s="2"/>
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="C183" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="D183" s="2"/>
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="C184" t="s" s="2">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="D184" s="2"/>
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="C185" t="s" s="2">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="D185" s="2"/>
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="C186" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="D186" s="2"/>
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="C187" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="D187" s="2"/>
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="C188" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="D188" s="2"/>
     </row>
     <row r="189">
       <c r="A189" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="C189" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="D189" s="2"/>
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="C190" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="D190" s="2"/>
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="C191" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="D191" s="2"/>
     </row>
     <row r="192">
       <c r="A192" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="C192" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="D192" s="2"/>
     </row>
     <row r="193">
       <c r="A193" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="C193" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D193" s="2"/>
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="C194" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="D194" s="2"/>
     </row>
     <row r="195">
       <c r="A195" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="C195" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="D195" s="2"/>
     </row>
     <row r="196">
       <c r="A196" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="C196" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="D196" s="2"/>
     </row>
     <row r="197">
       <c r="A197" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="C197" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="D197" s="2"/>
     </row>
     <row r="198">
       <c r="A198" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="C198" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="D198" s="2"/>
     </row>
     <row r="199">
       <c r="A199" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="C199" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="D199" s="2"/>
     </row>
     <row r="200">
       <c r="A200" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="C200" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="D200" s="2"/>
     </row>
     <row r="201">
       <c r="A201" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="C201" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="D201" s="2"/>
     </row>
     <row r="202">
       <c r="A202" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="C202" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="D202" s="2"/>
     </row>
     <row r="203">
       <c r="A203" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="C203" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="D203" s="2"/>
     </row>
     <row r="204">
       <c r="A204" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="C204" t="s" s="2">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="D204" s="2"/>
     </row>
     <row r="205">
       <c r="A205" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="C205" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="D205" s="2"/>
     </row>
     <row r="206">
       <c r="A206" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="C206" t="s" s="2">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="D206" s="2"/>
     </row>
     <row r="207">
       <c r="A207" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="C207" t="s" s="2">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="D207" s="2"/>
     </row>
     <row r="208">
       <c r="A208" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="C208" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="D208" s="2"/>
     </row>
     <row r="209">
       <c r="A209" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="C209" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="D209" s="2"/>
     </row>
     <row r="210">
       <c r="A210" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="C210" t="s" s="2">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="D210" s="2"/>
     </row>
     <row r="211">
       <c r="A211" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="C211" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="D211" s="2"/>
     </row>
     <row r="212">
       <c r="A212" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="C212" t="s" s="2">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="D212" s="2"/>
     </row>
     <row r="213">
       <c r="A213" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="C213" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="D213" s="2"/>
     </row>
     <row r="214">
       <c r="A214" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="C214" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="D214" s="2"/>
     </row>
     <row r="215">
       <c r="A215" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="C215" t="s" s="2">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="D215" s="2"/>
     </row>
     <row r="216">
       <c r="A216" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="C216" t="s" s="2">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="D216" s="2"/>
     </row>
     <row r="217">
       <c r="A217" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="C217" t="s" s="2">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="D217" s="2"/>
     </row>
     <row r="218">
       <c r="A218" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="C218" t="s" s="2">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="D218" s="2"/>
     </row>
     <row r="219">
       <c r="A219" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="C219" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="D219" s="2"/>
     </row>
     <row r="220">
       <c r="A220" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="C220" t="s" s="2">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="D220" s="2"/>
     </row>
     <row r="221">
       <c r="A221" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="C221" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="D221" s="2"/>
     </row>
     <row r="222">
       <c r="A222" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="C222" t="s" s="2">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="D222" s="2"/>
     </row>
     <row r="223">
       <c r="A223" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="C223" t="s" s="2">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="D223" s="2"/>
     </row>
     <row r="224">
       <c r="A224" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="C224" t="s" s="2">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="D224" s="2"/>
     </row>
     <row r="225">
       <c r="A225" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="C225" t="s" s="2">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="D225" s="2"/>
     </row>
     <row r="226">
       <c r="A226" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="C226" t="s" s="2">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="D226" s="2"/>
     </row>
     <row r="227">
       <c r="A227" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="C227" t="s" s="2">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="D227" s="2"/>
     </row>
     <row r="228">
       <c r="A228" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="C228" t="s" s="2">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="D228" s="2"/>
     </row>
     <row r="229">
       <c r="A229" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="C229" t="s" s="2">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="D229" s="2"/>
     </row>
     <row r="230">
       <c r="A230" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="C230" t="s" s="2">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="D230" s="2"/>
     </row>
     <row r="231">
       <c r="A231" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="C231" t="s" s="2">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="D231" s="2"/>
     </row>
     <row r="232">
       <c r="A232" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="C232" t="s" s="2">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="D232" s="2"/>
     </row>
     <row r="233">
       <c r="A233" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="C233" t="s" s="2">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="D233" s="2"/>
     </row>
     <row r="234">
       <c r="A234" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="C234" t="s" s="2">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="D234" s="2"/>
     </row>
     <row r="235">
       <c r="A235" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="C235" t="s" s="2">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="D235" s="2"/>
     </row>
     <row r="236">
       <c r="A236" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="C236" t="s" s="2">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="D236" s="2"/>
     </row>
     <row r="237">
       <c r="A237" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="C237" t="s" s="2">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="D237" s="2"/>
     </row>
     <row r="238">
       <c r="A238" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="C238" t="s" s="2">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="D238" s="2"/>
     </row>
     <row r="239">
       <c r="A239" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="C239" t="s" s="2">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="D239" s="2"/>
     </row>
     <row r="240">
       <c r="A240" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="C240" t="s" s="2">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="D240" s="2"/>
     </row>
     <row r="241">
       <c r="A241" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="C241" t="s" s="2">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="D241" s="2"/>
     </row>
     <row r="242">
       <c r="A242" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="C242" t="s" s="2">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="D242" s="2"/>
     </row>
     <row r="243">
       <c r="A243" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="C243" t="s" s="2">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="D243" s="2"/>
     </row>
     <row r="244">
       <c r="A244" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="C244" t="s" s="2">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="D244" s="2"/>
     </row>
     <row r="245">
       <c r="A245" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="C245" t="s" s="2">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="D245" s="2"/>
     </row>
     <row r="246">
       <c r="A246" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="C246" t="s" s="2">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="D246" s="2"/>
     </row>
     <row r="247">
       <c r="A247" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B247" t="s" s="2">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="C247" t="s" s="2">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="D247" s="2"/>
     </row>
     <row r="248">
       <c r="A248" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B248" t="s" s="2">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="C248" t="s" s="2">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="D248" s="2"/>
     </row>
     <row r="249">
       <c r="A249" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B249" t="s" s="2">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="C249" t="s" s="2">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="D249" s="2"/>
     </row>
     <row r="250">
       <c r="A250" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B250" t="s" s="2">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="C250" t="s" s="2">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="D250" s="2"/>
     </row>
     <row r="251">
       <c r="A251" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B251" t="s" s="2">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="C251" t="s" s="2">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="D251" s="2"/>
     </row>
     <row r="252">
       <c r="A252" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B252" t="s" s="2">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="C252" t="s" s="2">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="D252" s="2"/>
     </row>
     <row r="253">
       <c r="A253" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B253" t="s" s="2">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="C253" t="s" s="2">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="D253" s="2"/>
     </row>
     <row r="254">
       <c r="A254" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B254" t="s" s="2">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="C254" t="s" s="2">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="D254" s="2"/>
     </row>
     <row r="255">
       <c r="A255" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B255" t="s" s="2">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="C255" t="s" s="2">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="D255" s="2"/>
     </row>
     <row r="256">
       <c r="A256" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B256" t="s" s="2">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="C256" t="s" s="2">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="D256" s="2"/>
     </row>
     <row r="257">
       <c r="A257" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B257" t="s" s="2">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="C257" t="s" s="2">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="D257" s="2"/>
     </row>
     <row r="258">
       <c r="A258" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B258" t="s" s="2">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="C258" t="s" s="2">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="D258" s="2"/>
     </row>
     <row r="259">
       <c r="A259" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B259" t="s" s="2">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="C259" t="s" s="2">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="D259" s="2"/>
     </row>
     <row r="260">
       <c r="A260" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B260" t="s" s="2">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="C260" t="s" s="2">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="D260" s="2"/>
     </row>
     <row r="261">
       <c r="A261" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B261" t="s" s="2">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="C261" t="s" s="2">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="D261" s="2"/>
     </row>
     <row r="262">
       <c r="A262" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B262" t="s" s="2">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="C262" t="s" s="2">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="D262" s="2"/>
     </row>
     <row r="263">
       <c r="A263" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B263" t="s" s="2">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="C263" t="s" s="2">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="D263" s="2"/>
     </row>
     <row r="264">
       <c r="A264" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B264" t="s" s="2">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="C264" t="s" s="2">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="D264" s="2"/>
     </row>
     <row r="265">
       <c r="A265" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B265" t="s" s="2">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="C265" t="s" s="2">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="D265" s="2"/>
     </row>
     <row r="266">
       <c r="A266" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B266" t="s" s="2">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="C266" t="s" s="2">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="D266" s="2"/>
     </row>
     <row r="267">
       <c r="A267" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B267" t="s" s="2">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="C267" t="s" s="2">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="D267" s="2"/>
     </row>
     <row r="268">
       <c r="A268" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B268" t="s" s="2">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="C268" t="s" s="2">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="D268" s="2"/>
     </row>
     <row r="269">
       <c r="A269" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B269" t="s" s="2">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="C269" t="s" s="2">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="D269" s="2"/>
     </row>
     <row r="270">
       <c r="A270" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B270" t="s" s="2">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="C270" t="s" s="2">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="D270" s="2"/>
     </row>
     <row r="271">
       <c r="A271" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B271" t="s" s="2">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="C271" t="s" s="2">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="D271" s="2"/>
     </row>
     <row r="272">
       <c r="A272" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B272" t="s" s="2">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="C272" t="s" s="2">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="D272" s="2"/>
     </row>
     <row r="273">
       <c r="A273" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B273" t="s" s="2">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="C273" t="s" s="2">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="D273" s="2"/>
     </row>
     <row r="274">
       <c r="A274" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B274" t="s" s="2">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="C274" t="s" s="2">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="D274" s="2"/>
     </row>
     <row r="275">
       <c r="A275" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B275" t="s" s="2">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="C275" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="D275" s="2"/>
     </row>
     <row r="276">
       <c r="A276" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B276" t="s" s="2">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="C276" t="s" s="2">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="D276" s="2"/>
     </row>
     <row r="277">
       <c r="A277" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B277" t="s" s="2">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="C277" t="s" s="2">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="D277" s="2"/>
     </row>
     <row r="278">
       <c r="A278" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B278" t="s" s="2">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="C278" t="s" s="2">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="D278" s="2"/>
     </row>
     <row r="279">
       <c r="A279" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B279" t="s" s="2">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="C279" t="s" s="2">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="D279" s="2"/>
     </row>
     <row r="280">
       <c r="A280" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B280" t="s" s="2">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="C280" t="s" s="2">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="D280" s="2"/>
     </row>
     <row r="281">
       <c r="A281" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B281" t="s" s="2">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="C281" t="s" s="2">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="D281" s="2"/>
     </row>
     <row r="282">
       <c r="A282" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B282" t="s" s="2">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="C282" t="s" s="2">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="D282" s="2"/>
     </row>
     <row r="283">
       <c r="A283" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B283" t="s" s="2">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="C283" t="s" s="2">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="D283" s="2"/>
     </row>
     <row r="284">
       <c r="A284" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B284" t="s" s="2">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="C284" t="s" s="2">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="D284" s="2"/>
     </row>
     <row r="285">
       <c r="A285" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B285" t="s" s="2">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="C285" t="s" s="2">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="D285" s="2"/>
     </row>
     <row r="286">
       <c r="A286" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B286" t="s" s="2">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="C286" t="s" s="2">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="D286" s="2"/>
     </row>
     <row r="287">
       <c r="A287" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B287" t="s" s="2">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="C287" t="s" s="2">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="D287" s="2"/>
     </row>
     <row r="288">
       <c r="A288" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B288" t="s" s="2">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="C288" t="s" s="2">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="D288" s="2"/>
     </row>
     <row r="289">
       <c r="A289" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B289" t="s" s="2">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="C289" t="s" s="2">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="D289" s="2"/>
     </row>
     <row r="290">
       <c r="A290" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B290" t="s" s="2">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="C290" t="s" s="2">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="D290" s="2"/>
     </row>
     <row r="291">
       <c r="A291" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B291" t="s" s="2">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="C291" t="s" s="2">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="D291" s="2"/>
     </row>
     <row r="292">
       <c r="A292" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B292" t="s" s="2">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="C292" t="s" s="2">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="D292" s="2"/>
     </row>
     <row r="293">
       <c r="A293" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B293" t="s" s="2">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="C293" t="s" s="2">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="D293" s="2"/>
     </row>
     <row r="294">
       <c r="A294" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B294" t="s" s="2">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="C294" t="s" s="2">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="D294" s="2"/>
     </row>
     <row r="295">
       <c r="A295" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B295" t="s" s="2">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="C295" t="s" s="2">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="D295" s="2"/>
     </row>
     <row r="296">
       <c r="A296" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B296" t="s" s="2">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="C296" t="s" s="2">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="D296" s="2"/>
     </row>
     <row r="297">
       <c r="A297" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B297" t="s" s="2">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="C297" t="s" s="2">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="D297" s="2"/>
     </row>
     <row r="298">
       <c r="A298" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B298" t="s" s="2">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="C298" t="s" s="2">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="D298" s="2"/>
     </row>
     <row r="299">
       <c r="A299" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B299" t="s" s="2">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="C299" t="s" s="2">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="D299" s="2"/>
     </row>
     <row r="300">
       <c r="A300" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B300" t="s" s="2">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="C300" t="s" s="2">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="D300" s="2"/>
     </row>
     <row r="301">
       <c r="A301" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B301" t="s" s="2">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="C301" t="s" s="2">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="D301" s="2"/>
     </row>
     <row r="302">
       <c r="A302" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B302" t="s" s="2">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="C302" t="s" s="2">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="D302" s="2"/>
     </row>
     <row r="303">
       <c r="A303" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B303" t="s" s="2">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="C303" t="s" s="2">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="D303" s="2"/>
     </row>
     <row r="304">
       <c r="A304" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B304" t="s" s="2">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="C304" t="s" s="2">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="D304" s="2"/>
     </row>
     <row r="305">
       <c r="A305" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B305" t="s" s="2">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="C305" t="s" s="2">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="D305" s="2"/>
     </row>
     <row r="306">
       <c r="A306" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B306" t="s" s="2">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="C306" t="s" s="2">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="D306" s="2"/>
     </row>
     <row r="307">
       <c r="A307" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B307" t="s" s="2">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="C307" t="s" s="2">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="D307" s="2"/>
     </row>
     <row r="308">
       <c r="A308" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B308" t="s" s="2">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="C308" t="s" s="2">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="D308" s="2"/>
     </row>
     <row r="309">
       <c r="A309" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B309" t="s" s="2">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="C309" t="s" s="2">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="D309" s="2"/>
     </row>
     <row r="310">
       <c r="A310" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B310" t="s" s="2">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="C310" t="s" s="2">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="D310" s="2"/>
     </row>
     <row r="311">
       <c r="A311" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B311" t="s" s="2">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="C311" t="s" s="2">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="D311" s="2"/>
     </row>
     <row r="312">
       <c r="A312" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B312" t="s" s="2">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="C312" t="s" s="2">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="D312" s="2"/>
     </row>
     <row r="313">
       <c r="A313" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B313" t="s" s="2">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="C313" t="s" s="2">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="D313" s="2"/>
     </row>
     <row r="314">
       <c r="A314" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B314" t="s" s="2">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="C314" t="s" s="2">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="D314" s="2"/>
     </row>
     <row r="315">
       <c r="A315" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B315" t="s" s="2">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="C315" t="s" s="2">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="D315" s="2"/>
     </row>
     <row r="316">
       <c r="A316" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B316" t="s" s="2">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="C316" t="s" s="2">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="D316" s="2"/>
     </row>
     <row r="317">
       <c r="A317" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B317" t="s" s="2">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="C317" t="s" s="2">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="D317" s="2"/>
     </row>
     <row r="318">
       <c r="A318" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B318" t="s" s="2">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="C318" t="s" s="2">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="D318" s="2"/>
     </row>
     <row r="319">
       <c r="A319" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B319" t="s" s="2">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="C319" t="s" s="2">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="D319" s="2"/>
     </row>
     <row r="320">
       <c r="A320" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B320" t="s" s="2">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="C320" t="s" s="2">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="D320" s="2"/>
     </row>
     <row r="321">
       <c r="A321" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B321" t="s" s="2">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="C321" t="s" s="2">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="D321" s="2"/>
     </row>
     <row r="322">
       <c r="A322" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B322" t="s" s="2">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="C322" t="s" s="2">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="D322" s="2"/>
     </row>
     <row r="323">
       <c r="A323" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B323" t="s" s="2">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="C323" t="s" s="2">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="D323" s="2"/>
     </row>
     <row r="324">
       <c r="A324" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B324" t="s" s="2">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="C324" t="s" s="2">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="D324" s="2"/>
     </row>
     <row r="325">
       <c r="A325" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B325" t="s" s="2">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="C325" t="s" s="2">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="D325" s="2"/>
     </row>
     <row r="326">
       <c r="A326" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B326" t="s" s="2">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="C326" t="s" s="2">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="D326" s="2"/>
     </row>
     <row r="327">
       <c r="A327" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B327" t="s" s="2">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="C327" t="s" s="2">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="D327" s="2"/>
     </row>
     <row r="328">
       <c r="A328" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B328" t="s" s="2">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="C328" t="s" s="2">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="D328" s="2"/>
     </row>
     <row r="329">
       <c r="A329" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B329" t="s" s="2">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="C329" t="s" s="2">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="D329" s="2"/>
     </row>
     <row r="330">
       <c r="A330" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B330" t="s" s="2">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="C330" t="s" s="2">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="D330" s="2"/>
     </row>
     <row r="331">
       <c r="A331" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B331" t="s" s="2">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="C331" t="s" s="2">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="D331" s="2"/>
     </row>
     <row r="332">
       <c r="A332" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B332" t="s" s="2">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="C332" t="s" s="2">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="D332" s="2"/>
     </row>
     <row r="333">
       <c r="A333" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B333" t="s" s="2">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="C333" t="s" s="2">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="D333" s="2"/>
     </row>
     <row r="334">
       <c r="A334" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B334" t="s" s="2">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="C334" t="s" s="2">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="D334" s="2"/>
     </row>
     <row r="335">
       <c r="A335" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B335" t="s" s="2">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="C335" t="s" s="2">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="D335" s="2"/>
     </row>
     <row r="336">
       <c r="A336" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B336" t="s" s="2">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="C336" t="s" s="2">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="D336" s="2"/>
     </row>
     <row r="337">
       <c r="A337" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B337" t="s" s="2">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="C337" t="s" s="2">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="D337" s="2"/>
     </row>
     <row r="338">
       <c r="A338" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B338" t="s" s="2">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="C338" t="s" s="2">
-        <v>744</v>
+        <v>747</v>
       </c>
       <c r="D338" s="2"/>
     </row>
     <row r="339">
       <c r="A339" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B339" t="s" s="2">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="C339" t="s" s="2">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="D339" s="2"/>
     </row>
     <row r="340">
       <c r="A340" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B340" t="s" s="2">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="C340" t="s" s="2">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="D340" s="2"/>
     </row>
     <row r="341">
       <c r="A341" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B341" t="s" s="2">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="C341" t="s" s="2">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="D341" s="2"/>
     </row>
     <row r="342">
       <c r="A342" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B342" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C342" t="s" s="2">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="D342" s="2"/>
     </row>
     <row r="343">
       <c r="A343" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B343" t="s" s="2">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="C343" t="s" s="2">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="D343" s="2"/>
     </row>
     <row r="344">
       <c r="A344" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B344" t="s" s="2">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="C344" t="s" s="2">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="D344" s="2"/>
     </row>
     <row r="345">
       <c r="A345" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B345" t="s" s="2">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="C345" t="s" s="2">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="D345" s="2"/>
     </row>
     <row r="346">
       <c r="A346" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B346" t="s" s="2">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="C346" t="s" s="2">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="D346" s="2"/>
     </row>
     <row r="347">
       <c r="A347" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B347" t="s" s="2">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="C347" t="s" s="2">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="D347" s="2"/>
     </row>
     <row r="348">
       <c r="A348" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B348" t="s" s="2">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="C348" t="s" s="2">
-        <v>763</v>
+        <v>766</v>
       </c>
       <c r="D348" s="2"/>
     </row>
     <row r="349">
       <c r="A349" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B349" t="s" s="2">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="C349" t="s" s="2">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="D349" s="2"/>
     </row>
     <row r="350">
       <c r="A350" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B350" t="s" s="2">
-        <v>766</v>
+        <v>769</v>
       </c>
       <c r="C350" t="s" s="2">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="D350" s="2"/>
     </row>
     <row r="351">
       <c r="A351" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B351" t="s" s="2">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="C351" t="s" s="2">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="D351" s="2"/>
     </row>
     <row r="352">
       <c r="A352" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B352" t="s" s="2">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="C352" t="s" s="2">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="D352" s="2"/>
     </row>
     <row r="353">
       <c r="A353" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B353" t="s" s="2">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="C353" t="s" s="2">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="D353" s="2"/>
     </row>
     <row r="354">
       <c r="A354" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B354" t="s" s="2">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="C354" t="s" s="2">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="D354" s="2"/>
     </row>
     <row r="355">
       <c r="A355" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B355" t="s" s="2">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="C355" t="s" s="2">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="D355" s="2"/>
     </row>
     <row r="356">
       <c r="A356" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B356" t="s" s="2">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="C356" t="s" s="2">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="D356" s="2"/>
     </row>
     <row r="357">
       <c r="A357" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B357" t="s" s="2">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="C357" t="s" s="2">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="D357" s="2"/>
     </row>
     <row r="358">
       <c r="A358" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B358" t="s" s="2">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="C358" t="s" s="2">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="D358" s="2"/>
     </row>
     <row r="359">
       <c r="A359" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B359" t="s" s="2">
-        <v>784</v>
+        <v>787</v>
       </c>
       <c r="C359" t="s" s="2">
-        <v>785</v>
+        <v>788</v>
       </c>
       <c r="D359" s="2"/>
     </row>
     <row r="360">
       <c r="A360" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B360" t="s" s="2">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="C360" t="s" s="2">
-        <v>787</v>
+        <v>790</v>
       </c>
       <c r="D360" s="2"/>
     </row>
     <row r="361">
       <c r="A361" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B361" t="s" s="2">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="C361" t="s" s="2">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="D361" s="2"/>
     </row>
     <row r="362">
       <c r="A362" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B362" t="s" s="2">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="C362" t="s" s="2">
-        <v>791</v>
+        <v>794</v>
       </c>
       <c r="D362" s="2"/>
     </row>
     <row r="363">
       <c r="A363" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B363" t="s" s="2">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="C363" t="s" s="2">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="D363" s="2"/>
     </row>
     <row r="364">
       <c r="A364" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B364" t="s" s="2">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="C364" t="s" s="2">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="D364" s="2"/>
     </row>
     <row r="365">
       <c r="A365" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B365" t="s" s="2">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="C365" t="s" s="2">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="D365" s="2"/>
     </row>
     <row r="366">
       <c r="A366" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B366" t="s" s="2">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C366" t="s" s="2">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="D366" s="2"/>
     </row>
     <row r="367">
       <c r="A367" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B367" t="s" s="2">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="C367" t="s" s="2">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="D367" s="2"/>
     </row>
     <row r="368">
       <c r="A368" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B368" t="s" s="2">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="C368" t="s" s="2">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="D368" s="2"/>
     </row>
     <row r="369">
       <c r="A369" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B369" t="s" s="2">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="C369" t="s" s="2">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="D369" s="2"/>
     </row>
     <row r="370">
       <c r="A370" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B370" t="s" s="2">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="C370" t="s" s="2">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="D370" s="2"/>
     </row>
     <row r="371">
       <c r="A371" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B371" t="s" s="2">
-        <v>808</v>
+        <v>811</v>
       </c>
       <c r="C371" t="s" s="2">
-        <v>809</v>
+        <v>812</v>
       </c>
       <c r="D371" s="2"/>
     </row>
     <row r="372">
       <c r="A372" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B372" t="s" s="2">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="C372" t="s" s="2">
-        <v>811</v>
+        <v>814</v>
       </c>
       <c r="D372" s="2"/>
     </row>
     <row r="373">
       <c r="A373" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B373" t="s" s="2">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="C373" t="s" s="2">
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="D373" s="2"/>
     </row>
     <row r="374">
       <c r="A374" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B374" t="s" s="2">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="C374" t="s" s="2">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="D374" s="2"/>
     </row>
     <row r="375">
       <c r="A375" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B375" t="s" s="2">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="C375" t="s" s="2">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="D375" s="2"/>
     </row>
     <row r="376">
       <c r="A376" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B376" t="s" s="2">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="C376" t="s" s="2">
-        <v>819</v>
+        <v>822</v>
       </c>
       <c r="D376" s="2"/>
     </row>
     <row r="377">
       <c r="A377" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B377" t="s" s="2">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="C377" t="s" s="2">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="D377" s="2"/>
     </row>
     <row r="378">
       <c r="A378" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B378" t="s" s="2">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="C378" t="s" s="2">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="D378" s="2"/>
     </row>
     <row r="379">
       <c r="A379" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B379" t="s" s="2">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="C379" t="s" s="2">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="D379" t="s" s="2">
-        <v>825</v>
+        <v>828</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B380" t="s" s="2">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="C380" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="D380" s="2"/>
     </row>
     <row r="381">
       <c r="A381" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B381" t="s" s="2">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="C381" t="s" s="2">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="D381" s="2"/>
     </row>
     <row r="382">
       <c r="A382" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B382" t="s" s="2">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="C382" t="s" s="2">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="D382" s="2"/>
     </row>
     <row r="383">
       <c r="A383" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B383" t="s" s="2">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="C383" t="s" s="2">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="D383" s="2"/>
     </row>
     <row r="384">
       <c r="A384" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B384" t="s" s="2">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="C384" t="s" s="2">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="D384" s="2"/>
     </row>
     <row r="385">
       <c r="A385" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B385" t="s" s="2">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="C385" t="s" s="2">
-        <v>836</v>
+        <v>839</v>
       </c>
       <c r="D385" s="2"/>
     </row>
     <row r="386">
       <c r="A386" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B386" t="s" s="2">
-        <v>837</v>
+        <v>840</v>
       </c>
       <c r="C386" t="s" s="2">
-        <v>838</v>
+        <v>841</v>
       </c>
       <c r="D386" s="2"/>
     </row>
     <row r="387">
       <c r="A387" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B387" t="s" s="2">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="C387" t="s" s="2">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="D387" s="2"/>
     </row>
     <row r="388">
       <c r="A388" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B388" t="s" s="2">
-        <v>841</v>
+        <v>844</v>
       </c>
       <c r="C388" t="s" s="2">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="D388" s="2"/>
     </row>
     <row r="389">
       <c r="A389" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B389" t="s" s="2">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="C389" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D389" s="2"/>
     </row>
     <row r="390">
       <c r="A390" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B390" t="s" s="2">
-        <v>844</v>
+        <v>847</v>
       </c>
       <c r="C390" t="s" s="2">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="D390" s="2"/>
     </row>
     <row r="391">
       <c r="A391" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B391" t="s" s="2">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="C391" t="s" s="2">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="D391" s="2"/>
     </row>
     <row r="392">
       <c r="A392" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B392" t="s" s="2">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="C392" t="s" s="2">
-        <v>849</v>
+        <v>852</v>
       </c>
       <c r="D392" s="2"/>
     </row>
     <row r="393">
       <c r="A393" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B393" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="C393" t="s" s="2">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="D393" s="2"/>
     </row>
     <row r="394">
       <c r="A394" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B394" t="s" s="2">
-        <v>852</v>
+        <v>855</v>
       </c>
       <c r="C394" t="s" s="2">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="D394" s="2"/>
     </row>
     <row r="395">
       <c r="A395" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B395" t="s" s="2">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="C395" t="s" s="2">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="D395" s="2"/>
     </row>
     <row r="396">
       <c r="A396" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B396" t="s" s="2">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="C396" t="s" s="2">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="D396" s="2"/>
     </row>
     <row r="397">
       <c r="A397" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B397" t="s" s="2">
-        <v>858</v>
+        <v>861</v>
       </c>
       <c r="C397" t="s" s="2">
-        <v>859</v>
+        <v>862</v>
       </c>
       <c r="D397" s="2"/>
     </row>
     <row r="398">
       <c r="A398" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B398" t="s" s="2">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="C398" t="s" s="2">
-        <v>861</v>
+        <v>864</v>
       </c>
       <c r="D398" s="2"/>
     </row>
     <row r="399">
       <c r="A399" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B399" t="s" s="2">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="C399" t="s" s="2">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="D399" s="2"/>
     </row>
     <row r="400">
       <c r="A400" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B400" t="s" s="2">
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="C400" t="s" s="2">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="D400" s="2"/>
     </row>
     <row r="401">
       <c r="A401" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B401" t="s" s="2">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="C401" t="s" s="2">
-        <v>867</v>
+        <v>870</v>
       </c>
       <c r="D401" s="2"/>
     </row>
     <row r="402">
       <c r="A402" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B402" t="s" s="2">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="C402" t="s" s="2">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="D402" s="2"/>
     </row>
     <row r="403">
       <c r="A403" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B403" t="s" s="2">
-        <v>870</v>
+        <v>873</v>
       </c>
       <c r="C403" t="s" s="2">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="D403" s="2"/>
     </row>
     <row r="404">
       <c r="A404" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B404" t="s" s="2">
-        <v>872</v>
+        <v>875</v>
       </c>
       <c r="C404" t="s" s="2">
-        <v>873</v>
+        <v>876</v>
       </c>
       <c r="D404" s="2"/>
     </row>
     <row r="405">
       <c r="A405" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B405" t="s" s="2">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="C405" t="s" s="2">
-        <v>875</v>
+        <v>878</v>
       </c>
       <c r="D405" s="2"/>
     </row>
     <row r="406">
       <c r="A406" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B406" t="s" s="2">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="C406" t="s" s="2">
-        <v>877</v>
+        <v>880</v>
       </c>
       <c r="D406" s="2"/>
     </row>
     <row r="407">
       <c r="A407" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B407" t="s" s="2">
-        <v>878</v>
+        <v>881</v>
       </c>
       <c r="C407" t="s" s="2">
-        <v>879</v>
+        <v>882</v>
       </c>
       <c r="D407" s="2"/>
     </row>
     <row r="408">
       <c r="A408" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B408" t="s" s="2">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="C408" t="s" s="2">
-        <v>881</v>
+        <v>884</v>
       </c>
       <c r="D408" s="2"/>
     </row>
     <row r="409">
       <c r="A409" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B409" t="s" s="2">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="C409" t="s" s="2">
-        <v>883</v>
+        <v>886</v>
       </c>
       <c r="D409" s="2"/>
     </row>
     <row r="410">
       <c r="A410" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B410" t="s" s="2">
-        <v>884</v>
+        <v>887</v>
       </c>
       <c r="C410" t="s" s="2">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="D410" s="2"/>
     </row>
     <row r="411">
       <c r="A411" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B411" t="s" s="2">
-        <v>886</v>
+        <v>889</v>
       </c>
       <c r="C411" t="s" s="2">
-        <v>887</v>
+        <v>890</v>
       </c>
       <c r="D411" s="2"/>
     </row>
     <row r="412">
       <c r="A412" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B412" t="s" s="2">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="C412" t="s" s="2">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="D412" s="2"/>
     </row>
     <row r="413">
       <c r="A413" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B413" t="s" s="2">
-        <v>890</v>
+        <v>893</v>
       </c>
       <c r="C413" t="s" s="2">
-        <v>891</v>
+        <v>894</v>
       </c>
       <c r="D413" s="2"/>
     </row>
     <row r="414">
       <c r="A414" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B414" t="s" s="2">
-        <v>892</v>
+        <v>895</v>
       </c>
       <c r="C414" t="s" s="2">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="D414" s="2"/>
     </row>
     <row r="415">
       <c r="A415" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B415" t="s" s="2">
-        <v>894</v>
+        <v>897</v>
       </c>
       <c r="C415" t="s" s="2">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="D415" s="2"/>
     </row>
     <row r="416">
       <c r="A416" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B416" t="s" s="2">
-        <v>896</v>
+        <v>899</v>
       </c>
       <c r="C416" t="s" s="2">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="D416" s="2"/>
     </row>
     <row r="417">
       <c r="A417" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B417" t="s" s="2">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="C417" t="s" s="2">
-        <v>899</v>
+        <v>902</v>
       </c>
       <c r="D417" s="2"/>
     </row>
     <row r="418">
       <c r="A418" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B418" t="s" s="2">
-        <v>900</v>
+        <v>903</v>
       </c>
       <c r="C418" t="s" s="2">
-        <v>901</v>
+        <v>904</v>
       </c>
       <c r="D418" s="2"/>
     </row>
     <row r="419">
       <c r="A419" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B419" t="s" s="2">
-        <v>902</v>
+        <v>905</v>
       </c>
       <c r="C419" t="s" s="2">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="D419" s="2"/>
     </row>
     <row r="420">
       <c r="A420" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B420" t="s" s="2">
-        <v>904</v>
+        <v>907</v>
       </c>
       <c r="C420" t="s" s="2">
-        <v>905</v>
+        <v>908</v>
       </c>
       <c r="D420" s="2"/>
     </row>
     <row r="421">
       <c r="A421" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B421" t="s" s="2">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="C421" t="s" s="2">
-        <v>907</v>
+        <v>910</v>
       </c>
       <c r="D421" s="2"/>
     </row>
     <row r="422">
       <c r="A422" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B422" t="s" s="2">
-        <v>908</v>
+        <v>911</v>
       </c>
       <c r="C422" t="s" s="2">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="D422" s="2"/>
     </row>
     <row r="423">
       <c r="A423" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B423" t="s" s="2">
-        <v>910</v>
+        <v>913</v>
       </c>
       <c r="C423" t="s" s="2">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="D423" t="s" s="2">
-        <v>912</v>
+        <v>915</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B424" t="s" s="2">
-        <v>913</v>
+        <v>916</v>
       </c>
       <c r="C424" t="s" s="2">
-        <v>914</v>
+        <v>917</v>
       </c>
       <c r="D424" t="s" s="2">
-        <v>912</v>
+        <v>915</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B425" t="s" s="2">
+        <v>918</v>
+      </c>
+      <c r="C425" t="s" s="2">
+        <v>919</v>
+      </c>
+      <c r="D425" t="s" s="2">
         <v>915</v>
-      </c>
-      <c r="C425" t="s" s="2">
-        <v>916</v>
-      </c>
-      <c r="D425" t="s" s="2">
-        <v>912</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B426" t="s" s="2">
-        <v>917</v>
+        <v>920</v>
       </c>
       <c r="C426" t="s" s="2">
-        <v>918</v>
+        <v>921</v>
       </c>
       <c r="D426" s="2"/>
     </row>
     <row r="427">
       <c r="A427" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B427" t="s" s="2">
-        <v>919</v>
+        <v>922</v>
       </c>
       <c r="C427" t="s" s="2">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="D427" t="s" s="2">
-        <v>921</v>
+        <v>924</v>
       </c>
     </row>
   </sheetData>

--- a/ig/DM_FINESS_New/CodeSystem-tre-r397-categorie-entite-geographique-exercice.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-tre-r397-categorie-entite-geographique-exercice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1379" uniqueCount="925">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1383" uniqueCount="928">
   <si>
     <t>Property</t>
   </si>
@@ -118,2172 +118,2172 @@
     <t>Count</t>
   </si>
   <si>
+    <t>427</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Uri</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>niveau</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#niveau</t>
+  </si>
+  <si>
+    <t>Permet d'indiquer le niveau hiérarchique du code</t>
+  </si>
+  <si>
+    <t>integer</t>
+  </si>
+  <si>
+    <t>parent</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/concept-properties#parent</t>
+  </si>
+  <si>
+    <t>An immediate parent of the concept in the hierarchy</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>domaine</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#domaine</t>
+  </si>
+  <si>
+    <t>Domaine de la categorie d etablissement</t>
+  </si>
+  <si>
+    <t>Coding</t>
+  </si>
+  <si>
+    <t>dateValid</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateValid</t>
+  </si>
+  <si>
+    <t>date de validité d'un code concept</t>
+  </si>
+  <si>
+    <t>dateTime</t>
+  </si>
+  <si>
+    <t>dateMaj</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateMaj</t>
+  </si>
+  <si>
+    <t>Date de mise à jour d'un code concept</t>
+  </si>
+  <si>
+    <t>dateFin</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateFin</t>
+  </si>
+  <si>
+    <t>Date de fin d'exploitation d'un code concept</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/concept-properties#status</t>
+  </si>
+  <si>
+    <t>A property that indicates the status of the concept.</t>
+  </si>
+  <si>
+    <t>deprecationDate</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/concept-properties#deprecationDate</t>
+  </si>
+  <si>
+    <t>Date Concept was deprecated</t>
+  </si>
+  <si>
+    <t>retirementDate</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/concept-properties#retirementDate</t>
+  </si>
+  <si>
+    <t>Date Concept was retired</t>
+  </si>
+  <si>
+    <t>specialisationRor</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#specialisationRor</t>
+  </si>
+  <si>
+    <t>Propriété permettant de spécifier les codes exclusifs appartenant au ROR</t>
+  </si>
+  <si>
+    <t>boolean</t>
+  </si>
+  <si>
+    <t>ror</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#ror</t>
+  </si>
+  <si>
+    <t>Permet de définir les codes concepts uilisés par le ROR</t>
+  </si>
+  <si>
+    <t>cisis</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#cisis</t>
+  </si>
+  <si>
+    <t>Permet de définir les codes concepts uilisés par le CISIS</t>
+  </si>
+  <si>
+    <t>rass</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#rass</t>
+  </si>
+  <si>
+    <t>Permet de définir les codes concepts uilisés par le RASS</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>Display</t>
+  </si>
+  <si>
+    <t>Definition</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>0100</t>
+  </si>
+  <si>
+    <t>Etablissements d'administration</t>
+  </si>
+  <si>
+    <t>1000</t>
+  </si>
+  <si>
+    <t>Etablissements Relevant de la Loi Hospitalière</t>
+  </si>
+  <si>
+    <t>2000</t>
+  </si>
+  <si>
+    <t>Autres Etablissements de Soins et Prévention</t>
+  </si>
+  <si>
+    <t>3000</t>
+  </si>
+  <si>
+    <t>Autres Etablissements à Caractère Sanitaire</t>
+  </si>
+  <si>
+    <t>4000</t>
+  </si>
+  <si>
+    <t>Etab.Serv.Soc.d'Accueil Hébergement Assistance Réadaptation</t>
+  </si>
+  <si>
+    <t>5000</t>
+  </si>
+  <si>
+    <t>Etablissements et Services Sociaux d'Aide à la Famille</t>
+  </si>
+  <si>
+    <t>6000</t>
+  </si>
+  <si>
+    <t>Etab.de Formation des Personnels Sanitaires et Sociaux</t>
+  </si>
+  <si>
+    <t>0110</t>
+  </si>
+  <si>
+    <t>Etablissements d'Administration</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>1100</t>
+  </si>
+  <si>
+    <t>Etablissements Hospitaliers</t>
+  </si>
+  <si>
+    <t>1200</t>
+  </si>
+  <si>
+    <t>Autres Etablissements Relevant de la Loi Hospitalière</t>
+  </si>
+  <si>
+    <t>2100</t>
+  </si>
+  <si>
+    <t>Cabinets Libéraux</t>
+  </si>
+  <si>
+    <t>2200</t>
+  </si>
+  <si>
+    <t>3100</t>
+  </si>
+  <si>
+    <t>Laboratoires de Biologie Médicale</t>
+  </si>
+  <si>
+    <t>3200</t>
+  </si>
+  <si>
+    <t>Commerce de Biens à Usage Médicaux</t>
+  </si>
+  <si>
+    <t>3400</t>
+  </si>
+  <si>
+    <t>4100</t>
+  </si>
+  <si>
+    <t>Etab.et Serv.pour l'Enfance et la Jeunesse Handicapée</t>
+  </si>
+  <si>
+    <t>4200</t>
+  </si>
+  <si>
+    <t>Etablissements ou Classes d'Enseignement Spécial</t>
+  </si>
+  <si>
+    <t>4300</t>
+  </si>
+  <si>
+    <t>Etablissements et Services pour Adultes Handicapés</t>
+  </si>
+  <si>
+    <t>4400</t>
+  </si>
+  <si>
+    <t>Etablissements et Services pour Personnes Agées</t>
+  </si>
+  <si>
+    <t>4500</t>
+  </si>
+  <si>
+    <t>Etab.et Serv.Sociaux Concourant à la Protection de l'Enfance</t>
+  </si>
+  <si>
+    <t>4600</t>
+  </si>
+  <si>
+    <t>Autres Etab. Accueil, Hébergement, Réadaptation et Services</t>
+  </si>
+  <si>
+    <t>5100</t>
+  </si>
+  <si>
+    <t>6100</t>
+  </si>
+  <si>
+    <t>Etablissements de Formation des Personnels Sanitaires</t>
+  </si>
+  <si>
+    <t>6200</t>
+  </si>
+  <si>
+    <t>Etablissements de Formation des Personnels Sociaux</t>
+  </si>
+  <si>
+    <t>6300</t>
+  </si>
+  <si>
+    <t>Etablissements de Formation Polyvalente</t>
+  </si>
+  <si>
+    <t>0101</t>
+  </si>
+  <si>
+    <t>1101</t>
+  </si>
+  <si>
+    <t>Centres Hospitaliers Régionaux</t>
+  </si>
+  <si>
+    <t>1102</t>
+  </si>
+  <si>
+    <t>Centres Hospitaliers</t>
+  </si>
+  <si>
+    <t>1103</t>
+  </si>
+  <si>
+    <t>Centres Hospitaliers Spécialisés Lutte Maladies Mentales</t>
+  </si>
+  <si>
+    <t>1104</t>
+  </si>
+  <si>
+    <t>Centres de Lutte contre le Cancer</t>
+  </si>
+  <si>
+    <t>1106</t>
+  </si>
+  <si>
+    <t>Hôpitaux Locaux</t>
+  </si>
+  <si>
+    <t>1107</t>
+  </si>
+  <si>
+    <t>Etablissements de santé privé autorisés en SSR</t>
+  </si>
+  <si>
+    <t>1108</t>
+  </si>
+  <si>
+    <t>Centre de Moyen et de Long Séjour</t>
+  </si>
+  <si>
+    <t>1109</t>
+  </si>
+  <si>
+    <t>Etablissements de Soins de Longue Durée</t>
+  </si>
+  <si>
+    <t>1110</t>
+  </si>
+  <si>
+    <t>Etablissements de Soins de Courte Durée</t>
+  </si>
+  <si>
+    <t>1111</t>
+  </si>
+  <si>
+    <t>Autres Etablissements de Lutte contre les Maladies Mentales</t>
+  </si>
+  <si>
+    <t>1112</t>
+  </si>
+  <si>
+    <t>Etablissements d'Enfants à Caractère Sanitaire</t>
+  </si>
+  <si>
+    <t>1113</t>
+  </si>
+  <si>
+    <t>Etablissements de Lutte contre l'Alcoolisme</t>
+  </si>
+  <si>
+    <t>1201</t>
+  </si>
+  <si>
+    <t>Traitements et Soins à Domicile</t>
+  </si>
+  <si>
+    <t>1202</t>
+  </si>
+  <si>
+    <t>Santé Mentale</t>
+  </si>
+  <si>
+    <t>1203</t>
+  </si>
+  <si>
+    <t>Dialyse ambulatoire</t>
+  </si>
+  <si>
+    <t>1204</t>
+  </si>
+  <si>
+    <t>Urgence et Réanimation</t>
+  </si>
+  <si>
+    <t>1205</t>
+  </si>
+  <si>
+    <t>2101</t>
+  </si>
+  <si>
+    <t>Cabinets Libéraux de Médecins</t>
+  </si>
+  <si>
+    <t>2102</t>
+  </si>
+  <si>
+    <t>Cabinet de Groupe</t>
+  </si>
+  <si>
+    <t>2103</t>
+  </si>
+  <si>
+    <t>Autres structures d'exercice libéral</t>
+  </si>
+  <si>
+    <t>2105</t>
+  </si>
+  <si>
+    <t>Cabinet d'Auxiliaires Médicaux</t>
+  </si>
+  <si>
+    <t>2201</t>
+  </si>
+  <si>
+    <t>Dispensaires ou Centres de Soins</t>
+  </si>
+  <si>
+    <t>2202</t>
+  </si>
+  <si>
+    <t>Etablissements de PMI et de Planification Familiale</t>
+  </si>
+  <si>
+    <t>2203</t>
+  </si>
+  <si>
+    <t>Etablissements de Soins Dentaires</t>
+  </si>
+  <si>
+    <t>2204</t>
+  </si>
+  <si>
+    <t>Etablissements ne relevant pas de la Loi Hospitalière</t>
+  </si>
+  <si>
+    <t>2205</t>
+  </si>
+  <si>
+    <t>Etab.de soins relevant du service de santé des armées</t>
+  </si>
+  <si>
+    <t>2206</t>
+  </si>
+  <si>
+    <t>Centres de Santé</t>
+  </si>
+  <si>
+    <t>3101</t>
+  </si>
+  <si>
+    <t>3201</t>
+  </si>
+  <si>
+    <t>3202</t>
+  </si>
+  <si>
+    <t>Commerce de Biens Médicaux</t>
+  </si>
+  <si>
+    <t>3401</t>
+  </si>
+  <si>
+    <t>Transfusion Sanguine</t>
+  </si>
+  <si>
+    <t>3402</t>
+  </si>
+  <si>
+    <t>Conservation et Stockage d'autres Produits Humains</t>
+  </si>
+  <si>
+    <t>3403</t>
+  </si>
+  <si>
+    <t>Centre Antipoison</t>
+  </si>
+  <si>
+    <t>3404</t>
+  </si>
+  <si>
+    <t>Service d'Ambulances</t>
+  </si>
+  <si>
+    <t>3405</t>
+  </si>
+  <si>
+    <t>Installations autonomes de chirurgie esthétique</t>
+  </si>
+  <si>
+    <t>3406</t>
+  </si>
+  <si>
+    <t>Maisons de Naissance</t>
+  </si>
+  <si>
+    <t>3407</t>
+  </si>
+  <si>
+    <t>Etablissements Expérimentaux en Santé</t>
+  </si>
+  <si>
+    <t>3408</t>
+  </si>
+  <si>
+    <t>Centre de ressources transverse</t>
+  </si>
+  <si>
+    <t>3409</t>
+  </si>
+  <si>
+    <t>Services de Prévention et de Santé au Travail (SPST)</t>
+  </si>
+  <si>
+    <t>3410</t>
+  </si>
+  <si>
+    <t>Services d'incendie et de secours</t>
+  </si>
+  <si>
+    <t>4101</t>
+  </si>
+  <si>
+    <t>Etab.Educ.Spéciale pour Déficients Mentaux et Handicapés</t>
+  </si>
+  <si>
+    <t>4102</t>
+  </si>
+  <si>
+    <t>Etab.Educ Spéciale pour Enfants Trouble Conduite et Comport</t>
+  </si>
+  <si>
+    <t>4103</t>
+  </si>
+  <si>
+    <t>Etablissements d'Education Spéciale pour Handicapés Moteurs</t>
+  </si>
+  <si>
+    <t>4104</t>
+  </si>
+  <si>
+    <t>Etab.Education Spéciale pour Déficients Sensoriels</t>
+  </si>
+  <si>
+    <t>4105</t>
+  </si>
+  <si>
+    <t>Etablissements et Services Hébergement Enfants Handicapés</t>
+  </si>
+  <si>
+    <t>4106</t>
+  </si>
+  <si>
+    <t>Services à Domicile ou Ambulatoires pour Handicapés</t>
+  </si>
+  <si>
+    <t>4107</t>
+  </si>
+  <si>
+    <t>Etab. Expérimentaux en Faveur de l'Enfance Handicapée</t>
+  </si>
+  <si>
+    <t>4201</t>
+  </si>
+  <si>
+    <t>Etablissements ou Classes de Pré-Élémentaire et Élémentaire</t>
+  </si>
+  <si>
+    <t>4202</t>
+  </si>
+  <si>
+    <t>Etablissements d'Enseignement Secondaire</t>
+  </si>
+  <si>
+    <t>4301</t>
+  </si>
+  <si>
+    <t>Etab. et Services d'Hébergement pour Adultes Handicapés</t>
+  </si>
+  <si>
+    <t>4302</t>
+  </si>
+  <si>
+    <t>Etab.et Services de Travail Protégé pour Adultes Handicapés</t>
+  </si>
+  <si>
+    <t>4303</t>
+  </si>
+  <si>
+    <t>Etab.et Services de Réinsertion Prof pour Adultes Handicapés</t>
+  </si>
+  <si>
+    <t>4304</t>
+  </si>
+  <si>
+    <t>Etab.Expérimentaux en Faveur des Adultes Handicapés</t>
+  </si>
+  <si>
+    <t>4305</t>
+  </si>
+  <si>
+    <t>Services de Maintien à Domicile pour Handicapés</t>
+  </si>
+  <si>
+    <t>4401</t>
+  </si>
+  <si>
+    <t>Etablissements d'Hébergement pour Personnes Âgées</t>
+  </si>
+  <si>
+    <t>4402</t>
+  </si>
+  <si>
+    <t>Services de Maintien à Domicile pour Personnes Âgées</t>
+  </si>
+  <si>
+    <t>4403</t>
+  </si>
+  <si>
+    <t>Services Sociaux en Faveur des Personnes Âgées</t>
+  </si>
+  <si>
+    <t>4404</t>
+  </si>
+  <si>
+    <t>Etablissements Expérimentaux en Faveur des Personnes Âgées</t>
+  </si>
+  <si>
+    <t>4501</t>
+  </si>
+  <si>
+    <t>Etablissements de l'Aide Sociale à l'Enfance</t>
+  </si>
+  <si>
+    <t>4502</t>
+  </si>
+  <si>
+    <t>Etab.et Services du Ministère de la Justice pour Mineurs</t>
+  </si>
+  <si>
+    <t>4504</t>
+  </si>
+  <si>
+    <t>Services Concourant à la Protection de l'Enfance</t>
+  </si>
+  <si>
+    <t>4505</t>
+  </si>
+  <si>
+    <t>Etab. Expérimentaux en Faveur de l'Enfance Protégée</t>
+  </si>
+  <si>
+    <t>4601</t>
+  </si>
+  <si>
+    <t>Etablissements pour Adultes et Familles en Difficulté</t>
+  </si>
+  <si>
+    <t>4602</t>
+  </si>
+  <si>
+    <t>Autres Etablissements Sociaux d'Hébergement et d'Accueil</t>
+  </si>
+  <si>
+    <t>4603</t>
+  </si>
+  <si>
+    <t>Etablissements Expérimentaux en Faveur des Adultes</t>
+  </si>
+  <si>
+    <t>4604</t>
+  </si>
+  <si>
+    <t>Autres Etablissements médico-sociaux</t>
+  </si>
+  <si>
+    <t>4605</t>
+  </si>
+  <si>
+    <t>Etablissements et services multi-clientèles</t>
+  </si>
+  <si>
+    <t>4606</t>
+  </si>
+  <si>
+    <t>Centres de ressources</t>
+  </si>
+  <si>
+    <t>4607</t>
+  </si>
+  <si>
+    <t>Logements en Structure Collective</t>
+  </si>
+  <si>
+    <t>4608</t>
+  </si>
+  <si>
+    <t>Protection des majeurs</t>
+  </si>
+  <si>
+    <t>4609</t>
+  </si>
+  <si>
+    <t>Centres prestataires de services pr personnes cérébro-lésées</t>
+  </si>
+  <si>
+    <t>5101</t>
+  </si>
+  <si>
+    <t>Etablissements Garde d'Enfants d'Age pré-Scolaire</t>
+  </si>
+  <si>
+    <t>5102</t>
+  </si>
+  <si>
+    <t>Etablissements d'Hébergement pour Enfants d'Age Scolaire</t>
+  </si>
+  <si>
+    <t>5103</t>
+  </si>
+  <si>
+    <t>Etablissements Sociaux pour Loisirs et Vacances</t>
+  </si>
+  <si>
+    <t>5104</t>
+  </si>
+  <si>
+    <t>Etablissements ou Services Divers d'Aide à la Famille</t>
+  </si>
+  <si>
+    <t>6101</t>
+  </si>
+  <si>
+    <t>6102</t>
+  </si>
+  <si>
+    <t>Etablissements de Formation des Personnels Techniques</t>
+  </si>
+  <si>
+    <t>6103</t>
+  </si>
+  <si>
+    <t>Autres Etablissements de Formation des Personnels Techniques</t>
+  </si>
+  <si>
+    <t>6201</t>
+  </si>
+  <si>
+    <t>6301</t>
+  </si>
+  <si>
+    <t>001</t>
+  </si>
+  <si>
+    <t>Autres lits de m.R.</t>
+  </si>
+  <si>
+    <t>002</t>
+  </si>
+  <si>
+    <t>Autres places de l-f.</t>
+  </si>
+  <si>
+    <t>003</t>
+  </si>
+  <si>
+    <t>Autres lits de l-s</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>Centre Hospitalier Régional (C.H.R.)</t>
+  </si>
+  <si>
+    <t>106</t>
+  </si>
+  <si>
+    <t>Centre hospitalier, ex Hôpital local</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>Etablissement de Convalescence et de Repos</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>Etablissement de santé privé autorisé en SSR</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>Centre de Convalescence Cure ou Réadaptation</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>Hôpital des armées</t>
+  </si>
+  <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t>Etablissement de Soins du Service de Santé des Armées</t>
+  </si>
+  <si>
+    <t>119</t>
+  </si>
+  <si>
+    <t>Maison de Régime</t>
+  </si>
+  <si>
+    <t>122</t>
+  </si>
+  <si>
+    <t>Etablissement Soins Obstétriques Chirurgico-Gynécologiques</t>
+  </si>
+  <si>
+    <t>124</t>
+  </si>
+  <si>
+    <t>Centre de Santé</t>
+  </si>
+  <si>
+    <t>125</t>
+  </si>
+  <si>
+    <t>Centre de Santé Dentaire</t>
+  </si>
+  <si>
+    <t>126</t>
+  </si>
+  <si>
+    <t>Etablissement Thermal</t>
+  </si>
+  <si>
+    <t>127</t>
+  </si>
+  <si>
+    <t>Hospitalisation à Domicile</t>
+  </si>
+  <si>
+    <t>128</t>
+  </si>
+  <si>
+    <t>Etablissement de Soins Chirurgicaux</t>
+  </si>
+  <si>
+    <t>129</t>
+  </si>
+  <si>
+    <t>Etablissement de Soins Médicaux</t>
+  </si>
+  <si>
+    <t>130</t>
+  </si>
+  <si>
+    <t>Centre de Soins Médicaux</t>
+  </si>
+  <si>
+    <t>131</t>
+  </si>
+  <si>
+    <t>Centre de Lutte Contre Cancer</t>
+  </si>
+  <si>
+    <t>132</t>
+  </si>
+  <si>
+    <t>Etablissement de Transfusion Sanguine</t>
+  </si>
+  <si>
+    <t>135</t>
+  </si>
+  <si>
+    <t>Etablissement Réadaptation Fonctionnelle</t>
+  </si>
+  <si>
+    <t>136</t>
+  </si>
+  <si>
+    <t>Banque de Sperme</t>
+  </si>
+  <si>
+    <t>137</t>
+  </si>
+  <si>
+    <t>Banque d'Organes</t>
+  </si>
+  <si>
+    <t>138</t>
+  </si>
+  <si>
+    <t>Centre de Dialyse Périodique</t>
+  </si>
+  <si>
+    <t>139</t>
+  </si>
+  <si>
+    <t>Centre de Dialyse et d'entraînement à la Dialyse</t>
+  </si>
+  <si>
+    <t>140</t>
+  </si>
+  <si>
+    <t>Centre d'Entraînement à la Dialyse</t>
+  </si>
+  <si>
+    <t>141</t>
+  </si>
+  <si>
+    <t>Centre de dialyse</t>
+  </si>
+  <si>
+    <t>142</t>
+  </si>
+  <si>
+    <t>Dispensaire Antituberculeux</t>
+  </si>
+  <si>
+    <t>143</t>
+  </si>
+  <si>
+    <t>Centre de Vaccination BCG</t>
+  </si>
+  <si>
+    <t>144</t>
+  </si>
+  <si>
+    <t>Etablissement de Lutte Contre la Tuberculose</t>
+  </si>
+  <si>
+    <t>146</t>
+  </si>
+  <si>
+    <t>Structure d'Alternative à la dialyse en centre</t>
+  </si>
+  <si>
+    <t>156</t>
+  </si>
+  <si>
+    <t>Centre Médico-Psychologique (C.M.P.)</t>
+  </si>
+  <si>
+    <t>157</t>
+  </si>
+  <si>
+    <t>Centre de Postcure</t>
+  </si>
+  <si>
+    <t>159</t>
+  </si>
+  <si>
+    <t>Centre Parental</t>
+  </si>
+  <si>
+    <t>160</t>
+  </si>
+  <si>
+    <t>Centre de Soins Spécifiques pour Toxicomanes (C.S.S.T.)</t>
+  </si>
+  <si>
+    <t>161</t>
+  </si>
+  <si>
+    <t>Maison de Santé pour Maladies Mentales</t>
+  </si>
+  <si>
+    <t>162</t>
+  </si>
+  <si>
+    <t>Centre de Cure Ambulatoire en Alcoologie (C.C.A.A.)</t>
+  </si>
+  <si>
+    <t>163</t>
+  </si>
+  <si>
+    <t>Maison d'Enfants à Caractère Sanitaire Temporaire</t>
+  </si>
+  <si>
+    <t>164</t>
+  </si>
+  <si>
+    <t>Etablissements Expérimentaux Accueil de la Petite Enfance</t>
+  </si>
+  <si>
+    <t>165</t>
+  </si>
+  <si>
+    <t>Appartement de Coordination Thérapeutique (A.C.T.)</t>
+  </si>
+  <si>
+    <t>166</t>
+  </si>
+  <si>
+    <t>Etablissement d'Accueil Mère-Enfant</t>
+  </si>
+  <si>
+    <t>167</t>
+  </si>
+  <si>
+    <t>Crèche Collective</t>
+  </si>
+  <si>
+    <t>168</t>
+  </si>
+  <si>
+    <t>Service Accueil Familial pour la Petite Enfance</t>
+  </si>
+  <si>
+    <t>169</t>
+  </si>
+  <si>
+    <t>Crèche Multi Accueil Collectif et Familial</t>
+  </si>
+  <si>
+    <t>170</t>
+  </si>
+  <si>
+    <t>Halte Garderie</t>
+  </si>
+  <si>
+    <t>171</t>
+  </si>
+  <si>
+    <t>Garderie et Jardin d'Enfants</t>
+  </si>
+  <si>
+    <t>172</t>
+  </si>
+  <si>
+    <t>Pouponnière à Caractère Social</t>
+  </si>
+  <si>
+    <t>173</t>
+  </si>
+  <si>
+    <t>Pouponnière à Caractère Sanitaire</t>
+  </si>
+  <si>
+    <t>174</t>
+  </si>
+  <si>
+    <t>Etablissement d'Accueil Collectif Régulier et Occasionnel</t>
+  </si>
+  <si>
+    <t>175</t>
+  </si>
+  <si>
+    <t>Foyer de l'Enfance</t>
+  </si>
+  <si>
+    <t>176</t>
+  </si>
+  <si>
+    <t>Village d'Enfants</t>
+  </si>
+  <si>
+    <t>177</t>
+  </si>
+  <si>
+    <t>Maison d'Enfants à Caractère Social</t>
+  </si>
+  <si>
+    <t>178</t>
+  </si>
+  <si>
+    <t>Ctre.Accueil- Accomp.Réduc.Risq.Usag. Drogues (C.A.A.R.U.D.)</t>
+  </si>
+  <si>
+    <t>179</t>
+  </si>
+  <si>
+    <t>Maison d'Enfants à Caractère Sanitaire Permanente</t>
+  </si>
+  <si>
+    <t>180</t>
+  </si>
+  <si>
+    <t>Lits Halte Soins Santé (L.H.S.S.)</t>
+  </si>
+  <si>
+    <t>181</t>
+  </si>
+  <si>
+    <t>Maison Familiale de Vacances</t>
+  </si>
+  <si>
+    <t>182</t>
+  </si>
+  <si>
+    <t>Service d'Éducation Spéciale et de Soins à Domicile</t>
+  </si>
+  <si>
+    <t>183</t>
+  </si>
+  <si>
+    <t>Institut Médico-Educatif (I.M.E.)</t>
+  </si>
+  <si>
+    <t>184</t>
+  </si>
+  <si>
+    <t>Institut Médico-Pédagogique (I.M.P.)</t>
+  </si>
+  <si>
+    <t>185</t>
+  </si>
+  <si>
+    <t>Institut Médico-Professionnel (I.M.Pro.)</t>
+  </si>
+  <si>
+    <t>186</t>
+  </si>
+  <si>
+    <t>Institut Thérapeutique Éducatif et Pédagogique (I.T.E.P.)</t>
+  </si>
+  <si>
+    <t>188</t>
+  </si>
+  <si>
+    <t>Etablissement pour Enfants ou Adolescents Polyhandicapés</t>
+  </si>
+  <si>
+    <t>189</t>
+  </si>
+  <si>
+    <t>Centre Médico-Psycho-Pédagogique (C.M.P.P.)</t>
+  </si>
+  <si>
+    <t>190</t>
+  </si>
+  <si>
+    <t>Centre Action Médico-Sociale Précoce (C.A.M.S.P.)</t>
+  </si>
+  <si>
+    <t>191</t>
+  </si>
+  <si>
+    <t>Etablissement pour Déficients Moteurs Cérébraux</t>
+  </si>
+  <si>
+    <t>192</t>
+  </si>
+  <si>
+    <t>Institut d'éducation motrice</t>
+  </si>
+  <si>
+    <t>193</t>
+  </si>
+  <si>
+    <t>Etablissement pour Déficients Moteurs et Moteurs Cérébraux</t>
+  </si>
+  <si>
+    <t>194</t>
+  </si>
+  <si>
+    <t>Institut pour Déficients Visuels</t>
+  </si>
+  <si>
+    <t>195</t>
+  </si>
+  <si>
+    <t>Institut pour Déficients Auditifs</t>
+  </si>
+  <si>
+    <t>196</t>
+  </si>
+  <si>
+    <t>Institut d'Education Sensorielle Sourd-Aveugle</t>
+  </si>
+  <si>
+    <t>197</t>
+  </si>
+  <si>
+    <t>Centre soins accompagnement prévention addictologie (CSAPA)</t>
+  </si>
+  <si>
+    <t>198</t>
+  </si>
+  <si>
+    <t>Établissement et Service de Préorientation</t>
+  </si>
+  <si>
+    <t>199</t>
+  </si>
+  <si>
+    <t>Hospice</t>
+  </si>
+  <si>
+    <t>200</t>
+  </si>
+  <si>
+    <t>Maison de Retraite</t>
+  </si>
+  <si>
+    <t>202</t>
+  </si>
+  <si>
+    <t>Résidences autonomie</t>
+  </si>
+  <si>
+    <t>205</t>
+  </si>
+  <si>
+    <t>Foyer Club Restaurant</t>
+  </si>
+  <si>
+    <t>207</t>
+  </si>
+  <si>
+    <t>Centre de Jour pour Personnes Agées</t>
+  </si>
+  <si>
+    <t>208</t>
+  </si>
+  <si>
+    <t>Service d'Aide Ménagère à Domicile</t>
+  </si>
+  <si>
+    <t>209</t>
+  </si>
+  <si>
+    <t>Service autonomie aide et soins (SAAS)</t>
+  </si>
+  <si>
+    <t>212</t>
+  </si>
+  <si>
+    <t>Alarme Médico-Sociale</t>
+  </si>
+  <si>
+    <t>213</t>
+  </si>
+  <si>
+    <t>Lits d'Accueil Médicalisés (L.A.M.)</t>
+  </si>
+  <si>
+    <t>214</t>
+  </si>
+  <si>
+    <t>Centre Hébergement &amp; Réinsertion Sociale (C.H.R.S.)</t>
+  </si>
+  <si>
+    <t>215</t>
+  </si>
+  <si>
+    <t>Maison Relai</t>
+  </si>
+  <si>
+    <t>216</t>
+  </si>
+  <si>
+    <t>Résidence Hôtelière à Vocation Sociale (R.H.V.S)</t>
+  </si>
+  <si>
+    <t>217</t>
+  </si>
+  <si>
+    <t>Cité de Transit</t>
+  </si>
+  <si>
+    <t>218</t>
+  </si>
+  <si>
+    <t>Aire Station Nomades</t>
+  </si>
+  <si>
+    <t>219</t>
+  </si>
+  <si>
+    <t>Autre Centre d'Accueil</t>
+  </si>
+  <si>
+    <t>220</t>
+  </si>
+  <si>
+    <t>Centre Social</t>
+  </si>
+  <si>
+    <t>221</t>
+  </si>
+  <si>
+    <t>Bureau d'Aide Psychologique Universitaire (B.A.P.U.)</t>
+  </si>
+  <si>
+    <t>223</t>
+  </si>
+  <si>
+    <t>Protection Maternelle et Infantile (P.M.I.)</t>
+  </si>
+  <si>
+    <t>224</t>
+  </si>
+  <si>
+    <t>Etablissement de Consultation Pré et Post-natale</t>
+  </si>
+  <si>
+    <t>225</t>
+  </si>
+  <si>
+    <t>Consultations de Nourrissons</t>
+  </si>
+  <si>
+    <t>228</t>
+  </si>
+  <si>
+    <t>Centre de Santé Sexuelle</t>
+  </si>
+  <si>
+    <t>229</t>
+  </si>
+  <si>
+    <t>Consultation Problèmes naissance</t>
+  </si>
+  <si>
+    <t>230</t>
+  </si>
+  <si>
+    <t>Etablissement Consultation Protection Infantile</t>
+  </si>
+  <si>
+    <t>231</t>
+  </si>
+  <si>
+    <t>Etablissement Information Consultation Conseil Familial</t>
+  </si>
+  <si>
+    <t>233</t>
+  </si>
+  <si>
+    <t>Lactarium</t>
+  </si>
+  <si>
+    <t>236</t>
+  </si>
+  <si>
+    <t>Centre Placement Familial Socio-Educatif (C.P.F.S.E.)</t>
+  </si>
+  <si>
+    <t>237</t>
+  </si>
+  <si>
+    <t>Centre de Placement Familial Spécialisé</t>
+  </si>
+  <si>
+    <t>238</t>
+  </si>
+  <si>
+    <t>Centre d'Accueil Familial Spécialisé</t>
+  </si>
+  <si>
+    <t>241</t>
+  </si>
+  <si>
+    <t>Établissement de Placement</t>
+  </si>
+  <si>
+    <t>242</t>
+  </si>
+  <si>
+    <t>Service d’Activité de Jour</t>
+  </si>
+  <si>
+    <t>246</t>
+  </si>
+  <si>
+    <t>Etablissement et Service d'Aide par le Travail (E.S.A.T.)</t>
+  </si>
+  <si>
+    <t>247</t>
+  </si>
+  <si>
+    <t>Entreprise adaptée</t>
+  </si>
+  <si>
+    <t>249</t>
+  </si>
+  <si>
+    <t>Établissement et Service de Réadaptation Professionnelle</t>
+  </si>
+  <si>
+    <t>250</t>
+  </si>
+  <si>
+    <t>Centre Réentrainement au travail</t>
+  </si>
+  <si>
+    <t>251</t>
+  </si>
+  <si>
+    <t>Maison Vacances pour Handicapés</t>
+  </si>
+  <si>
+    <t>252</t>
+  </si>
+  <si>
+    <t>Foyer Hébergement Adultes Handicapés</t>
+  </si>
+  <si>
+    <t>253</t>
+  </si>
+  <si>
+    <t>Foyer d'Accueil Polyvalent pour Adultes Handicapés</t>
+  </si>
+  <si>
+    <t>255</t>
+  </si>
+  <si>
+    <t>Maison d'Accueil Spécialisée (M.A.S.)</t>
+  </si>
+  <si>
+    <t>256</t>
+  </si>
+  <si>
+    <t>Foyer Travailleurs Migrants non transformé en Résidence Soc.</t>
+  </si>
+  <si>
+    <t>257</t>
+  </si>
+  <si>
+    <t>Foyers de jeunes travailleurs</t>
+  </si>
+  <si>
+    <t>258</t>
+  </si>
+  <si>
+    <t>Maisons Relais - Pensions de Famille</t>
+  </si>
+  <si>
+    <t>259</t>
+  </si>
+  <si>
+    <t>Autres résidences sociales</t>
+  </si>
+  <si>
+    <t>261</t>
+  </si>
+  <si>
+    <t>D.D.A.S.S.</t>
+  </si>
+  <si>
+    <t>262</t>
+  </si>
+  <si>
+    <t>Etablissement Régional d'Enseignement Adapté</t>
+  </si>
+  <si>
+    <t>265</t>
+  </si>
+  <si>
+    <t>Section Education Spéciale Classe Atelier</t>
+  </si>
+  <si>
+    <t>266</t>
+  </si>
+  <si>
+    <t>Dispensaire Antivénérien</t>
+  </si>
+  <si>
+    <t>267</t>
+  </si>
+  <si>
+    <t>Dispensaire Antihansénien</t>
+  </si>
+  <si>
+    <t>268</t>
+  </si>
+  <si>
+    <t>Centre Médico-Scolaire</t>
+  </si>
+  <si>
+    <t>269</t>
+  </si>
+  <si>
+    <t>Centre de Médecine Universitaire</t>
+  </si>
+  <si>
+    <t>270</t>
+  </si>
+  <si>
+    <t>Centre de Médecine Sportive</t>
+  </si>
+  <si>
+    <t>271</t>
+  </si>
+  <si>
+    <t>Maison d'accueil Hospitalière</t>
+  </si>
+  <si>
+    <t>272</t>
+  </si>
+  <si>
+    <t>Ecole d'ambulanciers</t>
+  </si>
+  <si>
+    <t>273</t>
+  </si>
+  <si>
+    <t>Institut de formation en soins infirmiers (I.F.S.I.)</t>
+  </si>
+  <si>
+    <t>274</t>
+  </si>
+  <si>
+    <t>Ecole de sages_femmes</t>
+  </si>
+  <si>
+    <t>275</t>
+  </si>
+  <si>
+    <t>Ecole de masseurs-kinésithérapeutes</t>
+  </si>
+  <si>
+    <t>276</t>
+  </si>
+  <si>
+    <t>Ecole de laborantins d'analyses médicales</t>
+  </si>
+  <si>
+    <t>277</t>
+  </si>
+  <si>
+    <t>Ecole de péricultrices</t>
+  </si>
+  <si>
+    <t>278</t>
+  </si>
+  <si>
+    <t>Etablissement de formation polyvalent</t>
+  </si>
+  <si>
+    <t>279</t>
+  </si>
+  <si>
+    <t>Ecole de service social</t>
+  </si>
+  <si>
+    <t>280</t>
+  </si>
+  <si>
+    <t>Ecole d'éducateurs spécialisés</t>
+  </si>
+  <si>
+    <t>281</t>
+  </si>
+  <si>
+    <t>Centre de formation d'aides soignants</t>
+  </si>
+  <si>
+    <t>282</t>
+  </si>
+  <si>
+    <t>Ecole de pédicures-podologues</t>
+  </si>
+  <si>
+    <t>283</t>
+  </si>
+  <si>
+    <t>Ecole de manipulateurs d'électro-radiologie</t>
+  </si>
+  <si>
+    <t>284</t>
+  </si>
+  <si>
+    <t>Ecole de travailleuses familiales</t>
+  </si>
+  <si>
+    <t>285</t>
+  </si>
+  <si>
+    <t>Centres de Loisirs sans Hébergement</t>
+  </si>
+  <si>
+    <t>286</t>
+  </si>
+  <si>
+    <t>Club Equipe de Prévention</t>
+  </si>
+  <si>
+    <t>289</t>
+  </si>
+  <si>
+    <t>Centre de Soins Infirmiers</t>
+  </si>
+  <si>
+    <t>292</t>
+  </si>
+  <si>
+    <t>Centre Hospitalier Spécialisé lutte Maladies Mentales</t>
+  </si>
+  <si>
+    <t>294</t>
+  </si>
+  <si>
+    <t>Centre de Consultations Cancer</t>
+  </si>
+  <si>
+    <t>295</t>
+  </si>
+  <si>
+    <t>Service AEMO et AED</t>
+  </si>
+  <si>
+    <t>297</t>
+  </si>
+  <si>
+    <t>Dispensaire Polyvalent</t>
+  </si>
+  <si>
+    <t>300</t>
+  </si>
+  <si>
+    <t>Ecoles Formant aux Professions Sanitaires</t>
+  </si>
+  <si>
+    <t>303</t>
+  </si>
+  <si>
+    <t>Ecole de conseillers en économie sociale et familiale</t>
+  </si>
+  <si>
+    <t>304</t>
+  </si>
+  <si>
+    <t>Ecole d'ergothérapeutes</t>
+  </si>
+  <si>
+    <t>305</t>
+  </si>
+  <si>
+    <t>Ecole de psycho-motriciens</t>
+  </si>
+  <si>
+    <t>306</t>
+  </si>
+  <si>
+    <t>Ecole d'infirmiers anesthésistes</t>
+  </si>
+  <si>
+    <t>307</t>
+  </si>
+  <si>
+    <t>Ecole d'infirmiers de bloc opératoire</t>
+  </si>
+  <si>
+    <t>308</t>
+  </si>
+  <si>
+    <t>Centre de formation professionnelle de secteur psychiatrique</t>
+  </si>
+  <si>
+    <t>309</t>
+  </si>
+  <si>
+    <t>Ecole de cadres infirmiers</t>
+  </si>
+  <si>
+    <t>310</t>
+  </si>
+  <si>
+    <t>Ecole de cadres de secteur psychiatrique</t>
+  </si>
+  <si>
+    <t>311</t>
+  </si>
+  <si>
+    <t>Ecole de cadres de masseurs-kinésithérapeutes</t>
+  </si>
+  <si>
+    <t>312</t>
+  </si>
+  <si>
+    <t>Ecole de cadres de manipulateurs d'électro-radiologie</t>
+  </si>
+  <si>
+    <t>313</t>
+  </si>
+  <si>
+    <t>Ecole d'éducateurs de jeunes enfants</t>
+  </si>
+  <si>
+    <t>314</t>
+  </si>
+  <si>
+    <t>Ecole d'éducateurs techniques spécialisés</t>
+  </si>
+  <si>
+    <t>315</t>
+  </si>
+  <si>
+    <t>Ecole de moniteurs-éducateurs</t>
+  </si>
+  <si>
+    <t>316</t>
+  </si>
+  <si>
+    <t>Ecole d'aides médico-psychologiques</t>
+  </si>
+  <si>
+    <t>317</t>
+  </si>
+  <si>
+    <t>Ecole d'animateurs socio-éducatifs</t>
+  </si>
+  <si>
+    <t>319</t>
+  </si>
+  <si>
+    <t>Inst. régional de formation des travailleurs sociaux</t>
+  </si>
+  <si>
+    <t>320</t>
+  </si>
+  <si>
+    <t>S.A.M.U. et Centre 15</t>
+  </si>
+  <si>
+    <t>321</t>
+  </si>
+  <si>
+    <t>Unité Mobile Hospitalière</t>
+  </si>
+  <si>
+    <t>322</t>
+  </si>
+  <si>
+    <t>Centre Rég.Informatiq.Hospit.</t>
+  </si>
+  <si>
+    <t>324</t>
+  </si>
+  <si>
+    <t>Logement Foyer non Spécialisé</t>
+  </si>
+  <si>
+    <t>326</t>
+  </si>
+  <si>
+    <t>Ecole de cadres</t>
+  </si>
+  <si>
+    <t>327</t>
+  </si>
+  <si>
+    <t>328</t>
+  </si>
+  <si>
+    <t>Centre Consultation Soins Dentaire</t>
+  </si>
+  <si>
+    <t>329</t>
+  </si>
+  <si>
+    <t>Sectorisation Psychiatrique</t>
+  </si>
+  <si>
+    <t>330</t>
+  </si>
+  <si>
+    <t>Ecoles Formant aux Professions Sociales</t>
+  </si>
+  <si>
+    <t>340</t>
+  </si>
+  <si>
+    <t>Service mandataire judiciaire à la protection des majeurs</t>
+  </si>
+  <si>
+    <t>341</t>
+  </si>
+  <si>
+    <t>Service dédié mesures d'accompagnement social personnalisé</t>
+  </si>
+  <si>
+    <t>342</t>
+  </si>
+  <si>
+    <t>Service d'information et de soutien aux tuteurs familiaux</t>
+  </si>
+  <si>
+    <t>343</t>
+  </si>
+  <si>
+    <t>Equipe Préparation et Suite Reclassement (EPSR)</t>
+  </si>
+  <si>
+    <t>344</t>
+  </si>
+  <si>
+    <t>Service délégué aux prestations familiales</t>
+  </si>
+  <si>
+    <t>345</t>
+  </si>
+  <si>
+    <t>Service Tutelle Prestation Sociale</t>
+  </si>
+  <si>
+    <t>346</t>
+  </si>
+  <si>
+    <t>Service de Travailleuses Familiales</t>
+  </si>
+  <si>
+    <t>347</t>
+  </si>
+  <si>
+    <t>Centre d'Examens de Santé</t>
+  </si>
+  <si>
+    <t>349</t>
+  </si>
+  <si>
+    <t>Ecole de cadres de sages-femmes</t>
+  </si>
+  <si>
+    <t>350</t>
+  </si>
+  <si>
+    <t>Centre de formation d'auxiliaires de puériculture</t>
+  </si>
+  <si>
+    <t>352</t>
+  </si>
+  <si>
+    <t>Centre de Psychothérapie</t>
+  </si>
+  <si>
+    <t>353</t>
+  </si>
+  <si>
+    <t>Hôpital de Jour Spécialités Médicales</t>
+  </si>
+  <si>
+    <t>354</t>
+  </si>
+  <si>
+    <t>Service de Soins Infirmiers A Domicile (S.S.I.A.D)</t>
+  </si>
+  <si>
+    <t>355</t>
+  </si>
+  <si>
+    <t>Centre Hospitalier (C.H.)</t>
+  </si>
+  <si>
+    <t>357</t>
+  </si>
+  <si>
+    <t>Association Aide aux Insuffisants Respiratoires</t>
+  </si>
+  <si>
+    <t>359</t>
+  </si>
+  <si>
+    <t>Centre Circonscription Sanitaire et Sociale</t>
+  </si>
+  <si>
+    <t>361</t>
+  </si>
+  <si>
+    <t>Centre de Cure Médicale</t>
+  </si>
+  <si>
+    <t>362</t>
+  </si>
+  <si>
+    <t>Etablissement de Soins Longue Durée</t>
+  </si>
+  <si>
+    <t>363</t>
+  </si>
+  <si>
+    <t>Centre moyen et long séjour</t>
+  </si>
+  <si>
+    <t>365</t>
+  </si>
+  <si>
+    <t>Etablissement de Soins Pluridisciplinaire</t>
+  </si>
+  <si>
+    <t>366</t>
+  </si>
+  <si>
+    <t>Atelier Thérapeutique</t>
+  </si>
+  <si>
+    <t>367</t>
+  </si>
+  <si>
+    <t>Maison d'Enfants non Conventionnée ni Habilitée</t>
+  </si>
+  <si>
+    <t>368</t>
+  </si>
+  <si>
+    <t>Service de Repas à Domicile</t>
+  </si>
+  <si>
+    <t>369</t>
+  </si>
+  <si>
+    <t>Centre Adaptation Vie Active (C.A.V.A.)</t>
+  </si>
+  <si>
+    <t>370</t>
+  </si>
+  <si>
+    <t>Etablissement Expérimental pour personnes handicapées</t>
+  </si>
+  <si>
+    <t>371</t>
+  </si>
+  <si>
+    <t>Service Action Socio-Educative pour Familles en difficulté</t>
+  </si>
+  <si>
+    <t>373</t>
+  </si>
+  <si>
+    <t>Centre de formation supérieure des travailleurs sociaux</t>
+  </si>
+  <si>
+    <t>374</t>
+  </si>
+  <si>
+    <t>Ecole Nationale Santé Publique (E.N.S.P.)</t>
+  </si>
+  <si>
+    <t>375</t>
+  </si>
+  <si>
+    <t>Classe d'Adaptation</t>
+  </si>
+  <si>
+    <t>376</t>
+  </si>
+  <si>
+    <t>Classe Spéciale Ecole Primaire</t>
+  </si>
+  <si>
+    <t>377</t>
+  </si>
+  <si>
+    <t>Etablissement Expérimental pour Enfance Handicapée</t>
+  </si>
+  <si>
+    <t>378</t>
+  </si>
+  <si>
+    <t>Etablissement Expérimental Enfance Protégée</t>
+  </si>
+  <si>
+    <t>379</t>
+  </si>
+  <si>
+    <t>Etablissement Expérimental pour Adultes Handicapés</t>
+  </si>
+  <si>
+    <t>380</t>
+  </si>
+  <si>
+    <t>Etablissement Expérimental Autres Adultes</t>
+  </si>
+  <si>
+    <t>381</t>
+  </si>
+  <si>
+    <t>Etablissement Expérimental pour Personnes Agées</t>
+  </si>
+  <si>
+    <t>382</t>
+  </si>
+  <si>
+    <t>Foyer de Vie pour Adultes Handicapés</t>
+  </si>
+  <si>
+    <t>386</t>
+  </si>
+  <si>
+    <t>Ecole Secondaire Spéciale</t>
+  </si>
+  <si>
+    <t>390</t>
+  </si>
+  <si>
+    <t>Etablissement d'Accueil Temporaire d'Enfants Handicapés</t>
+  </si>
+  <si>
+    <t>393</t>
+  </si>
+  <si>
+    <t>Autre résidence But lucratif pr personnes Âgées</t>
+  </si>
+  <si>
+    <t>394</t>
+  </si>
+  <si>
+    <t>Etablissement d'Accueil Temporaire pour Personnes Agées</t>
+  </si>
+  <si>
+    <t>395</t>
+  </si>
+  <si>
+    <t>Etablissement d'Accueil Temporaire pour Adultes Handicapés</t>
+  </si>
+  <si>
+    <t>396</t>
+  </si>
+  <si>
+    <t>Foyer Hébergement Enfants et Adolescents Handicapés</t>
+  </si>
+  <si>
+    <t>397</t>
+  </si>
+  <si>
+    <t>Service Auxiliaire de Vie pour Handicapés</t>
+  </si>
+  <si>
+    <t>398</t>
+  </si>
+  <si>
+    <t>Crèche Parentale</t>
+  </si>
+  <si>
+    <t>399</t>
+  </si>
+  <si>
+    <t>Halte Garderie Parentale</t>
+  </si>
+  <si>
+    <t>400</t>
+  </si>
+  <si>
+    <t>Centre de Services pour Associations</t>
+  </si>
+  <si>
+    <t>401</t>
+  </si>
+  <si>
+    <t>D.R.A.S.S.</t>
+  </si>
+  <si>
+    <t>402</t>
+  </si>
+  <si>
+    <t>Jardin d'Enfants Spécialisé</t>
+  </si>
+  <si>
+    <t>403</t>
+  </si>
+  <si>
+    <t>Service Social Spécialisé ou Polyvalent de Catégorie</t>
+  </si>
+  <si>
+    <t>404</t>
+  </si>
+  <si>
+    <t>Etablissement Acc.Collect.Parental Régulier &amp; Occasionnel</t>
+  </si>
+  <si>
+    <t>405</t>
+  </si>
+  <si>
+    <t>Service Social Polyvalent de Secteur</t>
+  </si>
+  <si>
+    <t>411</t>
+  </si>
+  <si>
+    <t>Intermédiaire de Placement Social</t>
+  </si>
+  <si>
+    <t>412</t>
+  </si>
+  <si>
+    <t>Appartement Thérapeutique</t>
+  </si>
+  <si>
+    <t>413</t>
+  </si>
+  <si>
+    <t>C.E.C.O.S</t>
+  </si>
+  <si>
+    <t>414</t>
+  </si>
+  <si>
+    <t>Centre Anti Poison</t>
+  </si>
+  <si>
+    <t>415</t>
+  </si>
+  <si>
+    <t>Service Médico-Psychologique Régional (S.M.P.R.)</t>
+  </si>
+  <si>
+    <t>418</t>
+  </si>
+  <si>
+    <t>Service d'Enquêtes Sociales (S.E.S.)</t>
+  </si>
+  <si>
+    <t>419</t>
+  </si>
+  <si>
+    <t>Centre d'Accueil Toxicomanes</t>
+  </si>
+  <si>
+    <t>420</t>
+  </si>
+  <si>
+    <t>Entreprise d'Insertion</t>
+  </si>
+  <si>
+    <t>421</t>
+  </si>
+  <si>
+    <t>Centre d'enseignement aux secours d'urgence</t>
+  </si>
+  <si>
+    <t>422</t>
+  </si>
+  <si>
+    <t>Traitements Spécialisés à Domicile</t>
+  </si>
+  <si>
+    <t>423</t>
+  </si>
+  <si>
+    <t>Ecole des cadres de laborantins d'analyses médicales</t>
+  </si>
+  <si>
+    <t>425</t>
+  </si>
+  <si>
+    <t>Centre d'Accueil Thérapeutique à temps partiel (C.A.T.T.P.)</t>
+  </si>
+  <si>
     <t>426</t>
   </si>
   <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>Uri</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>niveau</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/concept-properties#niveau</t>
-  </si>
-  <si>
-    <t>Permet d'indiquer le niveau hiérarchique du code</t>
-  </si>
-  <si>
-    <t>integer</t>
-  </si>
-  <si>
-    <t>parent</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/concept-properties#parent</t>
-  </si>
-  <si>
-    <t>An immediate parent of the concept in the hierarchy</t>
-  </si>
-  <si>
-    <t>code</t>
-  </si>
-  <si>
-    <t>domaine</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/concept-properties#domaine</t>
-  </si>
-  <si>
-    <t>Domaine de la categorie d etablissement</t>
-  </si>
-  <si>
-    <t>Coding</t>
-  </si>
-  <si>
-    <t>dateValid</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateValid</t>
-  </si>
-  <si>
-    <t>date de validité d'un code concept</t>
-  </si>
-  <si>
-    <t>dateTime</t>
-  </si>
-  <si>
-    <t>dateMaj</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateMaj</t>
-  </si>
-  <si>
-    <t>Date de mise à jour d'un code concept</t>
-  </si>
-  <si>
-    <t>dateFin</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateFin</t>
-  </si>
-  <si>
-    <t>Date de fin d'exploitation d'un code concept</t>
-  </si>
-  <si>
-    <t>status</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/concept-properties#status</t>
-  </si>
-  <si>
-    <t>A property that indicates the status of the concept.</t>
-  </si>
-  <si>
-    <t>deprecationDate</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/concept-properties#deprecationDate</t>
-  </si>
-  <si>
-    <t>Date Concept was deprecated</t>
-  </si>
-  <si>
-    <t>retirementDate</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/concept-properties#retirementDate</t>
-  </si>
-  <si>
-    <t>Date Concept was retired</t>
-  </si>
-  <si>
-    <t>specialisationRor</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/concept-properties#specialisationRor</t>
-  </si>
-  <si>
-    <t>Propriété permettant de spécifier les codes exclusifs appartenant au ROR</t>
-  </si>
-  <si>
-    <t>boolean</t>
-  </si>
-  <si>
-    <t>ror</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/concept-properties#ror</t>
-  </si>
-  <si>
-    <t>Permet de définir les codes concepts uilisés par le ROR</t>
-  </si>
-  <si>
-    <t>cisis</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/concept-properties#cisis</t>
-  </si>
-  <si>
-    <t>Permet de définir les codes concepts uilisés par le CISIS</t>
-  </si>
-  <si>
-    <t>rass</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/concept-properties#rass</t>
-  </si>
-  <si>
-    <t>Permet de définir les codes concepts uilisés par le RASS</t>
-  </si>
-  <si>
-    <t>Level</t>
-  </si>
-  <si>
-    <t>Display</t>
-  </si>
-  <si>
-    <t>Definition</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>0100</t>
-  </si>
-  <si>
-    <t>Etablissements d'administration</t>
-  </si>
-  <si>
-    <t>1000</t>
-  </si>
-  <si>
-    <t>Etablissements Relevant de la Loi Hospitalière</t>
-  </si>
-  <si>
-    <t>2000</t>
-  </si>
-  <si>
-    <t>Autres Etablissements de Soins et Prévention</t>
-  </si>
-  <si>
-    <t>3000</t>
-  </si>
-  <si>
-    <t>Autres Etablissements à Caractère Sanitaire</t>
-  </si>
-  <si>
-    <t>4000</t>
-  </si>
-  <si>
-    <t>Etab.Serv.Soc.d'Accueil Hébergement Assistance Réadaptation</t>
-  </si>
-  <si>
-    <t>5000</t>
-  </si>
-  <si>
-    <t>Etablissements et Services Sociaux d'Aide à la Famille</t>
-  </si>
-  <si>
-    <t>6000</t>
-  </si>
-  <si>
-    <t>Etab.de Formation des Personnels Sanitaires et Sociaux</t>
-  </si>
-  <si>
-    <t>0110</t>
-  </si>
-  <si>
-    <t>Etablissements d'Administration</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>1100</t>
-  </si>
-  <si>
-    <t>Etablissements Hospitaliers</t>
-  </si>
-  <si>
-    <t>1200</t>
-  </si>
-  <si>
-    <t>Autres Etablissements Relevant de la Loi Hospitalière</t>
-  </si>
-  <si>
-    <t>2100</t>
-  </si>
-  <si>
-    <t>Cabinets Libéraux</t>
-  </si>
-  <si>
-    <t>2200</t>
-  </si>
-  <si>
-    <t>3100</t>
-  </si>
-  <si>
-    <t>Laboratoires de Biologie Médicale</t>
-  </si>
-  <si>
-    <t>3200</t>
-  </si>
-  <si>
-    <t>Commerce de Biens à Usage Médicaux</t>
-  </si>
-  <si>
-    <t>3400</t>
-  </si>
-  <si>
-    <t>4100</t>
-  </si>
-  <si>
-    <t>Etab.et Serv.pour l'Enfance et la Jeunesse Handicapée</t>
-  </si>
-  <si>
-    <t>4200</t>
-  </si>
-  <si>
-    <t>Etablissements ou Classes d'Enseignement Spécial</t>
-  </si>
-  <si>
-    <t>4300</t>
-  </si>
-  <si>
-    <t>Etablissements et Services pour Adultes Handicapés</t>
-  </si>
-  <si>
-    <t>4400</t>
-  </si>
-  <si>
-    <t>Etablissements et Services pour Personnes Agées</t>
-  </si>
-  <si>
-    <t>4500</t>
-  </si>
-  <si>
-    <t>Etab.et Serv.Sociaux Concourant à la Protection de l'Enfance</t>
-  </si>
-  <si>
-    <t>4600</t>
-  </si>
-  <si>
-    <t>Autres Etab. Accueil, Hébergement, Réadaptation et Services</t>
-  </si>
-  <si>
-    <t>5100</t>
-  </si>
-  <si>
-    <t>6100</t>
-  </si>
-  <si>
-    <t>Etablissements de Formation des Personnels Sanitaires</t>
-  </si>
-  <si>
-    <t>6200</t>
-  </si>
-  <si>
-    <t>Etablissements de Formation des Personnels Sociaux</t>
-  </si>
-  <si>
-    <t>6300</t>
-  </si>
-  <si>
-    <t>Etablissements de Formation Polyvalente</t>
-  </si>
-  <si>
-    <t>0101</t>
-  </si>
-  <si>
-    <t>1101</t>
-  </si>
-  <si>
-    <t>Centres Hospitaliers Régionaux</t>
-  </si>
-  <si>
-    <t>1102</t>
-  </si>
-  <si>
-    <t>Centres Hospitaliers</t>
-  </si>
-  <si>
-    <t>1103</t>
-  </si>
-  <si>
-    <t>Centres Hospitaliers Spécialisés Lutte Maladies Mentales</t>
-  </si>
-  <si>
-    <t>1104</t>
-  </si>
-  <si>
-    <t>Centres de Lutte contre le Cancer</t>
-  </si>
-  <si>
-    <t>1106</t>
-  </si>
-  <si>
-    <t>Hôpitaux Locaux</t>
-  </si>
-  <si>
-    <t>1107</t>
-  </si>
-  <si>
-    <t>Etablissements de santé privé autorisés en SSR</t>
-  </si>
-  <si>
-    <t>1108</t>
-  </si>
-  <si>
-    <t>Centre de Moyen et de Long Séjour</t>
-  </si>
-  <si>
-    <t>1109</t>
-  </si>
-  <si>
-    <t>Etablissements de Soins de Longue Durée</t>
-  </si>
-  <si>
-    <t>1110</t>
-  </si>
-  <si>
-    <t>Etablissements de Soins de Courte Durée</t>
-  </si>
-  <si>
-    <t>1111</t>
-  </si>
-  <si>
-    <t>Autres Etablissements de Lutte contre les Maladies Mentales</t>
-  </si>
-  <si>
-    <t>1112</t>
-  </si>
-  <si>
-    <t>Etablissements d'Enfants à Caractère Sanitaire</t>
-  </si>
-  <si>
-    <t>1113</t>
-  </si>
-  <si>
-    <t>Etablissements de Lutte contre l'Alcoolisme</t>
-  </si>
-  <si>
-    <t>1201</t>
-  </si>
-  <si>
-    <t>Traitements et Soins à Domicile</t>
-  </si>
-  <si>
-    <t>1202</t>
-  </si>
-  <si>
-    <t>Santé Mentale</t>
-  </si>
-  <si>
-    <t>1203</t>
-  </si>
-  <si>
-    <t>Dialyse ambulatoire</t>
-  </si>
-  <si>
-    <t>1204</t>
-  </si>
-  <si>
-    <t>Urgence et Réanimation</t>
-  </si>
-  <si>
-    <t>1205</t>
-  </si>
-  <si>
-    <t>2101</t>
-  </si>
-  <si>
-    <t>Cabinets Libéraux de Médecins</t>
-  </si>
-  <si>
-    <t>2102</t>
-  </si>
-  <si>
-    <t>Cabinet de Groupe</t>
-  </si>
-  <si>
-    <t>2103</t>
-  </si>
-  <si>
-    <t>Autres structures d'exercice libéral</t>
-  </si>
-  <si>
-    <t>2105</t>
-  </si>
-  <si>
-    <t>Cabinet d'Auxiliaires Médicaux</t>
-  </si>
-  <si>
-    <t>2201</t>
-  </si>
-  <si>
-    <t>Dispensaires ou Centres de Soins</t>
-  </si>
-  <si>
-    <t>2202</t>
-  </si>
-  <si>
-    <t>Etablissements de PMI et de Planification Familiale</t>
-  </si>
-  <si>
-    <t>2203</t>
-  </si>
-  <si>
-    <t>Etablissements de Soins Dentaires</t>
-  </si>
-  <si>
-    <t>2204</t>
-  </si>
-  <si>
-    <t>Etablissements ne relevant pas de la Loi Hospitalière</t>
-  </si>
-  <si>
-    <t>2205</t>
-  </si>
-  <si>
-    <t>Etab.de soins relevant du service de santé des armées</t>
-  </si>
-  <si>
-    <t>2206</t>
-  </si>
-  <si>
-    <t>Centres de Santé</t>
-  </si>
-  <si>
-    <t>3101</t>
-  </si>
-  <si>
-    <t>3201</t>
-  </si>
-  <si>
-    <t>3202</t>
-  </si>
-  <si>
-    <t>Commerce de Biens Médicaux</t>
-  </si>
-  <si>
-    <t>3401</t>
-  </si>
-  <si>
-    <t>Transfusion Sanguine</t>
-  </si>
-  <si>
-    <t>3402</t>
-  </si>
-  <si>
-    <t>Conservation et Stockage d'autres Produits Humains</t>
-  </si>
-  <si>
-    <t>3403</t>
-  </si>
-  <si>
-    <t>Centre Antipoison</t>
-  </si>
-  <si>
-    <t>3404</t>
-  </si>
-  <si>
-    <t>Service d'Ambulances</t>
-  </si>
-  <si>
-    <t>3405</t>
-  </si>
-  <si>
-    <t>Installations autonomes de chirurgie esthétique</t>
-  </si>
-  <si>
-    <t>3406</t>
-  </si>
-  <si>
-    <t>Maisons de Naissance</t>
-  </si>
-  <si>
-    <t>3407</t>
-  </si>
-  <si>
-    <t>Etablissements Expérimentaux en Santé</t>
-  </si>
-  <si>
-    <t>3408</t>
-  </si>
-  <si>
-    <t>Centre de ressources transverse</t>
-  </si>
-  <si>
-    <t>3409</t>
-  </si>
-  <si>
-    <t>Services de Prévention et de Santé au Travail (SPST)</t>
-  </si>
-  <si>
-    <t>3410</t>
-  </si>
-  <si>
-    <t>Services d'incendie et de secours</t>
-  </si>
-  <si>
-    <t>4101</t>
-  </si>
-  <si>
-    <t>Etab.Educ.Spéciale pour Déficients Mentaux et Handicapés</t>
-  </si>
-  <si>
-    <t>4102</t>
-  </si>
-  <si>
-    <t>Etab.Educ Spéciale pour Enfants Trouble Conduite et Comport</t>
-  </si>
-  <si>
-    <t>4103</t>
-  </si>
-  <si>
-    <t>Etablissements d'Education Spéciale pour Handicapés Moteurs</t>
-  </si>
-  <si>
-    <t>4104</t>
-  </si>
-  <si>
-    <t>Etab.Education Spéciale pour Déficients Sensoriels</t>
-  </si>
-  <si>
-    <t>4105</t>
-  </si>
-  <si>
-    <t>Etablissements et Services Hébergement Enfants Handicapés</t>
-  </si>
-  <si>
-    <t>4106</t>
-  </si>
-  <si>
-    <t>Services à Domicile ou Ambulatoires pour Handicapés</t>
-  </si>
-  <si>
-    <t>4107</t>
-  </si>
-  <si>
-    <t>Etab. Expérimentaux en Faveur de l'Enfance Handicapée</t>
-  </si>
-  <si>
-    <t>4201</t>
-  </si>
-  <si>
-    <t>Etablissements ou Classes de Pré-Élémentaire et Élémentaire</t>
-  </si>
-  <si>
-    <t>4202</t>
-  </si>
-  <si>
-    <t>Etablissements d'Enseignement Secondaire</t>
-  </si>
-  <si>
-    <t>4301</t>
-  </si>
-  <si>
-    <t>Etab. et Services d'Hébergement pour Adultes Handicapés</t>
-  </si>
-  <si>
-    <t>4302</t>
-  </si>
-  <si>
-    <t>Etab.et Services de Travail Protégé pour Adultes Handicapés</t>
-  </si>
-  <si>
-    <t>4303</t>
-  </si>
-  <si>
-    <t>Etab.et Services de Réinsertion Prof pour Adultes Handicapés</t>
-  </si>
-  <si>
-    <t>4304</t>
-  </si>
-  <si>
-    <t>Etab.Expérimentaux en Faveur des Adultes Handicapés</t>
-  </si>
-  <si>
-    <t>4305</t>
-  </si>
-  <si>
-    <t>Services de Maintien à Domicile pour Handicapés</t>
-  </si>
-  <si>
-    <t>4401</t>
-  </si>
-  <si>
-    <t>Etablissements d'Hébergement pour Personnes Âgées</t>
-  </si>
-  <si>
-    <t>4402</t>
-  </si>
-  <si>
-    <t>Services de Maintien à Domicile pour Personnes Âgées</t>
-  </si>
-  <si>
-    <t>4403</t>
-  </si>
-  <si>
-    <t>Services Sociaux en Faveur des Personnes Âgées</t>
-  </si>
-  <si>
-    <t>4404</t>
-  </si>
-  <si>
-    <t>Etablissements Expérimentaux en Faveur des Personnes Âgées</t>
-  </si>
-  <si>
-    <t>4501</t>
-  </si>
-  <si>
-    <t>Etablissements de l'Aide Sociale à l'Enfance</t>
-  </si>
-  <si>
-    <t>4502</t>
-  </si>
-  <si>
-    <t>Etab.et Services du Ministère de la Justice pour Mineurs</t>
-  </si>
-  <si>
-    <t>4504</t>
-  </si>
-  <si>
-    <t>Services Concourant à la Protection de l'Enfance</t>
-  </si>
-  <si>
-    <t>4505</t>
-  </si>
-  <si>
-    <t>Etab. Expérimentaux en Faveur de l'Enfance Protégée</t>
-  </si>
-  <si>
-    <t>4601</t>
-  </si>
-  <si>
-    <t>Etablissements pour Adultes et Familles en Difficulté</t>
-  </si>
-  <si>
-    <t>4602</t>
-  </si>
-  <si>
-    <t>Autres Etablissements Sociaux d'Hébergement et d'Accueil</t>
-  </si>
-  <si>
-    <t>4603</t>
-  </si>
-  <si>
-    <t>Etablissements Expérimentaux en Faveur des Adultes</t>
-  </si>
-  <si>
-    <t>4604</t>
-  </si>
-  <si>
-    <t>Autres Etablissements médico-sociaux</t>
-  </si>
-  <si>
-    <t>4605</t>
-  </si>
-  <si>
-    <t>Etablissements et services multi-clientèles</t>
-  </si>
-  <si>
-    <t>4606</t>
-  </si>
-  <si>
-    <t>Centres de ressources</t>
-  </si>
-  <si>
-    <t>4607</t>
-  </si>
-  <si>
-    <t>Logements en Structure Collective</t>
-  </si>
-  <si>
-    <t>4608</t>
-  </si>
-  <si>
-    <t>Protection des majeurs</t>
-  </si>
-  <si>
-    <t>4609</t>
-  </si>
-  <si>
-    <t>Centres prestataires de services pr personnes cérébro-lésées</t>
-  </si>
-  <si>
-    <t>5101</t>
-  </si>
-  <si>
-    <t>Etablissements Garde d'Enfants d'Age pré-Scolaire</t>
-  </si>
-  <si>
-    <t>5102</t>
-  </si>
-  <si>
-    <t>Etablissements d'Hébergement pour Enfants d'Age Scolaire</t>
-  </si>
-  <si>
-    <t>5103</t>
-  </si>
-  <si>
-    <t>Etablissements Sociaux pour Loisirs et Vacances</t>
-  </si>
-  <si>
-    <t>5104</t>
-  </si>
-  <si>
-    <t>Etablissements ou Services Divers d'Aide à la Famille</t>
-  </si>
-  <si>
-    <t>6101</t>
-  </si>
-  <si>
-    <t>6102</t>
-  </si>
-  <si>
-    <t>Etablissements de Formation des Personnels Techniques</t>
-  </si>
-  <si>
-    <t>6103</t>
-  </si>
-  <si>
-    <t>Autres Etablissements de Formation des Personnels Techniques</t>
-  </si>
-  <si>
-    <t>6201</t>
-  </si>
-  <si>
-    <t>6301</t>
-  </si>
-  <si>
-    <t>001</t>
-  </si>
-  <si>
-    <t>Autres lits de m.R.</t>
-  </si>
-  <si>
-    <t>002</t>
-  </si>
-  <si>
-    <t>Autres places de l-f.</t>
-  </si>
-  <si>
-    <t>003</t>
-  </si>
-  <si>
-    <t>Autres lits de l-s</t>
-  </si>
-  <si>
-    <t>101</t>
-  </si>
-  <si>
-    <t>Centre Hospitalier Régional (C.H.R.)</t>
-  </si>
-  <si>
-    <t>106</t>
-  </si>
-  <si>
-    <t>Centre hospitalier, ex Hôpital local</t>
-  </si>
-  <si>
-    <t>108</t>
-  </si>
-  <si>
-    <t>Etablissement de Convalescence et de Repos</t>
-  </si>
-  <si>
-    <t>109</t>
-  </si>
-  <si>
-    <t>Etablissement de santé privé autorisé en SSR</t>
-  </si>
-  <si>
-    <t>112</t>
-  </si>
-  <si>
-    <t>Centre de Convalescence Cure ou Réadaptation</t>
-  </si>
-  <si>
-    <t>114</t>
-  </si>
-  <si>
-    <t>Hôpital des armées</t>
-  </si>
-  <si>
-    <t>115</t>
-  </si>
-  <si>
-    <t>Etablissement de Soins du Service de Santé des Armées</t>
-  </si>
-  <si>
-    <t>119</t>
-  </si>
-  <si>
-    <t>Maison de Régime</t>
-  </si>
-  <si>
-    <t>122</t>
-  </si>
-  <si>
-    <t>Etablissement Soins Obstétriques Chirurgico-Gynécologiques</t>
-  </si>
-  <si>
-    <t>124</t>
-  </si>
-  <si>
-    <t>Centre de Santé</t>
-  </si>
-  <si>
-    <t>125</t>
-  </si>
-  <si>
-    <t>Centre de Santé Dentaire</t>
-  </si>
-  <si>
-    <t>126</t>
-  </si>
-  <si>
-    <t>Etablissement Thermal</t>
-  </si>
-  <si>
-    <t>127</t>
-  </si>
-  <si>
-    <t>Hospitalisation à Domicile</t>
-  </si>
-  <si>
-    <t>128</t>
-  </si>
-  <si>
-    <t>Etablissement de Soins Chirurgicaux</t>
-  </si>
-  <si>
-    <t>129</t>
-  </si>
-  <si>
-    <t>Etablissement de Soins Médicaux</t>
-  </si>
-  <si>
-    <t>130</t>
-  </si>
-  <si>
-    <t>Centre de Soins Médicaux</t>
-  </si>
-  <si>
-    <t>131</t>
-  </si>
-  <si>
-    <t>Centre de Lutte Contre Cancer</t>
-  </si>
-  <si>
-    <t>132</t>
-  </si>
-  <si>
-    <t>Etablissement de Transfusion Sanguine</t>
-  </si>
-  <si>
-    <t>135</t>
-  </si>
-  <si>
-    <t>Etablissement Réadaptation Fonctionnelle</t>
-  </si>
-  <si>
-    <t>136</t>
-  </si>
-  <si>
-    <t>Banque de Sperme</t>
-  </si>
-  <si>
-    <t>137</t>
-  </si>
-  <si>
-    <t>Banque d'Organes</t>
-  </si>
-  <si>
-    <t>138</t>
-  </si>
-  <si>
-    <t>Centre de Dialyse Périodique</t>
-  </si>
-  <si>
-    <t>139</t>
-  </si>
-  <si>
-    <t>Centre de Dialyse et d'entraînement à la Dialyse</t>
-  </si>
-  <si>
-    <t>140</t>
-  </si>
-  <si>
-    <t>Centre d'Entraînement à la Dialyse</t>
-  </si>
-  <si>
-    <t>141</t>
-  </si>
-  <si>
-    <t>Centre de dialyse</t>
-  </si>
-  <si>
-    <t>142</t>
-  </si>
-  <si>
-    <t>Dispensaire Antituberculeux</t>
-  </si>
-  <si>
-    <t>143</t>
-  </si>
-  <si>
-    <t>Centre de Vaccination BCG</t>
-  </si>
-  <si>
-    <t>144</t>
-  </si>
-  <si>
-    <t>Etablissement de Lutte Contre la Tuberculose</t>
-  </si>
-  <si>
-    <t>146</t>
-  </si>
-  <si>
-    <t>Structure d'Alternative à la dialyse en centre</t>
-  </si>
-  <si>
-    <t>156</t>
-  </si>
-  <si>
-    <t>Centre Médico-Psychologique (C.M.P.)</t>
-  </si>
-  <si>
-    <t>157</t>
-  </si>
-  <si>
-    <t>Centre de Postcure</t>
-  </si>
-  <si>
-    <t>159</t>
-  </si>
-  <si>
-    <t>Centre Parental</t>
-  </si>
-  <si>
-    <t>160</t>
-  </si>
-  <si>
-    <t>Centre de Soins Spécifiques pour Toxicomanes (C.S.S.T.)</t>
-  </si>
-  <si>
-    <t>161</t>
-  </si>
-  <si>
-    <t>Maison de Santé pour Maladies Mentales</t>
-  </si>
-  <si>
-    <t>162</t>
-  </si>
-  <si>
-    <t>Centre de Cure Ambulatoire en Alcoologie (C.C.A.A.)</t>
-  </si>
-  <si>
-    <t>163</t>
-  </si>
-  <si>
-    <t>Maison d'Enfants à Caractère Sanitaire Temporaire</t>
-  </si>
-  <si>
-    <t>164</t>
-  </si>
-  <si>
-    <t>Etablissements Expérimentaux Accueil de la Petite Enfance</t>
-  </si>
-  <si>
-    <t>165</t>
-  </si>
-  <si>
-    <t>Appartement de Coordination Thérapeutique (A.C.T.)</t>
-  </si>
-  <si>
-    <t>166</t>
-  </si>
-  <si>
-    <t>Etablissement d'Accueil Mère-Enfant</t>
-  </si>
-  <si>
-    <t>167</t>
-  </si>
-  <si>
-    <t>Crèche Collective</t>
-  </si>
-  <si>
-    <t>168</t>
-  </si>
-  <si>
-    <t>Service Accueil Familial pour la Petite Enfance</t>
-  </si>
-  <si>
-    <t>169</t>
-  </si>
-  <si>
-    <t>Crèche Multi Accueil Collectif et Familial</t>
-  </si>
-  <si>
-    <t>170</t>
-  </si>
-  <si>
-    <t>Halte Garderie</t>
-  </si>
-  <si>
-    <t>171</t>
-  </si>
-  <si>
-    <t>Garderie et Jardin d'Enfants</t>
-  </si>
-  <si>
-    <t>172</t>
-  </si>
-  <si>
-    <t>Pouponnière à Caractère Social</t>
-  </si>
-  <si>
-    <t>173</t>
-  </si>
-  <si>
-    <t>Pouponnière à Caractère Sanitaire</t>
-  </si>
-  <si>
-    <t>174</t>
-  </si>
-  <si>
-    <t>Etablissement d'Accueil Collectif Régulier et Occasionnel</t>
-  </si>
-  <si>
-    <t>175</t>
-  </si>
-  <si>
-    <t>Foyer de l'Enfance</t>
-  </si>
-  <si>
-    <t>176</t>
-  </si>
-  <si>
-    <t>Village d'Enfants</t>
-  </si>
-  <si>
-    <t>177</t>
-  </si>
-  <si>
-    <t>Maison d'Enfants à Caractère Social</t>
-  </si>
-  <si>
-    <t>178</t>
-  </si>
-  <si>
-    <t>Ctre.Accueil- Accomp.Réduc.Risq.Usag. Drogues (C.A.A.R.U.D.)</t>
-  </si>
-  <si>
-    <t>179</t>
-  </si>
-  <si>
-    <t>Maison d'Enfants à Caractère Sanitaire Permanente</t>
-  </si>
-  <si>
-    <t>180</t>
-  </si>
-  <si>
-    <t>Lits Halte Soins Santé (L.H.S.S.)</t>
-  </si>
-  <si>
-    <t>181</t>
-  </si>
-  <si>
-    <t>Maison Familiale de Vacances</t>
-  </si>
-  <si>
-    <t>182</t>
-  </si>
-  <si>
-    <t>Service d'Éducation Spéciale et de Soins à Domicile</t>
-  </si>
-  <si>
-    <t>183</t>
-  </si>
-  <si>
-    <t>Institut Médico-Educatif (I.M.E.)</t>
-  </si>
-  <si>
-    <t>184</t>
-  </si>
-  <si>
-    <t>Institut Médico-Pédagogique (I.M.P.)</t>
-  </si>
-  <si>
-    <t>185</t>
-  </si>
-  <si>
-    <t>Institut Médico-Professionnel (I.M.Pro.)</t>
-  </si>
-  <si>
-    <t>186</t>
-  </si>
-  <si>
-    <t>Institut Thérapeutique Éducatif et Pédagogique (I.T.E.P.)</t>
-  </si>
-  <si>
-    <t>188</t>
-  </si>
-  <si>
-    <t>Etablissement pour Enfants ou Adolescents Polyhandicapés</t>
-  </si>
-  <si>
-    <t>189</t>
-  </si>
-  <si>
-    <t>Centre Médico-Psycho-Pédagogique (C.M.P.P.)</t>
-  </si>
-  <si>
-    <t>190</t>
-  </si>
-  <si>
-    <t>Centre Action Médico-Sociale Précoce (C.A.M.S.P.)</t>
-  </si>
-  <si>
-    <t>191</t>
-  </si>
-  <si>
-    <t>Etablissement pour Déficients Moteurs Cérébraux</t>
-  </si>
-  <si>
-    <t>192</t>
-  </si>
-  <si>
-    <t>Institut d'éducation motrice</t>
-  </si>
-  <si>
-    <t>193</t>
-  </si>
-  <si>
-    <t>Etablissement pour Déficients Moteurs et Moteurs Cérébraux</t>
-  </si>
-  <si>
-    <t>194</t>
-  </si>
-  <si>
-    <t>Institut pour Déficients Visuels</t>
-  </si>
-  <si>
-    <t>195</t>
-  </si>
-  <si>
-    <t>Institut pour Déficients Auditifs</t>
-  </si>
-  <si>
-    <t>196</t>
-  </si>
-  <si>
-    <t>Institut d'Education Sensorielle Sourd-Aveugle</t>
-  </si>
-  <si>
-    <t>197</t>
-  </si>
-  <si>
-    <t>Centre soins accompagnement prévention addictologie (CSAPA)</t>
-  </si>
-  <si>
-    <t>198</t>
-  </si>
-  <si>
-    <t>Établissement et Service de Préorientation</t>
-  </si>
-  <si>
-    <t>199</t>
-  </si>
-  <si>
-    <t>Hospice</t>
-  </si>
-  <si>
-    <t>200</t>
-  </si>
-  <si>
-    <t>Maison de Retraite</t>
-  </si>
-  <si>
-    <t>202</t>
-  </si>
-  <si>
-    <t>Résidences autonomie</t>
-  </si>
-  <si>
-    <t>205</t>
-  </si>
-  <si>
-    <t>Foyer Club Restaurant</t>
-  </si>
-  <si>
-    <t>207</t>
-  </si>
-  <si>
-    <t>Centre de Jour pour Personnes Agées</t>
-  </si>
-  <si>
-    <t>208</t>
-  </si>
-  <si>
-    <t>Service d'Aide Ménagère à Domicile</t>
-  </si>
-  <si>
-    <t>209</t>
-  </si>
-  <si>
-    <t>Service autonomie aide et soins (SAAS)</t>
-  </si>
-  <si>
-    <t>212</t>
-  </si>
-  <si>
-    <t>Alarme Médico-Sociale</t>
-  </si>
-  <si>
-    <t>213</t>
-  </si>
-  <si>
-    <t>Lits d'Accueil Médicalisés (L.A.M.)</t>
-  </si>
-  <si>
-    <t>214</t>
-  </si>
-  <si>
-    <t>Centre Hébergement &amp; Réinsertion Sociale (C.H.R.S.)</t>
-  </si>
-  <si>
-    <t>215</t>
-  </si>
-  <si>
-    <t>Maison Relai</t>
-  </si>
-  <si>
-    <t>216</t>
-  </si>
-  <si>
-    <t>Résidence Hôtelière à Vocation Sociale (R.H.V.S)</t>
-  </si>
-  <si>
-    <t>217</t>
-  </si>
-  <si>
-    <t>Cité de Transit</t>
-  </si>
-  <si>
-    <t>218</t>
-  </si>
-  <si>
-    <t>Aire Station Nomades</t>
-  </si>
-  <si>
-    <t>219</t>
-  </si>
-  <si>
-    <t>Autre Centre d'Accueil</t>
-  </si>
-  <si>
-    <t>220</t>
-  </si>
-  <si>
-    <t>Centre Social</t>
-  </si>
-  <si>
-    <t>221</t>
-  </si>
-  <si>
-    <t>Bureau d'Aide Psychologique Universitaire (B.A.P.U.)</t>
-  </si>
-  <si>
-    <t>223</t>
-  </si>
-  <si>
-    <t>Protection Maternelle et Infantile (P.M.I.)</t>
-  </si>
-  <si>
-    <t>224</t>
-  </si>
-  <si>
-    <t>Etablissement de Consultation Pré et Post-natale</t>
-  </si>
-  <si>
-    <t>225</t>
-  </si>
-  <si>
-    <t>Consultations de Nourrissons</t>
-  </si>
-  <si>
-    <t>228</t>
-  </si>
-  <si>
-    <t>Centre de Santé Sexuelle</t>
-  </si>
-  <si>
-    <t>229</t>
-  </si>
-  <si>
-    <t>Consultation Problèmes naissance</t>
-  </si>
-  <si>
-    <t>230</t>
-  </si>
-  <si>
-    <t>Etablissement Consultation Protection Infantile</t>
-  </si>
-  <si>
-    <t>231</t>
-  </si>
-  <si>
-    <t>Etablissement Information Consultation Conseil Familial</t>
-  </si>
-  <si>
-    <t>233</t>
-  </si>
-  <si>
-    <t>Lactarium</t>
-  </si>
-  <si>
-    <t>236</t>
-  </si>
-  <si>
-    <t>Centre Placement Familial Socio-Educatif (C.P.F.S.E.)</t>
-  </si>
-  <si>
-    <t>237</t>
-  </si>
-  <si>
-    <t>Centre de Placement Familial Spécialisé</t>
-  </si>
-  <si>
-    <t>238</t>
-  </si>
-  <si>
-    <t>Centre d'Accueil Familial Spécialisé</t>
-  </si>
-  <si>
-    <t>241</t>
-  </si>
-  <si>
-    <t>Établissement de Placement</t>
-  </si>
-  <si>
-    <t>242</t>
-  </si>
-  <si>
-    <t>Service d’Activité de Jour</t>
-  </si>
-  <si>
-    <t>246</t>
-  </si>
-  <si>
-    <t>Etablissement et Service d'Aide par le Travail (E.S.A.T.)</t>
-  </si>
-  <si>
-    <t>247</t>
-  </si>
-  <si>
-    <t>Entreprise adaptée</t>
-  </si>
-  <si>
-    <t>249</t>
-  </si>
-  <si>
-    <t>Établissement et Service de Réadaptation Professionnelle</t>
-  </si>
-  <si>
-    <t>250</t>
-  </si>
-  <si>
-    <t>Centre Réentrainement au travail</t>
-  </si>
-  <si>
-    <t>251</t>
-  </si>
-  <si>
-    <t>Maison Vacances pour Handicapés</t>
-  </si>
-  <si>
-    <t>252</t>
-  </si>
-  <si>
-    <t>Foyer Hébergement Adultes Handicapés</t>
-  </si>
-  <si>
-    <t>253</t>
-  </si>
-  <si>
-    <t>Foyer d'Accueil Polyvalent pour Adultes Handicapés</t>
-  </si>
-  <si>
-    <t>255</t>
-  </si>
-  <si>
-    <t>Maison d'Accueil Spécialisée (M.A.S.)</t>
-  </si>
-  <si>
-    <t>256</t>
-  </si>
-  <si>
-    <t>Foyer Travailleurs Migrants non transformé en Résidence Soc.</t>
-  </si>
-  <si>
-    <t>257</t>
-  </si>
-  <si>
-    <t>Foyers de jeunes travailleurs</t>
-  </si>
-  <si>
-    <t>258</t>
-  </si>
-  <si>
-    <t>Maisons Relais - Pensions de Famille</t>
-  </si>
-  <si>
-    <t>259</t>
-  </si>
-  <si>
-    <t>Autres résidences sociales</t>
-  </si>
-  <si>
-    <t>261</t>
-  </si>
-  <si>
-    <t>D.D.A.S.S.</t>
-  </si>
-  <si>
-    <t>262</t>
-  </si>
-  <si>
-    <t>Etablissement Régional d'Enseignement Adapté</t>
-  </si>
-  <si>
-    <t>265</t>
-  </si>
-  <si>
-    <t>Section Education Spéciale Classe Atelier</t>
-  </si>
-  <si>
-    <t>266</t>
-  </si>
-  <si>
-    <t>Dispensaire Antivénérien</t>
-  </si>
-  <si>
-    <t>267</t>
-  </si>
-  <si>
-    <t>Dispensaire Antihansénien</t>
-  </si>
-  <si>
-    <t>268</t>
-  </si>
-  <si>
-    <t>Centre Médico-Scolaire</t>
-  </si>
-  <si>
-    <t>269</t>
-  </si>
-  <si>
-    <t>Centre de Médecine Universitaire</t>
-  </si>
-  <si>
-    <t>270</t>
-  </si>
-  <si>
-    <t>Centre de Médecine Sportive</t>
-  </si>
-  <si>
-    <t>271</t>
-  </si>
-  <si>
-    <t>Maison d'accueil Hospitalière</t>
-  </si>
-  <si>
-    <t>272</t>
-  </si>
-  <si>
-    <t>Ecole d'ambulanciers</t>
-  </si>
-  <si>
-    <t>273</t>
-  </si>
-  <si>
-    <t>Institut de formation en soins infirmiers (I.F.S.I.)</t>
-  </si>
-  <si>
-    <t>274</t>
-  </si>
-  <si>
-    <t>Ecole de sages_femmes</t>
-  </si>
-  <si>
-    <t>275</t>
-  </si>
-  <si>
-    <t>Ecole de masseurs-kinésithérapeutes</t>
-  </si>
-  <si>
-    <t>276</t>
-  </si>
-  <si>
-    <t>Ecole de laborantins d'analyses médicales</t>
-  </si>
-  <si>
-    <t>277</t>
-  </si>
-  <si>
-    <t>Ecole de péricultrices</t>
-  </si>
-  <si>
-    <t>278</t>
-  </si>
-  <si>
-    <t>Etablissement de formation polyvalent</t>
-  </si>
-  <si>
-    <t>279</t>
-  </si>
-  <si>
-    <t>Ecole de service social</t>
-  </si>
-  <si>
-    <t>280</t>
-  </si>
-  <si>
-    <t>Ecole d'éducateurs spécialisés</t>
-  </si>
-  <si>
-    <t>281</t>
-  </si>
-  <si>
-    <t>Centre de formation d'aides soignants</t>
-  </si>
-  <si>
-    <t>282</t>
-  </si>
-  <si>
-    <t>Ecole de pédicures-podologues</t>
-  </si>
-  <si>
-    <t>283</t>
-  </si>
-  <si>
-    <t>Ecole de manipulateurs d'électro-radiologie</t>
-  </si>
-  <si>
-    <t>284</t>
-  </si>
-  <si>
-    <t>Ecole de travailleuses familiales</t>
-  </si>
-  <si>
-    <t>285</t>
-  </si>
-  <si>
-    <t>Centres de Loisirs sans Hébergement</t>
-  </si>
-  <si>
-    <t>286</t>
-  </si>
-  <si>
-    <t>Club Equipe de Prévention</t>
-  </si>
-  <si>
-    <t>289</t>
-  </si>
-  <si>
-    <t>Centre de Soins Infirmiers</t>
-  </si>
-  <si>
-    <t>292</t>
-  </si>
-  <si>
-    <t>Centre Hospitalier Spécialisé lutte Maladies Mentales</t>
-  </si>
-  <si>
-    <t>294</t>
-  </si>
-  <si>
-    <t>Centre de Consultations Cancer</t>
-  </si>
-  <si>
-    <t>295</t>
-  </si>
-  <si>
-    <t>Service AEMO et AED</t>
-  </si>
-  <si>
-    <t>297</t>
-  </si>
-  <si>
-    <t>Dispensaire Polyvalent</t>
-  </si>
-  <si>
-    <t>300</t>
-  </si>
-  <si>
-    <t>Ecoles Formant aux Professions Sanitaires</t>
-  </si>
-  <si>
-    <t>303</t>
-  </si>
-  <si>
-    <t>Ecole de conseillers en économie sociale et familiale</t>
-  </si>
-  <si>
-    <t>304</t>
-  </si>
-  <si>
-    <t>Ecole d'ergothérapeutes</t>
-  </si>
-  <si>
-    <t>305</t>
-  </si>
-  <si>
-    <t>Ecole de psycho-motriciens</t>
-  </si>
-  <si>
-    <t>306</t>
-  </si>
-  <si>
-    <t>Ecole d'infirmiers anesthésistes</t>
-  </si>
-  <si>
-    <t>307</t>
-  </si>
-  <si>
-    <t>Ecole d'infirmiers de bloc opératoire</t>
-  </si>
-  <si>
-    <t>308</t>
-  </si>
-  <si>
-    <t>Centre de formation professionnelle de secteur psychiatrique</t>
-  </si>
-  <si>
-    <t>309</t>
-  </si>
-  <si>
-    <t>Ecole de cadres infirmiers</t>
-  </si>
-  <si>
-    <t>310</t>
-  </si>
-  <si>
-    <t>Ecole de cadres de secteur psychiatrique</t>
-  </si>
-  <si>
-    <t>311</t>
-  </si>
-  <si>
-    <t>Ecole de cadres de masseurs-kinésithérapeutes</t>
-  </si>
-  <si>
-    <t>312</t>
-  </si>
-  <si>
-    <t>Ecole de cadres de manipulateurs d'électro-radiologie</t>
-  </si>
-  <si>
-    <t>313</t>
-  </si>
-  <si>
-    <t>Ecole d'éducateurs de jeunes enfants</t>
-  </si>
-  <si>
-    <t>314</t>
-  </si>
-  <si>
-    <t>Ecole d'éducateurs techniques spécialisés</t>
-  </si>
-  <si>
-    <t>315</t>
-  </si>
-  <si>
-    <t>Ecole de moniteurs-éducateurs</t>
-  </si>
-  <si>
-    <t>316</t>
-  </si>
-  <si>
-    <t>Ecole d'aides médico-psychologiques</t>
-  </si>
-  <si>
-    <t>317</t>
-  </si>
-  <si>
-    <t>Ecole d'animateurs socio-éducatifs</t>
-  </si>
-  <si>
-    <t>319</t>
-  </si>
-  <si>
-    <t>Inst. régional de formation des travailleurs sociaux</t>
-  </si>
-  <si>
-    <t>320</t>
-  </si>
-  <si>
-    <t>S.A.M.U. et Centre 15</t>
-  </si>
-  <si>
-    <t>321</t>
-  </si>
-  <si>
-    <t>Unité Mobile Hospitalière</t>
-  </si>
-  <si>
-    <t>322</t>
-  </si>
-  <si>
-    <t>Centre Rég.Informatiq.Hospit.</t>
-  </si>
-  <si>
-    <t>324</t>
-  </si>
-  <si>
-    <t>Logement Foyer non Spécialisé</t>
-  </si>
-  <si>
-    <t>326</t>
-  </si>
-  <si>
-    <t>Ecole de cadres</t>
-  </si>
-  <si>
-    <t>327</t>
-  </si>
-  <si>
-    <t>328</t>
-  </si>
-  <si>
-    <t>Centre Consultation Soins Dentaire</t>
-  </si>
-  <si>
-    <t>329</t>
-  </si>
-  <si>
-    <t>Sectorisation Psychiatrique</t>
-  </si>
-  <si>
-    <t>330</t>
-  </si>
-  <si>
-    <t>Ecoles Formant aux Professions Sociales</t>
-  </si>
-  <si>
-    <t>340</t>
-  </si>
-  <si>
-    <t>Service mandataire judiciaire à la protection des majeurs</t>
-  </si>
-  <si>
-    <t>341</t>
-  </si>
-  <si>
-    <t>Service dédié mesures d'accompagnement social personnalisé</t>
-  </si>
-  <si>
-    <t>342</t>
-  </si>
-  <si>
-    <t>Service d'information et de soutien aux tuteurs familiaux</t>
-  </si>
-  <si>
-    <t>343</t>
-  </si>
-  <si>
-    <t>Equipe Préparation et Suite Reclassement (EPSR)</t>
-  </si>
-  <si>
-    <t>344</t>
-  </si>
-  <si>
-    <t>Service délégué aux prestations familiales</t>
-  </si>
-  <si>
-    <t>345</t>
-  </si>
-  <si>
-    <t>Service Tutelle Prestation Sociale</t>
-  </si>
-  <si>
-    <t>346</t>
-  </si>
-  <si>
-    <t>Service de Travailleuses Familiales</t>
-  </si>
-  <si>
-    <t>347</t>
-  </si>
-  <si>
-    <t>Centre d'Examens de Santé</t>
-  </si>
-  <si>
-    <t>349</t>
-  </si>
-  <si>
-    <t>Ecole de cadres de sages-femmes</t>
-  </si>
-  <si>
-    <t>350</t>
-  </si>
-  <si>
-    <t>Centre de formation d'auxiliaires de puériculture</t>
-  </si>
-  <si>
-    <t>352</t>
-  </si>
-  <si>
-    <t>Centre de Psychothérapie</t>
-  </si>
-  <si>
-    <t>353</t>
-  </si>
-  <si>
-    <t>Hôpital de Jour Spécialités Médicales</t>
-  </si>
-  <si>
-    <t>354</t>
-  </si>
-  <si>
-    <t>Service de Soins Infirmiers A Domicile (S.S.I.A.D)</t>
-  </si>
-  <si>
-    <t>355</t>
-  </si>
-  <si>
-    <t>Centre Hospitalier (C.H.)</t>
-  </si>
-  <si>
-    <t>357</t>
-  </si>
-  <si>
-    <t>Association Aide aux Insuffisants Respiratoires</t>
-  </si>
-  <si>
-    <t>359</t>
-  </si>
-  <si>
-    <t>Centre Circonscription Sanitaire et Sociale</t>
-  </si>
-  <si>
-    <t>361</t>
-  </si>
-  <si>
-    <t>Centre de Cure Médicale</t>
-  </si>
-  <si>
-    <t>362</t>
-  </si>
-  <si>
-    <t>Etablissement de Soins Longue Durée</t>
-  </si>
-  <si>
-    <t>363</t>
-  </si>
-  <si>
-    <t>Centre moyen et long séjour</t>
-  </si>
-  <si>
-    <t>365</t>
-  </si>
-  <si>
-    <t>Etablissement de Soins Pluridisciplinaire</t>
-  </si>
-  <si>
-    <t>366</t>
-  </si>
-  <si>
-    <t>Atelier Thérapeutique</t>
-  </si>
-  <si>
-    <t>367</t>
-  </si>
-  <si>
-    <t>Maison d'Enfants non Conventionnée ni Habilitée</t>
-  </si>
-  <si>
-    <t>368</t>
-  </si>
-  <si>
-    <t>Service de Repas à Domicile</t>
-  </si>
-  <si>
-    <t>369</t>
-  </si>
-  <si>
-    <t>Centre Adaptation Vie Active (C.A.V.A.)</t>
-  </si>
-  <si>
-    <t>370</t>
-  </si>
-  <si>
-    <t>Etablissement Expérimental pour personnes handicapées</t>
-  </si>
-  <si>
-    <t>371</t>
-  </si>
-  <si>
-    <t>Service Action Socio-Educative pour Familles en difficulté</t>
-  </si>
-  <si>
-    <t>373</t>
-  </si>
-  <si>
-    <t>Centre de formation supérieure des travailleurs sociaux</t>
-  </si>
-  <si>
-    <t>374</t>
-  </si>
-  <si>
-    <t>Ecole Nationale Santé Publique (E.N.S.P.)</t>
-  </si>
-  <si>
-    <t>375</t>
-  </si>
-  <si>
-    <t>Classe d'Adaptation</t>
-  </si>
-  <si>
-    <t>376</t>
-  </si>
-  <si>
-    <t>Classe Spéciale Ecole Primaire</t>
-  </si>
-  <si>
-    <t>377</t>
-  </si>
-  <si>
-    <t>Etablissement Expérimental pour Enfance Handicapée</t>
-  </si>
-  <si>
-    <t>378</t>
-  </si>
-  <si>
-    <t>Etablissement Expérimental Enfance Protégée</t>
-  </si>
-  <si>
-    <t>379</t>
-  </si>
-  <si>
-    <t>Etablissement Expérimental pour Adultes Handicapés</t>
-  </si>
-  <si>
-    <t>380</t>
-  </si>
-  <si>
-    <t>Etablissement Expérimental Autres Adultes</t>
-  </si>
-  <si>
-    <t>381</t>
-  </si>
-  <si>
-    <t>Etablissement Expérimental pour Personnes Agées</t>
-  </si>
-  <si>
-    <t>382</t>
-  </si>
-  <si>
-    <t>Foyer de Vie pour Adultes Handicapés</t>
-  </si>
-  <si>
-    <t>386</t>
-  </si>
-  <si>
-    <t>Ecole Secondaire Spéciale</t>
-  </si>
-  <si>
-    <t>390</t>
-  </si>
-  <si>
-    <t>Etablissement d'Accueil Temporaire d'Enfants Handicapés</t>
-  </si>
-  <si>
-    <t>393</t>
-  </si>
-  <si>
-    <t>Autre résidence But lucratif pr personnes Âgées</t>
-  </si>
-  <si>
-    <t>394</t>
-  </si>
-  <si>
-    <t>Etablissement d'Accueil Temporaire pour Personnes Agées</t>
-  </si>
-  <si>
-    <t>395</t>
-  </si>
-  <si>
-    <t>Etablissement d'Accueil Temporaire pour Adultes Handicapés</t>
-  </si>
-  <si>
-    <t>396</t>
-  </si>
-  <si>
-    <t>Foyer Hébergement Enfants et Adolescents Handicapés</t>
-  </si>
-  <si>
-    <t>397</t>
-  </si>
-  <si>
-    <t>Service Auxiliaire de Vie pour Handicapés</t>
-  </si>
-  <si>
-    <t>398</t>
-  </si>
-  <si>
-    <t>Crèche Parentale</t>
-  </si>
-  <si>
-    <t>399</t>
-  </si>
-  <si>
-    <t>Halte Garderie Parentale</t>
-  </si>
-  <si>
-    <t>400</t>
-  </si>
-  <si>
-    <t>Centre de Services pour Associations</t>
-  </si>
-  <si>
-    <t>401</t>
-  </si>
-  <si>
-    <t>D.R.A.S.S.</t>
-  </si>
-  <si>
-    <t>402</t>
-  </si>
-  <si>
-    <t>Jardin d'Enfants Spécialisé</t>
-  </si>
-  <si>
-    <t>403</t>
-  </si>
-  <si>
-    <t>Service Social Spécialisé ou Polyvalent de Catégorie</t>
-  </si>
-  <si>
-    <t>404</t>
-  </si>
-  <si>
-    <t>Etablissement Acc.Collect.Parental Régulier &amp; Occasionnel</t>
-  </si>
-  <si>
-    <t>405</t>
-  </si>
-  <si>
-    <t>Service Social Polyvalent de Secteur</t>
-  </si>
-  <si>
-    <t>411</t>
-  </si>
-  <si>
-    <t>Intermédiaire de Placement Social</t>
-  </si>
-  <si>
-    <t>412</t>
-  </si>
-  <si>
-    <t>Appartement Thérapeutique</t>
-  </si>
-  <si>
-    <t>413</t>
-  </si>
-  <si>
-    <t>C.E.C.O.S</t>
-  </si>
-  <si>
-    <t>414</t>
-  </si>
-  <si>
-    <t>Centre Anti Poison</t>
-  </si>
-  <si>
-    <t>415</t>
-  </si>
-  <si>
-    <t>Service Médico-Psychologique Régional (S.M.P.R.)</t>
-  </si>
-  <si>
-    <t>418</t>
-  </si>
-  <si>
-    <t>Service d'Enquêtes Sociales (S.E.S.)</t>
-  </si>
-  <si>
-    <t>419</t>
-  </si>
-  <si>
-    <t>Centre d'Accueil Toxicomanes</t>
-  </si>
-  <si>
-    <t>420</t>
-  </si>
-  <si>
-    <t>Entreprise d'Insertion</t>
-  </si>
-  <si>
-    <t>421</t>
-  </si>
-  <si>
-    <t>Centre d'enseignement aux secours d'urgence</t>
-  </si>
-  <si>
-    <t>422</t>
-  </si>
-  <si>
-    <t>Traitements Spécialisés à Domicile</t>
-  </si>
-  <si>
-    <t>423</t>
-  </si>
-  <si>
-    <t>Ecole des cadres de laborantins d'analyses médicales</t>
-  </si>
-  <si>
-    <t>425</t>
-  </si>
-  <si>
-    <t>Centre d'Accueil Thérapeutique à temps partiel (C.A.T.T.P.)</t>
-  </si>
-  <si>
     <t>Syndicat Inter Hospitalier (S.I.H.)</t>
   </si>
   <si>
-    <t>427</t>
-  </si>
-  <si>
     <t>Service Educatif Auprès des Tribunaux (S.E.A.T.)</t>
   </si>
   <si>
@@ -2717,6 +2717,15 @@
   </si>
   <si>
     <t>Structure qui contribue au Service d'Accès aux Soins</t>
+  </si>
+  <si>
+    <t>649</t>
+  </si>
+  <si>
+    <t>Centre de santé et de médiation en santé sexuelle</t>
+  </si>
+  <si>
+    <t>Les centres de santé et de médiation en santé sexuelle (CSMSS) sont des établissements de santé dérogatoires relevant de l’article L. 6323-1 du code de la santé publique (CSP). Ils ont initialement fait l’objet d’une expérimentation dans le cadre du dispositif prévu à l’article 51 de la loi de financement de la sécurité sociale, au cours de laquelle ils étaient rattachés au numéro FINESS des centres de santé de droit commun. L’activité des centres de santé et de médiation en santé sexuelle (CSMSS) consiste à assurer l’accueil, l’information, la prévention, le dépistage et l’accompagnement des publics dans le domaine de la santé sexuelle dans une approche globale intégrant notamment la prévention et la prise en charge des infections sexuellement transmissibles (IST) et du VIH, la prescription de la contraception et la mise en place de parcours en santé sexuelle.</t>
   </si>
   <si>
     <t>690</t>
@@ -3298,7 +3307,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D427"/>
+  <dimension ref="A1:D428"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -7400,10 +7409,10 @@
         <v>85</v>
       </c>
       <c r="B342" t="s" s="2">
-        <v>34</v>
+        <v>754</v>
       </c>
       <c r="C342" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="D342" s="2"/>
     </row>
@@ -7412,7 +7421,7 @@
         <v>85</v>
       </c>
       <c r="B343" t="s" s="2">
-        <v>755</v>
+        <v>34</v>
       </c>
       <c r="C343" t="s" s="2">
         <v>756</v>
@@ -8307,17 +8316,19 @@
       <c r="C417" t="s" s="2">
         <v>902</v>
       </c>
-      <c r="D417" s="2"/>
+      <c r="D417" t="s" s="2">
+        <v>903</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="s" s="2">
         <v>85</v>
       </c>
       <c r="B418" t="s" s="2">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="C418" t="s" s="2">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="D418" s="2"/>
     </row>
@@ -8326,10 +8337,10 @@
         <v>85</v>
       </c>
       <c r="B419" t="s" s="2">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="C419" t="s" s="2">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="D419" s="2"/>
     </row>
@@ -8338,10 +8349,10 @@
         <v>85</v>
       </c>
       <c r="B420" t="s" s="2">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="C420" t="s" s="2">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="D420" s="2"/>
     </row>
@@ -8350,10 +8361,10 @@
         <v>85</v>
       </c>
       <c r="B421" t="s" s="2">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="C421" t="s" s="2">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="D421" s="2"/>
     </row>
@@ -8362,10 +8373,10 @@
         <v>85</v>
       </c>
       <c r="B422" t="s" s="2">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="C422" t="s" s="2">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="D422" s="2"/>
     </row>
@@ -8374,14 +8385,12 @@
         <v>85</v>
       </c>
       <c r="B423" t="s" s="2">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="C423" t="s" s="2">
-        <v>914</v>
-      </c>
-      <c r="D423" t="s" s="2">
         <v>915</v>
       </c>
+      <c r="D423" s="2"/>
     </row>
     <row r="424">
       <c r="A424" t="s" s="2">
@@ -8394,7 +8403,7 @@
         <v>917</v>
       </c>
       <c r="D424" t="s" s="2">
-        <v>915</v>
+        <v>918</v>
       </c>
     </row>
     <row r="425">
@@ -8402,13 +8411,13 @@
         <v>85</v>
       </c>
       <c r="B425" t="s" s="2">
+        <v>919</v>
+      </c>
+      <c r="C425" t="s" s="2">
+        <v>920</v>
+      </c>
+      <c r="D425" t="s" s="2">
         <v>918</v>
-      </c>
-      <c r="C425" t="s" s="2">
-        <v>919</v>
-      </c>
-      <c r="D425" t="s" s="2">
-        <v>915</v>
       </c>
     </row>
     <row r="426">
@@ -8416,25 +8425,39 @@
         <v>85</v>
       </c>
       <c r="B426" t="s" s="2">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="C426" t="s" s="2">
-        <v>921</v>
-      </c>
-      <c r="D426" s="2"/>
+        <v>922</v>
+      </c>
+      <c r="D426" t="s" s="2">
+        <v>918</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="s" s="2">
         <v>85</v>
       </c>
       <c r="B427" t="s" s="2">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="C427" t="s" s="2">
-        <v>923</v>
-      </c>
-      <c r="D427" t="s" s="2">
         <v>924</v>
+      </c>
+      <c r="D427" s="2"/>
+    </row>
+    <row r="428">
+      <c r="A428" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="B428" t="s" s="2">
+        <v>925</v>
+      </c>
+      <c r="C428" t="s" s="2">
+        <v>926</v>
+      </c>
+      <c r="D428" t="s" s="2">
+        <v>927</v>
       </c>
     </row>
   </sheetData>

--- a/ig/DM_FINESS_New/CodeSystem-tre-r397-categorie-entite-geographique-exercice.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-tre-r397-categorie-entite-geographique-exercice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1383" uniqueCount="928">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1384" uniqueCount="929">
   <si>
     <t>Property</t>
   </si>
@@ -1462,7 +1462,7 @@
     <t>231</t>
   </si>
   <si>
-    <t>Etablissement Information Consultation Conseil Familial</t>
+    <t>Espaces de vie affective, relationnelle et sexuelle (EVARS)</t>
   </si>
   <si>
     <t>233</t>
@@ -2560,7 +2560,10 @@
     <t>617</t>
   </si>
   <si>
-    <t>Maison médicale de garde (MMG)</t>
+    <t>Lieu de soins non programmés</t>
+  </si>
+  <si>
+    <t>Un lieu de soins non programmés est un lieu fixe dédié à la médecine générale, ouvert uniquement pendant les périodes de permanence des soins : soirées, nuits, week-ends et jours fériés.</t>
   </si>
   <si>
     <t>618</t>
@@ -7992,17 +7995,19 @@
       <c r="C390" t="s" s="2">
         <v>848</v>
       </c>
-      <c r="D390" s="2"/>
+      <c r="D390" t="s" s="2">
+        <v>849</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="s" s="2">
         <v>85</v>
       </c>
       <c r="B391" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C391" t="s" s="2">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="D391" s="2"/>
     </row>
@@ -8011,10 +8016,10 @@
         <v>85</v>
       </c>
       <c r="B392" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="C392" t="s" s="2">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="D392" s="2"/>
     </row>
@@ -8023,10 +8028,10 @@
         <v>85</v>
       </c>
       <c r="B393" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="C393" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="D393" s="2"/>
     </row>
@@ -8035,10 +8040,10 @@
         <v>85</v>
       </c>
       <c r="B394" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="C394" t="s" s="2">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="D394" s="2"/>
     </row>
@@ -8047,10 +8052,10 @@
         <v>85</v>
       </c>
       <c r="B395" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="C395" t="s" s="2">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="D395" s="2"/>
     </row>
@@ -8059,10 +8064,10 @@
         <v>85</v>
       </c>
       <c r="B396" t="s" s="2">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="C396" t="s" s="2">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="D396" s="2"/>
     </row>
@@ -8071,10 +8076,10 @@
         <v>85</v>
       </c>
       <c r="B397" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="C397" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="D397" s="2"/>
     </row>
@@ -8083,10 +8088,10 @@
         <v>85</v>
       </c>
       <c r="B398" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="C398" t="s" s="2">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="D398" s="2"/>
     </row>
@@ -8095,10 +8100,10 @@
         <v>85</v>
       </c>
       <c r="B399" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="C399" t="s" s="2">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="D399" s="2"/>
     </row>
@@ -8107,10 +8112,10 @@
         <v>85</v>
       </c>
       <c r="B400" t="s" s="2">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="C400" t="s" s="2">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="D400" s="2"/>
     </row>
@@ -8119,10 +8124,10 @@
         <v>85</v>
       </c>
       <c r="B401" t="s" s="2">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="C401" t="s" s="2">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="D401" s="2"/>
     </row>
@@ -8131,10 +8136,10 @@
         <v>85</v>
       </c>
       <c r="B402" t="s" s="2">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="C402" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="D402" s="2"/>
     </row>
@@ -8143,10 +8148,10 @@
         <v>85</v>
       </c>
       <c r="B403" t="s" s="2">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="C403" t="s" s="2">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="D403" s="2"/>
     </row>
@@ -8155,10 +8160,10 @@
         <v>85</v>
       </c>
       <c r="B404" t="s" s="2">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="C404" t="s" s="2">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="D404" s="2"/>
     </row>
@@ -8167,10 +8172,10 @@
         <v>85</v>
       </c>
       <c r="B405" t="s" s="2">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="C405" t="s" s="2">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="D405" s="2"/>
     </row>
@@ -8179,10 +8184,10 @@
         <v>85</v>
       </c>
       <c r="B406" t="s" s="2">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="C406" t="s" s="2">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="D406" s="2"/>
     </row>
@@ -8191,10 +8196,10 @@
         <v>85</v>
       </c>
       <c r="B407" t="s" s="2">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="C407" t="s" s="2">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="D407" s="2"/>
     </row>
@@ -8203,10 +8208,10 @@
         <v>85</v>
       </c>
       <c r="B408" t="s" s="2">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="C408" t="s" s="2">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="D408" s="2"/>
     </row>
@@ -8215,10 +8220,10 @@
         <v>85</v>
       </c>
       <c r="B409" t="s" s="2">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="C409" t="s" s="2">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="D409" s="2"/>
     </row>
@@ -8227,10 +8232,10 @@
         <v>85</v>
       </c>
       <c r="B410" t="s" s="2">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="C410" t="s" s="2">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="D410" s="2"/>
     </row>
@@ -8239,10 +8244,10 @@
         <v>85</v>
       </c>
       <c r="B411" t="s" s="2">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="C411" t="s" s="2">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="D411" s="2"/>
     </row>
@@ -8251,10 +8256,10 @@
         <v>85</v>
       </c>
       <c r="B412" t="s" s="2">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="C412" t="s" s="2">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="D412" s="2"/>
     </row>
@@ -8263,10 +8268,10 @@
         <v>85</v>
       </c>
       <c r="B413" t="s" s="2">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="C413" t="s" s="2">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="D413" s="2"/>
     </row>
@@ -8275,10 +8280,10 @@
         <v>85</v>
       </c>
       <c r="B414" t="s" s="2">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="C414" t="s" s="2">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="D414" s="2"/>
     </row>
@@ -8287,10 +8292,10 @@
         <v>85</v>
       </c>
       <c r="B415" t="s" s="2">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="C415" t="s" s="2">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="D415" s="2"/>
     </row>
@@ -8299,10 +8304,10 @@
         <v>85</v>
       </c>
       <c r="B416" t="s" s="2">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="C416" t="s" s="2">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="D416" s="2"/>
     </row>
@@ -8311,13 +8316,13 @@
         <v>85</v>
       </c>
       <c r="B417" t="s" s="2">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="C417" t="s" s="2">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="D417" t="s" s="2">
-        <v>903</v>
+        <v>904</v>
       </c>
     </row>
     <row r="418">
@@ -8325,10 +8330,10 @@
         <v>85</v>
       </c>
       <c r="B418" t="s" s="2">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="C418" t="s" s="2">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="D418" s="2"/>
     </row>
@@ -8337,10 +8342,10 @@
         <v>85</v>
       </c>
       <c r="B419" t="s" s="2">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="C419" t="s" s="2">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="D419" s="2"/>
     </row>
@@ -8349,10 +8354,10 @@
         <v>85</v>
       </c>
       <c r="B420" t="s" s="2">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="C420" t="s" s="2">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="D420" s="2"/>
     </row>
@@ -8361,10 +8366,10 @@
         <v>85</v>
       </c>
       <c r="B421" t="s" s="2">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="C421" t="s" s="2">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="D421" s="2"/>
     </row>
@@ -8373,10 +8378,10 @@
         <v>85</v>
       </c>
       <c r="B422" t="s" s="2">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="C422" t="s" s="2">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="D422" s="2"/>
     </row>
@@ -8385,10 +8390,10 @@
         <v>85</v>
       </c>
       <c r="B423" t="s" s="2">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="C423" t="s" s="2">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="D423" s="2"/>
     </row>
@@ -8397,13 +8402,13 @@
         <v>85</v>
       </c>
       <c r="B424" t="s" s="2">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="C424" t="s" s="2">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="D424" t="s" s="2">
-        <v>918</v>
+        <v>919</v>
       </c>
     </row>
     <row r="425">
@@ -8411,13 +8416,13 @@
         <v>85</v>
       </c>
       <c r="B425" t="s" s="2">
+        <v>920</v>
+      </c>
+      <c r="C425" t="s" s="2">
+        <v>921</v>
+      </c>
+      <c r="D425" t="s" s="2">
         <v>919</v>
-      </c>
-      <c r="C425" t="s" s="2">
-        <v>920</v>
-      </c>
-      <c r="D425" t="s" s="2">
-        <v>918</v>
       </c>
     </row>
     <row r="426">
@@ -8425,13 +8430,13 @@
         <v>85</v>
       </c>
       <c r="B426" t="s" s="2">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="C426" t="s" s="2">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="D426" t="s" s="2">
-        <v>918</v>
+        <v>919</v>
       </c>
     </row>
     <row r="427">
@@ -8439,10 +8444,10 @@
         <v>85</v>
       </c>
       <c r="B427" t="s" s="2">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="C427" t="s" s="2">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="D427" s="2"/>
     </row>
@@ -8451,13 +8456,13 @@
         <v>85</v>
       </c>
       <c r="B428" t="s" s="2">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="C428" t="s" s="2">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="D428" t="s" s="2">
-        <v>927</v>
+        <v>928</v>
       </c>
     </row>
   </sheetData>

--- a/ig/DM_FINESS_New/CodeSystem-tre-r397-categorie-entite-geographique-exercice.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-tre-r397-categorie-entite-geographique-exercice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1384" uniqueCount="929">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1388" uniqueCount="933">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20251222120000</t>
+    <t>20260223120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-22T12:00:00+01:00</t>
+    <t>2026-02-23T12:00:00.000+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -79,7 +79,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Catégorie d'établissements - TRE Hierarchique qui remplace la TRE R66</t>
+    <t>Cette TRE hierarchique remplace les TRE actuelles TRE_R66_CategorieEtablissement, TRE-R63-AgregatCategorieEtablissementNiv1, TRE-R64-AgregatCategorieEtablissementNiv2, TRE-R65-AgregatCategorieEtablissement et ASS-X10-AgregatCategorieEtablissement. Cette TRE possède des propriétésspécifiques : le niveau d'agrégat des EGE de 1 à 4 (du plus large au plus fin), le parent d'un agrégat d'EGE ou d'un EGE, la relation entre un code et le domaine ( TRE R62), un indicateur pour les EGE spécifiques au ROR ( non finess) et les relations nécessaires à la construction des JDV dynamiques associés</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -118,2172 +118,2175 @@
     <t>Count</t>
   </si>
   <si>
+    <t>428</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Uri</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>niveau</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#niveau</t>
+  </si>
+  <si>
+    <t>Permet d'indiquer le niveau hiérarchique du code</t>
+  </si>
+  <si>
+    <t>integer</t>
+  </si>
+  <si>
+    <t>parent</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/concept-properties#parent</t>
+  </si>
+  <si>
+    <t>An immediate parent of the concept in the hierarchy</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>domaine</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#domaine</t>
+  </si>
+  <si>
+    <t>Domaine de la categorie d etablissement</t>
+  </si>
+  <si>
+    <t>Coding</t>
+  </si>
+  <si>
+    <t>dateValid</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateValid</t>
+  </si>
+  <si>
+    <t>date de validité d'un code concept</t>
+  </si>
+  <si>
+    <t>dateTime</t>
+  </si>
+  <si>
+    <t>dateMaj</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateMaj</t>
+  </si>
+  <si>
+    <t>Date de mise à jour d'un code concept</t>
+  </si>
+  <si>
+    <t>dateFin</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateFin</t>
+  </si>
+  <si>
+    <t>Date de fin d'exploitation d'un code concept</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/concept-properties#status</t>
+  </si>
+  <si>
+    <t>A property that indicates the status of the concept.</t>
+  </si>
+  <si>
+    <t>deprecationDate</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/concept-properties#deprecationDate</t>
+  </si>
+  <si>
+    <t>Date Concept was deprecated</t>
+  </si>
+  <si>
+    <t>retirementDate</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/concept-properties#retirementDate</t>
+  </si>
+  <si>
+    <t>Date Concept was retired</t>
+  </si>
+  <si>
+    <t>specialisationRor</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#specialisationRor</t>
+  </si>
+  <si>
+    <t>Propriété permettant de spécifier les codes exclusifs appartenant au ROR</t>
+  </si>
+  <si>
+    <t>boolean</t>
+  </si>
+  <si>
+    <t>ror</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#ror</t>
+  </si>
+  <si>
+    <t>Permet de définir les codes concepts uilisés par le ROR</t>
+  </si>
+  <si>
+    <t>cisis</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#cisis</t>
+  </si>
+  <si>
+    <t>Permet de définir les codes concepts uilisés par le CISIS</t>
+  </si>
+  <si>
+    <t>rass</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#rass</t>
+  </si>
+  <si>
+    <t>Permet de définir les codes concepts uilisés par le RASS</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>Display</t>
+  </si>
+  <si>
+    <t>Definition</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>0100</t>
+  </si>
+  <si>
+    <t>Etablissements d'administration</t>
+  </si>
+  <si>
+    <t>1000</t>
+  </si>
+  <si>
+    <t>Etablissements Relevant de la Loi Hospitalière</t>
+  </si>
+  <si>
+    <t>2000</t>
+  </si>
+  <si>
+    <t>Autres Etablissements de Soins et Prévention</t>
+  </si>
+  <si>
+    <t>3000</t>
+  </si>
+  <si>
+    <t>Autres Etablissements à Caractère Sanitaire</t>
+  </si>
+  <si>
+    <t>4000</t>
+  </si>
+  <si>
+    <t>Etab.Serv.Soc.d'Accueil Hébergement Assistance Réadaptation</t>
+  </si>
+  <si>
+    <t>5000</t>
+  </si>
+  <si>
+    <t>Etablissements et Services Sociaux d'Aide à la Famille</t>
+  </si>
+  <si>
+    <t>6000</t>
+  </si>
+  <si>
+    <t>Etab.de Formation des Personnels Sanitaires et Sociaux</t>
+  </si>
+  <si>
+    <t>0110</t>
+  </si>
+  <si>
+    <t>Etablissements d'Administration</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>1100</t>
+  </si>
+  <si>
+    <t>Etablissements Hospitaliers</t>
+  </si>
+  <si>
+    <t>1200</t>
+  </si>
+  <si>
+    <t>Autres Etablissements Relevant de la Loi Hospitalière</t>
+  </si>
+  <si>
+    <t>2100</t>
+  </si>
+  <si>
+    <t>Cabinets Libéraux</t>
+  </si>
+  <si>
+    <t>2200</t>
+  </si>
+  <si>
+    <t>3100</t>
+  </si>
+  <si>
+    <t>Laboratoires de Biologie Médicale</t>
+  </si>
+  <si>
+    <t>3200</t>
+  </si>
+  <si>
+    <t>Commerce de Biens à Usage Médicaux</t>
+  </si>
+  <si>
+    <t>3400</t>
+  </si>
+  <si>
+    <t>4100</t>
+  </si>
+  <si>
+    <t>Etab.et Serv.pour l'Enfance et la Jeunesse Handicapée</t>
+  </si>
+  <si>
+    <t>4200</t>
+  </si>
+  <si>
+    <t>Etablissements ou Classes d'Enseignement Spécial</t>
+  </si>
+  <si>
+    <t>4300</t>
+  </si>
+  <si>
+    <t>Etablissements et Services pour Adultes Handicapés</t>
+  </si>
+  <si>
+    <t>4400</t>
+  </si>
+  <si>
+    <t>Etablissements et Services pour Personnes Agées</t>
+  </si>
+  <si>
+    <t>4500</t>
+  </si>
+  <si>
+    <t>Etab.et Serv.Sociaux Concourant à la Protection de l'Enfance</t>
+  </si>
+  <si>
+    <t>4600</t>
+  </si>
+  <si>
+    <t>Autres Etab. Accueil, Hébergement, Réadaptation et Services</t>
+  </si>
+  <si>
+    <t>5100</t>
+  </si>
+  <si>
+    <t>6100</t>
+  </si>
+  <si>
+    <t>Etablissements de Formation des Personnels Sanitaires</t>
+  </si>
+  <si>
+    <t>6200</t>
+  </si>
+  <si>
+    <t>Etablissements de Formation des Personnels Sociaux</t>
+  </si>
+  <si>
+    <t>6300</t>
+  </si>
+  <si>
+    <t>Etablissements de Formation Polyvalente</t>
+  </si>
+  <si>
+    <t>0101</t>
+  </si>
+  <si>
+    <t>1101</t>
+  </si>
+  <si>
+    <t>Centres Hospitaliers Régionaux</t>
+  </si>
+  <si>
+    <t>1102</t>
+  </si>
+  <si>
+    <t>Centres Hospitaliers</t>
+  </si>
+  <si>
+    <t>1103</t>
+  </si>
+  <si>
+    <t>Centres Hospitaliers Spécialisés Lutte Maladies Mentales</t>
+  </si>
+  <si>
+    <t>1104</t>
+  </si>
+  <si>
+    <t>Centres de Lutte contre le Cancer</t>
+  </si>
+  <si>
+    <t>1106</t>
+  </si>
+  <si>
+    <t>Hôpitaux Locaux</t>
+  </si>
+  <si>
+    <t>1107</t>
+  </si>
+  <si>
+    <t>Etablissements de santé privé autorisés en SSR</t>
+  </si>
+  <si>
+    <t>1108</t>
+  </si>
+  <si>
+    <t>Centre de Moyen et de Long Séjour</t>
+  </si>
+  <si>
+    <t>1109</t>
+  </si>
+  <si>
+    <t>Etablissements de Soins de Longue Durée</t>
+  </si>
+  <si>
+    <t>1110</t>
+  </si>
+  <si>
+    <t>Etablissements de Soins de Courte Durée</t>
+  </si>
+  <si>
+    <t>1111</t>
+  </si>
+  <si>
+    <t>Autres Etablissements de Lutte contre les Maladies Mentales</t>
+  </si>
+  <si>
+    <t>1112</t>
+  </si>
+  <si>
+    <t>Etablissements d'Enfants à Caractère Sanitaire</t>
+  </si>
+  <si>
+    <t>1113</t>
+  </si>
+  <si>
+    <t>Etablissements de Lutte contre l'Alcoolisme</t>
+  </si>
+  <si>
+    <t>1201</t>
+  </si>
+  <si>
+    <t>Traitements et Soins à Domicile</t>
+  </si>
+  <si>
+    <t>1202</t>
+  </si>
+  <si>
+    <t>Santé Mentale</t>
+  </si>
+  <si>
+    <t>1203</t>
+  </si>
+  <si>
+    <t>Dialyse ambulatoire</t>
+  </si>
+  <si>
+    <t>1204</t>
+  </si>
+  <si>
+    <t>Urgence et Réanimation</t>
+  </si>
+  <si>
+    <t>1205</t>
+  </si>
+  <si>
+    <t>2101</t>
+  </si>
+  <si>
+    <t>Cabinets Libéraux de Médecins</t>
+  </si>
+  <si>
+    <t>2102</t>
+  </si>
+  <si>
+    <t>Cabinet de Groupe</t>
+  </si>
+  <si>
+    <t>2103</t>
+  </si>
+  <si>
+    <t>Autres structures d'exercice libéral</t>
+  </si>
+  <si>
+    <t>2105</t>
+  </si>
+  <si>
+    <t>Cabinet d'Auxiliaires Médicaux</t>
+  </si>
+  <si>
+    <t>2201</t>
+  </si>
+  <si>
+    <t>Dispensaires ou Centres de Soins</t>
+  </si>
+  <si>
+    <t>2202</t>
+  </si>
+  <si>
+    <t>Etablissements de PMI et de Planification Familiale</t>
+  </si>
+  <si>
+    <t>2203</t>
+  </si>
+  <si>
+    <t>Etablissements de Soins Dentaires</t>
+  </si>
+  <si>
+    <t>2204</t>
+  </si>
+  <si>
+    <t>Etablissements ne relevant pas de la Loi Hospitalière</t>
+  </si>
+  <si>
+    <t>2205</t>
+  </si>
+  <si>
+    <t>Etab.de soins relevant du service de santé des armées</t>
+  </si>
+  <si>
+    <t>2206</t>
+  </si>
+  <si>
+    <t>Centres de Santé</t>
+  </si>
+  <si>
+    <t>3101</t>
+  </si>
+  <si>
+    <t>3201</t>
+  </si>
+  <si>
+    <t>3202</t>
+  </si>
+  <si>
+    <t>Commerce de Biens Médicaux</t>
+  </si>
+  <si>
+    <t>3401</t>
+  </si>
+  <si>
+    <t>Transfusion Sanguine</t>
+  </si>
+  <si>
+    <t>3402</t>
+  </si>
+  <si>
+    <t>Conservation et Stockage d'autres Produits Humains</t>
+  </si>
+  <si>
+    <t>3403</t>
+  </si>
+  <si>
+    <t>Centre Antipoison</t>
+  </si>
+  <si>
+    <t>3404</t>
+  </si>
+  <si>
+    <t>Service d'Ambulances</t>
+  </si>
+  <si>
+    <t>3405</t>
+  </si>
+  <si>
+    <t>Installations autonomes de chirurgie esthétique</t>
+  </si>
+  <si>
+    <t>3406</t>
+  </si>
+  <si>
+    <t>Maisons de Naissance</t>
+  </si>
+  <si>
+    <t>3407</t>
+  </si>
+  <si>
+    <t>Etablissements Expérimentaux en Santé</t>
+  </si>
+  <si>
+    <t>3408</t>
+  </si>
+  <si>
+    <t>Centre de ressources transverse</t>
+  </si>
+  <si>
+    <t>3409</t>
+  </si>
+  <si>
+    <t>Services de Prévention et de Santé au Travail (SPST)</t>
+  </si>
+  <si>
+    <t>3410</t>
+  </si>
+  <si>
+    <t>Services d'incendie et de secours</t>
+  </si>
+  <si>
+    <t>4101</t>
+  </si>
+  <si>
+    <t>Etab.Educ.Spéciale pour Déficients Mentaux et Handicapés</t>
+  </si>
+  <si>
+    <t>4102</t>
+  </si>
+  <si>
+    <t>Etab.Educ Spéciale pour Enfants Trouble Conduite et Comport</t>
+  </si>
+  <si>
+    <t>4103</t>
+  </si>
+  <si>
+    <t>Etablissements d'Education Spéciale pour Handicapés Moteurs</t>
+  </si>
+  <si>
+    <t>4104</t>
+  </si>
+  <si>
+    <t>Etab.Education Spéciale pour Déficients Sensoriels</t>
+  </si>
+  <si>
+    <t>4105</t>
+  </si>
+  <si>
+    <t>Etablissements et Services Hébergement Enfants Handicapés</t>
+  </si>
+  <si>
+    <t>4106</t>
+  </si>
+  <si>
+    <t>Services à Domicile ou Ambulatoires pour Handicapés</t>
+  </si>
+  <si>
+    <t>4107</t>
+  </si>
+  <si>
+    <t>Etab. Expérimentaux en Faveur de l'Enfance Handicapée</t>
+  </si>
+  <si>
+    <t>4201</t>
+  </si>
+  <si>
+    <t>Etablissements ou Classes de Pré-Élémentaire et Élémentaire</t>
+  </si>
+  <si>
+    <t>4202</t>
+  </si>
+  <si>
+    <t>Etablissements d'Enseignement Secondaire</t>
+  </si>
+  <si>
+    <t>4301</t>
+  </si>
+  <si>
+    <t>Etab. et Services d'Hébergement pour Adultes Handicapés</t>
+  </si>
+  <si>
+    <t>4302</t>
+  </si>
+  <si>
+    <t>Etab.et Services de Travail Protégé pour Adultes Handicapés</t>
+  </si>
+  <si>
+    <t>4303</t>
+  </si>
+  <si>
+    <t>Etab.et Services de Réinsertion Prof pour Adultes Handicapés</t>
+  </si>
+  <si>
+    <t>4304</t>
+  </si>
+  <si>
+    <t>Etab.Expérimentaux en Faveur des Adultes Handicapés</t>
+  </si>
+  <si>
+    <t>4305</t>
+  </si>
+  <si>
+    <t>Services de Maintien à Domicile pour Handicapés</t>
+  </si>
+  <si>
+    <t>4401</t>
+  </si>
+  <si>
+    <t>Etablissements d'Hébergement pour Personnes Âgées</t>
+  </si>
+  <si>
+    <t>4402</t>
+  </si>
+  <si>
+    <t>Services de Maintien à Domicile pour Personnes Âgées</t>
+  </si>
+  <si>
+    <t>4403</t>
+  </si>
+  <si>
+    <t>Services Sociaux en Faveur des Personnes Âgées</t>
+  </si>
+  <si>
+    <t>4404</t>
+  </si>
+  <si>
+    <t>Etablissements Expérimentaux en Faveur des Personnes Âgées</t>
+  </si>
+  <si>
+    <t>4501</t>
+  </si>
+  <si>
+    <t>Etablissements de l'Aide Sociale à l'Enfance</t>
+  </si>
+  <si>
+    <t>4502</t>
+  </si>
+  <si>
+    <t>Etab.et Services du Ministère de la Justice pour Mineurs</t>
+  </si>
+  <si>
+    <t>4504</t>
+  </si>
+  <si>
+    <t>Services Concourant à la Protection de l'Enfance</t>
+  </si>
+  <si>
+    <t>4505</t>
+  </si>
+  <si>
+    <t>Etab. Expérimentaux en Faveur de l'Enfance Protégée</t>
+  </si>
+  <si>
+    <t>4601</t>
+  </si>
+  <si>
+    <t>Etablissements pour Adultes et Familles en Difficulté</t>
+  </si>
+  <si>
+    <t>4602</t>
+  </si>
+  <si>
+    <t>Autres Etablissements Sociaux d'Hébergement et d'Accueil</t>
+  </si>
+  <si>
+    <t>4603</t>
+  </si>
+  <si>
+    <t>Etablissements Expérimentaux en Faveur des Adultes</t>
+  </si>
+  <si>
+    <t>4604</t>
+  </si>
+  <si>
+    <t>Autres Etablissements médico-sociaux</t>
+  </si>
+  <si>
+    <t>4605</t>
+  </si>
+  <si>
+    <t>Etablissements et services multi-clientèles</t>
+  </si>
+  <si>
+    <t>4606</t>
+  </si>
+  <si>
+    <t>Centres de ressources</t>
+  </si>
+  <si>
+    <t>4607</t>
+  </si>
+  <si>
+    <t>Logements en Structure Collective</t>
+  </si>
+  <si>
+    <t>4608</t>
+  </si>
+  <si>
+    <t>Protection des majeurs</t>
+  </si>
+  <si>
+    <t>4609</t>
+  </si>
+  <si>
+    <t>Centres prestataires de services pr personnes cérébro-lésées</t>
+  </si>
+  <si>
+    <t>5101</t>
+  </si>
+  <si>
+    <t>Etablissements Garde d'Enfants d'Age pré-Scolaire</t>
+  </si>
+  <si>
+    <t>5102</t>
+  </si>
+  <si>
+    <t>Etablissements d'Hébergement pour Enfants d'Age Scolaire</t>
+  </si>
+  <si>
+    <t>5103</t>
+  </si>
+  <si>
+    <t>Etablissements Sociaux pour Loisirs et Vacances</t>
+  </si>
+  <si>
+    <t>5104</t>
+  </si>
+  <si>
+    <t>Etablissements ou Services Divers d'Aide à la Famille</t>
+  </si>
+  <si>
+    <t>6101</t>
+  </si>
+  <si>
+    <t>6102</t>
+  </si>
+  <si>
+    <t>Etablissements de Formation des Personnels Techniques</t>
+  </si>
+  <si>
+    <t>6103</t>
+  </si>
+  <si>
+    <t>Autres Etablissements de Formation des Personnels Techniques</t>
+  </si>
+  <si>
+    <t>6201</t>
+  </si>
+  <si>
+    <t>6301</t>
+  </si>
+  <si>
+    <t>001</t>
+  </si>
+  <si>
+    <t>Autres lits de m.R.</t>
+  </si>
+  <si>
+    <t>002</t>
+  </si>
+  <si>
+    <t>Autres places de l-f.</t>
+  </si>
+  <si>
+    <t>003</t>
+  </si>
+  <si>
+    <t>Autres lits de l-s</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>Centre Hospitalier Régional (C.H.R.)</t>
+  </si>
+  <si>
+    <t>106</t>
+  </si>
+  <si>
+    <t>Centre hospitalier, ex Hôpital local</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>Etablissement de Convalescence et de Repos</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>Etablissement de santé privé autorisé en SSR</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>Centre de Convalescence Cure ou Réadaptation</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>Hôpital des armées</t>
+  </si>
+  <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t>Etablissement de Soins du Service de Santé des Armées</t>
+  </si>
+  <si>
+    <t>119</t>
+  </si>
+  <si>
+    <t>Maison de Régime</t>
+  </si>
+  <si>
+    <t>122</t>
+  </si>
+  <si>
+    <t>Etablissement Soins Obstétriques Chirurgico-Gynécologiques</t>
+  </si>
+  <si>
+    <t>124</t>
+  </si>
+  <si>
+    <t>Centre de Santé</t>
+  </si>
+  <si>
+    <t>125</t>
+  </si>
+  <si>
+    <t>Centre de Santé Dentaire</t>
+  </si>
+  <si>
+    <t>126</t>
+  </si>
+  <si>
+    <t>Etablissement Thermal</t>
+  </si>
+  <si>
+    <t>127</t>
+  </si>
+  <si>
+    <t>Hospitalisation à Domicile</t>
+  </si>
+  <si>
+    <t>128</t>
+  </si>
+  <si>
+    <t>Etablissement de Soins Chirurgicaux</t>
+  </si>
+  <si>
+    <t>129</t>
+  </si>
+  <si>
+    <t>Etablissement de Soins Médicaux</t>
+  </si>
+  <si>
+    <t>130</t>
+  </si>
+  <si>
+    <t>Centre de Soins Médicaux</t>
+  </si>
+  <si>
+    <t>131</t>
+  </si>
+  <si>
+    <t>Centre de Lutte Contre Cancer</t>
+  </si>
+  <si>
+    <t>132</t>
+  </si>
+  <si>
+    <t>Etablissement de Transfusion Sanguine</t>
+  </si>
+  <si>
+    <t>135</t>
+  </si>
+  <si>
+    <t>Etablissement Réadaptation Fonctionnelle</t>
+  </si>
+  <si>
+    <t>136</t>
+  </si>
+  <si>
+    <t>Banque de Sperme</t>
+  </si>
+  <si>
+    <t>137</t>
+  </si>
+  <si>
+    <t>Banque d'Organes</t>
+  </si>
+  <si>
+    <t>138</t>
+  </si>
+  <si>
+    <t>Centre de Dialyse Périodique</t>
+  </si>
+  <si>
+    <t>139</t>
+  </si>
+  <si>
+    <t>Centre de Dialyse et d'entraînement à la Dialyse</t>
+  </si>
+  <si>
+    <t>140</t>
+  </si>
+  <si>
+    <t>Centre d'Entraînement à la Dialyse</t>
+  </si>
+  <si>
+    <t>141</t>
+  </si>
+  <si>
+    <t>Centre de dialyse</t>
+  </si>
+  <si>
+    <t>142</t>
+  </si>
+  <si>
+    <t>Dispensaire Antituberculeux</t>
+  </si>
+  <si>
+    <t>143</t>
+  </si>
+  <si>
+    <t>Centre de Vaccination BCG</t>
+  </si>
+  <si>
+    <t>144</t>
+  </si>
+  <si>
+    <t>Etablissement de Lutte Contre la Tuberculose</t>
+  </si>
+  <si>
+    <t>146</t>
+  </si>
+  <si>
+    <t>Structure d'Alternative à la dialyse en centre</t>
+  </si>
+  <si>
+    <t>156</t>
+  </si>
+  <si>
+    <t>Centre Médico-Psychologique (C.M.P.)</t>
+  </si>
+  <si>
+    <t>157</t>
+  </si>
+  <si>
+    <t>Centre de Postcure</t>
+  </si>
+  <si>
+    <t>159</t>
+  </si>
+  <si>
+    <t>Centre Parental</t>
+  </si>
+  <si>
+    <t>160</t>
+  </si>
+  <si>
+    <t>Centre de Soins Spécifiques pour Toxicomanes (C.S.S.T.)</t>
+  </si>
+  <si>
+    <t>161</t>
+  </si>
+  <si>
+    <t>Maison de Santé pour Maladies Mentales</t>
+  </si>
+  <si>
+    <t>162</t>
+  </si>
+  <si>
+    <t>Centre de Cure Ambulatoire en Alcoologie (C.C.A.A.)</t>
+  </si>
+  <si>
+    <t>163</t>
+  </si>
+  <si>
+    <t>Maison d'Enfants à Caractère Sanitaire Temporaire</t>
+  </si>
+  <si>
+    <t>164</t>
+  </si>
+  <si>
+    <t>Etablissements Expérimentaux Accueil de la Petite Enfance</t>
+  </si>
+  <si>
+    <t>165</t>
+  </si>
+  <si>
+    <t>Appartement de Coordination Thérapeutique (A.C.T.)</t>
+  </si>
+  <si>
+    <t>166</t>
+  </si>
+  <si>
+    <t>Centre Parents-Enfants de moins de 3 ans</t>
+  </si>
+  <si>
+    <t>167</t>
+  </si>
+  <si>
+    <t>Crèche Collective</t>
+  </si>
+  <si>
+    <t>168</t>
+  </si>
+  <si>
+    <t>Service Accueil Familial pour la Petite Enfance</t>
+  </si>
+  <si>
+    <t>169</t>
+  </si>
+  <si>
+    <t>Crèche Multi Accueil Collectif et Familial</t>
+  </si>
+  <si>
+    <t>170</t>
+  </si>
+  <si>
+    <t>Halte Garderie</t>
+  </si>
+  <si>
+    <t>171</t>
+  </si>
+  <si>
+    <t>Garderie et Jardin d'Enfants</t>
+  </si>
+  <si>
+    <t>172</t>
+  </si>
+  <si>
+    <t>Pouponnière à Caractère Social</t>
+  </si>
+  <si>
+    <t>173</t>
+  </si>
+  <si>
+    <t>Pouponnière à Caractère Sanitaire</t>
+  </si>
+  <si>
+    <t>174</t>
+  </si>
+  <si>
+    <t>Etablissement d'Accueil Collectif Régulier et Occasionnel</t>
+  </si>
+  <si>
+    <t>175</t>
+  </si>
+  <si>
+    <t>Foyer de l'Enfance</t>
+  </si>
+  <si>
+    <t>176</t>
+  </si>
+  <si>
+    <t>Village d'Enfants</t>
+  </si>
+  <si>
+    <t>177</t>
+  </si>
+  <si>
+    <t>Maison d'Enfants à Caractère Social</t>
+  </si>
+  <si>
+    <t>178</t>
+  </si>
+  <si>
+    <t>Ctre.Accueil- Accomp.Réduc.Risq.Usag. Drogues (C.A.A.R.U.D.)</t>
+  </si>
+  <si>
+    <t>179</t>
+  </si>
+  <si>
+    <t>Maison d'Enfants à Caractère Sanitaire Permanente</t>
+  </si>
+  <si>
+    <t>180</t>
+  </si>
+  <si>
+    <t>Lits Halte Soins Santé (L.H.S.S.)</t>
+  </si>
+  <si>
+    <t>181</t>
+  </si>
+  <si>
+    <t>Maison Familiale de Vacances</t>
+  </si>
+  <si>
+    <t>182</t>
+  </si>
+  <si>
+    <t>Service d'Éducation Spéciale et de Soins à Domicile</t>
+  </si>
+  <si>
+    <t>183</t>
+  </si>
+  <si>
+    <t>Institut Médico-Educatif (I.M.E.)</t>
+  </si>
+  <si>
+    <t>184</t>
+  </si>
+  <si>
+    <t>Institut Médico-Pédagogique (I.M.P.)</t>
+  </si>
+  <si>
+    <t>185</t>
+  </si>
+  <si>
+    <t>Institut Médico-Professionnel (I.M.Pro.)</t>
+  </si>
+  <si>
+    <t>186</t>
+  </si>
+  <si>
+    <t>Institut Thérapeutique Éducatif et Pédagogique (I.T.E.P.)</t>
+  </si>
+  <si>
+    <t>188</t>
+  </si>
+  <si>
+    <t>Etablissement pour Enfants ou Adolescents Polyhandicapés</t>
+  </si>
+  <si>
+    <t>189</t>
+  </si>
+  <si>
+    <t>Centre Médico-Psycho-Pédagogique (C.M.P.P.)</t>
+  </si>
+  <si>
+    <t>190</t>
+  </si>
+  <si>
+    <t>Centre Action Médico-Sociale Précoce (C.A.M.S.P.)</t>
+  </si>
+  <si>
+    <t>191</t>
+  </si>
+  <si>
+    <t>Etablissement pour Déficients Moteurs Cérébraux</t>
+  </si>
+  <si>
+    <t>192</t>
+  </si>
+  <si>
+    <t>Institut d'éducation motrice</t>
+  </si>
+  <si>
+    <t>193</t>
+  </si>
+  <si>
+    <t>Etablissement pour Déficients Moteurs et Moteurs Cérébraux</t>
+  </si>
+  <si>
+    <t>194</t>
+  </si>
+  <si>
+    <t>Institut pour Déficients Visuels</t>
+  </si>
+  <si>
+    <t>195</t>
+  </si>
+  <si>
+    <t>Institut pour Déficients Auditifs</t>
+  </si>
+  <si>
+    <t>196</t>
+  </si>
+  <si>
+    <t>Institut d'Education Sensorielle Sourd-Aveugle</t>
+  </si>
+  <si>
+    <t>197</t>
+  </si>
+  <si>
+    <t>Centre soins accompagnement prévention addictologie (CSAPA)</t>
+  </si>
+  <si>
+    <t>198</t>
+  </si>
+  <si>
+    <t>Établissement et Service de Préorientation</t>
+  </si>
+  <si>
+    <t>199</t>
+  </si>
+  <si>
+    <t>Hospice</t>
+  </si>
+  <si>
+    <t>200</t>
+  </si>
+  <si>
+    <t>Maison de Retraite</t>
+  </si>
+  <si>
+    <t>202</t>
+  </si>
+  <si>
+    <t>Résidences autonomie</t>
+  </si>
+  <si>
+    <t>205</t>
+  </si>
+  <si>
+    <t>Foyer Club Restaurant</t>
+  </si>
+  <si>
+    <t>207</t>
+  </si>
+  <si>
+    <t>Centre de Jour pour Personnes Agées</t>
+  </si>
+  <si>
+    <t>208</t>
+  </si>
+  <si>
+    <t>Service d'Aide Ménagère à Domicile</t>
+  </si>
+  <si>
+    <t>209</t>
+  </si>
+  <si>
+    <t>Service autonomie aide et soins (SAAS)</t>
+  </si>
+  <si>
+    <t>212</t>
+  </si>
+  <si>
+    <t>Alarme Médico-Sociale</t>
+  </si>
+  <si>
+    <t>213</t>
+  </si>
+  <si>
+    <t>Lits d'Accueil Médicalisés (L.A.M.)</t>
+  </si>
+  <si>
+    <t>214</t>
+  </si>
+  <si>
+    <t>Centre Hébergement &amp; Réinsertion Sociale (C.H.R.S.)</t>
+  </si>
+  <si>
+    <t>215</t>
+  </si>
+  <si>
+    <t>Maison Relai</t>
+  </si>
+  <si>
+    <t>216</t>
+  </si>
+  <si>
+    <t>Résidence Hôtelière à Vocation Sociale (R.H.V.S)</t>
+  </si>
+  <si>
+    <t>217</t>
+  </si>
+  <si>
+    <t>Cité de Transit</t>
+  </si>
+  <si>
+    <t>218</t>
+  </si>
+  <si>
+    <t>Aire Station Nomades</t>
+  </si>
+  <si>
+    <t>219</t>
+  </si>
+  <si>
+    <t>Autre Centre d'Accueil</t>
+  </si>
+  <si>
+    <t>220</t>
+  </si>
+  <si>
+    <t>Centre Social</t>
+  </si>
+  <si>
+    <t>221</t>
+  </si>
+  <si>
+    <t>Bureau d'Aide Psychologique Universitaire (B.A.P.U.)</t>
+  </si>
+  <si>
+    <t>223</t>
+  </si>
+  <si>
+    <t>Protection Maternelle et Infantile (P.M.I.)</t>
+  </si>
+  <si>
+    <t>224</t>
+  </si>
+  <si>
+    <t>Etablissement de Consultation Pré et Post-natale</t>
+  </si>
+  <si>
+    <t>225</t>
+  </si>
+  <si>
+    <t>Consultations de Nourrissons</t>
+  </si>
+  <si>
+    <t>228</t>
+  </si>
+  <si>
+    <t>Centre de Santé Sexuelle</t>
+  </si>
+  <si>
+    <t>229</t>
+  </si>
+  <si>
+    <t>Consultation Problèmes naissance</t>
+  </si>
+  <si>
+    <t>230</t>
+  </si>
+  <si>
+    <t>Etablissement Consultation Protection Infantile</t>
+  </si>
+  <si>
+    <t>231</t>
+  </si>
+  <si>
+    <t>Espaces de vie affective, relationnelle et sexuelle (EVARS)</t>
+  </si>
+  <si>
+    <t>233</t>
+  </si>
+  <si>
+    <t>Lactarium</t>
+  </si>
+  <si>
+    <t>236</t>
+  </si>
+  <si>
+    <t>Centre Placement Familial Socio-Educatif (C.P.F.S.E.)</t>
+  </si>
+  <si>
+    <t>237</t>
+  </si>
+  <si>
+    <t>Centre de Placement Familial Spécialisé</t>
+  </si>
+  <si>
+    <t>238</t>
+  </si>
+  <si>
+    <t>Centre d'Accueil Familial Spécialisé</t>
+  </si>
+  <si>
+    <t>241</t>
+  </si>
+  <si>
+    <t>Établissement de Placement</t>
+  </si>
+  <si>
+    <t>242</t>
+  </si>
+  <si>
+    <t>Service d’Activité de Jour</t>
+  </si>
+  <si>
+    <t>246</t>
+  </si>
+  <si>
+    <t>Etablissement et Service d'Aide par le Travail (E.S.A.T.)</t>
+  </si>
+  <si>
+    <t>247</t>
+  </si>
+  <si>
+    <t>Entreprise adaptée</t>
+  </si>
+  <si>
+    <t>249</t>
+  </si>
+  <si>
+    <t>Établissement et Service de Réadaptation Professionnelle</t>
+  </si>
+  <si>
+    <t>250</t>
+  </si>
+  <si>
+    <t>Centre Réentrainement au travail</t>
+  </si>
+  <si>
+    <t>251</t>
+  </si>
+  <si>
+    <t>Maison Vacances pour Handicapés</t>
+  </si>
+  <si>
+    <t>252</t>
+  </si>
+  <si>
+    <t>Foyer Hébergement Adultes Handicapés</t>
+  </si>
+  <si>
+    <t>253</t>
+  </si>
+  <si>
+    <t>Foyer d'Accueil Polyvalent pour Adultes Handicapés</t>
+  </si>
+  <si>
+    <t>255</t>
+  </si>
+  <si>
+    <t>Maison d'Accueil Spécialisée (M.A.S.)</t>
+  </si>
+  <si>
+    <t>256</t>
+  </si>
+  <si>
+    <t>Foyer Travailleurs Migrants non transformé en Résidence Soc.</t>
+  </si>
+  <si>
+    <t>257</t>
+  </si>
+  <si>
+    <t>Foyers de jeunes travailleurs</t>
+  </si>
+  <si>
+    <t>258</t>
+  </si>
+  <si>
+    <t>Maisons Relais - Pensions de Famille</t>
+  </si>
+  <si>
+    <t>259</t>
+  </si>
+  <si>
+    <t>Autres résidences sociales</t>
+  </si>
+  <si>
+    <t>261</t>
+  </si>
+  <si>
+    <t>D.D.A.S.S.</t>
+  </si>
+  <si>
+    <t>262</t>
+  </si>
+  <si>
+    <t>Etablissement Régional d'Enseignement Adapté</t>
+  </si>
+  <si>
+    <t>265</t>
+  </si>
+  <si>
+    <t>Section Education Spéciale Classe Atelier</t>
+  </si>
+  <si>
+    <t>266</t>
+  </si>
+  <si>
+    <t>Dispensaire Antivénérien</t>
+  </si>
+  <si>
+    <t>267</t>
+  </si>
+  <si>
+    <t>Dispensaire Antihansénien</t>
+  </si>
+  <si>
+    <t>268</t>
+  </si>
+  <si>
+    <t>Centre Médico-Scolaire</t>
+  </si>
+  <si>
+    <t>269</t>
+  </si>
+  <si>
+    <t>Centre de Médecine Universitaire</t>
+  </si>
+  <si>
+    <t>270</t>
+  </si>
+  <si>
+    <t>Centre de Médecine Sportive</t>
+  </si>
+  <si>
+    <t>271</t>
+  </si>
+  <si>
+    <t>Maison d'accueil Hospitalière</t>
+  </si>
+  <si>
+    <t>272</t>
+  </si>
+  <si>
+    <t>Ecole d'ambulanciers</t>
+  </si>
+  <si>
+    <t>273</t>
+  </si>
+  <si>
+    <t>Institut de formation en soins infirmiers (I.F.S.I.)</t>
+  </si>
+  <si>
+    <t>274</t>
+  </si>
+  <si>
+    <t>Ecole de sages_femmes</t>
+  </si>
+  <si>
+    <t>275</t>
+  </si>
+  <si>
+    <t>Ecole de masseurs-kinésithérapeutes</t>
+  </si>
+  <si>
+    <t>276</t>
+  </si>
+  <si>
+    <t>Ecole de laborantins d'analyses médicales</t>
+  </si>
+  <si>
+    <t>277</t>
+  </si>
+  <si>
+    <t>Ecole de péricultrices</t>
+  </si>
+  <si>
+    <t>278</t>
+  </si>
+  <si>
+    <t>Etablissement de formation polyvalent</t>
+  </si>
+  <si>
+    <t>279</t>
+  </si>
+  <si>
+    <t>Ecole de service social</t>
+  </si>
+  <si>
+    <t>280</t>
+  </si>
+  <si>
+    <t>Ecole d'éducateurs spécialisés</t>
+  </si>
+  <si>
+    <t>281</t>
+  </si>
+  <si>
+    <t>Centre de formation d'aides soignants</t>
+  </si>
+  <si>
+    <t>282</t>
+  </si>
+  <si>
+    <t>Ecole de pédicures-podologues</t>
+  </si>
+  <si>
+    <t>283</t>
+  </si>
+  <si>
+    <t>Ecole de manipulateurs d'électro-radiologie</t>
+  </si>
+  <si>
+    <t>284</t>
+  </si>
+  <si>
+    <t>Ecole de travailleuses familiales</t>
+  </si>
+  <si>
+    <t>285</t>
+  </si>
+  <si>
+    <t>Centres de Loisirs sans Hébergement</t>
+  </si>
+  <si>
+    <t>286</t>
+  </si>
+  <si>
+    <t>Service de prévention spécialisée</t>
+  </si>
+  <si>
+    <t>289</t>
+  </si>
+  <si>
+    <t>Centre de Soins Infirmiers</t>
+  </si>
+  <si>
+    <t>292</t>
+  </si>
+  <si>
+    <t>Centre Hospitalier Spécialisé lutte Maladies Mentales</t>
+  </si>
+  <si>
+    <t>294</t>
+  </si>
+  <si>
+    <t>Centre de Consultations Cancer</t>
+  </si>
+  <si>
+    <t>295</t>
+  </si>
+  <si>
+    <t>Service AEMO et AED</t>
+  </si>
+  <si>
+    <t>297</t>
+  </si>
+  <si>
+    <t>Dispensaire Polyvalent</t>
+  </si>
+  <si>
+    <t>300</t>
+  </si>
+  <si>
+    <t>Ecoles Formant aux Professions Sanitaires</t>
+  </si>
+  <si>
+    <t>303</t>
+  </si>
+  <si>
+    <t>Ecole de conseillers en économie sociale et familiale</t>
+  </si>
+  <si>
+    <t>304</t>
+  </si>
+  <si>
+    <t>Ecole d'ergothérapeutes</t>
+  </si>
+  <si>
+    <t>305</t>
+  </si>
+  <si>
+    <t>Ecole de psycho-motriciens</t>
+  </si>
+  <si>
+    <t>306</t>
+  </si>
+  <si>
+    <t>Ecole d'infirmiers anesthésistes</t>
+  </si>
+  <si>
+    <t>307</t>
+  </si>
+  <si>
+    <t>Ecole d'infirmiers de bloc opératoire</t>
+  </si>
+  <si>
+    <t>308</t>
+  </si>
+  <si>
+    <t>Centre de formation professionnelle de secteur psychiatrique</t>
+  </si>
+  <si>
+    <t>309</t>
+  </si>
+  <si>
+    <t>Ecole de cadres infirmiers</t>
+  </si>
+  <si>
+    <t>310</t>
+  </si>
+  <si>
+    <t>Ecole de cadres de secteur psychiatrique</t>
+  </si>
+  <si>
+    <t>311</t>
+  </si>
+  <si>
+    <t>Ecole de cadres de masseurs-kinésithérapeutes</t>
+  </si>
+  <si>
+    <t>312</t>
+  </si>
+  <si>
+    <t>Ecole de cadres de manipulateurs d'électro-radiologie</t>
+  </si>
+  <si>
+    <t>313</t>
+  </si>
+  <si>
+    <t>Ecole d'éducateurs de jeunes enfants</t>
+  </si>
+  <si>
+    <t>314</t>
+  </si>
+  <si>
+    <t>Ecole d'éducateurs techniques spécialisés</t>
+  </si>
+  <si>
+    <t>315</t>
+  </si>
+  <si>
+    <t>Ecole de moniteurs-éducateurs</t>
+  </si>
+  <si>
+    <t>316</t>
+  </si>
+  <si>
+    <t>Ecole d'aides médico-psychologiques</t>
+  </si>
+  <si>
+    <t>317</t>
+  </si>
+  <si>
+    <t>Ecole d'animateurs socio-éducatifs</t>
+  </si>
+  <si>
+    <t>319</t>
+  </si>
+  <si>
+    <t>Inst. régional de formation des travailleurs sociaux</t>
+  </si>
+  <si>
+    <t>320</t>
+  </si>
+  <si>
+    <t>S.A.M.U. et Centre 15</t>
+  </si>
+  <si>
+    <t>321</t>
+  </si>
+  <si>
+    <t>Unité Mobile Hospitalière</t>
+  </si>
+  <si>
+    <t>322</t>
+  </si>
+  <si>
+    <t>Centre Rég.Informatiq.Hospit.</t>
+  </si>
+  <si>
+    <t>324</t>
+  </si>
+  <si>
+    <t>Logement Foyer non Spécialisé</t>
+  </si>
+  <si>
+    <t>326</t>
+  </si>
+  <si>
+    <t>Ecole de cadres</t>
+  </si>
+  <si>
+    <t>327</t>
+  </si>
+  <si>
+    <t>328</t>
+  </si>
+  <si>
+    <t>Centre Consultation Soins Dentaire</t>
+  </si>
+  <si>
+    <t>329</t>
+  </si>
+  <si>
+    <t>Sectorisation Psychiatrique</t>
+  </si>
+  <si>
+    <t>330</t>
+  </si>
+  <si>
+    <t>Ecoles Formant aux Professions Sociales</t>
+  </si>
+  <si>
+    <t>340</t>
+  </si>
+  <si>
+    <t>Service mandataire judiciaire à la protection des majeurs</t>
+  </si>
+  <si>
+    <t>341</t>
+  </si>
+  <si>
+    <t>Service dédié mesures d'accompagnement social personnalisé</t>
+  </si>
+  <si>
+    <t>342</t>
+  </si>
+  <si>
+    <t>Service d'information et de soutien aux tuteurs familiaux</t>
+  </si>
+  <si>
+    <t>343</t>
+  </si>
+  <si>
+    <t>Equipe Préparation et Suite Reclassement (EPSR)</t>
+  </si>
+  <si>
+    <t>344</t>
+  </si>
+  <si>
+    <t>Service délégué aux prestations familiales</t>
+  </si>
+  <si>
+    <t>345</t>
+  </si>
+  <si>
+    <t>Service Tutelle Prestation Sociale</t>
+  </si>
+  <si>
+    <t>346</t>
+  </si>
+  <si>
+    <t>Service de Travailleuses Familiales</t>
+  </si>
+  <si>
+    <t>347</t>
+  </si>
+  <si>
+    <t>Centre d'Examens de Santé</t>
+  </si>
+  <si>
+    <t>349</t>
+  </si>
+  <si>
+    <t>Ecole de cadres de sages-femmes</t>
+  </si>
+  <si>
+    <t>350</t>
+  </si>
+  <si>
+    <t>Centre de formation d'auxiliaires de puériculture</t>
+  </si>
+  <si>
+    <t>352</t>
+  </si>
+  <si>
+    <t>Centre de Psychothérapie</t>
+  </si>
+  <si>
+    <t>353</t>
+  </si>
+  <si>
+    <t>Hôpital de Jour Spécialités Médicales</t>
+  </si>
+  <si>
+    <t>354</t>
+  </si>
+  <si>
+    <t>Service de Soins Infirmiers A Domicile (S.S.I.A.D)</t>
+  </si>
+  <si>
+    <t>355</t>
+  </si>
+  <si>
+    <t>Centre Hospitalier (C.H.)</t>
+  </si>
+  <si>
+    <t>357</t>
+  </si>
+  <si>
+    <t>Association Aide aux Insuffisants Respiratoires</t>
+  </si>
+  <si>
+    <t>359</t>
+  </si>
+  <si>
+    <t>Centre Circonscription Sanitaire et Sociale</t>
+  </si>
+  <si>
+    <t>361</t>
+  </si>
+  <si>
+    <t>Centre de Cure Médicale</t>
+  </si>
+  <si>
+    <t>362</t>
+  </si>
+  <si>
+    <t>Etablissement de Soins Longue Durée</t>
+  </si>
+  <si>
+    <t>363</t>
+  </si>
+  <si>
+    <t>Centre moyen et long séjour</t>
+  </si>
+  <si>
+    <t>365</t>
+  </si>
+  <si>
+    <t>Etablissement de Soins Pluridisciplinaire</t>
+  </si>
+  <si>
+    <t>366</t>
+  </si>
+  <si>
+    <t>Atelier Thérapeutique</t>
+  </si>
+  <si>
+    <t>367</t>
+  </si>
+  <si>
+    <t>Maison d'Enfants non Conventionnée ni Habilitée</t>
+  </si>
+  <si>
+    <t>368</t>
+  </si>
+  <si>
+    <t>Service de Repas à Domicile</t>
+  </si>
+  <si>
+    <t>369</t>
+  </si>
+  <si>
+    <t>Centre Adaptation Vie Active (C.A.V.A.)</t>
+  </si>
+  <si>
+    <t>370</t>
+  </si>
+  <si>
+    <t>Etablissement Expérimental pour personnes handicapées</t>
+  </si>
+  <si>
+    <t>371</t>
+  </si>
+  <si>
+    <t>Service Action Socio-Educative pour Familles en difficulté</t>
+  </si>
+  <si>
+    <t>373</t>
+  </si>
+  <si>
+    <t>Centre de formation supérieure des travailleurs sociaux</t>
+  </si>
+  <si>
+    <t>374</t>
+  </si>
+  <si>
+    <t>Ecole Nationale Santé Publique (E.N.S.P.)</t>
+  </si>
+  <si>
+    <t>375</t>
+  </si>
+  <si>
+    <t>Classe d'Adaptation</t>
+  </si>
+  <si>
+    <t>376</t>
+  </si>
+  <si>
+    <t>Classe Spéciale Ecole Primaire</t>
+  </si>
+  <si>
+    <t>377</t>
+  </si>
+  <si>
+    <t>Etablissement Expérimental pour Enfance Handicapée</t>
+  </si>
+  <si>
+    <t>378</t>
+  </si>
+  <si>
+    <t>Etablissement Expérimental Enfance Protégée</t>
+  </si>
+  <si>
+    <t>379</t>
+  </si>
+  <si>
+    <t>Etablissement Expérimental pour Adultes Handicapés</t>
+  </si>
+  <si>
+    <t>380</t>
+  </si>
+  <si>
+    <t>Etablissement Expérimental Autres Adultes</t>
+  </si>
+  <si>
+    <t>381</t>
+  </si>
+  <si>
+    <t>Etablissement Expérimental pour Personnes Agées</t>
+  </si>
+  <si>
+    <t>382</t>
+  </si>
+  <si>
+    <t>Foyer de Vie pour Adultes Handicapés</t>
+  </si>
+  <si>
+    <t>386</t>
+  </si>
+  <si>
+    <t>Ecole Secondaire Spéciale</t>
+  </si>
+  <si>
+    <t>390</t>
+  </si>
+  <si>
+    <t>Etablissement d'Accueil Temporaire d'Enfants Handicapés</t>
+  </si>
+  <si>
+    <t>393</t>
+  </si>
+  <si>
+    <t>Autre résidence But lucratif pr personnes Âgées</t>
+  </si>
+  <si>
+    <t>394</t>
+  </si>
+  <si>
+    <t>Etablissement d'Accueil Temporaire pour Personnes Agées</t>
+  </si>
+  <si>
+    <t>395</t>
+  </si>
+  <si>
+    <t>Etablissement d'Accueil Temporaire pour Adultes Handicapés</t>
+  </si>
+  <si>
+    <t>396</t>
+  </si>
+  <si>
+    <t>Foyer Hébergement Enfants et Adolescents Handicapés</t>
+  </si>
+  <si>
+    <t>397</t>
+  </si>
+  <si>
+    <t>Service Auxiliaire de Vie pour Handicapés</t>
+  </si>
+  <si>
+    <t>398</t>
+  </si>
+  <si>
+    <t>Crèche Parentale</t>
+  </si>
+  <si>
+    <t>399</t>
+  </si>
+  <si>
+    <t>Halte Garderie Parentale</t>
+  </si>
+  <si>
+    <t>400</t>
+  </si>
+  <si>
+    <t>Centre de Services pour Associations</t>
+  </si>
+  <si>
+    <t>401</t>
+  </si>
+  <si>
+    <t>D.R.A.S.S.</t>
+  </si>
+  <si>
+    <t>402</t>
+  </si>
+  <si>
+    <t>Jardin d'Enfants Spécialisé</t>
+  </si>
+  <si>
+    <t>403</t>
+  </si>
+  <si>
+    <t>Service Social Spécialisé ou Polyvalent de Catégorie</t>
+  </si>
+  <si>
+    <t>404</t>
+  </si>
+  <si>
+    <t>Etablissement Acc.Collect.Parental Régulier &amp; Occasionnel</t>
+  </si>
+  <si>
+    <t>405</t>
+  </si>
+  <si>
+    <t>Service Social Polyvalent de Secteur</t>
+  </si>
+  <si>
+    <t>411</t>
+  </si>
+  <si>
+    <t>Intermédiaire de Placement Social</t>
+  </si>
+  <si>
+    <t>412</t>
+  </si>
+  <si>
+    <t>Appartement Thérapeutique</t>
+  </si>
+  <si>
+    <t>413</t>
+  </si>
+  <si>
+    <t>C.E.C.O.S</t>
+  </si>
+  <si>
+    <t>414</t>
+  </si>
+  <si>
+    <t>Centre Anti Poison</t>
+  </si>
+  <si>
+    <t>415</t>
+  </si>
+  <si>
+    <t>Service Médico-Psychologique Régional (S.M.P.R.)</t>
+  </si>
+  <si>
+    <t>418</t>
+  </si>
+  <si>
+    <t>Service d'Enquêtes Sociales (S.E.S.)</t>
+  </si>
+  <si>
+    <t>419</t>
+  </si>
+  <si>
+    <t>Centre d'Accueil Toxicomanes</t>
+  </si>
+  <si>
+    <t>420</t>
+  </si>
+  <si>
+    <t>Entreprise d'Insertion</t>
+  </si>
+  <si>
+    <t>421</t>
+  </si>
+  <si>
+    <t>Centre d'enseignement aux secours d'urgence</t>
+  </si>
+  <si>
+    <t>422</t>
+  </si>
+  <si>
+    <t>Traitements Spécialisés à Domicile</t>
+  </si>
+  <si>
+    <t>423</t>
+  </si>
+  <si>
+    <t>Ecole des cadres de laborantins d'analyses médicales</t>
+  </si>
+  <si>
+    <t>425</t>
+  </si>
+  <si>
+    <t>Centre d'Accueil Thérapeutique à temps partiel (C.A.T.T.P.)</t>
+  </si>
+  <si>
+    <t>426</t>
+  </si>
+  <si>
+    <t>Syndicat Inter Hospitalier (S.I.H.)</t>
+  </si>
+  <si>
     <t>427</t>
   </si>
   <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>Uri</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>niveau</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/concept-properties#niveau</t>
-  </si>
-  <si>
-    <t>Permet d'indiquer le niveau hiérarchique du code</t>
-  </si>
-  <si>
-    <t>integer</t>
-  </si>
-  <si>
-    <t>parent</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/concept-properties#parent</t>
-  </si>
-  <si>
-    <t>An immediate parent of the concept in the hierarchy</t>
-  </si>
-  <si>
-    <t>code</t>
-  </si>
-  <si>
-    <t>domaine</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/concept-properties#domaine</t>
-  </si>
-  <si>
-    <t>Domaine de la categorie d etablissement</t>
-  </si>
-  <si>
-    <t>Coding</t>
-  </si>
-  <si>
-    <t>dateValid</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateValid</t>
-  </si>
-  <si>
-    <t>date de validité d'un code concept</t>
-  </si>
-  <si>
-    <t>dateTime</t>
-  </si>
-  <si>
-    <t>dateMaj</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateMaj</t>
-  </si>
-  <si>
-    <t>Date de mise à jour d'un code concept</t>
-  </si>
-  <si>
-    <t>dateFin</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateFin</t>
-  </si>
-  <si>
-    <t>Date de fin d'exploitation d'un code concept</t>
-  </si>
-  <si>
-    <t>status</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/concept-properties#status</t>
-  </si>
-  <si>
-    <t>A property that indicates the status of the concept.</t>
-  </si>
-  <si>
-    <t>deprecationDate</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/concept-properties#deprecationDate</t>
-  </si>
-  <si>
-    <t>Date Concept was deprecated</t>
-  </si>
-  <si>
-    <t>retirementDate</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/concept-properties#retirementDate</t>
-  </si>
-  <si>
-    <t>Date Concept was retired</t>
-  </si>
-  <si>
-    <t>specialisationRor</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/concept-properties#specialisationRor</t>
-  </si>
-  <si>
-    <t>Propriété permettant de spécifier les codes exclusifs appartenant au ROR</t>
-  </si>
-  <si>
-    <t>boolean</t>
-  </si>
-  <si>
-    <t>ror</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/concept-properties#ror</t>
-  </si>
-  <si>
-    <t>Permet de définir les codes concepts uilisés par le ROR</t>
-  </si>
-  <si>
-    <t>cisis</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/concept-properties#cisis</t>
-  </si>
-  <si>
-    <t>Permet de définir les codes concepts uilisés par le CISIS</t>
-  </si>
-  <si>
-    <t>rass</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/concept-properties#rass</t>
-  </si>
-  <si>
-    <t>Permet de définir les codes concepts uilisés par le RASS</t>
-  </si>
-  <si>
-    <t>Level</t>
-  </si>
-  <si>
-    <t>Display</t>
-  </si>
-  <si>
-    <t>Definition</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>0100</t>
-  </si>
-  <si>
-    <t>Etablissements d'administration</t>
-  </si>
-  <si>
-    <t>1000</t>
-  </si>
-  <si>
-    <t>Etablissements Relevant de la Loi Hospitalière</t>
-  </si>
-  <si>
-    <t>2000</t>
-  </si>
-  <si>
-    <t>Autres Etablissements de Soins et Prévention</t>
-  </si>
-  <si>
-    <t>3000</t>
-  </si>
-  <si>
-    <t>Autres Etablissements à Caractère Sanitaire</t>
-  </si>
-  <si>
-    <t>4000</t>
-  </si>
-  <si>
-    <t>Etab.Serv.Soc.d'Accueil Hébergement Assistance Réadaptation</t>
-  </si>
-  <si>
-    <t>5000</t>
-  </si>
-  <si>
-    <t>Etablissements et Services Sociaux d'Aide à la Famille</t>
-  </si>
-  <si>
-    <t>6000</t>
-  </si>
-  <si>
-    <t>Etab.de Formation des Personnels Sanitaires et Sociaux</t>
-  </si>
-  <si>
-    <t>0110</t>
-  </si>
-  <si>
-    <t>Etablissements d'Administration</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>1100</t>
-  </si>
-  <si>
-    <t>Etablissements Hospitaliers</t>
-  </si>
-  <si>
-    <t>1200</t>
-  </si>
-  <si>
-    <t>Autres Etablissements Relevant de la Loi Hospitalière</t>
-  </si>
-  <si>
-    <t>2100</t>
-  </si>
-  <si>
-    <t>Cabinets Libéraux</t>
-  </si>
-  <si>
-    <t>2200</t>
-  </si>
-  <si>
-    <t>3100</t>
-  </si>
-  <si>
-    <t>Laboratoires de Biologie Médicale</t>
-  </si>
-  <si>
-    <t>3200</t>
-  </si>
-  <si>
-    <t>Commerce de Biens à Usage Médicaux</t>
-  </si>
-  <si>
-    <t>3400</t>
-  </si>
-  <si>
-    <t>4100</t>
-  </si>
-  <si>
-    <t>Etab.et Serv.pour l'Enfance et la Jeunesse Handicapée</t>
-  </si>
-  <si>
-    <t>4200</t>
-  </si>
-  <si>
-    <t>Etablissements ou Classes d'Enseignement Spécial</t>
-  </si>
-  <si>
-    <t>4300</t>
-  </si>
-  <si>
-    <t>Etablissements et Services pour Adultes Handicapés</t>
-  </si>
-  <si>
-    <t>4400</t>
-  </si>
-  <si>
-    <t>Etablissements et Services pour Personnes Agées</t>
-  </si>
-  <si>
-    <t>4500</t>
-  </si>
-  <si>
-    <t>Etab.et Serv.Sociaux Concourant à la Protection de l'Enfance</t>
-  </si>
-  <si>
-    <t>4600</t>
-  </si>
-  <si>
-    <t>Autres Etab. Accueil, Hébergement, Réadaptation et Services</t>
-  </si>
-  <si>
-    <t>5100</t>
-  </si>
-  <si>
-    <t>6100</t>
-  </si>
-  <si>
-    <t>Etablissements de Formation des Personnels Sanitaires</t>
-  </si>
-  <si>
-    <t>6200</t>
-  </si>
-  <si>
-    <t>Etablissements de Formation des Personnels Sociaux</t>
-  </si>
-  <si>
-    <t>6300</t>
-  </si>
-  <si>
-    <t>Etablissements de Formation Polyvalente</t>
-  </si>
-  <si>
-    <t>0101</t>
-  </si>
-  <si>
-    <t>1101</t>
-  </si>
-  <si>
-    <t>Centres Hospitaliers Régionaux</t>
-  </si>
-  <si>
-    <t>1102</t>
-  </si>
-  <si>
-    <t>Centres Hospitaliers</t>
-  </si>
-  <si>
-    <t>1103</t>
-  </si>
-  <si>
-    <t>Centres Hospitaliers Spécialisés Lutte Maladies Mentales</t>
-  </si>
-  <si>
-    <t>1104</t>
-  </si>
-  <si>
-    <t>Centres de Lutte contre le Cancer</t>
-  </si>
-  <si>
-    <t>1106</t>
-  </si>
-  <si>
-    <t>Hôpitaux Locaux</t>
-  </si>
-  <si>
-    <t>1107</t>
-  </si>
-  <si>
-    <t>Etablissements de santé privé autorisés en SSR</t>
-  </si>
-  <si>
-    <t>1108</t>
-  </si>
-  <si>
-    <t>Centre de Moyen et de Long Séjour</t>
-  </si>
-  <si>
-    <t>1109</t>
-  </si>
-  <si>
-    <t>Etablissements de Soins de Longue Durée</t>
-  </si>
-  <si>
-    <t>1110</t>
-  </si>
-  <si>
-    <t>Etablissements de Soins de Courte Durée</t>
-  </si>
-  <si>
-    <t>1111</t>
-  </si>
-  <si>
-    <t>Autres Etablissements de Lutte contre les Maladies Mentales</t>
-  </si>
-  <si>
-    <t>1112</t>
-  </si>
-  <si>
-    <t>Etablissements d'Enfants à Caractère Sanitaire</t>
-  </si>
-  <si>
-    <t>1113</t>
-  </si>
-  <si>
-    <t>Etablissements de Lutte contre l'Alcoolisme</t>
-  </si>
-  <si>
-    <t>1201</t>
-  </si>
-  <si>
-    <t>Traitements et Soins à Domicile</t>
-  </si>
-  <si>
-    <t>1202</t>
-  </si>
-  <si>
-    <t>Santé Mentale</t>
-  </si>
-  <si>
-    <t>1203</t>
-  </si>
-  <si>
-    <t>Dialyse ambulatoire</t>
-  </si>
-  <si>
-    <t>1204</t>
-  </si>
-  <si>
-    <t>Urgence et Réanimation</t>
-  </si>
-  <si>
-    <t>1205</t>
-  </si>
-  <si>
-    <t>2101</t>
-  </si>
-  <si>
-    <t>Cabinets Libéraux de Médecins</t>
-  </si>
-  <si>
-    <t>2102</t>
-  </si>
-  <si>
-    <t>Cabinet de Groupe</t>
-  </si>
-  <si>
-    <t>2103</t>
-  </si>
-  <si>
-    <t>Autres structures d'exercice libéral</t>
-  </si>
-  <si>
-    <t>2105</t>
-  </si>
-  <si>
-    <t>Cabinet d'Auxiliaires Médicaux</t>
-  </si>
-  <si>
-    <t>2201</t>
-  </si>
-  <si>
-    <t>Dispensaires ou Centres de Soins</t>
-  </si>
-  <si>
-    <t>2202</t>
-  </si>
-  <si>
-    <t>Etablissements de PMI et de Planification Familiale</t>
-  </si>
-  <si>
-    <t>2203</t>
-  </si>
-  <si>
-    <t>Etablissements de Soins Dentaires</t>
-  </si>
-  <si>
-    <t>2204</t>
-  </si>
-  <si>
-    <t>Etablissements ne relevant pas de la Loi Hospitalière</t>
-  </si>
-  <si>
-    <t>2205</t>
-  </si>
-  <si>
-    <t>Etab.de soins relevant du service de santé des armées</t>
-  </si>
-  <si>
-    <t>2206</t>
-  </si>
-  <si>
-    <t>Centres de Santé</t>
-  </si>
-  <si>
-    <t>3101</t>
-  </si>
-  <si>
-    <t>3201</t>
-  </si>
-  <si>
-    <t>3202</t>
-  </si>
-  <si>
-    <t>Commerce de Biens Médicaux</t>
-  </si>
-  <si>
-    <t>3401</t>
-  </si>
-  <si>
-    <t>Transfusion Sanguine</t>
-  </si>
-  <si>
-    <t>3402</t>
-  </si>
-  <si>
-    <t>Conservation et Stockage d'autres Produits Humains</t>
-  </si>
-  <si>
-    <t>3403</t>
-  </si>
-  <si>
-    <t>Centre Antipoison</t>
-  </si>
-  <si>
-    <t>3404</t>
-  </si>
-  <si>
-    <t>Service d'Ambulances</t>
-  </si>
-  <si>
-    <t>3405</t>
-  </si>
-  <si>
-    <t>Installations autonomes de chirurgie esthétique</t>
-  </si>
-  <si>
-    <t>3406</t>
-  </si>
-  <si>
-    <t>Maisons de Naissance</t>
-  </si>
-  <si>
-    <t>3407</t>
-  </si>
-  <si>
-    <t>Etablissements Expérimentaux en Santé</t>
-  </si>
-  <si>
-    <t>3408</t>
-  </si>
-  <si>
-    <t>Centre de ressources transverse</t>
-  </si>
-  <si>
-    <t>3409</t>
-  </si>
-  <si>
-    <t>Services de Prévention et de Santé au Travail (SPST)</t>
-  </si>
-  <si>
-    <t>3410</t>
-  </si>
-  <si>
-    <t>Services d'incendie et de secours</t>
-  </si>
-  <si>
-    <t>4101</t>
-  </si>
-  <si>
-    <t>Etab.Educ.Spéciale pour Déficients Mentaux et Handicapés</t>
-  </si>
-  <si>
-    <t>4102</t>
-  </si>
-  <si>
-    <t>Etab.Educ Spéciale pour Enfants Trouble Conduite et Comport</t>
-  </si>
-  <si>
-    <t>4103</t>
-  </si>
-  <si>
-    <t>Etablissements d'Education Spéciale pour Handicapés Moteurs</t>
-  </si>
-  <si>
-    <t>4104</t>
-  </si>
-  <si>
-    <t>Etab.Education Spéciale pour Déficients Sensoriels</t>
-  </si>
-  <si>
-    <t>4105</t>
-  </si>
-  <si>
-    <t>Etablissements et Services Hébergement Enfants Handicapés</t>
-  </si>
-  <si>
-    <t>4106</t>
-  </si>
-  <si>
-    <t>Services à Domicile ou Ambulatoires pour Handicapés</t>
-  </si>
-  <si>
-    <t>4107</t>
-  </si>
-  <si>
-    <t>Etab. Expérimentaux en Faveur de l'Enfance Handicapée</t>
-  </si>
-  <si>
-    <t>4201</t>
-  </si>
-  <si>
-    <t>Etablissements ou Classes de Pré-Élémentaire et Élémentaire</t>
-  </si>
-  <si>
-    <t>4202</t>
-  </si>
-  <si>
-    <t>Etablissements d'Enseignement Secondaire</t>
-  </si>
-  <si>
-    <t>4301</t>
-  </si>
-  <si>
-    <t>Etab. et Services d'Hébergement pour Adultes Handicapés</t>
-  </si>
-  <si>
-    <t>4302</t>
-  </si>
-  <si>
-    <t>Etab.et Services de Travail Protégé pour Adultes Handicapés</t>
-  </si>
-  <si>
-    <t>4303</t>
-  </si>
-  <si>
-    <t>Etab.et Services de Réinsertion Prof pour Adultes Handicapés</t>
-  </si>
-  <si>
-    <t>4304</t>
-  </si>
-  <si>
-    <t>Etab.Expérimentaux en Faveur des Adultes Handicapés</t>
-  </si>
-  <si>
-    <t>4305</t>
-  </si>
-  <si>
-    <t>Services de Maintien à Domicile pour Handicapés</t>
-  </si>
-  <si>
-    <t>4401</t>
-  </si>
-  <si>
-    <t>Etablissements d'Hébergement pour Personnes Âgées</t>
-  </si>
-  <si>
-    <t>4402</t>
-  </si>
-  <si>
-    <t>Services de Maintien à Domicile pour Personnes Âgées</t>
-  </si>
-  <si>
-    <t>4403</t>
-  </si>
-  <si>
-    <t>Services Sociaux en Faveur des Personnes Âgées</t>
-  </si>
-  <si>
-    <t>4404</t>
-  </si>
-  <si>
-    <t>Etablissements Expérimentaux en Faveur des Personnes Âgées</t>
-  </si>
-  <si>
-    <t>4501</t>
-  </si>
-  <si>
-    <t>Etablissements de l'Aide Sociale à l'Enfance</t>
-  </si>
-  <si>
-    <t>4502</t>
-  </si>
-  <si>
-    <t>Etab.et Services du Ministère de la Justice pour Mineurs</t>
-  </si>
-  <si>
-    <t>4504</t>
-  </si>
-  <si>
-    <t>Services Concourant à la Protection de l'Enfance</t>
-  </si>
-  <si>
-    <t>4505</t>
-  </si>
-  <si>
-    <t>Etab. Expérimentaux en Faveur de l'Enfance Protégée</t>
-  </si>
-  <si>
-    <t>4601</t>
-  </si>
-  <si>
-    <t>Etablissements pour Adultes et Familles en Difficulté</t>
-  </si>
-  <si>
-    <t>4602</t>
-  </si>
-  <si>
-    <t>Autres Etablissements Sociaux d'Hébergement et d'Accueil</t>
-  </si>
-  <si>
-    <t>4603</t>
-  </si>
-  <si>
-    <t>Etablissements Expérimentaux en Faveur des Adultes</t>
-  </si>
-  <si>
-    <t>4604</t>
-  </si>
-  <si>
-    <t>Autres Etablissements médico-sociaux</t>
-  </si>
-  <si>
-    <t>4605</t>
-  </si>
-  <si>
-    <t>Etablissements et services multi-clientèles</t>
-  </si>
-  <si>
-    <t>4606</t>
-  </si>
-  <si>
-    <t>Centres de ressources</t>
-  </si>
-  <si>
-    <t>4607</t>
-  </si>
-  <si>
-    <t>Logements en Structure Collective</t>
-  </si>
-  <si>
-    <t>4608</t>
-  </si>
-  <si>
-    <t>Protection des majeurs</t>
-  </si>
-  <si>
-    <t>4609</t>
-  </si>
-  <si>
-    <t>Centres prestataires de services pr personnes cérébro-lésées</t>
-  </si>
-  <si>
-    <t>5101</t>
-  </si>
-  <si>
-    <t>Etablissements Garde d'Enfants d'Age pré-Scolaire</t>
-  </si>
-  <si>
-    <t>5102</t>
-  </si>
-  <si>
-    <t>Etablissements d'Hébergement pour Enfants d'Age Scolaire</t>
-  </si>
-  <si>
-    <t>5103</t>
-  </si>
-  <si>
-    <t>Etablissements Sociaux pour Loisirs et Vacances</t>
-  </si>
-  <si>
-    <t>5104</t>
-  </si>
-  <si>
-    <t>Etablissements ou Services Divers d'Aide à la Famille</t>
-  </si>
-  <si>
-    <t>6101</t>
-  </si>
-  <si>
-    <t>6102</t>
-  </si>
-  <si>
-    <t>Etablissements de Formation des Personnels Techniques</t>
-  </si>
-  <si>
-    <t>6103</t>
-  </si>
-  <si>
-    <t>Autres Etablissements de Formation des Personnels Techniques</t>
-  </si>
-  <si>
-    <t>6201</t>
-  </si>
-  <si>
-    <t>6301</t>
-  </si>
-  <si>
-    <t>001</t>
-  </si>
-  <si>
-    <t>Autres lits de m.R.</t>
-  </si>
-  <si>
-    <t>002</t>
-  </si>
-  <si>
-    <t>Autres places de l-f.</t>
-  </si>
-  <si>
-    <t>003</t>
-  </si>
-  <si>
-    <t>Autres lits de l-s</t>
-  </si>
-  <si>
-    <t>101</t>
-  </si>
-  <si>
-    <t>Centre Hospitalier Régional (C.H.R.)</t>
-  </si>
-  <si>
-    <t>106</t>
-  </si>
-  <si>
-    <t>Centre hospitalier, ex Hôpital local</t>
-  </si>
-  <si>
-    <t>108</t>
-  </si>
-  <si>
-    <t>Etablissement de Convalescence et de Repos</t>
-  </si>
-  <si>
-    <t>109</t>
-  </si>
-  <si>
-    <t>Etablissement de santé privé autorisé en SSR</t>
-  </si>
-  <si>
-    <t>112</t>
-  </si>
-  <si>
-    <t>Centre de Convalescence Cure ou Réadaptation</t>
-  </si>
-  <si>
-    <t>114</t>
-  </si>
-  <si>
-    <t>Hôpital des armées</t>
-  </si>
-  <si>
-    <t>115</t>
-  </si>
-  <si>
-    <t>Etablissement de Soins du Service de Santé des Armées</t>
-  </si>
-  <si>
-    <t>119</t>
-  </si>
-  <si>
-    <t>Maison de Régime</t>
-  </si>
-  <si>
-    <t>122</t>
-  </si>
-  <si>
-    <t>Etablissement Soins Obstétriques Chirurgico-Gynécologiques</t>
-  </si>
-  <si>
-    <t>124</t>
-  </si>
-  <si>
-    <t>Centre de Santé</t>
-  </si>
-  <si>
-    <t>125</t>
-  </si>
-  <si>
-    <t>Centre de Santé Dentaire</t>
-  </si>
-  <si>
-    <t>126</t>
-  </si>
-  <si>
-    <t>Etablissement Thermal</t>
-  </si>
-  <si>
-    <t>127</t>
-  </si>
-  <si>
-    <t>Hospitalisation à Domicile</t>
-  </si>
-  <si>
-    <t>128</t>
-  </si>
-  <si>
-    <t>Etablissement de Soins Chirurgicaux</t>
-  </si>
-  <si>
-    <t>129</t>
-  </si>
-  <si>
-    <t>Etablissement de Soins Médicaux</t>
-  </si>
-  <si>
-    <t>130</t>
-  </si>
-  <si>
-    <t>Centre de Soins Médicaux</t>
-  </si>
-  <si>
-    <t>131</t>
-  </si>
-  <si>
-    <t>Centre de Lutte Contre Cancer</t>
-  </si>
-  <si>
-    <t>132</t>
-  </si>
-  <si>
-    <t>Etablissement de Transfusion Sanguine</t>
-  </si>
-  <si>
-    <t>135</t>
-  </si>
-  <si>
-    <t>Etablissement Réadaptation Fonctionnelle</t>
-  </si>
-  <si>
-    <t>136</t>
-  </si>
-  <si>
-    <t>Banque de Sperme</t>
-  </si>
-  <si>
-    <t>137</t>
-  </si>
-  <si>
-    <t>Banque d'Organes</t>
-  </si>
-  <si>
-    <t>138</t>
-  </si>
-  <si>
-    <t>Centre de Dialyse Périodique</t>
-  </si>
-  <si>
-    <t>139</t>
-  </si>
-  <si>
-    <t>Centre de Dialyse et d'entraînement à la Dialyse</t>
-  </si>
-  <si>
-    <t>140</t>
-  </si>
-  <si>
-    <t>Centre d'Entraînement à la Dialyse</t>
-  </si>
-  <si>
-    <t>141</t>
-  </si>
-  <si>
-    <t>Centre de dialyse</t>
-  </si>
-  <si>
-    <t>142</t>
-  </si>
-  <si>
-    <t>Dispensaire Antituberculeux</t>
-  </si>
-  <si>
-    <t>143</t>
-  </si>
-  <si>
-    <t>Centre de Vaccination BCG</t>
-  </si>
-  <si>
-    <t>144</t>
-  </si>
-  <si>
-    <t>Etablissement de Lutte Contre la Tuberculose</t>
-  </si>
-  <si>
-    <t>146</t>
-  </si>
-  <si>
-    <t>Structure d'Alternative à la dialyse en centre</t>
-  </si>
-  <si>
-    <t>156</t>
-  </si>
-  <si>
-    <t>Centre Médico-Psychologique (C.M.P.)</t>
-  </si>
-  <si>
-    <t>157</t>
-  </si>
-  <si>
-    <t>Centre de Postcure</t>
-  </si>
-  <si>
-    <t>159</t>
-  </si>
-  <si>
-    <t>Centre Parental</t>
-  </si>
-  <si>
-    <t>160</t>
-  </si>
-  <si>
-    <t>Centre de Soins Spécifiques pour Toxicomanes (C.S.S.T.)</t>
-  </si>
-  <si>
-    <t>161</t>
-  </si>
-  <si>
-    <t>Maison de Santé pour Maladies Mentales</t>
-  </si>
-  <si>
-    <t>162</t>
-  </si>
-  <si>
-    <t>Centre de Cure Ambulatoire en Alcoologie (C.C.A.A.)</t>
-  </si>
-  <si>
-    <t>163</t>
-  </si>
-  <si>
-    <t>Maison d'Enfants à Caractère Sanitaire Temporaire</t>
-  </si>
-  <si>
-    <t>164</t>
-  </si>
-  <si>
-    <t>Etablissements Expérimentaux Accueil de la Petite Enfance</t>
-  </si>
-  <si>
-    <t>165</t>
-  </si>
-  <si>
-    <t>Appartement de Coordination Thérapeutique (A.C.T.)</t>
-  </si>
-  <si>
-    <t>166</t>
-  </si>
-  <si>
-    <t>Etablissement d'Accueil Mère-Enfant</t>
-  </si>
-  <si>
-    <t>167</t>
-  </si>
-  <si>
-    <t>Crèche Collective</t>
-  </si>
-  <si>
-    <t>168</t>
-  </si>
-  <si>
-    <t>Service Accueil Familial pour la Petite Enfance</t>
-  </si>
-  <si>
-    <t>169</t>
-  </si>
-  <si>
-    <t>Crèche Multi Accueil Collectif et Familial</t>
-  </si>
-  <si>
-    <t>170</t>
-  </si>
-  <si>
-    <t>Halte Garderie</t>
-  </si>
-  <si>
-    <t>171</t>
-  </si>
-  <si>
-    <t>Garderie et Jardin d'Enfants</t>
-  </si>
-  <si>
-    <t>172</t>
-  </si>
-  <si>
-    <t>Pouponnière à Caractère Social</t>
-  </si>
-  <si>
-    <t>173</t>
-  </si>
-  <si>
-    <t>Pouponnière à Caractère Sanitaire</t>
-  </si>
-  <si>
-    <t>174</t>
-  </si>
-  <si>
-    <t>Etablissement d'Accueil Collectif Régulier et Occasionnel</t>
-  </si>
-  <si>
-    <t>175</t>
-  </si>
-  <si>
-    <t>Foyer de l'Enfance</t>
-  </si>
-  <si>
-    <t>176</t>
-  </si>
-  <si>
-    <t>Village d'Enfants</t>
-  </si>
-  <si>
-    <t>177</t>
-  </si>
-  <si>
-    <t>Maison d'Enfants à Caractère Social</t>
-  </si>
-  <si>
-    <t>178</t>
-  </si>
-  <si>
-    <t>Ctre.Accueil- Accomp.Réduc.Risq.Usag. Drogues (C.A.A.R.U.D.)</t>
-  </si>
-  <si>
-    <t>179</t>
-  </si>
-  <si>
-    <t>Maison d'Enfants à Caractère Sanitaire Permanente</t>
-  </si>
-  <si>
-    <t>180</t>
-  </si>
-  <si>
-    <t>Lits Halte Soins Santé (L.H.S.S.)</t>
-  </si>
-  <si>
-    <t>181</t>
-  </si>
-  <si>
-    <t>Maison Familiale de Vacances</t>
-  </si>
-  <si>
-    <t>182</t>
-  </si>
-  <si>
-    <t>Service d'Éducation Spéciale et de Soins à Domicile</t>
-  </si>
-  <si>
-    <t>183</t>
-  </si>
-  <si>
-    <t>Institut Médico-Educatif (I.M.E.)</t>
-  </si>
-  <si>
-    <t>184</t>
-  </si>
-  <si>
-    <t>Institut Médico-Pédagogique (I.M.P.)</t>
-  </si>
-  <si>
-    <t>185</t>
-  </si>
-  <si>
-    <t>Institut Médico-Professionnel (I.M.Pro.)</t>
-  </si>
-  <si>
-    <t>186</t>
-  </si>
-  <si>
-    <t>Institut Thérapeutique Éducatif et Pédagogique (I.T.E.P.)</t>
-  </si>
-  <si>
-    <t>188</t>
-  </si>
-  <si>
-    <t>Etablissement pour Enfants ou Adolescents Polyhandicapés</t>
-  </si>
-  <si>
-    <t>189</t>
-  </si>
-  <si>
-    <t>Centre Médico-Psycho-Pédagogique (C.M.P.P.)</t>
-  </si>
-  <si>
-    <t>190</t>
-  </si>
-  <si>
-    <t>Centre Action Médico-Sociale Précoce (C.A.M.S.P.)</t>
-  </si>
-  <si>
-    <t>191</t>
-  </si>
-  <si>
-    <t>Etablissement pour Déficients Moteurs Cérébraux</t>
-  </si>
-  <si>
-    <t>192</t>
-  </si>
-  <si>
-    <t>Institut d'éducation motrice</t>
-  </si>
-  <si>
-    <t>193</t>
-  </si>
-  <si>
-    <t>Etablissement pour Déficients Moteurs et Moteurs Cérébraux</t>
-  </si>
-  <si>
-    <t>194</t>
-  </si>
-  <si>
-    <t>Institut pour Déficients Visuels</t>
-  </si>
-  <si>
-    <t>195</t>
-  </si>
-  <si>
-    <t>Institut pour Déficients Auditifs</t>
-  </si>
-  <si>
-    <t>196</t>
-  </si>
-  <si>
-    <t>Institut d'Education Sensorielle Sourd-Aveugle</t>
-  </si>
-  <si>
-    <t>197</t>
-  </si>
-  <si>
-    <t>Centre soins accompagnement prévention addictologie (CSAPA)</t>
-  </si>
-  <si>
-    <t>198</t>
-  </si>
-  <si>
-    <t>Établissement et Service de Préorientation</t>
-  </si>
-  <si>
-    <t>199</t>
-  </si>
-  <si>
-    <t>Hospice</t>
-  </si>
-  <si>
-    <t>200</t>
-  </si>
-  <si>
-    <t>Maison de Retraite</t>
-  </si>
-  <si>
-    <t>202</t>
-  </si>
-  <si>
-    <t>Résidences autonomie</t>
-  </si>
-  <si>
-    <t>205</t>
-  </si>
-  <si>
-    <t>Foyer Club Restaurant</t>
-  </si>
-  <si>
-    <t>207</t>
-  </si>
-  <si>
-    <t>Centre de Jour pour Personnes Agées</t>
-  </si>
-  <si>
-    <t>208</t>
-  </si>
-  <si>
-    <t>Service d'Aide Ménagère à Domicile</t>
-  </si>
-  <si>
-    <t>209</t>
-  </si>
-  <si>
-    <t>Service autonomie aide et soins (SAAS)</t>
-  </si>
-  <si>
-    <t>212</t>
-  </si>
-  <si>
-    <t>Alarme Médico-Sociale</t>
-  </si>
-  <si>
-    <t>213</t>
-  </si>
-  <si>
-    <t>Lits d'Accueil Médicalisés (L.A.M.)</t>
-  </si>
-  <si>
-    <t>214</t>
-  </si>
-  <si>
-    <t>Centre Hébergement &amp; Réinsertion Sociale (C.H.R.S.)</t>
-  </si>
-  <si>
-    <t>215</t>
-  </si>
-  <si>
-    <t>Maison Relai</t>
-  </si>
-  <si>
-    <t>216</t>
-  </si>
-  <si>
-    <t>Résidence Hôtelière à Vocation Sociale (R.H.V.S)</t>
-  </si>
-  <si>
-    <t>217</t>
-  </si>
-  <si>
-    <t>Cité de Transit</t>
-  </si>
-  <si>
-    <t>218</t>
-  </si>
-  <si>
-    <t>Aire Station Nomades</t>
-  </si>
-  <si>
-    <t>219</t>
-  </si>
-  <si>
-    <t>Autre Centre d'Accueil</t>
-  </si>
-  <si>
-    <t>220</t>
-  </si>
-  <si>
-    <t>Centre Social</t>
-  </si>
-  <si>
-    <t>221</t>
-  </si>
-  <si>
-    <t>Bureau d'Aide Psychologique Universitaire (B.A.P.U.)</t>
-  </si>
-  <si>
-    <t>223</t>
-  </si>
-  <si>
-    <t>Protection Maternelle et Infantile (P.M.I.)</t>
-  </si>
-  <si>
-    <t>224</t>
-  </si>
-  <si>
-    <t>Etablissement de Consultation Pré et Post-natale</t>
-  </si>
-  <si>
-    <t>225</t>
-  </si>
-  <si>
-    <t>Consultations de Nourrissons</t>
-  </si>
-  <si>
-    <t>228</t>
-  </si>
-  <si>
-    <t>Centre de Santé Sexuelle</t>
-  </si>
-  <si>
-    <t>229</t>
-  </si>
-  <si>
-    <t>Consultation Problèmes naissance</t>
-  </si>
-  <si>
-    <t>230</t>
-  </si>
-  <si>
-    <t>Etablissement Consultation Protection Infantile</t>
-  </si>
-  <si>
-    <t>231</t>
-  </si>
-  <si>
-    <t>Espaces de vie affective, relationnelle et sexuelle (EVARS)</t>
-  </si>
-  <si>
-    <t>233</t>
-  </si>
-  <si>
-    <t>Lactarium</t>
-  </si>
-  <si>
-    <t>236</t>
-  </si>
-  <si>
-    <t>Centre Placement Familial Socio-Educatif (C.P.F.S.E.)</t>
-  </si>
-  <si>
-    <t>237</t>
-  </si>
-  <si>
-    <t>Centre de Placement Familial Spécialisé</t>
-  </si>
-  <si>
-    <t>238</t>
-  </si>
-  <si>
-    <t>Centre d'Accueil Familial Spécialisé</t>
-  </si>
-  <si>
-    <t>241</t>
-  </si>
-  <si>
-    <t>Établissement de Placement</t>
-  </si>
-  <si>
-    <t>242</t>
-  </si>
-  <si>
-    <t>Service d’Activité de Jour</t>
-  </si>
-  <si>
-    <t>246</t>
-  </si>
-  <si>
-    <t>Etablissement et Service d'Aide par le Travail (E.S.A.T.)</t>
-  </si>
-  <si>
-    <t>247</t>
-  </si>
-  <si>
-    <t>Entreprise adaptée</t>
-  </si>
-  <si>
-    <t>249</t>
-  </si>
-  <si>
-    <t>Établissement et Service de Réadaptation Professionnelle</t>
-  </si>
-  <si>
-    <t>250</t>
-  </si>
-  <si>
-    <t>Centre Réentrainement au travail</t>
-  </si>
-  <si>
-    <t>251</t>
-  </si>
-  <si>
-    <t>Maison Vacances pour Handicapés</t>
-  </si>
-  <si>
-    <t>252</t>
-  </si>
-  <si>
-    <t>Foyer Hébergement Adultes Handicapés</t>
-  </si>
-  <si>
-    <t>253</t>
-  </si>
-  <si>
-    <t>Foyer d'Accueil Polyvalent pour Adultes Handicapés</t>
-  </si>
-  <si>
-    <t>255</t>
-  </si>
-  <si>
-    <t>Maison d'Accueil Spécialisée (M.A.S.)</t>
-  </si>
-  <si>
-    <t>256</t>
-  </si>
-  <si>
-    <t>Foyer Travailleurs Migrants non transformé en Résidence Soc.</t>
-  </si>
-  <si>
-    <t>257</t>
-  </si>
-  <si>
-    <t>Foyers de jeunes travailleurs</t>
-  </si>
-  <si>
-    <t>258</t>
-  </si>
-  <si>
-    <t>Maisons Relais - Pensions de Famille</t>
-  </si>
-  <si>
-    <t>259</t>
-  </si>
-  <si>
-    <t>Autres résidences sociales</t>
-  </si>
-  <si>
-    <t>261</t>
-  </si>
-  <si>
-    <t>D.D.A.S.S.</t>
-  </si>
-  <si>
-    <t>262</t>
-  </si>
-  <si>
-    <t>Etablissement Régional d'Enseignement Adapté</t>
-  </si>
-  <si>
-    <t>265</t>
-  </si>
-  <si>
-    <t>Section Education Spéciale Classe Atelier</t>
-  </si>
-  <si>
-    <t>266</t>
-  </si>
-  <si>
-    <t>Dispensaire Antivénérien</t>
-  </si>
-  <si>
-    <t>267</t>
-  </si>
-  <si>
-    <t>Dispensaire Antihansénien</t>
-  </si>
-  <si>
-    <t>268</t>
-  </si>
-  <si>
-    <t>Centre Médico-Scolaire</t>
-  </si>
-  <si>
-    <t>269</t>
-  </si>
-  <si>
-    <t>Centre de Médecine Universitaire</t>
-  </si>
-  <si>
-    <t>270</t>
-  </si>
-  <si>
-    <t>Centre de Médecine Sportive</t>
-  </si>
-  <si>
-    <t>271</t>
-  </si>
-  <si>
-    <t>Maison d'accueil Hospitalière</t>
-  </si>
-  <si>
-    <t>272</t>
-  </si>
-  <si>
-    <t>Ecole d'ambulanciers</t>
-  </si>
-  <si>
-    <t>273</t>
-  </si>
-  <si>
-    <t>Institut de formation en soins infirmiers (I.F.S.I.)</t>
-  </si>
-  <si>
-    <t>274</t>
-  </si>
-  <si>
-    <t>Ecole de sages_femmes</t>
-  </si>
-  <si>
-    <t>275</t>
-  </si>
-  <si>
-    <t>Ecole de masseurs-kinésithérapeutes</t>
-  </si>
-  <si>
-    <t>276</t>
-  </si>
-  <si>
-    <t>Ecole de laborantins d'analyses médicales</t>
-  </si>
-  <si>
-    <t>277</t>
-  </si>
-  <si>
-    <t>Ecole de péricultrices</t>
-  </si>
-  <si>
-    <t>278</t>
-  </si>
-  <si>
-    <t>Etablissement de formation polyvalent</t>
-  </si>
-  <si>
-    <t>279</t>
-  </si>
-  <si>
-    <t>Ecole de service social</t>
-  </si>
-  <si>
-    <t>280</t>
-  </si>
-  <si>
-    <t>Ecole d'éducateurs spécialisés</t>
-  </si>
-  <si>
-    <t>281</t>
-  </si>
-  <si>
-    <t>Centre de formation d'aides soignants</t>
-  </si>
-  <si>
-    <t>282</t>
-  </si>
-  <si>
-    <t>Ecole de pédicures-podologues</t>
-  </si>
-  <si>
-    <t>283</t>
-  </si>
-  <si>
-    <t>Ecole de manipulateurs d'électro-radiologie</t>
-  </si>
-  <si>
-    <t>284</t>
-  </si>
-  <si>
-    <t>Ecole de travailleuses familiales</t>
-  </si>
-  <si>
-    <t>285</t>
-  </si>
-  <si>
-    <t>Centres de Loisirs sans Hébergement</t>
-  </si>
-  <si>
-    <t>286</t>
-  </si>
-  <si>
-    <t>Club Equipe de Prévention</t>
-  </si>
-  <si>
-    <t>289</t>
-  </si>
-  <si>
-    <t>Centre de Soins Infirmiers</t>
-  </si>
-  <si>
-    <t>292</t>
-  </si>
-  <si>
-    <t>Centre Hospitalier Spécialisé lutte Maladies Mentales</t>
-  </si>
-  <si>
-    <t>294</t>
-  </si>
-  <si>
-    <t>Centre de Consultations Cancer</t>
-  </si>
-  <si>
-    <t>295</t>
-  </si>
-  <si>
-    <t>Service AEMO et AED</t>
-  </si>
-  <si>
-    <t>297</t>
-  </si>
-  <si>
-    <t>Dispensaire Polyvalent</t>
-  </si>
-  <si>
-    <t>300</t>
-  </si>
-  <si>
-    <t>Ecoles Formant aux Professions Sanitaires</t>
-  </si>
-  <si>
-    <t>303</t>
-  </si>
-  <si>
-    <t>Ecole de conseillers en économie sociale et familiale</t>
-  </si>
-  <si>
-    <t>304</t>
-  </si>
-  <si>
-    <t>Ecole d'ergothérapeutes</t>
-  </si>
-  <si>
-    <t>305</t>
-  </si>
-  <si>
-    <t>Ecole de psycho-motriciens</t>
-  </si>
-  <si>
-    <t>306</t>
-  </si>
-  <si>
-    <t>Ecole d'infirmiers anesthésistes</t>
-  </si>
-  <si>
-    <t>307</t>
-  </si>
-  <si>
-    <t>Ecole d'infirmiers de bloc opératoire</t>
-  </si>
-  <si>
-    <t>308</t>
-  </si>
-  <si>
-    <t>Centre de formation professionnelle de secteur psychiatrique</t>
-  </si>
-  <si>
-    <t>309</t>
-  </si>
-  <si>
-    <t>Ecole de cadres infirmiers</t>
-  </si>
-  <si>
-    <t>310</t>
-  </si>
-  <si>
-    <t>Ecole de cadres de secteur psychiatrique</t>
-  </si>
-  <si>
-    <t>311</t>
-  </si>
-  <si>
-    <t>Ecole de cadres de masseurs-kinésithérapeutes</t>
-  </si>
-  <si>
-    <t>312</t>
-  </si>
-  <si>
-    <t>Ecole de cadres de manipulateurs d'électro-radiologie</t>
-  </si>
-  <si>
-    <t>313</t>
-  </si>
-  <si>
-    <t>Ecole d'éducateurs de jeunes enfants</t>
-  </si>
-  <si>
-    <t>314</t>
-  </si>
-  <si>
-    <t>Ecole d'éducateurs techniques spécialisés</t>
-  </si>
-  <si>
-    <t>315</t>
-  </si>
-  <si>
-    <t>Ecole de moniteurs-éducateurs</t>
-  </si>
-  <si>
-    <t>316</t>
-  </si>
-  <si>
-    <t>Ecole d'aides médico-psychologiques</t>
-  </si>
-  <si>
-    <t>317</t>
-  </si>
-  <si>
-    <t>Ecole d'animateurs socio-éducatifs</t>
-  </si>
-  <si>
-    <t>319</t>
-  </si>
-  <si>
-    <t>Inst. régional de formation des travailleurs sociaux</t>
-  </si>
-  <si>
-    <t>320</t>
-  </si>
-  <si>
-    <t>S.A.M.U. et Centre 15</t>
-  </si>
-  <si>
-    <t>321</t>
-  </si>
-  <si>
-    <t>Unité Mobile Hospitalière</t>
-  </si>
-  <si>
-    <t>322</t>
-  </si>
-  <si>
-    <t>Centre Rég.Informatiq.Hospit.</t>
-  </si>
-  <si>
-    <t>324</t>
-  </si>
-  <si>
-    <t>Logement Foyer non Spécialisé</t>
-  </si>
-  <si>
-    <t>326</t>
-  </si>
-  <si>
-    <t>Ecole de cadres</t>
-  </si>
-  <si>
-    <t>327</t>
-  </si>
-  <si>
-    <t>328</t>
-  </si>
-  <si>
-    <t>Centre Consultation Soins Dentaire</t>
-  </si>
-  <si>
-    <t>329</t>
-  </si>
-  <si>
-    <t>Sectorisation Psychiatrique</t>
-  </si>
-  <si>
-    <t>330</t>
-  </si>
-  <si>
-    <t>Ecoles Formant aux Professions Sociales</t>
-  </si>
-  <si>
-    <t>340</t>
-  </si>
-  <si>
-    <t>Service mandataire judiciaire à la protection des majeurs</t>
-  </si>
-  <si>
-    <t>341</t>
-  </si>
-  <si>
-    <t>Service dédié mesures d'accompagnement social personnalisé</t>
-  </si>
-  <si>
-    <t>342</t>
-  </si>
-  <si>
-    <t>Service d'information et de soutien aux tuteurs familiaux</t>
-  </si>
-  <si>
-    <t>343</t>
-  </si>
-  <si>
-    <t>Equipe Préparation et Suite Reclassement (EPSR)</t>
-  </si>
-  <si>
-    <t>344</t>
-  </si>
-  <si>
-    <t>Service délégué aux prestations familiales</t>
-  </si>
-  <si>
-    <t>345</t>
-  </si>
-  <si>
-    <t>Service Tutelle Prestation Sociale</t>
-  </si>
-  <si>
-    <t>346</t>
-  </si>
-  <si>
-    <t>Service de Travailleuses Familiales</t>
-  </si>
-  <si>
-    <t>347</t>
-  </si>
-  <si>
-    <t>Centre d'Examens de Santé</t>
-  </si>
-  <si>
-    <t>349</t>
-  </si>
-  <si>
-    <t>Ecole de cadres de sages-femmes</t>
-  </si>
-  <si>
-    <t>350</t>
-  </si>
-  <si>
-    <t>Centre de formation d'auxiliaires de puériculture</t>
-  </si>
-  <si>
-    <t>352</t>
-  </si>
-  <si>
-    <t>Centre de Psychothérapie</t>
-  </si>
-  <si>
-    <t>353</t>
-  </si>
-  <si>
-    <t>Hôpital de Jour Spécialités Médicales</t>
-  </si>
-  <si>
-    <t>354</t>
-  </si>
-  <si>
-    <t>Service de Soins Infirmiers A Domicile (S.S.I.A.D)</t>
-  </si>
-  <si>
-    <t>355</t>
-  </si>
-  <si>
-    <t>Centre Hospitalier (C.H.)</t>
-  </si>
-  <si>
-    <t>357</t>
-  </si>
-  <si>
-    <t>Association Aide aux Insuffisants Respiratoires</t>
-  </si>
-  <si>
-    <t>359</t>
-  </si>
-  <si>
-    <t>Centre Circonscription Sanitaire et Sociale</t>
-  </si>
-  <si>
-    <t>361</t>
-  </si>
-  <si>
-    <t>Centre de Cure Médicale</t>
-  </si>
-  <si>
-    <t>362</t>
-  </si>
-  <si>
-    <t>Etablissement de Soins Longue Durée</t>
-  </si>
-  <si>
-    <t>363</t>
-  </si>
-  <si>
-    <t>Centre moyen et long séjour</t>
-  </si>
-  <si>
-    <t>365</t>
-  </si>
-  <si>
-    <t>Etablissement de Soins Pluridisciplinaire</t>
-  </si>
-  <si>
-    <t>366</t>
-  </si>
-  <si>
-    <t>Atelier Thérapeutique</t>
-  </si>
-  <si>
-    <t>367</t>
-  </si>
-  <si>
-    <t>Maison d'Enfants non Conventionnée ni Habilitée</t>
-  </si>
-  <si>
-    <t>368</t>
-  </si>
-  <si>
-    <t>Service de Repas à Domicile</t>
-  </si>
-  <si>
-    <t>369</t>
-  </si>
-  <si>
-    <t>Centre Adaptation Vie Active (C.A.V.A.)</t>
-  </si>
-  <si>
-    <t>370</t>
-  </si>
-  <si>
-    <t>Etablissement Expérimental pour personnes handicapées</t>
-  </si>
-  <si>
-    <t>371</t>
-  </si>
-  <si>
-    <t>Service Action Socio-Educative pour Familles en difficulté</t>
-  </si>
-  <si>
-    <t>373</t>
-  </si>
-  <si>
-    <t>Centre de formation supérieure des travailleurs sociaux</t>
-  </si>
-  <si>
-    <t>374</t>
-  </si>
-  <si>
-    <t>Ecole Nationale Santé Publique (E.N.S.P.)</t>
-  </si>
-  <si>
-    <t>375</t>
-  </si>
-  <si>
-    <t>Classe d'Adaptation</t>
-  </si>
-  <si>
-    <t>376</t>
-  </si>
-  <si>
-    <t>Classe Spéciale Ecole Primaire</t>
-  </si>
-  <si>
-    <t>377</t>
-  </si>
-  <si>
-    <t>Etablissement Expérimental pour Enfance Handicapée</t>
-  </si>
-  <si>
-    <t>378</t>
-  </si>
-  <si>
-    <t>Etablissement Expérimental Enfance Protégée</t>
-  </si>
-  <si>
-    <t>379</t>
-  </si>
-  <si>
-    <t>Etablissement Expérimental pour Adultes Handicapés</t>
-  </si>
-  <si>
-    <t>380</t>
-  </si>
-  <si>
-    <t>Etablissement Expérimental Autres Adultes</t>
-  </si>
-  <si>
-    <t>381</t>
-  </si>
-  <si>
-    <t>Etablissement Expérimental pour Personnes Agées</t>
-  </si>
-  <si>
-    <t>382</t>
-  </si>
-  <si>
-    <t>Foyer de Vie pour Adultes Handicapés</t>
-  </si>
-  <si>
-    <t>386</t>
-  </si>
-  <si>
-    <t>Ecole Secondaire Spéciale</t>
-  </si>
-  <si>
-    <t>390</t>
-  </si>
-  <si>
-    <t>Etablissement d'Accueil Temporaire d'Enfants Handicapés</t>
-  </si>
-  <si>
-    <t>393</t>
-  </si>
-  <si>
-    <t>Autre résidence But lucratif pr personnes Âgées</t>
-  </si>
-  <si>
-    <t>394</t>
-  </si>
-  <si>
-    <t>Etablissement d'Accueil Temporaire pour Personnes Agées</t>
-  </si>
-  <si>
-    <t>395</t>
-  </si>
-  <si>
-    <t>Etablissement d'Accueil Temporaire pour Adultes Handicapés</t>
-  </si>
-  <si>
-    <t>396</t>
-  </si>
-  <si>
-    <t>Foyer Hébergement Enfants et Adolescents Handicapés</t>
-  </si>
-  <si>
-    <t>397</t>
-  </si>
-  <si>
-    <t>Service Auxiliaire de Vie pour Handicapés</t>
-  </si>
-  <si>
-    <t>398</t>
-  </si>
-  <si>
-    <t>Crèche Parentale</t>
-  </si>
-  <si>
-    <t>399</t>
-  </si>
-  <si>
-    <t>Halte Garderie Parentale</t>
-  </si>
-  <si>
-    <t>400</t>
-  </si>
-  <si>
-    <t>Centre de Services pour Associations</t>
-  </si>
-  <si>
-    <t>401</t>
-  </si>
-  <si>
-    <t>D.R.A.S.S.</t>
-  </si>
-  <si>
-    <t>402</t>
-  </si>
-  <si>
-    <t>Jardin d'Enfants Spécialisé</t>
-  </si>
-  <si>
-    <t>403</t>
-  </si>
-  <si>
-    <t>Service Social Spécialisé ou Polyvalent de Catégorie</t>
-  </si>
-  <si>
-    <t>404</t>
-  </si>
-  <si>
-    <t>Etablissement Acc.Collect.Parental Régulier &amp; Occasionnel</t>
-  </si>
-  <si>
-    <t>405</t>
-  </si>
-  <si>
-    <t>Service Social Polyvalent de Secteur</t>
-  </si>
-  <si>
-    <t>411</t>
-  </si>
-  <si>
-    <t>Intermédiaire de Placement Social</t>
-  </si>
-  <si>
-    <t>412</t>
-  </si>
-  <si>
-    <t>Appartement Thérapeutique</t>
-  </si>
-  <si>
-    <t>413</t>
-  </si>
-  <si>
-    <t>C.E.C.O.S</t>
-  </si>
-  <si>
-    <t>414</t>
-  </si>
-  <si>
-    <t>Centre Anti Poison</t>
-  </si>
-  <si>
-    <t>415</t>
-  </si>
-  <si>
-    <t>Service Médico-Psychologique Régional (S.M.P.R.)</t>
-  </si>
-  <si>
-    <t>418</t>
-  </si>
-  <si>
-    <t>Service d'Enquêtes Sociales (S.E.S.)</t>
-  </si>
-  <si>
-    <t>419</t>
-  </si>
-  <si>
-    <t>Centre d'Accueil Toxicomanes</t>
-  </si>
-  <si>
-    <t>420</t>
-  </si>
-  <si>
-    <t>Entreprise d'Insertion</t>
-  </si>
-  <si>
-    <t>421</t>
-  </si>
-  <si>
-    <t>Centre d'enseignement aux secours d'urgence</t>
-  </si>
-  <si>
-    <t>422</t>
-  </si>
-  <si>
-    <t>Traitements Spécialisés à Domicile</t>
-  </si>
-  <si>
-    <t>423</t>
-  </si>
-  <si>
-    <t>Ecole des cadres de laborantins d'analyses médicales</t>
-  </si>
-  <si>
-    <t>425</t>
-  </si>
-  <si>
-    <t>Centre d'Accueil Thérapeutique à temps partiel (C.A.T.T.P.)</t>
-  </si>
-  <si>
-    <t>426</t>
-  </si>
-  <si>
-    <t>Syndicat Inter Hospitalier (S.I.H.)</t>
-  </si>
-  <si>
     <t>Service Educatif Auprès des Tribunaux (S.E.A.T.)</t>
   </si>
   <si>
@@ -2729,6 +2732,15 @@
   </si>
   <si>
     <t>Les centres de santé et de médiation en santé sexuelle (CSMSS) sont des établissements de santé dérogatoires relevant de l’article L. 6323-1 du code de la santé publique (CSP). Ils ont initialement fait l’objet d’une expérimentation dans le cadre du dispositif prévu à l’article 51 de la loi de financement de la sécurité sociale, au cours de laquelle ils étaient rattachés au numéro FINESS des centres de santé de droit commun. L’activité des centres de santé et de médiation en santé sexuelle (CSMSS) consiste à assurer l’accueil, l’information, la prévention, le dépistage et l’accompagnement des publics dans le domaine de la santé sexuelle dans une approche globale intégrant notamment la prévention et la prise en charge des infections sexuellement transmissibles (IST) et du VIH, la prescription de la contraception et la mise en place de parcours en santé sexuelle.</t>
+  </si>
+  <si>
+    <t>650</t>
+  </si>
+  <si>
+    <t>Dispositifs Spécifiques Régionaux en périnatalité</t>
+  </si>
+  <si>
+    <t>Les DSRP ont pour mission principale l’animation régionale des professionnels de la périnatalité et l’accompagnement des évolutions de l’offre et des pratiques, dans un contexte marqué par des enjeux forts en matière de qualité des soins, de prévention, de démographie médicale et d’organisation des parcours. Ils contribuent à la lisibilité et à la cohérence de l’offre de soins périnatals sur les territoires, en favorisant la coordination entre la ville, l’hôpital et les services de protection maternelle et infantile (PMI).</t>
   </si>
   <si>
     <t>690</t>
@@ -3310,7 +3322,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D428"/>
+  <dimension ref="A1:D429"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -7424,10 +7436,10 @@
         <v>85</v>
       </c>
       <c r="B343" t="s" s="2">
-        <v>34</v>
+        <v>756</v>
       </c>
       <c r="C343" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="D343" s="2"/>
     </row>
@@ -7436,10 +7448,10 @@
         <v>85</v>
       </c>
       <c r="B344" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="C344" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="D344" s="2"/>
     </row>
@@ -7448,10 +7460,10 @@
         <v>85</v>
       </c>
       <c r="B345" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="C345" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="D345" s="2"/>
     </row>
@@ -7460,10 +7472,10 @@
         <v>85</v>
       </c>
       <c r="B346" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C346" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="D346" s="2"/>
     </row>
@@ -7472,10 +7484,10 @@
         <v>85</v>
       </c>
       <c r="B347" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="C347" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="D347" s="2"/>
     </row>
@@ -7484,10 +7496,10 @@
         <v>85</v>
       </c>
       <c r="B348" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="C348" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="D348" s="2"/>
     </row>
@@ -7496,10 +7508,10 @@
         <v>85</v>
       </c>
       <c r="B349" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C349" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="D349" s="2"/>
     </row>
@@ -7508,10 +7520,10 @@
         <v>85</v>
       </c>
       <c r="B350" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="C350" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="D350" s="2"/>
     </row>
@@ -7520,10 +7532,10 @@
         <v>85</v>
       </c>
       <c r="B351" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="C351" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="D351" s="2"/>
     </row>
@@ -7532,10 +7544,10 @@
         <v>85</v>
       </c>
       <c r="B352" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="C352" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="D352" s="2"/>
     </row>
@@ -7544,10 +7556,10 @@
         <v>85</v>
       </c>
       <c r="B353" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="C353" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="D353" s="2"/>
     </row>
@@ -7556,10 +7568,10 @@
         <v>85</v>
       </c>
       <c r="B354" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="C354" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="D354" s="2"/>
     </row>
@@ -7568,10 +7580,10 @@
         <v>85</v>
       </c>
       <c r="B355" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="C355" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="D355" s="2"/>
     </row>
@@ -7580,10 +7592,10 @@
         <v>85</v>
       </c>
       <c r="B356" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="C356" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="D356" s="2"/>
     </row>
@@ -7592,10 +7604,10 @@
         <v>85</v>
       </c>
       <c r="B357" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="C357" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="D357" s="2"/>
     </row>
@@ -7604,10 +7616,10 @@
         <v>85</v>
       </c>
       <c r="B358" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C358" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="D358" s="2"/>
     </row>
@@ -7616,10 +7628,10 @@
         <v>85</v>
       </c>
       <c r="B359" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="C359" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="D359" s="2"/>
     </row>
@@ -7628,10 +7640,10 @@
         <v>85</v>
       </c>
       <c r="B360" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="C360" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="D360" s="2"/>
     </row>
@@ -7640,10 +7652,10 @@
         <v>85</v>
       </c>
       <c r="B361" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="C361" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="D361" s="2"/>
     </row>
@@ -7652,10 +7664,10 @@
         <v>85</v>
       </c>
       <c r="B362" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C362" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="D362" s="2"/>
     </row>
@@ -7664,10 +7676,10 @@
         <v>85</v>
       </c>
       <c r="B363" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C363" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="D363" s="2"/>
     </row>
@@ -7676,10 +7688,10 @@
         <v>85</v>
       </c>
       <c r="B364" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C364" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="D364" s="2"/>
     </row>
@@ -7688,10 +7700,10 @@
         <v>85</v>
       </c>
       <c r="B365" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="C365" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="D365" s="2"/>
     </row>
@@ -7700,10 +7712,10 @@
         <v>85</v>
       </c>
       <c r="B366" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="C366" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="D366" s="2"/>
     </row>
@@ -7712,10 +7724,10 @@
         <v>85</v>
       </c>
       <c r="B367" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="C367" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="D367" s="2"/>
     </row>
@@ -7724,10 +7736,10 @@
         <v>85</v>
       </c>
       <c r="B368" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="C368" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="D368" s="2"/>
     </row>
@@ -7736,10 +7748,10 @@
         <v>85</v>
       </c>
       <c r="B369" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="C369" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="D369" s="2"/>
     </row>
@@ -7748,10 +7760,10 @@
         <v>85</v>
       </c>
       <c r="B370" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C370" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="D370" s="2"/>
     </row>
@@ -7760,10 +7772,10 @@
         <v>85</v>
       </c>
       <c r="B371" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="C371" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="D371" s="2"/>
     </row>
@@ -7772,10 +7784,10 @@
         <v>85</v>
       </c>
       <c r="B372" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="C372" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="D372" s="2"/>
     </row>
@@ -7784,10 +7796,10 @@
         <v>85</v>
       </c>
       <c r="B373" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="C373" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="D373" s="2"/>
     </row>
@@ -7796,10 +7808,10 @@
         <v>85</v>
       </c>
       <c r="B374" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="C374" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="D374" s="2"/>
     </row>
@@ -7808,10 +7820,10 @@
         <v>85</v>
       </c>
       <c r="B375" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="C375" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="D375" s="2"/>
     </row>
@@ -7820,10 +7832,10 @@
         <v>85</v>
       </c>
       <c r="B376" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C376" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="D376" s="2"/>
     </row>
@@ -7832,7 +7844,7 @@
         <v>85</v>
       </c>
       <c r="B377" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="C377" t="s" s="2">
         <v>171</v>
@@ -7844,10 +7856,10 @@
         <v>85</v>
       </c>
       <c r="B378" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="C378" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="D378" s="2"/>
     </row>
@@ -7856,13 +7868,13 @@
         <v>85</v>
       </c>
       <c r="B379" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="C379" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="D379" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
     </row>
     <row r="380">
@@ -7870,7 +7882,7 @@
         <v>85</v>
       </c>
       <c r="B380" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="C380" t="s" s="2">
         <v>175</v>
@@ -7882,10 +7894,10 @@
         <v>85</v>
       </c>
       <c r="B381" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="C381" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="D381" s="2"/>
     </row>
@@ -7894,10 +7906,10 @@
         <v>85</v>
       </c>
       <c r="B382" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="C382" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="D382" s="2"/>
     </row>
@@ -7906,10 +7918,10 @@
         <v>85</v>
       </c>
       <c r="B383" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="C383" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="D383" s="2"/>
     </row>
@@ -7918,10 +7930,10 @@
         <v>85</v>
       </c>
       <c r="B384" t="s" s="2">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="C384" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="D384" s="2"/>
     </row>
@@ -7930,10 +7942,10 @@
         <v>85</v>
       </c>
       <c r="B385" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="C385" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="D385" s="2"/>
     </row>
@@ -7942,10 +7954,10 @@
         <v>85</v>
       </c>
       <c r="B386" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="C386" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="D386" s="2"/>
     </row>
@@ -7954,10 +7966,10 @@
         <v>85</v>
       </c>
       <c r="B387" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="C387" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="D387" s="2"/>
     </row>
@@ -7966,10 +7978,10 @@
         <v>85</v>
       </c>
       <c r="B388" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="C388" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="D388" s="2"/>
     </row>
@@ -7978,7 +7990,7 @@
         <v>85</v>
       </c>
       <c r="B389" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="C389" t="s" s="2">
         <v>209</v>
@@ -7990,13 +8002,13 @@
         <v>85</v>
       </c>
       <c r="B390" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="C390" t="s" s="2">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="D390" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
     </row>
     <row r="391">
@@ -8004,10 +8016,10 @@
         <v>85</v>
       </c>
       <c r="B391" t="s" s="2">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="C391" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="D391" s="2"/>
     </row>
@@ -8016,10 +8028,10 @@
         <v>85</v>
       </c>
       <c r="B392" t="s" s="2">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="C392" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="D392" s="2"/>
     </row>
@@ -8028,10 +8040,10 @@
         <v>85</v>
       </c>
       <c r="B393" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="C393" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="D393" s="2"/>
     </row>
@@ -8040,10 +8052,10 @@
         <v>85</v>
       </c>
       <c r="B394" t="s" s="2">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="C394" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="D394" s="2"/>
     </row>
@@ -8052,10 +8064,10 @@
         <v>85</v>
       </c>
       <c r="B395" t="s" s="2">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="C395" t="s" s="2">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="D395" s="2"/>
     </row>
@@ -8064,10 +8076,10 @@
         <v>85</v>
       </c>
       <c r="B396" t="s" s="2">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="C396" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="D396" s="2"/>
     </row>
@@ -8076,10 +8088,10 @@
         <v>85</v>
       </c>
       <c r="B397" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="C397" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="D397" s="2"/>
     </row>
@@ -8088,10 +8100,10 @@
         <v>85</v>
       </c>
       <c r="B398" t="s" s="2">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="C398" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="D398" s="2"/>
     </row>
@@ -8100,10 +8112,10 @@
         <v>85</v>
       </c>
       <c r="B399" t="s" s="2">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C399" t="s" s="2">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="D399" s="2"/>
     </row>
@@ -8112,10 +8124,10 @@
         <v>85</v>
       </c>
       <c r="B400" t="s" s="2">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="C400" t="s" s="2">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="D400" s="2"/>
     </row>
@@ -8124,10 +8136,10 @@
         <v>85</v>
       </c>
       <c r="B401" t="s" s="2">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="C401" t="s" s="2">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="D401" s="2"/>
     </row>
@@ -8136,10 +8148,10 @@
         <v>85</v>
       </c>
       <c r="B402" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="C402" t="s" s="2">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="D402" s="2"/>
     </row>
@@ -8148,10 +8160,10 @@
         <v>85</v>
       </c>
       <c r="B403" t="s" s="2">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C403" t="s" s="2">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="D403" s="2"/>
     </row>
@@ -8160,10 +8172,10 @@
         <v>85</v>
       </c>
       <c r="B404" t="s" s="2">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="C404" t="s" s="2">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="D404" s="2"/>
     </row>
@@ -8172,10 +8184,10 @@
         <v>85</v>
       </c>
       <c r="B405" t="s" s="2">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="C405" t="s" s="2">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="D405" s="2"/>
     </row>
@@ -8184,10 +8196,10 @@
         <v>85</v>
       </c>
       <c r="B406" t="s" s="2">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="C406" t="s" s="2">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="D406" s="2"/>
     </row>
@@ -8196,10 +8208,10 @@
         <v>85</v>
       </c>
       <c r="B407" t="s" s="2">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="C407" t="s" s="2">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="D407" s="2"/>
     </row>
@@ -8208,10 +8220,10 @@
         <v>85</v>
       </c>
       <c r="B408" t="s" s="2">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="C408" t="s" s="2">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="D408" s="2"/>
     </row>
@@ -8220,10 +8232,10 @@
         <v>85</v>
       </c>
       <c r="B409" t="s" s="2">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="C409" t="s" s="2">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="D409" s="2"/>
     </row>
@@ -8232,10 +8244,10 @@
         <v>85</v>
       </c>
       <c r="B410" t="s" s="2">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="C410" t="s" s="2">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="D410" s="2"/>
     </row>
@@ -8244,10 +8256,10 @@
         <v>85</v>
       </c>
       <c r="B411" t="s" s="2">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="C411" t="s" s="2">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="D411" s="2"/>
     </row>
@@ -8256,10 +8268,10 @@
         <v>85</v>
       </c>
       <c r="B412" t="s" s="2">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="C412" t="s" s="2">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="D412" s="2"/>
     </row>
@@ -8268,10 +8280,10 @@
         <v>85</v>
       </c>
       <c r="B413" t="s" s="2">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="C413" t="s" s="2">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="D413" s="2"/>
     </row>
@@ -8280,10 +8292,10 @@
         <v>85</v>
       </c>
       <c r="B414" t="s" s="2">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="C414" t="s" s="2">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="D414" s="2"/>
     </row>
@@ -8292,10 +8304,10 @@
         <v>85</v>
       </c>
       <c r="B415" t="s" s="2">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="C415" t="s" s="2">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="D415" s="2"/>
     </row>
@@ -8304,10 +8316,10 @@
         <v>85</v>
       </c>
       <c r="B416" t="s" s="2">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="C416" t="s" s="2">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="D416" s="2"/>
     </row>
@@ -8316,13 +8328,13 @@
         <v>85</v>
       </c>
       <c r="B417" t="s" s="2">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="C417" t="s" s="2">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="D417" t="s" s="2">
-        <v>904</v>
+        <v>905</v>
       </c>
     </row>
     <row r="418">
@@ -8330,22 +8342,24 @@
         <v>85</v>
       </c>
       <c r="B418" t="s" s="2">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="C418" t="s" s="2">
-        <v>906</v>
-      </c>
-      <c r="D418" s="2"/>
+        <v>907</v>
+      </c>
+      <c r="D418" t="s" s="2">
+        <v>908</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="s" s="2">
         <v>85</v>
       </c>
       <c r="B419" t="s" s="2">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="C419" t="s" s="2">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="D419" s="2"/>
     </row>
@@ -8354,10 +8368,10 @@
         <v>85</v>
       </c>
       <c r="B420" t="s" s="2">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="C420" t="s" s="2">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="D420" s="2"/>
     </row>
@@ -8366,10 +8380,10 @@
         <v>85</v>
       </c>
       <c r="B421" t="s" s="2">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="C421" t="s" s="2">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="D421" s="2"/>
     </row>
@@ -8378,10 +8392,10 @@
         <v>85</v>
       </c>
       <c r="B422" t="s" s="2">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="C422" t="s" s="2">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="D422" s="2"/>
     </row>
@@ -8390,10 +8404,10 @@
         <v>85</v>
       </c>
       <c r="B423" t="s" s="2">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="C423" t="s" s="2">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="D423" s="2"/>
     </row>
@@ -8402,27 +8416,25 @@
         <v>85</v>
       </c>
       <c r="B424" t="s" s="2">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="C424" t="s" s="2">
-        <v>918</v>
-      </c>
-      <c r="D424" t="s" s="2">
-        <v>919</v>
-      </c>
+        <v>920</v>
+      </c>
+      <c r="D424" s="2"/>
     </row>
     <row r="425">
       <c r="A425" t="s" s="2">
         <v>85</v>
       </c>
       <c r="B425" t="s" s="2">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="C425" t="s" s="2">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="D425" t="s" s="2">
-        <v>919</v>
+        <v>923</v>
       </c>
     </row>
     <row r="426">
@@ -8430,13 +8442,13 @@
         <v>85</v>
       </c>
       <c r="B426" t="s" s="2">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="C426" t="s" s="2">
+        <v>925</v>
+      </c>
+      <c r="D426" t="s" s="2">
         <v>923</v>
-      </c>
-      <c r="D426" t="s" s="2">
-        <v>919</v>
       </c>
     </row>
     <row r="427">
@@ -8444,25 +8456,39 @@
         <v>85</v>
       </c>
       <c r="B427" t="s" s="2">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="C427" t="s" s="2">
-        <v>925</v>
-      </c>
-      <c r="D427" s="2"/>
+        <v>927</v>
+      </c>
+      <c r="D427" t="s" s="2">
+        <v>923</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="s" s="2">
         <v>85</v>
       </c>
       <c r="B428" t="s" s="2">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="C428" t="s" s="2">
-        <v>927</v>
-      </c>
-      <c r="D428" t="s" s="2">
-        <v>928</v>
+        <v>929</v>
+      </c>
+      <c r="D428" s="2"/>
+    </row>
+    <row r="429">
+      <c r="A429" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="B429" t="s" s="2">
+        <v>930</v>
+      </c>
+      <c r="C429" t="s" s="2">
+        <v>931</v>
+      </c>
+      <c r="D429" t="s" s="2">
+        <v>932</v>
       </c>
     </row>
   </sheetData>

--- a/ig/DM_FINESS_New/CodeSystem-tre-r397-categorie-entite-geographique-exercice.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-tre-r397-categorie-entite-geographique-exercice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1388" uniqueCount="933">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1392" uniqueCount="935">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260223120000</t>
+    <t>20260330120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T12:00:00.000+00:00</t>
+    <t>2026-03-30T12:00:00.000+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -118,7 +118,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>428</t>
+    <t>429</t>
   </si>
   <si>
     <t>Code</t>
@@ -2813,6 +2813,12 @@
   </si>
   <si>
     <t>Points locaux d'information dédiés aux personnes âgées. Ces services peuvent être rattachés à des CCAS ( Centre Communaux d'Action Sociale)</t>
+  </si>
+  <si>
+    <t>705</t>
+  </si>
+  <si>
+    <t>Groupe d’Entraide Mutuelle (GEM)</t>
   </si>
 </sst>
 </file>
@@ -3322,7 +3328,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D429"/>
+  <dimension ref="A1:D430"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -8491,6 +8497,20 @@
         <v>932</v>
       </c>
     </row>
+    <row r="430">
+      <c r="A430" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="B430" t="s" s="2">
+        <v>933</v>
+      </c>
+      <c r="C430" t="s" s="2">
+        <v>934</v>
+      </c>
+      <c r="D430" t="s" s="2">
+        <v>923</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/ig/DM_FINESS_New/CodeSystem-tre-r397-categorie-entite-geographique-exercice.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-tre-r397-categorie-entite-geographique-exercice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1392" uniqueCount="935">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1393" uniqueCount="936">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260330120000</t>
+    <t>20260505120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T12:00:00.000+00:00</t>
+    <t>2026-05-05T12:00:00.000+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1474,7 +1474,10 @@
     <t>236</t>
   </si>
   <si>
-    <t>Centre Placement Familial Socio-Educatif (C.P.F.S.E.)</t>
+    <t>Service de placement familial</t>
+  </si>
+  <si>
+    <t>Le placement familial est, au sens strict du terme, un dispositif qui permet de prendre en charge un enfant dans une autre famille que la sienne, afin de résoudre une situation de danger le concernant. Remarque : Suite à une réunion avec l'ASE (DGCS), il a été décidé que le changement de nom de la catégorie Centre Placement Familial Socio-Educatif (C.P.F.S.E.)  en « Service de placement familial» (catégorie 236).</t>
   </si>
   <si>
     <t>237</t>
@@ -5815,17 +5818,19 @@
       <c r="C207" t="s" s="2">
         <v>486</v>
       </c>
-      <c r="D207" s="2"/>
+      <c r="D207" t="s" s="2">
+        <v>487</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="s" s="2">
         <v>85</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C208" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D208" s="2"/>
     </row>
@@ -5834,10 +5839,10 @@
         <v>85</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C209" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="D209" s="2"/>
     </row>
@@ -5846,10 +5851,10 @@
         <v>85</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C210" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D210" s="2"/>
     </row>
@@ -5858,10 +5863,10 @@
         <v>85</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C211" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D211" s="2"/>
     </row>
@@ -5870,10 +5875,10 @@
         <v>85</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C212" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D212" s="2"/>
     </row>
@@ -5882,10 +5887,10 @@
         <v>85</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C213" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D213" s="2"/>
     </row>
@@ -5894,10 +5899,10 @@
         <v>85</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C214" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D214" s="2"/>
     </row>
@@ -5906,10 +5911,10 @@
         <v>85</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C215" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D215" s="2"/>
     </row>
@@ -5918,10 +5923,10 @@
         <v>85</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C216" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D216" s="2"/>
     </row>
@@ -5930,10 +5935,10 @@
         <v>85</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C217" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D217" s="2"/>
     </row>
@@ -5942,10 +5947,10 @@
         <v>85</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C218" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D218" s="2"/>
     </row>
@@ -5954,10 +5959,10 @@
         <v>85</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C219" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="D219" s="2"/>
     </row>
@@ -5966,10 +5971,10 @@
         <v>85</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C220" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D220" s="2"/>
     </row>
@@ -5978,10 +5983,10 @@
         <v>85</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C221" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D221" s="2"/>
     </row>
@@ -5990,10 +5995,10 @@
         <v>85</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C222" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D222" s="2"/>
     </row>
@@ -6002,10 +6007,10 @@
         <v>85</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C223" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="D223" s="2"/>
     </row>
@@ -6014,10 +6019,10 @@
         <v>85</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C224" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="D224" s="2"/>
     </row>
@@ -6026,10 +6031,10 @@
         <v>85</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C225" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D225" s="2"/>
     </row>
@@ -6038,10 +6043,10 @@
         <v>85</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C226" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="D226" s="2"/>
     </row>
@@ -6050,10 +6055,10 @@
         <v>85</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C227" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="D227" s="2"/>
     </row>
@@ -6062,10 +6067,10 @@
         <v>85</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C228" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="D228" s="2"/>
     </row>
@@ -6074,10 +6079,10 @@
         <v>85</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C229" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D229" s="2"/>
     </row>
@@ -6086,10 +6091,10 @@
         <v>85</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C230" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="D230" s="2"/>
     </row>
@@ -6098,10 +6103,10 @@
         <v>85</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C231" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="D231" s="2"/>
     </row>
@@ -6110,10 +6115,10 @@
         <v>85</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C232" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D232" s="2"/>
     </row>
@@ -6122,10 +6127,10 @@
         <v>85</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C233" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="D233" s="2"/>
     </row>
@@ -6134,10 +6139,10 @@
         <v>85</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C234" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D234" s="2"/>
     </row>
@@ -6146,10 +6151,10 @@
         <v>85</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C235" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="D235" s="2"/>
     </row>
@@ -6158,10 +6163,10 @@
         <v>85</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C236" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="D236" s="2"/>
     </row>
@@ -6170,10 +6175,10 @@
         <v>85</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C237" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="D237" s="2"/>
     </row>
@@ -6182,10 +6187,10 @@
         <v>85</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C238" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D238" s="2"/>
     </row>
@@ -6194,10 +6199,10 @@
         <v>85</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C239" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="D239" s="2"/>
     </row>
@@ -6206,10 +6211,10 @@
         <v>85</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C240" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D240" s="2"/>
     </row>
@@ -6218,10 +6223,10 @@
         <v>85</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C241" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="D241" s="2"/>
     </row>
@@ -6230,10 +6235,10 @@
         <v>85</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C242" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D242" s="2"/>
     </row>
@@ -6242,10 +6247,10 @@
         <v>85</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C243" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D243" s="2"/>
     </row>
@@ -6254,10 +6259,10 @@
         <v>85</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C244" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D244" s="2"/>
     </row>
@@ -6266,10 +6271,10 @@
         <v>85</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C245" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="D245" s="2"/>
     </row>
@@ -6278,10 +6283,10 @@
         <v>85</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C246" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D246" s="2"/>
     </row>
@@ -6290,10 +6295,10 @@
         <v>85</v>
       </c>
       <c r="B247" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C247" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D247" s="2"/>
     </row>
@@ -6302,10 +6307,10 @@
         <v>85</v>
       </c>
       <c r="B248" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C248" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D248" s="2"/>
     </row>
@@ -6314,10 +6319,10 @@
         <v>85</v>
       </c>
       <c r="B249" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C249" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="D249" s="2"/>
     </row>
@@ -6326,10 +6331,10 @@
         <v>85</v>
       </c>
       <c r="B250" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C250" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="D250" s="2"/>
     </row>
@@ -6338,10 +6343,10 @@
         <v>85</v>
       </c>
       <c r="B251" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C251" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="D251" s="2"/>
     </row>
@@ -6350,10 +6355,10 @@
         <v>85</v>
       </c>
       <c r="B252" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C252" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D252" s="2"/>
     </row>
@@ -6362,10 +6367,10 @@
         <v>85</v>
       </c>
       <c r="B253" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C253" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="D253" s="2"/>
     </row>
@@ -6374,10 +6379,10 @@
         <v>85</v>
       </c>
       <c r="B254" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C254" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="D254" s="2"/>
     </row>
@@ -6386,10 +6391,10 @@
         <v>85</v>
       </c>
       <c r="B255" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C255" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="D255" s="2"/>
     </row>
@@ -6398,10 +6403,10 @@
         <v>85</v>
       </c>
       <c r="B256" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C256" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D256" s="2"/>
     </row>
@@ -6410,10 +6415,10 @@
         <v>85</v>
       </c>
       <c r="B257" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C257" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="D257" s="2"/>
     </row>
@@ -6422,10 +6427,10 @@
         <v>85</v>
       </c>
       <c r="B258" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C258" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="D258" s="2"/>
     </row>
@@ -6434,10 +6439,10 @@
         <v>85</v>
       </c>
       <c r="B259" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C259" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D259" s="2"/>
     </row>
@@ -6446,10 +6451,10 @@
         <v>85</v>
       </c>
       <c r="B260" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C260" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D260" s="2"/>
     </row>
@@ -6458,10 +6463,10 @@
         <v>85</v>
       </c>
       <c r="B261" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C261" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="D261" s="2"/>
     </row>
@@ -6470,10 +6475,10 @@
         <v>85</v>
       </c>
       <c r="B262" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C262" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="D262" s="2"/>
     </row>
@@ -6482,10 +6487,10 @@
         <v>85</v>
       </c>
       <c r="B263" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C263" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D263" s="2"/>
     </row>
@@ -6494,10 +6499,10 @@
         <v>85</v>
       </c>
       <c r="B264" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C264" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="D264" s="2"/>
     </row>
@@ -6506,10 +6511,10 @@
         <v>85</v>
       </c>
       <c r="B265" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C265" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="D265" s="2"/>
     </row>
@@ -6518,10 +6523,10 @@
         <v>85</v>
       </c>
       <c r="B266" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C266" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="D266" s="2"/>
     </row>
@@ -6530,10 +6535,10 @@
         <v>85</v>
       </c>
       <c r="B267" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C267" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="D267" s="2"/>
     </row>
@@ -6542,10 +6547,10 @@
         <v>85</v>
       </c>
       <c r="B268" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C268" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="D268" s="2"/>
     </row>
@@ -6554,10 +6559,10 @@
         <v>85</v>
       </c>
       <c r="B269" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C269" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="D269" s="2"/>
     </row>
@@ -6566,10 +6571,10 @@
         <v>85</v>
       </c>
       <c r="B270" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C270" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="D270" s="2"/>
     </row>
@@ -6578,10 +6583,10 @@
         <v>85</v>
       </c>
       <c r="B271" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C271" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="D271" s="2"/>
     </row>
@@ -6590,10 +6595,10 @@
         <v>85</v>
       </c>
       <c r="B272" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C272" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="D272" s="2"/>
     </row>
@@ -6602,10 +6607,10 @@
         <v>85</v>
       </c>
       <c r="B273" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C273" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="D273" s="2"/>
     </row>
@@ -6614,10 +6619,10 @@
         <v>85</v>
       </c>
       <c r="B274" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C274" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="D274" s="2"/>
     </row>
@@ -6626,7 +6631,7 @@
         <v>85</v>
       </c>
       <c r="B275" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C275" t="s" s="2">
         <v>199</v>
@@ -6638,10 +6643,10 @@
         <v>85</v>
       </c>
       <c r="B276" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C276" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="D276" s="2"/>
     </row>
@@ -6650,10 +6655,10 @@
         <v>85</v>
       </c>
       <c r="B277" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C277" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="D277" s="2"/>
     </row>
@@ -6662,10 +6667,10 @@
         <v>85</v>
       </c>
       <c r="B278" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C278" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="D278" s="2"/>
     </row>
@@ -6674,10 +6679,10 @@
         <v>85</v>
       </c>
       <c r="B279" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C279" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="D279" s="2"/>
     </row>
@@ -6686,10 +6691,10 @@
         <v>85</v>
       </c>
       <c r="B280" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C280" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="D280" s="2"/>
     </row>
@@ -6698,10 +6703,10 @@
         <v>85</v>
       </c>
       <c r="B281" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C281" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="D281" s="2"/>
     </row>
@@ -6710,10 +6715,10 @@
         <v>85</v>
       </c>
       <c r="B282" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C282" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="D282" s="2"/>
     </row>
@@ -6722,10 +6727,10 @@
         <v>85</v>
       </c>
       <c r="B283" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C283" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="D283" s="2"/>
     </row>
@@ -6734,10 +6739,10 @@
         <v>85</v>
       </c>
       <c r="B284" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C284" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="D284" s="2"/>
     </row>
@@ -6746,10 +6751,10 @@
         <v>85</v>
       </c>
       <c r="B285" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C285" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D285" s="2"/>
     </row>
@@ -6758,10 +6763,10 @@
         <v>85</v>
       </c>
       <c r="B286" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C286" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="D286" s="2"/>
     </row>
@@ -6770,10 +6775,10 @@
         <v>85</v>
       </c>
       <c r="B287" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C287" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="D287" s="2"/>
     </row>
@@ -6782,10 +6787,10 @@
         <v>85</v>
       </c>
       <c r="B288" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C288" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="D288" s="2"/>
     </row>
@@ -6794,10 +6799,10 @@
         <v>85</v>
       </c>
       <c r="B289" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C289" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="D289" s="2"/>
     </row>
@@ -6806,10 +6811,10 @@
         <v>85</v>
       </c>
       <c r="B290" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C290" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="D290" s="2"/>
     </row>
@@ -6818,10 +6823,10 @@
         <v>85</v>
       </c>
       <c r="B291" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C291" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="D291" s="2"/>
     </row>
@@ -6830,10 +6835,10 @@
         <v>85</v>
       </c>
       <c r="B292" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C292" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="D292" s="2"/>
     </row>
@@ -6842,10 +6847,10 @@
         <v>85</v>
       </c>
       <c r="B293" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C293" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="D293" s="2"/>
     </row>
@@ -6854,10 +6859,10 @@
         <v>85</v>
       </c>
       <c r="B294" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C294" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="D294" s="2"/>
     </row>
@@ -6866,10 +6871,10 @@
         <v>85</v>
       </c>
       <c r="B295" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C295" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="D295" s="2"/>
     </row>
@@ -6878,10 +6883,10 @@
         <v>85</v>
       </c>
       <c r="B296" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C296" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="D296" s="2"/>
     </row>
@@ -6890,10 +6895,10 @@
         <v>85</v>
       </c>
       <c r="B297" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C297" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="D297" s="2"/>
     </row>
@@ -6902,10 +6907,10 @@
         <v>85</v>
       </c>
       <c r="B298" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C298" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="D298" s="2"/>
     </row>
@@ -6914,10 +6919,10 @@
         <v>85</v>
       </c>
       <c r="B299" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C299" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="D299" s="2"/>
     </row>
@@ -6926,10 +6931,10 @@
         <v>85</v>
       </c>
       <c r="B300" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C300" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="D300" s="2"/>
     </row>
@@ -6938,10 +6943,10 @@
         <v>85</v>
       </c>
       <c r="B301" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C301" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="D301" s="2"/>
     </row>
@@ -6950,10 +6955,10 @@
         <v>85</v>
       </c>
       <c r="B302" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C302" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="D302" s="2"/>
     </row>
@@ -6962,10 +6967,10 @@
         <v>85</v>
       </c>
       <c r="B303" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C303" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="D303" s="2"/>
     </row>
@@ -6974,10 +6979,10 @@
         <v>85</v>
       </c>
       <c r="B304" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C304" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="D304" s="2"/>
     </row>
@@ -6986,10 +6991,10 @@
         <v>85</v>
       </c>
       <c r="B305" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C305" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="D305" s="2"/>
     </row>
@@ -6998,10 +7003,10 @@
         <v>85</v>
       </c>
       <c r="B306" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C306" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="D306" s="2"/>
     </row>
@@ -7010,10 +7015,10 @@
         <v>85</v>
       </c>
       <c r="B307" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C307" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="D307" s="2"/>
     </row>
@@ -7022,10 +7027,10 @@
         <v>85</v>
       </c>
       <c r="B308" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C308" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="D308" s="2"/>
     </row>
@@ -7034,10 +7039,10 @@
         <v>85</v>
       </c>
       <c r="B309" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C309" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="D309" s="2"/>
     </row>
@@ -7046,10 +7051,10 @@
         <v>85</v>
       </c>
       <c r="B310" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C310" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="D310" s="2"/>
     </row>
@@ -7058,10 +7063,10 @@
         <v>85</v>
       </c>
       <c r="B311" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C311" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="D311" s="2"/>
     </row>
@@ -7070,10 +7075,10 @@
         <v>85</v>
       </c>
       <c r="B312" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C312" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="D312" s="2"/>
     </row>
@@ -7082,10 +7087,10 @@
         <v>85</v>
       </c>
       <c r="B313" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C313" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="D313" s="2"/>
     </row>
@@ -7094,10 +7099,10 @@
         <v>85</v>
       </c>
       <c r="B314" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C314" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="D314" s="2"/>
     </row>
@@ -7106,10 +7111,10 @@
         <v>85</v>
       </c>
       <c r="B315" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C315" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="D315" s="2"/>
     </row>
@@ -7118,10 +7123,10 @@
         <v>85</v>
       </c>
       <c r="B316" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C316" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="D316" s="2"/>
     </row>
@@ -7130,10 +7135,10 @@
         <v>85</v>
       </c>
       <c r="B317" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C317" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="D317" s="2"/>
     </row>
@@ -7142,10 +7147,10 @@
         <v>85</v>
       </c>
       <c r="B318" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C318" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="D318" s="2"/>
     </row>
@@ -7154,10 +7159,10 @@
         <v>85</v>
       </c>
       <c r="B319" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="C319" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="D319" s="2"/>
     </row>
@@ -7166,10 +7171,10 @@
         <v>85</v>
       </c>
       <c r="B320" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="C320" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="D320" s="2"/>
     </row>
@@ -7178,10 +7183,10 @@
         <v>85</v>
       </c>
       <c r="B321" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="C321" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="D321" s="2"/>
     </row>
@@ -7190,10 +7195,10 @@
         <v>85</v>
       </c>
       <c r="B322" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C322" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="D322" s="2"/>
     </row>
@@ -7202,10 +7207,10 @@
         <v>85</v>
       </c>
       <c r="B323" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="C323" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="D323" s="2"/>
     </row>
@@ -7214,10 +7219,10 @@
         <v>85</v>
       </c>
       <c r="B324" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="C324" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="D324" s="2"/>
     </row>
@@ -7226,10 +7231,10 @@
         <v>85</v>
       </c>
       <c r="B325" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C325" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="D325" s="2"/>
     </row>
@@ -7238,10 +7243,10 @@
         <v>85</v>
       </c>
       <c r="B326" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="C326" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="D326" s="2"/>
     </row>
@@ -7250,10 +7255,10 @@
         <v>85</v>
       </c>
       <c r="B327" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="C327" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="D327" s="2"/>
     </row>
@@ -7262,10 +7267,10 @@
         <v>85</v>
       </c>
       <c r="B328" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="C328" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="D328" s="2"/>
     </row>
@@ -7274,10 +7279,10 @@
         <v>85</v>
       </c>
       <c r="B329" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="C329" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="D329" s="2"/>
     </row>
@@ -7286,10 +7291,10 @@
         <v>85</v>
       </c>
       <c r="B330" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="C330" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="D330" s="2"/>
     </row>
@@ -7298,10 +7303,10 @@
         <v>85</v>
       </c>
       <c r="B331" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="C331" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="D331" s="2"/>
     </row>
@@ -7310,10 +7315,10 @@
         <v>85</v>
       </c>
       <c r="B332" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C332" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="D332" s="2"/>
     </row>
@@ -7322,10 +7327,10 @@
         <v>85</v>
       </c>
       <c r="B333" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="C333" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="D333" s="2"/>
     </row>
@@ -7334,10 +7339,10 @@
         <v>85</v>
       </c>
       <c r="B334" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C334" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="D334" s="2"/>
     </row>
@@ -7346,10 +7351,10 @@
         <v>85</v>
       </c>
       <c r="B335" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C335" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="D335" s="2"/>
     </row>
@@ -7358,10 +7363,10 @@
         <v>85</v>
       </c>
       <c r="B336" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="C336" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="D336" s="2"/>
     </row>
@@ -7370,10 +7375,10 @@
         <v>85</v>
       </c>
       <c r="B337" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="C337" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="D337" s="2"/>
     </row>
@@ -7382,10 +7387,10 @@
         <v>85</v>
       </c>
       <c r="B338" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="C338" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="D338" s="2"/>
     </row>
@@ -7394,10 +7399,10 @@
         <v>85</v>
       </c>
       <c r="B339" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="C339" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="D339" s="2"/>
     </row>
@@ -7406,10 +7411,10 @@
         <v>85</v>
       </c>
       <c r="B340" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="C340" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="D340" s="2"/>
     </row>
@@ -7418,10 +7423,10 @@
         <v>85</v>
       </c>
       <c r="B341" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C341" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="D341" s="2"/>
     </row>
@@ -7430,10 +7435,10 @@
         <v>85</v>
       </c>
       <c r="B342" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="C342" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="D342" s="2"/>
     </row>
@@ -7442,10 +7447,10 @@
         <v>85</v>
       </c>
       <c r="B343" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="C343" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="D343" s="2"/>
     </row>
@@ -7454,10 +7459,10 @@
         <v>85</v>
       </c>
       <c r="B344" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="C344" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="D344" s="2"/>
     </row>
@@ -7466,10 +7471,10 @@
         <v>85</v>
       </c>
       <c r="B345" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="C345" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="D345" s="2"/>
     </row>
@@ -7478,10 +7483,10 @@
         <v>85</v>
       </c>
       <c r="B346" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="C346" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="D346" s="2"/>
     </row>
@@ -7490,10 +7495,10 @@
         <v>85</v>
       </c>
       <c r="B347" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="C347" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="D347" s="2"/>
     </row>
@@ -7502,10 +7507,10 @@
         <v>85</v>
       </c>
       <c r="B348" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C348" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D348" s="2"/>
     </row>
@@ -7514,10 +7519,10 @@
         <v>85</v>
       </c>
       <c r="B349" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="C349" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="D349" s="2"/>
     </row>
@@ -7526,10 +7531,10 @@
         <v>85</v>
       </c>
       <c r="B350" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="C350" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="D350" s="2"/>
     </row>
@@ -7538,10 +7543,10 @@
         <v>85</v>
       </c>
       <c r="B351" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="C351" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="D351" s="2"/>
     </row>
@@ -7550,10 +7555,10 @@
         <v>85</v>
       </c>
       <c r="B352" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="C352" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="D352" s="2"/>
     </row>
@@ -7562,10 +7567,10 @@
         <v>85</v>
       </c>
       <c r="B353" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="C353" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="D353" s="2"/>
     </row>
@@ -7574,10 +7579,10 @@
         <v>85</v>
       </c>
       <c r="B354" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="C354" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="D354" s="2"/>
     </row>
@@ -7586,10 +7591,10 @@
         <v>85</v>
       </c>
       <c r="B355" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="C355" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="D355" s="2"/>
     </row>
@@ -7598,10 +7603,10 @@
         <v>85</v>
       </c>
       <c r="B356" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="C356" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="D356" s="2"/>
     </row>
@@ -7610,10 +7615,10 @@
         <v>85</v>
       </c>
       <c r="B357" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="C357" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="D357" s="2"/>
     </row>
@@ -7622,10 +7627,10 @@
         <v>85</v>
       </c>
       <c r="B358" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="C358" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="D358" s="2"/>
     </row>
@@ -7634,10 +7639,10 @@
         <v>85</v>
       </c>
       <c r="B359" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="C359" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="D359" s="2"/>
     </row>
@@ -7646,10 +7651,10 @@
         <v>85</v>
       </c>
       <c r="B360" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C360" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="D360" s="2"/>
     </row>
@@ -7658,10 +7663,10 @@
         <v>85</v>
       </c>
       <c r="B361" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="C361" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="D361" s="2"/>
     </row>
@@ -7670,10 +7675,10 @@
         <v>85</v>
       </c>
       <c r="B362" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="C362" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="D362" s="2"/>
     </row>
@@ -7682,10 +7687,10 @@
         <v>85</v>
       </c>
       <c r="B363" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="C363" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="D363" s="2"/>
     </row>
@@ -7694,10 +7699,10 @@
         <v>85</v>
       </c>
       <c r="B364" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="C364" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="D364" s="2"/>
     </row>
@@ -7706,10 +7711,10 @@
         <v>85</v>
       </c>
       <c r="B365" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="C365" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="D365" s="2"/>
     </row>
@@ -7718,10 +7723,10 @@
         <v>85</v>
       </c>
       <c r="B366" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="C366" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="D366" s="2"/>
     </row>
@@ -7730,10 +7735,10 @@
         <v>85</v>
       </c>
       <c r="B367" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="C367" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="D367" s="2"/>
     </row>
@@ -7742,10 +7747,10 @@
         <v>85</v>
       </c>
       <c r="B368" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C368" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="D368" s="2"/>
     </row>
@@ -7754,10 +7759,10 @@
         <v>85</v>
       </c>
       <c r="B369" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="C369" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="D369" s="2"/>
     </row>
@@ -7766,10 +7771,10 @@
         <v>85</v>
       </c>
       <c r="B370" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="C370" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="D370" s="2"/>
     </row>
@@ -7778,10 +7783,10 @@
         <v>85</v>
       </c>
       <c r="B371" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="C371" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="D371" s="2"/>
     </row>
@@ -7790,10 +7795,10 @@
         <v>85</v>
       </c>
       <c r="B372" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="C372" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="D372" s="2"/>
     </row>
@@ -7802,10 +7807,10 @@
         <v>85</v>
       </c>
       <c r="B373" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="C373" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="D373" s="2"/>
     </row>
@@ -7814,10 +7819,10 @@
         <v>85</v>
       </c>
       <c r="B374" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C374" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="D374" s="2"/>
     </row>
@@ -7826,10 +7831,10 @@
         <v>85</v>
       </c>
       <c r="B375" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="C375" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="D375" s="2"/>
     </row>
@@ -7838,10 +7843,10 @@
         <v>85</v>
       </c>
       <c r="B376" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="C376" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D376" s="2"/>
     </row>
@@ -7850,7 +7855,7 @@
         <v>85</v>
       </c>
       <c r="B377" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="C377" t="s" s="2">
         <v>171</v>
@@ -7862,10 +7867,10 @@
         <v>85</v>
       </c>
       <c r="B378" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="C378" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="D378" s="2"/>
     </row>
@@ -7874,13 +7879,13 @@
         <v>85</v>
       </c>
       <c r="B379" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="C379" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="D379" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
     </row>
     <row r="380">
@@ -7888,7 +7893,7 @@
         <v>85</v>
       </c>
       <c r="B380" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="C380" t="s" s="2">
         <v>175</v>
@@ -7900,10 +7905,10 @@
         <v>85</v>
       </c>
       <c r="B381" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="C381" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="D381" s="2"/>
     </row>
@@ -7912,10 +7917,10 @@
         <v>85</v>
       </c>
       <c r="B382" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="C382" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="D382" s="2"/>
     </row>
@@ -7924,10 +7929,10 @@
         <v>85</v>
       </c>
       <c r="B383" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="C383" t="s" s="2">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="D383" s="2"/>
     </row>
@@ -7936,10 +7941,10 @@
         <v>85</v>
       </c>
       <c r="B384" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="C384" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="D384" s="2"/>
     </row>
@@ -7948,10 +7953,10 @@
         <v>85</v>
       </c>
       <c r="B385" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C385" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="D385" s="2"/>
     </row>
@@ -7960,10 +7965,10 @@
         <v>85</v>
       </c>
       <c r="B386" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="C386" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="D386" s="2"/>
     </row>
@@ -7972,10 +7977,10 @@
         <v>85</v>
       </c>
       <c r="B387" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="C387" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="D387" s="2"/>
     </row>
@@ -7984,10 +7989,10 @@
         <v>85</v>
       </c>
       <c r="B388" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="C388" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="D388" s="2"/>
     </row>
@@ -7996,7 +8001,7 @@
         <v>85</v>
       </c>
       <c r="B389" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="C389" t="s" s="2">
         <v>209</v>
@@ -8008,13 +8013,13 @@
         <v>85</v>
       </c>
       <c r="B390" t="s" s="2">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="C390" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="D390" t="s" s="2">
-        <v>850</v>
+        <v>851</v>
       </c>
     </row>
     <row r="391">
@@ -8022,10 +8027,10 @@
         <v>85</v>
       </c>
       <c r="B391" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="C391" t="s" s="2">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="D391" s="2"/>
     </row>
@@ -8034,10 +8039,10 @@
         <v>85</v>
       </c>
       <c r="B392" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="C392" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="D392" s="2"/>
     </row>
@@ -8046,10 +8051,10 @@
         <v>85</v>
       </c>
       <c r="B393" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="C393" t="s" s="2">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="D393" s="2"/>
     </row>
@@ -8058,10 +8063,10 @@
         <v>85</v>
       </c>
       <c r="B394" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="C394" t="s" s="2">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="D394" s="2"/>
     </row>
@@ -8070,10 +8075,10 @@
         <v>85</v>
       </c>
       <c r="B395" t="s" s="2">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="C395" t="s" s="2">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="D395" s="2"/>
     </row>
@@ -8082,10 +8087,10 @@
         <v>85</v>
       </c>
       <c r="B396" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="C396" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="D396" s="2"/>
     </row>
@@ -8094,10 +8099,10 @@
         <v>85</v>
       </c>
       <c r="B397" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="C397" t="s" s="2">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="D397" s="2"/>
     </row>
@@ -8106,10 +8111,10 @@
         <v>85</v>
       </c>
       <c r="B398" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="C398" t="s" s="2">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="D398" s="2"/>
     </row>
@@ -8118,10 +8123,10 @@
         <v>85</v>
       </c>
       <c r="B399" t="s" s="2">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="C399" t="s" s="2">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="D399" s="2"/>
     </row>
@@ -8130,10 +8135,10 @@
         <v>85</v>
       </c>
       <c r="B400" t="s" s="2">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="C400" t="s" s="2">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="D400" s="2"/>
     </row>
@@ -8142,10 +8147,10 @@
         <v>85</v>
       </c>
       <c r="B401" t="s" s="2">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="C401" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="D401" s="2"/>
     </row>
@@ -8154,10 +8159,10 @@
         <v>85</v>
       </c>
       <c r="B402" t="s" s="2">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="C402" t="s" s="2">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="D402" s="2"/>
     </row>
@@ -8166,10 +8171,10 @@
         <v>85</v>
       </c>
       <c r="B403" t="s" s="2">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="C403" t="s" s="2">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="D403" s="2"/>
     </row>
@@ -8178,10 +8183,10 @@
         <v>85</v>
       </c>
       <c r="B404" t="s" s="2">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="C404" t="s" s="2">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="D404" s="2"/>
     </row>
@@ -8190,10 +8195,10 @@
         <v>85</v>
       </c>
       <c r="B405" t="s" s="2">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="C405" t="s" s="2">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="D405" s="2"/>
     </row>
@@ -8202,10 +8207,10 @@
         <v>85</v>
       </c>
       <c r="B406" t="s" s="2">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="C406" t="s" s="2">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="D406" s="2"/>
     </row>
@@ -8214,10 +8219,10 @@
         <v>85</v>
       </c>
       <c r="B407" t="s" s="2">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="C407" t="s" s="2">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="D407" s="2"/>
     </row>
@@ -8226,10 +8231,10 @@
         <v>85</v>
       </c>
       <c r="B408" t="s" s="2">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="C408" t="s" s="2">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="D408" s="2"/>
     </row>
@@ -8238,10 +8243,10 @@
         <v>85</v>
       </c>
       <c r="B409" t="s" s="2">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="C409" t="s" s="2">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="D409" s="2"/>
     </row>
@@ -8250,10 +8255,10 @@
         <v>85</v>
       </c>
       <c r="B410" t="s" s="2">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="C410" t="s" s="2">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="D410" s="2"/>
     </row>
@@ -8262,10 +8267,10 @@
         <v>85</v>
       </c>
       <c r="B411" t="s" s="2">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="C411" t="s" s="2">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="D411" s="2"/>
     </row>
@@ -8274,10 +8279,10 @@
         <v>85</v>
       </c>
       <c r="B412" t="s" s="2">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="C412" t="s" s="2">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="D412" s="2"/>
     </row>
@@ -8286,10 +8291,10 @@
         <v>85</v>
       </c>
       <c r="B413" t="s" s="2">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="C413" t="s" s="2">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="D413" s="2"/>
     </row>
@@ -8298,10 +8303,10 @@
         <v>85</v>
       </c>
       <c r="B414" t="s" s="2">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="C414" t="s" s="2">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="D414" s="2"/>
     </row>
@@ -8310,10 +8315,10 @@
         <v>85</v>
       </c>
       <c r="B415" t="s" s="2">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="C415" t="s" s="2">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="D415" s="2"/>
     </row>
@@ -8322,10 +8327,10 @@
         <v>85</v>
       </c>
       <c r="B416" t="s" s="2">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="C416" t="s" s="2">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="D416" s="2"/>
     </row>
@@ -8334,13 +8339,13 @@
         <v>85</v>
       </c>
       <c r="B417" t="s" s="2">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="C417" t="s" s="2">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="D417" t="s" s="2">
-        <v>905</v>
+        <v>906</v>
       </c>
     </row>
     <row r="418">
@@ -8348,13 +8353,13 @@
         <v>85</v>
       </c>
       <c r="B418" t="s" s="2">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="C418" t="s" s="2">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="D418" t="s" s="2">
-        <v>908</v>
+        <v>909</v>
       </c>
     </row>
     <row r="419">
@@ -8362,10 +8367,10 @@
         <v>85</v>
       </c>
       <c r="B419" t="s" s="2">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="C419" t="s" s="2">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="D419" s="2"/>
     </row>
@@ -8374,10 +8379,10 @@
         <v>85</v>
       </c>
       <c r="B420" t="s" s="2">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="C420" t="s" s="2">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="D420" s="2"/>
     </row>
@@ -8386,10 +8391,10 @@
         <v>85</v>
       </c>
       <c r="B421" t="s" s="2">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="C421" t="s" s="2">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="D421" s="2"/>
     </row>
@@ -8398,10 +8403,10 @@
         <v>85</v>
       </c>
       <c r="B422" t="s" s="2">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="C422" t="s" s="2">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="D422" s="2"/>
     </row>
@@ -8410,10 +8415,10 @@
         <v>85</v>
       </c>
       <c r="B423" t="s" s="2">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="C423" t="s" s="2">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="D423" s="2"/>
     </row>
@@ -8422,10 +8427,10 @@
         <v>85</v>
       </c>
       <c r="B424" t="s" s="2">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="C424" t="s" s="2">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="D424" s="2"/>
     </row>
@@ -8434,13 +8439,13 @@
         <v>85</v>
       </c>
       <c r="B425" t="s" s="2">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="C425" t="s" s="2">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="D425" t="s" s="2">
-        <v>923</v>
+        <v>924</v>
       </c>
     </row>
     <row r="426">
@@ -8448,13 +8453,13 @@
         <v>85</v>
       </c>
       <c r="B426" t="s" s="2">
+        <v>925</v>
+      </c>
+      <c r="C426" t="s" s="2">
+        <v>926</v>
+      </c>
+      <c r="D426" t="s" s="2">
         <v>924</v>
-      </c>
-      <c r="C426" t="s" s="2">
-        <v>925</v>
-      </c>
-      <c r="D426" t="s" s="2">
-        <v>923</v>
       </c>
     </row>
     <row r="427">
@@ -8462,13 +8467,13 @@
         <v>85</v>
       </c>
       <c r="B427" t="s" s="2">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="C427" t="s" s="2">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="D427" t="s" s="2">
-        <v>923</v>
+        <v>924</v>
       </c>
     </row>
     <row r="428">
@@ -8476,10 +8481,10 @@
         <v>85</v>
       </c>
       <c r="B428" t="s" s="2">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="C428" t="s" s="2">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="D428" s="2"/>
     </row>
@@ -8488,13 +8493,13 @@
         <v>85</v>
       </c>
       <c r="B429" t="s" s="2">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="C429" t="s" s="2">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="D429" t="s" s="2">
-        <v>932</v>
+        <v>933</v>
       </c>
     </row>
     <row r="430">
@@ -8502,13 +8507,13 @@
         <v>85</v>
       </c>
       <c r="B430" t="s" s="2">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="C430" t="s" s="2">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="D430" t="s" s="2">
-        <v>923</v>
+        <v>924</v>
       </c>
     </row>
   </sheetData>

--- a/ig/DM_FINESS_New/CodeSystem-tre-r397-categorie-entite-geographique-exercice.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-tre-r397-categorie-entite-geographique-exercice.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1393" uniqueCount="936">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1390" uniqueCount="935">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260505120000</t>
+    <t>20260601120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-05T12:00:00.000+00:00</t>
+    <t>2026-06-01T12:00:00.000+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -118,7 +118,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>429</t>
+    <t>428</t>
   </si>
   <si>
     <t>Code</t>
@@ -320,9 +320,6 @@
   </si>
   <si>
     <t>Etablissements d'Administration</t>
-  </si>
-  <si>
-    <t>110</t>
   </si>
   <si>
     <t>1100</t>
@@ -3331,7 +3328,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D430"/>
+  <dimension ref="A1:D429"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -3452,7 +3449,7 @@
         <v>102</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D10" s="2"/>
     </row>
@@ -3461,10 +3458,10 @@
         <v>85</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D11" s="2"/>
     </row>
@@ -3473,10 +3470,10 @@
         <v>85</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D12" s="2"/>
     </row>
@@ -3485,10 +3482,10 @@
         <v>85</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="D13" s="2"/>
     </row>
@@ -3500,7 +3497,7 @@
         <v>109</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>91</v>
+        <v>110</v>
       </c>
       <c r="D14" s="2"/>
     </row>
@@ -3509,10 +3506,10 @@
         <v>85</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D15" s="2"/>
     </row>
@@ -3521,10 +3518,10 @@
         <v>85</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="D16" s="2"/>
     </row>
@@ -3536,7 +3533,7 @@
         <v>114</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="D17" s="2"/>
     </row>
@@ -3545,10 +3542,10 @@
         <v>85</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D18" s="2"/>
     </row>
@@ -3557,10 +3554,10 @@
         <v>85</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D19" s="2"/>
     </row>
@@ -3569,10 +3566,10 @@
         <v>85</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D20" s="2"/>
     </row>
@@ -3581,10 +3578,10 @@
         <v>85</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D21" s="2"/>
     </row>
@@ -3593,10 +3590,10 @@
         <v>85</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D22" s="2"/>
     </row>
@@ -3605,10 +3602,10 @@
         <v>85</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>126</v>
+        <v>97</v>
       </c>
       <c r="D23" s="2"/>
     </row>
@@ -3620,7 +3617,7 @@
         <v>127</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>97</v>
+        <v>128</v>
       </c>
       <c r="D24" s="2"/>
     </row>
@@ -3629,10 +3626,10 @@
         <v>85</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D25" s="2"/>
     </row>
@@ -3641,10 +3638,10 @@
         <v>85</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D26" s="2"/>
     </row>
@@ -3653,10 +3650,10 @@
         <v>85</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>133</v>
+        <v>101</v>
       </c>
       <c r="D27" s="2"/>
     </row>
@@ -3668,7 +3665,7 @@
         <v>134</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>101</v>
+        <v>135</v>
       </c>
       <c r="D28" s="2"/>
     </row>
@@ -3677,10 +3674,10 @@
         <v>85</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D29" s="2"/>
     </row>
@@ -3689,10 +3686,10 @@
         <v>85</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D30" s="2"/>
     </row>
@@ -3701,10 +3698,10 @@
         <v>85</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D31" s="2"/>
     </row>
@@ -3713,10 +3710,10 @@
         <v>85</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D32" s="2"/>
     </row>
@@ -3725,10 +3722,10 @@
         <v>85</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D33" s="2"/>
     </row>
@@ -3737,10 +3734,10 @@
         <v>85</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D34" s="2"/>
     </row>
@@ -3749,10 +3746,10 @@
         <v>85</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D35" s="2"/>
     </row>
@@ -3761,10 +3758,10 @@
         <v>85</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D36" s="2"/>
     </row>
@@ -3773,10 +3770,10 @@
         <v>85</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D37" s="2"/>
     </row>
@@ -3785,10 +3782,10 @@
         <v>85</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D38" s="2"/>
     </row>
@@ -3797,10 +3794,10 @@
         <v>85</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D39" s="2"/>
     </row>
@@ -3809,10 +3806,10 @@
         <v>85</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D40" s="2"/>
     </row>
@@ -3821,10 +3818,10 @@
         <v>85</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D41" s="2"/>
     </row>
@@ -3833,10 +3830,10 @@
         <v>85</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D42" s="2"/>
     </row>
@@ -3845,10 +3842,10 @@
         <v>85</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D43" s="2"/>
     </row>
@@ -3857,10 +3854,10 @@
         <v>85</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>166</v>
+        <v>105</v>
       </c>
       <c r="D44" s="2"/>
     </row>
@@ -3872,7 +3869,7 @@
         <v>167</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>106</v>
+        <v>168</v>
       </c>
       <c r="D45" s="2"/>
     </row>
@@ -3881,10 +3878,10 @@
         <v>85</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D46" s="2"/>
     </row>
@@ -3893,10 +3890,10 @@
         <v>85</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D47" s="2"/>
     </row>
@@ -3905,10 +3902,10 @@
         <v>85</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D48" s="2"/>
     </row>
@@ -3917,10 +3914,10 @@
         <v>85</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D49" s="2"/>
     </row>
@@ -3929,10 +3926,10 @@
         <v>85</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D50" s="2"/>
     </row>
@@ -3941,10 +3938,10 @@
         <v>85</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D51" s="2"/>
     </row>
@@ -3953,10 +3950,10 @@
         <v>85</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D52" s="2"/>
     </row>
@@ -3965,10 +3962,10 @@
         <v>85</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D53" s="2"/>
     </row>
@@ -3977,10 +3974,10 @@
         <v>85</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D54" s="2"/>
     </row>
@@ -3989,10 +3986,10 @@
         <v>85</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>187</v>
+        <v>110</v>
       </c>
       <c r="D55" s="2"/>
     </row>
@@ -4004,7 +4001,7 @@
         <v>188</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D56" s="2"/>
     </row>
@@ -4016,7 +4013,7 @@
         <v>189</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>113</v>
+        <v>190</v>
       </c>
       <c r="D57" s="2"/>
     </row>
@@ -4025,10 +4022,10 @@
         <v>85</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D58" s="2"/>
     </row>
@@ -4037,10 +4034,10 @@
         <v>85</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D59" s="2"/>
     </row>
@@ -4049,10 +4046,10 @@
         <v>85</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D60" s="2"/>
     </row>
@@ -4061,10 +4058,10 @@
         <v>85</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D61" s="2"/>
     </row>
@@ -4073,10 +4070,10 @@
         <v>85</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D62" s="2"/>
     </row>
@@ -4085,10 +4082,10 @@
         <v>85</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D63" s="2"/>
     </row>
@@ -4097,10 +4094,10 @@
         <v>85</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D64" s="2"/>
     </row>
@@ -4109,10 +4106,10 @@
         <v>85</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D65" s="2"/>
     </row>
@@ -4121,10 +4118,10 @@
         <v>85</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D66" s="2"/>
     </row>
@@ -4133,10 +4130,10 @@
         <v>85</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D67" s="2"/>
     </row>
@@ -4145,10 +4142,10 @@
         <v>85</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D68" s="2"/>
     </row>
@@ -4157,10 +4154,10 @@
         <v>85</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D69" s="2"/>
     </row>
@@ -4169,10 +4166,10 @@
         <v>85</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D70" s="2"/>
     </row>
@@ -4181,10 +4178,10 @@
         <v>85</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D71" s="2"/>
     </row>
@@ -4193,10 +4190,10 @@
         <v>85</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D72" s="2"/>
     </row>
@@ -4205,10 +4202,10 @@
         <v>85</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D73" s="2"/>
     </row>
@@ -4217,10 +4214,10 @@
         <v>85</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D74" s="2"/>
     </row>
@@ -4229,10 +4226,10 @@
         <v>85</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D75" s="2"/>
     </row>
@@ -4241,10 +4238,10 @@
         <v>85</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D76" s="2"/>
     </row>
@@ -4253,10 +4250,10 @@
         <v>85</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D77" s="2"/>
     </row>
@@ -4265,10 +4262,10 @@
         <v>85</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D78" s="2"/>
     </row>
@@ -4277,10 +4274,10 @@
         <v>85</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D79" s="2"/>
     </row>
@@ -4289,10 +4286,10 @@
         <v>85</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D80" s="2"/>
     </row>
@@ -4301,10 +4298,10 @@
         <v>85</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D81" s="2"/>
     </row>
@@ -4313,10 +4310,10 @@
         <v>85</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C82" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D82" s="2"/>
     </row>
@@ -4325,10 +4322,10 @@
         <v>85</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C83" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D83" s="2"/>
     </row>
@@ -4337,10 +4334,10 @@
         <v>85</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D84" s="2"/>
     </row>
@@ -4349,10 +4346,10 @@
         <v>85</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C85" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D85" s="2"/>
     </row>
@@ -4361,10 +4358,10 @@
         <v>85</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D86" s="2"/>
     </row>
@@ -4373,10 +4370,10 @@
         <v>85</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C87" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D87" s="2"/>
     </row>
@@ -4385,10 +4382,10 @@
         <v>85</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D88" s="2"/>
     </row>
@@ -4397,10 +4394,10 @@
         <v>85</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C89" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D89" s="2"/>
     </row>
@@ -4409,10 +4406,10 @@
         <v>85</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D90" s="2"/>
     </row>
@@ -4421,10 +4418,10 @@
         <v>85</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D91" s="2"/>
     </row>
@@ -4433,10 +4430,10 @@
         <v>85</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C92" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D92" s="2"/>
     </row>
@@ -4445,10 +4442,10 @@
         <v>85</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D93" s="2"/>
     </row>
@@ -4457,10 +4454,10 @@
         <v>85</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C94" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D94" s="2"/>
     </row>
@@ -4469,10 +4466,10 @@
         <v>85</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D95" s="2"/>
     </row>
@@ -4481,10 +4478,10 @@
         <v>85</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D96" s="2"/>
     </row>
@@ -4493,10 +4490,10 @@
         <v>85</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D97" s="2"/>
     </row>
@@ -4505,10 +4502,10 @@
         <v>85</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D98" s="2"/>
     </row>
@@ -4517,10 +4514,10 @@
         <v>85</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D99" s="2"/>
     </row>
@@ -4529,10 +4526,10 @@
         <v>85</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D100" s="2"/>
     </row>
@@ -4541,10 +4538,10 @@
         <v>85</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D101" s="2"/>
     </row>
@@ -4553,10 +4550,10 @@
         <v>85</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C102" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D102" s="2"/>
     </row>
@@ -4565,10 +4562,10 @@
         <v>85</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>281</v>
+        <v>128</v>
       </c>
       <c r="D103" s="2"/>
     </row>
@@ -4580,7 +4577,7 @@
         <v>282</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>129</v>
+        <v>283</v>
       </c>
       <c r="D104" s="2"/>
     </row>
@@ -4589,10 +4586,10 @@
         <v>85</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D105" s="2"/>
     </row>
@@ -4601,10 +4598,10 @@
         <v>85</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>286</v>
+        <v>130</v>
       </c>
       <c r="D106" s="2"/>
     </row>
@@ -4616,7 +4613,7 @@
         <v>287</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D107" s="2"/>
     </row>
@@ -4628,7 +4625,7 @@
         <v>288</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>133</v>
+        <v>289</v>
       </c>
       <c r="D108" s="2"/>
     </row>
@@ -4637,10 +4634,10 @@
         <v>85</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D109" s="2"/>
     </row>
@@ -4649,10 +4646,10 @@
         <v>85</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C110" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D110" s="2"/>
     </row>
@@ -4661,10 +4658,10 @@
         <v>85</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D111" s="2"/>
     </row>
@@ -4673,10 +4670,10 @@
         <v>85</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D112" s="2"/>
     </row>
@@ -4685,10 +4682,10 @@
         <v>85</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C113" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D113" s="2"/>
     </row>
@@ -4697,10 +4694,10 @@
         <v>85</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C114" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D114" s="2"/>
     </row>
@@ -4709,10 +4706,10 @@
         <v>85</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C115" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D115" s="2"/>
     </row>
@@ -4721,10 +4718,10 @@
         <v>85</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C116" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D116" s="2"/>
     </row>
@@ -4733,10 +4730,10 @@
         <v>85</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C117" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D117" s="2"/>
     </row>
@@ -4745,10 +4742,10 @@
         <v>85</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C118" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D118" s="2"/>
     </row>
@@ -4757,10 +4754,10 @@
         <v>85</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D119" s="2"/>
     </row>
@@ -4769,10 +4766,10 @@
         <v>85</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C120" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D120" s="2"/>
     </row>
@@ -4781,10 +4778,10 @@
         <v>85</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C121" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D121" s="2"/>
     </row>
@@ -4793,10 +4790,10 @@
         <v>85</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C122" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D122" s="2"/>
     </row>
@@ -4805,10 +4802,10 @@
         <v>85</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C123" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D123" s="2"/>
     </row>
@@ -4817,10 +4814,10 @@
         <v>85</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C124" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D124" s="2"/>
     </row>
@@ -4829,10 +4826,10 @@
         <v>85</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C125" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D125" s="2"/>
     </row>
@@ -4841,10 +4838,10 @@
         <v>85</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C126" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D126" s="2"/>
     </row>
@@ -4853,10 +4850,10 @@
         <v>85</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C127" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D127" s="2"/>
     </row>
@@ -4865,10 +4862,10 @@
         <v>85</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C128" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D128" s="2"/>
     </row>
@@ -4877,10 +4874,10 @@
         <v>85</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C129" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D129" s="2"/>
     </row>
@@ -4889,10 +4886,10 @@
         <v>85</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C130" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D130" s="2"/>
     </row>
@@ -4901,10 +4898,10 @@
         <v>85</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C131" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D131" s="2"/>
     </row>
@@ -4913,10 +4910,10 @@
         <v>85</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C132" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D132" s="2"/>
     </row>
@@ -4925,10 +4922,10 @@
         <v>85</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C133" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D133" s="2"/>
     </row>
@@ -4937,10 +4934,10 @@
         <v>85</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C134" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D134" s="2"/>
     </row>
@@ -4949,10 +4946,10 @@
         <v>85</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C135" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D135" s="2"/>
     </row>
@@ -4961,10 +4958,10 @@
         <v>85</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C136" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D136" s="2"/>
     </row>
@@ -4973,10 +4970,10 @@
         <v>85</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C137" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D137" s="2"/>
     </row>
@@ -4985,10 +4982,10 @@
         <v>85</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C138" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D138" s="2"/>
     </row>
@@ -4997,10 +4994,10 @@
         <v>85</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C139" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D139" s="2"/>
     </row>
@@ -5009,10 +5006,10 @@
         <v>85</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C140" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D140" s="2"/>
     </row>
@@ -5021,10 +5018,10 @@
         <v>85</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C141" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D141" s="2"/>
     </row>
@@ -5033,10 +5030,10 @@
         <v>85</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C142" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D142" s="2"/>
     </row>
@@ -5045,10 +5042,10 @@
         <v>85</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C143" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D143" s="2"/>
     </row>
@@ -5057,10 +5054,10 @@
         <v>85</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C144" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D144" s="2"/>
     </row>
@@ -5069,10 +5066,10 @@
         <v>85</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C145" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D145" s="2"/>
     </row>
@@ -5081,10 +5078,10 @@
         <v>85</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C146" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D146" s="2"/>
     </row>
@@ -5093,10 +5090,10 @@
         <v>85</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C147" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D147" s="2"/>
     </row>
@@ -5105,10 +5102,10 @@
         <v>85</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C148" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D148" s="2"/>
     </row>
@@ -5117,10 +5114,10 @@
         <v>85</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C149" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D149" s="2"/>
     </row>
@@ -5129,10 +5126,10 @@
         <v>85</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C150" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D150" s="2"/>
     </row>
@@ -5141,10 +5138,10 @@
         <v>85</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C151" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D151" s="2"/>
     </row>
@@ -5153,10 +5150,10 @@
         <v>85</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C152" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D152" s="2"/>
     </row>
@@ -5165,10 +5162,10 @@
         <v>85</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C153" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D153" s="2"/>
     </row>
@@ -5177,10 +5174,10 @@
         <v>85</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C154" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D154" s="2"/>
     </row>
@@ -5189,10 +5186,10 @@
         <v>85</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C155" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D155" s="2"/>
     </row>
@@ -5201,10 +5198,10 @@
         <v>85</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C156" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D156" s="2"/>
     </row>
@@ -5213,10 +5210,10 @@
         <v>85</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C157" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D157" s="2"/>
     </row>
@@ -5225,10 +5222,10 @@
         <v>85</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C158" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D158" s="2"/>
     </row>
@@ -5237,10 +5234,10 @@
         <v>85</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C159" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D159" s="2"/>
     </row>
@@ -5249,10 +5246,10 @@
         <v>85</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C160" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D160" s="2"/>
     </row>
@@ -5261,10 +5258,10 @@
         <v>85</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C161" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D161" s="2"/>
     </row>
@@ -5273,10 +5270,10 @@
         <v>85</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C162" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D162" s="2"/>
     </row>
@@ -5285,10 +5282,10 @@
         <v>85</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C163" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D163" s="2"/>
     </row>
@@ -5297,10 +5294,10 @@
         <v>85</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C164" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D164" s="2"/>
     </row>
@@ -5309,10 +5306,10 @@
         <v>85</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C165" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D165" s="2"/>
     </row>
@@ -5321,10 +5318,10 @@
         <v>85</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C166" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D166" s="2"/>
     </row>
@@ -5333,10 +5330,10 @@
         <v>85</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C167" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D167" s="2"/>
     </row>
@@ -5345,10 +5342,10 @@
         <v>85</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C168" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D168" s="2"/>
     </row>
@@ -5357,10 +5354,10 @@
         <v>85</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C169" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D169" s="2"/>
     </row>
@@ -5369,10 +5366,10 @@
         <v>85</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C170" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D170" s="2"/>
     </row>
@@ -5381,10 +5378,10 @@
         <v>85</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C171" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D171" s="2"/>
     </row>
@@ -5393,10 +5390,10 @@
         <v>85</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C172" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D172" s="2"/>
     </row>
@@ -5405,10 +5402,10 @@
         <v>85</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C173" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D173" s="2"/>
     </row>
@@ -5417,10 +5414,10 @@
         <v>85</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C174" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D174" s="2"/>
     </row>
@@ -5429,10 +5426,10 @@
         <v>85</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C175" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D175" s="2"/>
     </row>
@@ -5441,10 +5438,10 @@
         <v>85</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C176" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D176" s="2"/>
     </row>
@@ -5453,10 +5450,10 @@
         <v>85</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C177" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D177" s="2"/>
     </row>
@@ -5465,10 +5462,10 @@
         <v>85</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C178" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D178" s="2"/>
     </row>
@@ -5477,10 +5474,10 @@
         <v>85</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C179" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D179" s="2"/>
     </row>
@@ -5489,10 +5486,10 @@
         <v>85</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C180" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D180" s="2"/>
     </row>
@@ -5501,10 +5498,10 @@
         <v>85</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C181" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D181" s="2"/>
     </row>
@@ -5513,10 +5510,10 @@
         <v>85</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C182" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D182" s="2"/>
     </row>
@@ -5525,10 +5522,10 @@
         <v>85</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C183" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D183" s="2"/>
     </row>
@@ -5537,10 +5534,10 @@
         <v>85</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C184" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D184" s="2"/>
     </row>
@@ -5549,10 +5546,10 @@
         <v>85</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C185" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D185" s="2"/>
     </row>
@@ -5561,10 +5558,10 @@
         <v>85</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C186" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D186" s="2"/>
     </row>
@@ -5573,10 +5570,10 @@
         <v>85</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C187" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D187" s="2"/>
     </row>
@@ -5585,10 +5582,10 @@
         <v>85</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C188" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D188" s="2"/>
     </row>
@@ -5597,10 +5594,10 @@
         <v>85</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C189" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D189" s="2"/>
     </row>
@@ -5609,10 +5606,10 @@
         <v>85</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C190" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D190" s="2"/>
     </row>
@@ -5621,10 +5618,10 @@
         <v>85</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C191" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D191" s="2"/>
     </row>
@@ -5633,10 +5630,10 @@
         <v>85</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C192" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D192" s="2"/>
     </row>
@@ -5645,10 +5642,10 @@
         <v>85</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C193" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D193" s="2"/>
     </row>
@@ -5657,10 +5654,10 @@
         <v>85</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C194" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D194" s="2"/>
     </row>
@@ -5669,10 +5666,10 @@
         <v>85</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C195" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D195" s="2"/>
     </row>
@@ -5681,10 +5678,10 @@
         <v>85</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C196" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D196" s="2"/>
     </row>
@@ -5693,10 +5690,10 @@
         <v>85</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C197" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D197" s="2"/>
     </row>
@@ -5705,10 +5702,10 @@
         <v>85</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C198" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D198" s="2"/>
     </row>
@@ -5717,10 +5714,10 @@
         <v>85</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C199" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D199" s="2"/>
     </row>
@@ -5729,10 +5726,10 @@
         <v>85</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C200" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D200" s="2"/>
     </row>
@@ -5741,10 +5738,10 @@
         <v>85</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C201" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D201" s="2"/>
     </row>
@@ -5753,10 +5750,10 @@
         <v>85</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C202" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D202" s="2"/>
     </row>
@@ -5765,10 +5762,10 @@
         <v>85</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C203" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="D203" s="2"/>
     </row>
@@ -5777,10 +5774,10 @@
         <v>85</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C204" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D204" s="2"/>
     </row>
@@ -5789,10 +5786,10 @@
         <v>85</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C205" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="D205" s="2"/>
     </row>
@@ -5801,36 +5798,36 @@
         <v>85</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C206" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="D206" s="2"/>
+        <v>485</v>
+      </c>
+      <c r="D206" t="s" s="2">
+        <v>486</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="s" s="2">
         <v>85</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C207" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="D207" t="s" s="2">
-        <v>487</v>
-      </c>
+        <v>488</v>
+      </c>
+      <c r="D207" s="2"/>
     </row>
     <row r="208">
       <c r="A208" t="s" s="2">
         <v>85</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C208" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="D208" s="2"/>
     </row>
@@ -5839,10 +5836,10 @@
         <v>85</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C209" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D209" s="2"/>
     </row>
@@ -5851,10 +5848,10 @@
         <v>85</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C210" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D210" s="2"/>
     </row>
@@ -5863,10 +5860,10 @@
         <v>85</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C211" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D211" s="2"/>
     </row>
@@ -5875,10 +5872,10 @@
         <v>85</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C212" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D212" s="2"/>
     </row>
@@ -5887,10 +5884,10 @@
         <v>85</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C213" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D213" s="2"/>
     </row>
@@ -5899,10 +5896,10 @@
         <v>85</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C214" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="D214" s="2"/>
     </row>
@@ -5911,10 +5908,10 @@
         <v>85</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C215" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D215" s="2"/>
     </row>
@@ -5923,10 +5920,10 @@
         <v>85</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C216" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D216" s="2"/>
     </row>
@@ -5935,10 +5932,10 @@
         <v>85</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C217" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D217" s="2"/>
     </row>
@@ -5947,10 +5944,10 @@
         <v>85</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C218" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D218" s="2"/>
     </row>
@@ -5959,10 +5956,10 @@
         <v>85</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C219" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D219" s="2"/>
     </row>
@@ -5971,10 +5968,10 @@
         <v>85</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C220" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D220" s="2"/>
     </row>
@@ -5983,10 +5980,10 @@
         <v>85</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C221" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D221" s="2"/>
     </row>
@@ -5995,10 +5992,10 @@
         <v>85</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C222" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="D222" s="2"/>
     </row>
@@ -6007,10 +6004,10 @@
         <v>85</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C223" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D223" s="2"/>
     </row>
@@ -6019,10 +6016,10 @@
         <v>85</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C224" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D224" s="2"/>
     </row>
@@ -6031,10 +6028,10 @@
         <v>85</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C225" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D225" s="2"/>
     </row>
@@ -6043,10 +6040,10 @@
         <v>85</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C226" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D226" s="2"/>
     </row>
@@ -6055,10 +6052,10 @@
         <v>85</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C227" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D227" s="2"/>
     </row>
@@ -6067,10 +6064,10 @@
         <v>85</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C228" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D228" s="2"/>
     </row>
@@ -6079,10 +6076,10 @@
         <v>85</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C229" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="D229" s="2"/>
     </row>
@@ -6091,10 +6088,10 @@
         <v>85</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C230" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="D230" s="2"/>
     </row>
@@ -6103,10 +6100,10 @@
         <v>85</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C231" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D231" s="2"/>
     </row>
@@ -6115,10 +6112,10 @@
         <v>85</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C232" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="D232" s="2"/>
     </row>
@@ -6127,10 +6124,10 @@
         <v>85</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C233" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D233" s="2"/>
     </row>
@@ -6139,10 +6136,10 @@
         <v>85</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C234" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="D234" s="2"/>
     </row>
@@ -6151,10 +6148,10 @@
         <v>85</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C235" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D235" s="2"/>
     </row>
@@ -6163,10 +6160,10 @@
         <v>85</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C236" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D236" s="2"/>
     </row>
@@ -6175,10 +6172,10 @@
         <v>85</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C237" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="D237" s="2"/>
     </row>
@@ -6187,10 +6184,10 @@
         <v>85</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C238" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="D238" s="2"/>
     </row>
@@ -6199,10 +6196,10 @@
         <v>85</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C239" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D239" s="2"/>
     </row>
@@ -6211,10 +6208,10 @@
         <v>85</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C240" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="D240" s="2"/>
     </row>
@@ -6223,10 +6220,10 @@
         <v>85</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C241" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="D241" s="2"/>
     </row>
@@ -6235,10 +6232,10 @@
         <v>85</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C242" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D242" s="2"/>
     </row>
@@ -6247,10 +6244,10 @@
         <v>85</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C243" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="D243" s="2"/>
     </row>
@@ -6259,10 +6256,10 @@
         <v>85</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C244" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="D244" s="2"/>
     </row>
@@ -6271,10 +6268,10 @@
         <v>85</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C245" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D245" s="2"/>
     </row>
@@ -6283,10 +6280,10 @@
         <v>85</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C246" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="D246" s="2"/>
     </row>
@@ -6295,10 +6292,10 @@
         <v>85</v>
       </c>
       <c r="B247" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C247" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D247" s="2"/>
     </row>
@@ -6307,10 +6304,10 @@
         <v>85</v>
       </c>
       <c r="B248" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C248" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="D248" s="2"/>
     </row>
@@ -6319,10 +6316,10 @@
         <v>85</v>
       </c>
       <c r="B249" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C249" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="D249" s="2"/>
     </row>
@@ -6331,10 +6328,10 @@
         <v>85</v>
       </c>
       <c r="B250" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C250" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="D250" s="2"/>
     </row>
@@ -6343,10 +6340,10 @@
         <v>85</v>
       </c>
       <c r="B251" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C251" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="D251" s="2"/>
     </row>
@@ -6355,10 +6352,10 @@
         <v>85</v>
       </c>
       <c r="B252" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C252" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="D252" s="2"/>
     </row>
@@ -6367,10 +6364,10 @@
         <v>85</v>
       </c>
       <c r="B253" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C253" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="D253" s="2"/>
     </row>
@@ -6379,10 +6376,10 @@
         <v>85</v>
       </c>
       <c r="B254" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C254" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="D254" s="2"/>
     </row>
@@ -6391,10 +6388,10 @@
         <v>85</v>
       </c>
       <c r="B255" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C255" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="D255" s="2"/>
     </row>
@@ -6403,10 +6400,10 @@
         <v>85</v>
       </c>
       <c r="B256" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C256" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="D256" s="2"/>
     </row>
@@ -6415,10 +6412,10 @@
         <v>85</v>
       </c>
       <c r="B257" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C257" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D257" s="2"/>
     </row>
@@ -6427,10 +6424,10 @@
         <v>85</v>
       </c>
       <c r="B258" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C258" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="D258" s="2"/>
     </row>
@@ -6439,10 +6436,10 @@
         <v>85</v>
       </c>
       <c r="B259" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C259" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="D259" s="2"/>
     </row>
@@ -6451,10 +6448,10 @@
         <v>85</v>
       </c>
       <c r="B260" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C260" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="D260" s="2"/>
     </row>
@@ -6463,10 +6460,10 @@
         <v>85</v>
       </c>
       <c r="B261" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C261" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="D261" s="2"/>
     </row>
@@ -6475,10 +6472,10 @@
         <v>85</v>
       </c>
       <c r="B262" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C262" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D262" s="2"/>
     </row>
@@ -6487,10 +6484,10 @@
         <v>85</v>
       </c>
       <c r="B263" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C263" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="D263" s="2"/>
     </row>
@@ -6499,10 +6496,10 @@
         <v>85</v>
       </c>
       <c r="B264" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C264" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="D264" s="2"/>
     </row>
@@ -6511,10 +6508,10 @@
         <v>85</v>
       </c>
       <c r="B265" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C265" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="D265" s="2"/>
     </row>
@@ -6523,10 +6520,10 @@
         <v>85</v>
       </c>
       <c r="B266" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C266" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="D266" s="2"/>
     </row>
@@ -6535,10 +6532,10 @@
         <v>85</v>
       </c>
       <c r="B267" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C267" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="D267" s="2"/>
     </row>
@@ -6547,10 +6544,10 @@
         <v>85</v>
       </c>
       <c r="B268" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C268" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="D268" s="2"/>
     </row>
@@ -6559,10 +6556,10 @@
         <v>85</v>
       </c>
       <c r="B269" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C269" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="D269" s="2"/>
     </row>
@@ -6571,10 +6568,10 @@
         <v>85</v>
       </c>
       <c r="B270" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C270" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="D270" s="2"/>
     </row>
@@ -6583,10 +6580,10 @@
         <v>85</v>
       </c>
       <c r="B271" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C271" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="D271" s="2"/>
     </row>
@@ -6595,10 +6592,10 @@
         <v>85</v>
       </c>
       <c r="B272" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C272" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="D272" s="2"/>
     </row>
@@ -6607,10 +6604,10 @@
         <v>85</v>
       </c>
       <c r="B273" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C273" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="D273" s="2"/>
     </row>
@@ -6619,10 +6616,10 @@
         <v>85</v>
       </c>
       <c r="B274" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C274" t="s" s="2">
-        <v>621</v>
+        <v>198</v>
       </c>
       <c r="D274" s="2"/>
     </row>
@@ -6634,7 +6631,7 @@
         <v>622</v>
       </c>
       <c r="C275" t="s" s="2">
-        <v>199</v>
+        <v>623</v>
       </c>
       <c r="D275" s="2"/>
     </row>
@@ -6643,10 +6640,10 @@
         <v>85</v>
       </c>
       <c r="B276" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C276" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="D276" s="2"/>
     </row>
@@ -6655,10 +6652,10 @@
         <v>85</v>
       </c>
       <c r="B277" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C277" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D277" s="2"/>
     </row>
@@ -6667,10 +6664,10 @@
         <v>85</v>
       </c>
       <c r="B278" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C278" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="D278" s="2"/>
     </row>
@@ -6679,10 +6676,10 @@
         <v>85</v>
       </c>
       <c r="B279" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C279" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="D279" s="2"/>
     </row>
@@ -6691,10 +6688,10 @@
         <v>85</v>
       </c>
       <c r="B280" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C280" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="D280" s="2"/>
     </row>
@@ -6703,10 +6700,10 @@
         <v>85</v>
       </c>
       <c r="B281" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C281" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="D281" s="2"/>
     </row>
@@ -6715,10 +6712,10 @@
         <v>85</v>
       </c>
       <c r="B282" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C282" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="D282" s="2"/>
     </row>
@@ -6727,10 +6724,10 @@
         <v>85</v>
       </c>
       <c r="B283" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C283" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="D283" s="2"/>
     </row>
@@ -6739,10 +6736,10 @@
         <v>85</v>
       </c>
       <c r="B284" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C284" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="D284" s="2"/>
     </row>
@@ -6751,10 +6748,10 @@
         <v>85</v>
       </c>
       <c r="B285" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C285" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="D285" s="2"/>
     </row>
@@ -6763,10 +6760,10 @@
         <v>85</v>
       </c>
       <c r="B286" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C286" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="D286" s="2"/>
     </row>
@@ -6775,10 +6772,10 @@
         <v>85</v>
       </c>
       <c r="B287" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C287" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="D287" s="2"/>
     </row>
@@ -6787,10 +6784,10 @@
         <v>85</v>
       </c>
       <c r="B288" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C288" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="D288" s="2"/>
     </row>
@@ -6799,10 +6796,10 @@
         <v>85</v>
       </c>
       <c r="B289" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C289" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="D289" s="2"/>
     </row>
@@ -6811,10 +6808,10 @@
         <v>85</v>
       </c>
       <c r="B290" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C290" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="D290" s="2"/>
     </row>
@@ -6823,10 +6820,10 @@
         <v>85</v>
       </c>
       <c r="B291" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C291" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="D291" s="2"/>
     </row>
@@ -6835,10 +6832,10 @@
         <v>85</v>
       </c>
       <c r="B292" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C292" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="D292" s="2"/>
     </row>
@@ -6847,10 +6844,10 @@
         <v>85</v>
       </c>
       <c r="B293" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C293" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="D293" s="2"/>
     </row>
@@ -6859,10 +6856,10 @@
         <v>85</v>
       </c>
       <c r="B294" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C294" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="D294" s="2"/>
     </row>
@@ -6871,10 +6868,10 @@
         <v>85</v>
       </c>
       <c r="B295" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C295" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="D295" s="2"/>
     </row>
@@ -6883,10 +6880,10 @@
         <v>85</v>
       </c>
       <c r="B296" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C296" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D296" s="2"/>
     </row>
@@ -6895,10 +6892,10 @@
         <v>85</v>
       </c>
       <c r="B297" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C297" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="D297" s="2"/>
     </row>
@@ -6907,10 +6904,10 @@
         <v>85</v>
       </c>
       <c r="B298" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="C298" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="D298" s="2"/>
     </row>
@@ -6919,10 +6916,10 @@
         <v>85</v>
       </c>
       <c r="B299" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C299" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="D299" s="2"/>
     </row>
@@ -6931,10 +6928,10 @@
         <v>85</v>
       </c>
       <c r="B300" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C300" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="D300" s="2"/>
     </row>
@@ -6943,10 +6940,10 @@
         <v>85</v>
       </c>
       <c r="B301" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C301" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="D301" s="2"/>
     </row>
@@ -6955,10 +6952,10 @@
         <v>85</v>
       </c>
       <c r="B302" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C302" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="D302" s="2"/>
     </row>
@@ -6967,10 +6964,10 @@
         <v>85</v>
       </c>
       <c r="B303" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C303" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="D303" s="2"/>
     </row>
@@ -6979,10 +6976,10 @@
         <v>85</v>
       </c>
       <c r="B304" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C304" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="D304" s="2"/>
     </row>
@@ -6991,10 +6988,10 @@
         <v>85</v>
       </c>
       <c r="B305" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C305" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="D305" s="2"/>
     </row>
@@ -7003,10 +7000,10 @@
         <v>85</v>
       </c>
       <c r="B306" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C306" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="D306" s="2"/>
     </row>
@@ -7015,10 +7012,10 @@
         <v>85</v>
       </c>
       <c r="B307" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C307" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D307" s="2"/>
     </row>
@@ -7027,10 +7024,10 @@
         <v>85</v>
       </c>
       <c r="B308" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C308" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="D308" s="2"/>
     </row>
@@ -7039,10 +7036,10 @@
         <v>85</v>
       </c>
       <c r="B309" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C309" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="D309" s="2"/>
     </row>
@@ -7051,10 +7048,10 @@
         <v>85</v>
       </c>
       <c r="B310" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C310" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="D310" s="2"/>
     </row>
@@ -7063,10 +7060,10 @@
         <v>85</v>
       </c>
       <c r="B311" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C311" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="D311" s="2"/>
     </row>
@@ -7075,10 +7072,10 @@
         <v>85</v>
       </c>
       <c r="B312" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C312" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="D312" s="2"/>
     </row>
@@ -7087,10 +7084,10 @@
         <v>85</v>
       </c>
       <c r="B313" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C313" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="D313" s="2"/>
     </row>
@@ -7099,10 +7096,10 @@
         <v>85</v>
       </c>
       <c r="B314" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="C314" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="D314" s="2"/>
     </row>
@@ -7111,10 +7108,10 @@
         <v>85</v>
       </c>
       <c r="B315" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C315" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="D315" s="2"/>
     </row>
@@ -7123,10 +7120,10 @@
         <v>85</v>
       </c>
       <c r="B316" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="C316" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="D316" s="2"/>
     </row>
@@ -7135,10 +7132,10 @@
         <v>85</v>
       </c>
       <c r="B317" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="C317" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="D317" s="2"/>
     </row>
@@ -7147,10 +7144,10 @@
         <v>85</v>
       </c>
       <c r="B318" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="C318" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="D318" s="2"/>
     </row>
@@ -7159,10 +7156,10 @@
         <v>85</v>
       </c>
       <c r="B319" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C319" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="D319" s="2"/>
     </row>
@@ -7171,10 +7168,10 @@
         <v>85</v>
       </c>
       <c r="B320" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C320" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="D320" s="2"/>
     </row>
@@ -7183,10 +7180,10 @@
         <v>85</v>
       </c>
       <c r="B321" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="C321" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="D321" s="2"/>
     </row>
@@ -7195,10 +7192,10 @@
         <v>85</v>
       </c>
       <c r="B322" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="C322" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="D322" s="2"/>
     </row>
@@ -7207,10 +7204,10 @@
         <v>85</v>
       </c>
       <c r="B323" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="C323" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="D323" s="2"/>
     </row>
@@ -7219,10 +7216,10 @@
         <v>85</v>
       </c>
       <c r="B324" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C324" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="D324" s="2"/>
     </row>
@@ -7231,10 +7228,10 @@
         <v>85</v>
       </c>
       <c r="B325" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C325" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="D325" s="2"/>
     </row>
@@ -7243,10 +7240,10 @@
         <v>85</v>
       </c>
       <c r="B326" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C326" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="D326" s="2"/>
     </row>
@@ -7255,10 +7252,10 @@
         <v>85</v>
       </c>
       <c r="B327" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="C327" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="D327" s="2"/>
     </row>
@@ -7267,10 +7264,10 @@
         <v>85</v>
       </c>
       <c r="B328" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="C328" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="D328" s="2"/>
     </row>
@@ -7279,10 +7276,10 @@
         <v>85</v>
       </c>
       <c r="B329" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C329" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D329" s="2"/>
     </row>
@@ -7291,10 +7288,10 @@
         <v>85</v>
       </c>
       <c r="B330" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C330" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="D330" s="2"/>
     </row>
@@ -7303,10 +7300,10 @@
         <v>85</v>
       </c>
       <c r="B331" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C331" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="D331" s="2"/>
     </row>
@@ -7315,10 +7312,10 @@
         <v>85</v>
       </c>
       <c r="B332" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="C332" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="D332" s="2"/>
     </row>
@@ -7327,10 +7324,10 @@
         <v>85</v>
       </c>
       <c r="B333" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="C333" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="D333" s="2"/>
     </row>
@@ -7339,10 +7336,10 @@
         <v>85</v>
       </c>
       <c r="B334" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="C334" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="D334" s="2"/>
     </row>
@@ -7351,10 +7348,10 @@
         <v>85</v>
       </c>
       <c r="B335" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="C335" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="D335" s="2"/>
     </row>
@@ -7363,10 +7360,10 @@
         <v>85</v>
       </c>
       <c r="B336" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C336" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="D336" s="2"/>
     </row>
@@ -7375,10 +7372,10 @@
         <v>85</v>
       </c>
       <c r="B337" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="C337" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="D337" s="2"/>
     </row>
@@ -7387,10 +7384,10 @@
         <v>85</v>
       </c>
       <c r="B338" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="C338" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="D338" s="2"/>
     </row>
@@ -7399,10 +7396,10 @@
         <v>85</v>
       </c>
       <c r="B339" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="C339" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="D339" s="2"/>
     </row>
@@ -7411,10 +7408,10 @@
         <v>85</v>
       </c>
       <c r="B340" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="C340" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="D340" s="2"/>
     </row>
@@ -7423,10 +7420,10 @@
         <v>85</v>
       </c>
       <c r="B341" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="C341" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="D341" s="2"/>
     </row>
@@ -7435,10 +7432,10 @@
         <v>85</v>
       </c>
       <c r="B342" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="C342" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="D342" s="2"/>
     </row>
@@ -7447,10 +7444,10 @@
         <v>85</v>
       </c>
       <c r="B343" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="C343" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="D343" s="2"/>
     </row>
@@ -7459,10 +7456,10 @@
         <v>85</v>
       </c>
       <c r="B344" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="C344" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="D344" s="2"/>
     </row>
@@ -7471,10 +7468,10 @@
         <v>85</v>
       </c>
       <c r="B345" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C345" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="D345" s="2"/>
     </row>
@@ -7483,10 +7480,10 @@
         <v>85</v>
       </c>
       <c r="B346" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="C346" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="D346" s="2"/>
     </row>
@@ -7495,10 +7492,10 @@
         <v>85</v>
       </c>
       <c r="B347" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="C347" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="D347" s="2"/>
     </row>
@@ -7507,10 +7504,10 @@
         <v>85</v>
       </c>
       <c r="B348" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C348" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="D348" s="2"/>
     </row>
@@ -7519,10 +7516,10 @@
         <v>85</v>
       </c>
       <c r="B349" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="C349" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="D349" s="2"/>
     </row>
@@ -7531,10 +7528,10 @@
         <v>85</v>
       </c>
       <c r="B350" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="C350" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="D350" s="2"/>
     </row>
@@ -7543,10 +7540,10 @@
         <v>85</v>
       </c>
       <c r="B351" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="C351" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="D351" s="2"/>
     </row>
@@ -7555,10 +7552,10 @@
         <v>85</v>
       </c>
       <c r="B352" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="C352" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="D352" s="2"/>
     </row>
@@ -7567,10 +7564,10 @@
         <v>85</v>
       </c>
       <c r="B353" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="C353" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="D353" s="2"/>
     </row>
@@ -7579,10 +7576,10 @@
         <v>85</v>
       </c>
       <c r="B354" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="C354" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="D354" s="2"/>
     </row>
@@ -7591,10 +7588,10 @@
         <v>85</v>
       </c>
       <c r="B355" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="C355" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="D355" s="2"/>
     </row>
@@ -7603,10 +7600,10 @@
         <v>85</v>
       </c>
       <c r="B356" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="C356" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="D356" s="2"/>
     </row>
@@ -7615,10 +7612,10 @@
         <v>85</v>
       </c>
       <c r="B357" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C357" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="D357" s="2"/>
     </row>
@@ -7627,10 +7624,10 @@
         <v>85</v>
       </c>
       <c r="B358" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="C358" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="D358" s="2"/>
     </row>
@@ -7639,10 +7636,10 @@
         <v>85</v>
       </c>
       <c r="B359" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="C359" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="D359" s="2"/>
     </row>
@@ -7651,10 +7648,10 @@
         <v>85</v>
       </c>
       <c r="B360" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="C360" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="D360" s="2"/>
     </row>
@@ -7663,10 +7660,10 @@
         <v>85</v>
       </c>
       <c r="B361" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C361" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="D361" s="2"/>
     </row>
@@ -7675,10 +7672,10 @@
         <v>85</v>
       </c>
       <c r="B362" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C362" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="D362" s="2"/>
     </row>
@@ -7687,10 +7684,10 @@
         <v>85</v>
       </c>
       <c r="B363" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C363" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="D363" s="2"/>
     </row>
@@ -7699,10 +7696,10 @@
         <v>85</v>
       </c>
       <c r="B364" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="C364" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="D364" s="2"/>
     </row>
@@ -7711,10 +7708,10 @@
         <v>85</v>
       </c>
       <c r="B365" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="C365" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="D365" s="2"/>
     </row>
@@ -7723,10 +7720,10 @@
         <v>85</v>
       </c>
       <c r="B366" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="C366" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="D366" s="2"/>
     </row>
@@ -7735,10 +7732,10 @@
         <v>85</v>
       </c>
       <c r="B367" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="C367" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="D367" s="2"/>
     </row>
@@ -7747,10 +7744,10 @@
         <v>85</v>
       </c>
       <c r="B368" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="C368" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="D368" s="2"/>
     </row>
@@ -7759,10 +7756,10 @@
         <v>85</v>
       </c>
       <c r="B369" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C369" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="D369" s="2"/>
     </row>
@@ -7771,10 +7768,10 @@
         <v>85</v>
       </c>
       <c r="B370" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="C370" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="D370" s="2"/>
     </row>
@@ -7783,10 +7780,10 @@
         <v>85</v>
       </c>
       <c r="B371" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="C371" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="D371" s="2"/>
     </row>
@@ -7795,10 +7792,10 @@
         <v>85</v>
       </c>
       <c r="B372" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="C372" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="D372" s="2"/>
     </row>
@@ -7807,10 +7804,10 @@
         <v>85</v>
       </c>
       <c r="B373" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="C373" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="D373" s="2"/>
     </row>
@@ -7819,10 +7816,10 @@
         <v>85</v>
       </c>
       <c r="B374" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="C374" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="D374" s="2"/>
     </row>
@@ -7831,10 +7828,10 @@
         <v>85</v>
       </c>
       <c r="B375" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C375" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="D375" s="2"/>
     </row>
@@ -7843,10 +7840,10 @@
         <v>85</v>
       </c>
       <c r="B376" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="C376" t="s" s="2">
-        <v>824</v>
+        <v>170</v>
       </c>
       <c r="D376" s="2"/>
     </row>
@@ -7858,7 +7855,7 @@
         <v>825</v>
       </c>
       <c r="C377" t="s" s="2">
-        <v>171</v>
+        <v>826</v>
       </c>
       <c r="D377" s="2"/>
     </row>
@@ -7867,26 +7864,26 @@
         <v>85</v>
       </c>
       <c r="B378" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="C378" t="s" s="2">
-        <v>827</v>
-      </c>
-      <c r="D378" s="2"/>
+        <v>828</v>
+      </c>
+      <c r="D378" t="s" s="2">
+        <v>829</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="s" s="2">
         <v>85</v>
       </c>
       <c r="B379" t="s" s="2">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="C379" t="s" s="2">
-        <v>829</v>
-      </c>
-      <c r="D379" t="s" s="2">
-        <v>830</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="D379" s="2"/>
     </row>
     <row r="380">
       <c r="A380" t="s" s="2">
@@ -7896,7 +7893,7 @@
         <v>831</v>
       </c>
       <c r="C380" t="s" s="2">
-        <v>175</v>
+        <v>832</v>
       </c>
       <c r="D380" s="2"/>
     </row>
@@ -7905,10 +7902,10 @@
         <v>85</v>
       </c>
       <c r="B381" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="C381" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="D381" s="2"/>
     </row>
@@ -7917,10 +7914,10 @@
         <v>85</v>
       </c>
       <c r="B382" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="C382" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="D382" s="2"/>
     </row>
@@ -7929,10 +7926,10 @@
         <v>85</v>
       </c>
       <c r="B383" t="s" s="2">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="C383" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="D383" s="2"/>
     </row>
@@ -7941,10 +7938,10 @@
         <v>85</v>
       </c>
       <c r="B384" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="C384" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="D384" s="2"/>
     </row>
@@ -7953,10 +7950,10 @@
         <v>85</v>
       </c>
       <c r="B385" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="C385" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="D385" s="2"/>
     </row>
@@ -7965,10 +7962,10 @@
         <v>85</v>
       </c>
       <c r="B386" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="C386" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="D386" s="2"/>
     </row>
@@ -7977,10 +7974,10 @@
         <v>85</v>
       </c>
       <c r="B387" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="C387" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="D387" s="2"/>
     </row>
@@ -7989,10 +7986,10 @@
         <v>85</v>
       </c>
       <c r="B388" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="C388" t="s" s="2">
-        <v>847</v>
+        <v>208</v>
       </c>
       <c r="D388" s="2"/>
     </row>
@@ -8004,33 +8001,33 @@
         <v>848</v>
       </c>
       <c r="C389" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="D389" s="2"/>
+        <v>849</v>
+      </c>
+      <c r="D389" t="s" s="2">
+        <v>850</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="s" s="2">
         <v>85</v>
       </c>
       <c r="B390" t="s" s="2">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="C390" t="s" s="2">
-        <v>850</v>
-      </c>
-      <c r="D390" t="s" s="2">
-        <v>851</v>
-      </c>
+        <v>852</v>
+      </c>
+      <c r="D390" s="2"/>
     </row>
     <row r="391">
       <c r="A391" t="s" s="2">
         <v>85</v>
       </c>
       <c r="B391" t="s" s="2">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="C391" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="D391" s="2"/>
     </row>
@@ -8039,10 +8036,10 @@
         <v>85</v>
       </c>
       <c r="B392" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="C392" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="D392" s="2"/>
     </row>
@@ -8051,10 +8048,10 @@
         <v>85</v>
       </c>
       <c r="B393" t="s" s="2">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="C393" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="D393" s="2"/>
     </row>
@@ -8063,10 +8060,10 @@
         <v>85</v>
       </c>
       <c r="B394" t="s" s="2">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="C394" t="s" s="2">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="D394" s="2"/>
     </row>
@@ -8075,10 +8072,10 @@
         <v>85</v>
       </c>
       <c r="B395" t="s" s="2">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="C395" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="D395" s="2"/>
     </row>
@@ -8087,10 +8084,10 @@
         <v>85</v>
       </c>
       <c r="B396" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="C396" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="D396" s="2"/>
     </row>
@@ -8099,10 +8096,10 @@
         <v>85</v>
       </c>
       <c r="B397" t="s" s="2">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="C397" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="D397" s="2"/>
     </row>
@@ -8111,10 +8108,10 @@
         <v>85</v>
       </c>
       <c r="B398" t="s" s="2">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C398" t="s" s="2">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="D398" s="2"/>
     </row>
@@ -8123,10 +8120,10 @@
         <v>85</v>
       </c>
       <c r="B399" t="s" s="2">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="C399" t="s" s="2">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="D399" s="2"/>
     </row>
@@ -8135,10 +8132,10 @@
         <v>85</v>
       </c>
       <c r="B400" t="s" s="2">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="C400" t="s" s="2">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="D400" s="2"/>
     </row>
@@ -8147,10 +8144,10 @@
         <v>85</v>
       </c>
       <c r="B401" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="C401" t="s" s="2">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="D401" s="2"/>
     </row>
@@ -8159,10 +8156,10 @@
         <v>85</v>
       </c>
       <c r="B402" t="s" s="2">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C402" t="s" s="2">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="D402" s="2"/>
     </row>
@@ -8171,10 +8168,10 @@
         <v>85</v>
       </c>
       <c r="B403" t="s" s="2">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="C403" t="s" s="2">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="D403" s="2"/>
     </row>
@@ -8183,10 +8180,10 @@
         <v>85</v>
       </c>
       <c r="B404" t="s" s="2">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="C404" t="s" s="2">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="D404" s="2"/>
     </row>
@@ -8195,10 +8192,10 @@
         <v>85</v>
       </c>
       <c r="B405" t="s" s="2">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="C405" t="s" s="2">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="D405" s="2"/>
     </row>
@@ -8207,10 +8204,10 @@
         <v>85</v>
       </c>
       <c r="B406" t="s" s="2">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="C406" t="s" s="2">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="D406" s="2"/>
     </row>
@@ -8219,10 +8216,10 @@
         <v>85</v>
       </c>
       <c r="B407" t="s" s="2">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="C407" t="s" s="2">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="D407" s="2"/>
     </row>
@@ -8231,10 +8228,10 @@
         <v>85</v>
       </c>
       <c r="B408" t="s" s="2">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="C408" t="s" s="2">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="D408" s="2"/>
     </row>
@@ -8243,10 +8240,10 @@
         <v>85</v>
       </c>
       <c r="B409" t="s" s="2">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="C409" t="s" s="2">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="D409" s="2"/>
     </row>
@@ -8255,10 +8252,10 @@
         <v>85</v>
       </c>
       <c r="B410" t="s" s="2">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="C410" t="s" s="2">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="D410" s="2"/>
     </row>
@@ -8267,10 +8264,10 @@
         <v>85</v>
       </c>
       <c r="B411" t="s" s="2">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="C411" t="s" s="2">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="D411" s="2"/>
     </row>
@@ -8279,10 +8276,10 @@
         <v>85</v>
       </c>
       <c r="B412" t="s" s="2">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="C412" t="s" s="2">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="D412" s="2"/>
     </row>
@@ -8291,10 +8288,10 @@
         <v>85</v>
       </c>
       <c r="B413" t="s" s="2">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="C413" t="s" s="2">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="D413" s="2"/>
     </row>
@@ -8303,10 +8300,10 @@
         <v>85</v>
       </c>
       <c r="B414" t="s" s="2">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="C414" t="s" s="2">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="D414" s="2"/>
     </row>
@@ -8315,10 +8312,10 @@
         <v>85</v>
       </c>
       <c r="B415" t="s" s="2">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="C415" t="s" s="2">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="D415" s="2"/>
     </row>
@@ -8327,25 +8324,27 @@
         <v>85</v>
       </c>
       <c r="B416" t="s" s="2">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="C416" t="s" s="2">
-        <v>903</v>
-      </c>
-      <c r="D416" s="2"/>
+        <v>904</v>
+      </c>
+      <c r="D416" t="s" s="2">
+        <v>905</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="s" s="2">
         <v>85</v>
       </c>
       <c r="B417" t="s" s="2">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="C417" t="s" s="2">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="D417" t="s" s="2">
-        <v>906</v>
+        <v>908</v>
       </c>
     </row>
     <row r="418">
@@ -8353,24 +8352,22 @@
         <v>85</v>
       </c>
       <c r="B418" t="s" s="2">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="C418" t="s" s="2">
-        <v>908</v>
-      </c>
-      <c r="D418" t="s" s="2">
-        <v>909</v>
-      </c>
+        <v>910</v>
+      </c>
+      <c r="D418" s="2"/>
     </row>
     <row r="419">
       <c r="A419" t="s" s="2">
         <v>85</v>
       </c>
       <c r="B419" t="s" s="2">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="C419" t="s" s="2">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="D419" s="2"/>
     </row>
@@ -8379,10 +8376,10 @@
         <v>85</v>
       </c>
       <c r="B420" t="s" s="2">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="C420" t="s" s="2">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="D420" s="2"/>
     </row>
@@ -8391,10 +8388,10 @@
         <v>85</v>
       </c>
       <c r="B421" t="s" s="2">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="C421" t="s" s="2">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="D421" s="2"/>
     </row>
@@ -8403,10 +8400,10 @@
         <v>85</v>
       </c>
       <c r="B422" t="s" s="2">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="C422" t="s" s="2">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="D422" s="2"/>
     </row>
@@ -8415,10 +8412,10 @@
         <v>85</v>
       </c>
       <c r="B423" t="s" s="2">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="C423" t="s" s="2">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="D423" s="2"/>
     </row>
@@ -8427,25 +8424,27 @@
         <v>85</v>
       </c>
       <c r="B424" t="s" s="2">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="C424" t="s" s="2">
-        <v>921</v>
-      </c>
-      <c r="D424" s="2"/>
+        <v>922</v>
+      </c>
+      <c r="D424" t="s" s="2">
+        <v>923</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="s" s="2">
         <v>85</v>
       </c>
       <c r="B425" t="s" s="2">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="C425" t="s" s="2">
+        <v>925</v>
+      </c>
+      <c r="D425" t="s" s="2">
         <v>923</v>
-      </c>
-      <c r="D425" t="s" s="2">
-        <v>924</v>
       </c>
     </row>
     <row r="426">
@@ -8453,13 +8452,13 @@
         <v>85</v>
       </c>
       <c r="B426" t="s" s="2">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="C426" t="s" s="2">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="D426" t="s" s="2">
-        <v>924</v>
+        <v>923</v>
       </c>
     </row>
     <row r="427">
@@ -8467,53 +8466,39 @@
         <v>85</v>
       </c>
       <c r="B427" t="s" s="2">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="C427" t="s" s="2">
-        <v>928</v>
-      </c>
-      <c r="D427" t="s" s="2">
-        <v>924</v>
-      </c>
+        <v>929</v>
+      </c>
+      <c r="D427" s="2"/>
     </row>
     <row r="428">
       <c r="A428" t="s" s="2">
         <v>85</v>
       </c>
       <c r="B428" t="s" s="2">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="C428" t="s" s="2">
-        <v>930</v>
-      </c>
-      <c r="D428" s="2"/>
+        <v>931</v>
+      </c>
+      <c r="D428" t="s" s="2">
+        <v>932</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="s" s="2">
         <v>85</v>
       </c>
       <c r="B429" t="s" s="2">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="C429" t="s" s="2">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="D429" t="s" s="2">
-        <v>933</v>
-      </c>
-    </row>
-    <row r="430">
-      <c r="A430" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="B430" t="s" s="2">
-        <v>934</v>
-      </c>
-      <c r="C430" t="s" s="2">
-        <v>935</v>
-      </c>
-      <c r="D430" t="s" s="2">
-        <v>924</v>
+        <v>923</v>
       </c>
     </row>
   </sheetData>
